--- a/data/templates/financial_template_v2_2026.xlsx
+++ b/data/templates/financial_template_v2_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pfizer-my.sharepoint.com/personal/hoveyo_pfizer_com/Documents/financial-automation-project/data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{783183DD-73AE-4283-AD85-EEFD805851D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22295CCB-CECF-455D-B651-97A5106C5139}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="8_{783183DD-73AE-4283-AD85-EEFD805851D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74C06533-0487-4308-94B4-599F809304B1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" tabRatio="590" xr2:uid="{0996C49B-04E6-42AE-AA83-2F64BE89A626}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="212">
   <si>
     <t xml:space="preserve">Overall Capital </t>
   </si>
@@ -379,12 +379,358 @@
   <si>
     <t>EXPENSE END</t>
   </si>
+  <si>
+    <t>Ram</t>
+  </si>
+  <si>
+    <t>Infosys</t>
+  </si>
+  <si>
+    <t>IT-FBT0393-OG-JP-00</t>
+  </si>
+  <si>
+    <t>JAPAN</t>
+  </si>
+  <si>
+    <t>Tenon</t>
+  </si>
+  <si>
+    <t>IT-FBT0638-OG-JP-00</t>
+  </si>
+  <si>
+    <t>SHI INTERNATIONAL CORP</t>
+  </si>
+  <si>
+    <t>IT-SFT1434-OG-US-00</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>ORACLE AMERICA INC</t>
+  </si>
+  <si>
+    <t>Ram 50-50</t>
+  </si>
+  <si>
+    <t>SAP</t>
+  </si>
+  <si>
+    <t>IT-FBT0528-OG-US-0</t>
+  </si>
+  <si>
+    <t>From Karla to Ram on 2/13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT-FBT0245-OG-US-00 </t>
+  </si>
+  <si>
+    <t>To Do in October 2026</t>
+  </si>
+  <si>
+    <t>IT-SFT0170-86-OG-US</t>
+  </si>
+  <si>
+    <t>IT-SFT1441-OG-US-00</t>
+  </si>
+  <si>
+    <t>IT-FBT0588-OG-US-00</t>
+  </si>
+  <si>
+    <t>IT-FBT0403-OG-US-00</t>
+  </si>
+  <si>
+    <t>IT-FBT0770-OT-US-00</t>
+  </si>
+  <si>
+    <t>IT-FBT0665-OG-US-00</t>
+  </si>
+  <si>
+    <t>IT-FBT0675-OG-US-00</t>
+  </si>
+  <si>
+    <t>IT-FBT0693-OG-US-00</t>
+  </si>
+  <si>
+    <t>IT-FBT0769-OT-US-00</t>
+  </si>
+  <si>
+    <t>IT-FGS0298-SW-US-00</t>
+  </si>
+  <si>
+    <t>IT-FGS0299-OG-US-00</t>
+  </si>
+  <si>
+    <t>IT-FGS0301-OG-US-00</t>
+  </si>
+  <si>
+    <t>IT-SFT1155-86-OG-US</t>
+  </si>
+  <si>
+    <t>IT-SFT1194-86-OG-US</t>
+  </si>
+  <si>
+    <t>EP&amp;SCharges001</t>
+  </si>
+  <si>
+    <t>IT-FBT0600-OG-US-00</t>
+  </si>
+  <si>
+    <t>2026-XFR-0008-B</t>
+  </si>
+  <si>
+    <t>IT-FBT0074-OG-US-00</t>
+  </si>
+  <si>
+    <t>IT-FBT0528-OG-US-00</t>
+  </si>
+  <si>
+    <t>Old PO9501113130</t>
+  </si>
+  <si>
+    <t>IT-SFT1023-86-OG-US</t>
+  </si>
+  <si>
+    <t>Old PO9501113089</t>
+  </si>
+  <si>
+    <t>IT-SFT1023-86-OG-US/PF</t>
+  </si>
+  <si>
+    <t>IT-SFT0175-02-OG-US</t>
+  </si>
+  <si>
+    <t>IT-SFT0234-02-OG-US</t>
+  </si>
+  <si>
+    <t>Ram-OLD PO9500903186</t>
+  </si>
+  <si>
+    <t>TEAM COMPUTERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>IT-FBT0066-OG-IN-00</t>
+  </si>
+  <si>
+    <t>INDIA</t>
+  </si>
+  <si>
+    <t>PRIME SOFTWARE SOLUTION</t>
+  </si>
+  <si>
+    <t>IT-FBT0637-OG-IN-00</t>
+  </si>
+  <si>
+    <t>IT FBT0587 OG US 00</t>
+  </si>
+  <si>
+    <t>IT FBT0588 OG US 00</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>IT-FBT0281-OG-US-00</t>
+  </si>
+  <si>
+    <t>Ram-OLD PO9500914310</t>
+  </si>
+  <si>
+    <t>IT-FBT0282-OG-US-00</t>
+  </si>
+  <si>
+    <t>Ram-OLD PO9500914283</t>
+  </si>
+  <si>
+    <t>IT-MGS0204-OG-US-00</t>
+  </si>
+  <si>
+    <t>IT-MGS0202-OG-US-00</t>
+  </si>
+  <si>
+    <t>IT-MGS0203-OG-US-00</t>
+  </si>
+  <si>
+    <t>12/312026</t>
+  </si>
+  <si>
+    <t>IT-MGS0205-OG-US-00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT-FBT0282-OG-US-00 </t>
+  </si>
+  <si>
+    <t>Ram-OLD PO9500913294</t>
+  </si>
+  <si>
+    <t>IT-FBT0753-OT-US-00</t>
+  </si>
+  <si>
+    <t>IT-FBT0700-OG-US-00</t>
+  </si>
+  <si>
+    <t>Ram - PF</t>
+  </si>
+  <si>
+    <t>Oracle</t>
+  </si>
+  <si>
+    <t>IT-SFT0159-86-OG-US</t>
+  </si>
+  <si>
+    <t>Madhu Gopinath</t>
+  </si>
+  <si>
+    <t>IT-FBT0636-OG-IN-00</t>
+  </si>
+  <si>
+    <t>SAP FICO L2 Support 2026H1</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>Finance System Support FY2026</t>
+  </si>
+  <si>
+    <t>SWC Elasticsearch (4/25/2026 – 4/24/2027) (LeslieM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ariba Offshore Technical Consultant </t>
+  </si>
+  <si>
+    <t>Enterprise Integration Hub (EIH) repository and support</t>
+  </si>
+  <si>
+    <t>Tenon: Japan SAP BI &amp; SD Support</t>
+  </si>
+  <si>
+    <t>IT-SFT0170-86-OG-US - Broadcom (Job Scheduler)</t>
+  </si>
+  <si>
+    <t>IT-SFT1441-OG-US-00 - AIOps - IBM Process Automation Manager</t>
+  </si>
+  <si>
+    <t>IT-FBT0588-OG-US-00 - Infrastructure Charges - SSL VPN - Partner Connect (SAP AG iVPN site-to-site)</t>
+  </si>
+  <si>
+    <t>AI Center of Excellence (COE) Infrastructure Support &amp; GDO Support for Ariba Bot</t>
+  </si>
+  <si>
+    <t>Legacy PS HR &amp; GRW Related charges</t>
+  </si>
+  <si>
+    <t>Infrastructure Charges - SAP Backoffice - Cloud AWS</t>
+  </si>
+  <si>
+    <t>Infrastructure Charges</t>
+  </si>
+  <si>
+    <t>PFIZER APPS related charges (Cloud AWS, Data Protection)</t>
+  </si>
+  <si>
+    <t>JFrog Artifactory Repository Monthly Charge</t>
+  </si>
+  <si>
+    <t>Others (Vending, Meeting event, Devices Unreturned, Applecare, Mac-mgmt, IT Onboard, etc.)</t>
+  </si>
+  <si>
+    <t>Desktop on Demand (VDS)</t>
+  </si>
+  <si>
+    <t>Infrastructure Charges - BTAMS Automations</t>
+  </si>
+  <si>
+    <t>DevSecOps</t>
+  </si>
+  <si>
+    <t>Infrastructure Billing Charges</t>
+  </si>
+  <si>
+    <t>Compliance FSA Chargeback</t>
+  </si>
+  <si>
+    <t>Pfizer IBM AIOPS solution</t>
+  </si>
+  <si>
+    <t>SAP Fieldglass Vendor Management System Implementation:  - Application/Platform support and maintenance</t>
+  </si>
+  <si>
+    <t>Oracle E-Business Suite Archive Solutions</t>
+  </si>
+  <si>
+    <t>2022 Buy on Demand (BOD) Application Management Services (AMS) Support Costs - Ariba/SAP Product Vendor</t>
+  </si>
+  <si>
+    <t>Markov (Mainteannce Renewal) (Pullforward Debit)</t>
+  </si>
+  <si>
+    <t>Markov (Mainteannce Renewal) (Pullforward Credit)</t>
+  </si>
+  <si>
+    <t>BizTalk Kovai</t>
+  </si>
+  <si>
+    <t>Monotype Imaging</t>
+  </si>
+  <si>
+    <t>TCPL_SAP SOM SME CONSULTANT FROM 1ST DECEMBER 2025 TO 30TH N</t>
+  </si>
+  <si>
+    <t>PSS_SOFTWARE MAINTENANCE SUPPORT_1ST DECEMBER 2025 TO 30TH N</t>
+  </si>
+  <si>
+    <t>MPLS Circuit supporting Oracle EPM Cloud FastConnect</t>
+  </si>
+  <si>
+    <t>Eliminated in LE0 (no budget) - VPN Site to Site supporting SAP AG Germany iVPN</t>
+  </si>
+  <si>
+    <t>IBM: SAP APPLICATION MANAGED SERVICE (AMS) - CORE / IT-FBT02</t>
+  </si>
+  <si>
+    <t>SAP Application Managed Service (AMS) - CORE- PCR-01(Collaboration360 Support)</t>
+  </si>
+  <si>
+    <t>SAP Application Managed Service "AMS" - SAP Ariba BOD &amp; Ariba On Prem</t>
+  </si>
+  <si>
+    <t>SAP Application Managed Service "AMS" - Additional Applications (10 Apps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seagen Oracle (Annual "AMS" Order) </t>
+  </si>
+  <si>
+    <t>Oracle EBS Software Licenses</t>
+  </si>
+  <si>
+    <t>Oracle OCI Software Usage</t>
+  </si>
+  <si>
+    <t>SAP GLNS AMS 2026</t>
+  </si>
+  <si>
+    <t>IBM ISOW – Application Managed Service "AMS" (Concur PT&amp;E)</t>
+  </si>
+  <si>
+    <t>SAP Application Managed Service "AMS" - Delta Applications - FBO Scope</t>
+  </si>
+  <si>
+    <t>IBM: CELONIS APPLICATION MANAGED SERVICES (AMS) / IT-FBT0700</t>
+  </si>
+  <si>
+    <t>ORACLE: ORACLE CUSTOM MANAGED CLOUD SERVICES JDE OCI / IT-SF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India SAP Helpdesk Support (SAP L1 &amp; L1.5) for 2026-27 </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
@@ -555,7 +901,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="56">
     <border>
       <left/>
       <right/>
@@ -955,19 +1301,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -1247,6 +1580,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1254,7 +1613,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1348,22 +1707,22 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="6" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="2" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1384,40 +1743,35 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="43" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="45" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="46" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="48" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="49" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="48" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="50" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="51" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="53" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1426,11 +1780,32 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="14" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1441,13 +1816,13 @@
     <xf numFmtId="3" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1468,7 +1843,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency 2" xfId="2" xr:uid="{C819F491-96B6-415F-B3EE-ED5A59A1E95E}"/>
@@ -1808,7 +2182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177F1DEB-197D-49C6-A2E3-152C1AC7B373}">
-  <dimension ref="A1:EI18"/>
+  <dimension ref="A1:EI66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -1816,9 +2190,10 @@
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
     <col min="4" max="4" width="11.5703125" customWidth="1"/>
     <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.85546875" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="41" customWidth="1"/>
+    <col min="6" max="6" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="10.85546875" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="41" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="37.140625" customWidth="1"/>
     <col min="13" max="13" width="12.42578125" customWidth="1"/>
     <col min="14" max="73" width="8.85546875" customWidth="1"/>
@@ -1940,10 +2315,10 @@
     </row>
     <row r="8" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="104"/>
+      <c r="B9" s="112"/>
       <c r="D9" s="55" t="s">
         <v>8</v>
       </c>
@@ -1989,106 +2364,106 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="44"/>
-      <c r="L11" s="105" t="s">
+      <c r="L11" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="106"/>
-      <c r="N11" s="97" cm="1">
-        <f t="array" ref="N11">SUM(Q15:Q17)+SUM(_xlfn._xlws.FILTER(P15:P17,Q15:Q17=""))+SUM(_xlfn._xlws.FILTER(O15:O17,(P15:P17="")*(Q15:Q17="")))+SUMIFS(R15:R17,Q15:Q17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(N15:N17)</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="98"/>
-      <c r="P11" s="98"/>
-      <c r="Q11" s="98"/>
-      <c r="R11" s="99"/>
-      <c r="S11" s="97" cm="1">
-        <f t="array" ref="S11">SUM(V15:V17)+SUM(_xlfn._xlws.FILTER(U15:U17,V15:V17=""))+SUM(_xlfn._xlws.FILTER(T15:T17,(U15:U17="")*(V15:V17="")))+SUMIFS(W15:W17,V15:V17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(S15:S17)</f>
-        <v>0</v>
-      </c>
-      <c r="T11" s="98"/>
-      <c r="U11" s="98"/>
-      <c r="V11" s="98"/>
-      <c r="W11" s="99"/>
-      <c r="X11" s="97" cm="1">
-        <f t="array" ref="X11">SUM(AA15:AA17)+SUM(_xlfn._xlws.FILTER(Z15:Z17,AA15:AA17=""))+SUM(_xlfn._xlws.FILTER(Y15:Y17,(Z15:Z17="")*(AA15:AA17="")))+SUMIFS(AB15:AB17,AA15:AA17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(X15:X17)</f>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="98"/>
-      <c r="Z11" s="98"/>
-      <c r="AA11" s="98"/>
-      <c r="AB11" s="99"/>
-      <c r="AC11" s="97" cm="1">
-        <f t="array" ref="AC11">SUM(AF15:AF17)+SUM(_xlfn._xlws.FILTER(AE15:AE17,AF15:AF17=""))+SUM(_xlfn._xlws.FILTER(AD15:AD17,(AE15:AE17="")*(AF15:AF17="")))+SUMIFS(AG15:AG17,AF15:AF17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(AC15:AC17)</f>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="98"/>
-      <c r="AE11" s="98"/>
-      <c r="AF11" s="98"/>
-      <c r="AG11" s="99"/>
-      <c r="AH11" s="97" cm="1">
-        <f t="array" ref="AH11">SUM(AK15:AK17)+SUM(_xlfn._xlws.FILTER(AJ15:AJ17,AK15:AK17=""))+SUM(_xlfn._xlws.FILTER(AI15:AI17,(AJ15:AJ17="")*(AK15:AK17="")))+SUMIFS(AL15:AL17,AK15:AK17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(AH15:AH17)</f>
-        <v>0</v>
-      </c>
-      <c r="AI11" s="98"/>
-      <c r="AJ11" s="98"/>
-      <c r="AK11" s="98"/>
-      <c r="AL11" s="99"/>
-      <c r="AM11" s="97" cm="1">
-        <f t="array" ref="AM11">SUM(AP15:AP17)+SUM(_xlfn._xlws.FILTER(AO15:AO17,AP15:AP17=""))+SUM(_xlfn._xlws.FILTER(AN15:AN17,(AO15:AO17="")*(AP15:AP17="")))+SUMIFS(AQ15:AQ17,AP15:AP17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(AM15:AM17)</f>
-        <v>0</v>
-      </c>
-      <c r="AN11" s="98"/>
-      <c r="AO11" s="98"/>
-      <c r="AP11" s="98"/>
-      <c r="AQ11" s="99"/>
-      <c r="AR11" s="97" cm="1">
-        <f t="array" ref="AR11">SUM(AU15:AU17)+SUM(_xlfn._xlws.FILTER(AT15:AT17,AU15:AU17=""))+SUM(_xlfn._xlws.FILTER(AS15:AS17,(AT15:AT17="")*(AU15:AU17="")))+SUMIFS(AV15:AV17,AU15:AU17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(AR15:AR17)</f>
-        <v>0</v>
-      </c>
-      <c r="AS11" s="98"/>
-      <c r="AT11" s="98"/>
-      <c r="AU11" s="98"/>
-      <c r="AV11" s="99"/>
-      <c r="AW11" s="97" cm="1">
-        <f t="array" ref="AW11">SUM(AZ15:AZ17)+SUM(_xlfn._xlws.FILTER(AY15:AY17,AZ15:AZ17=""))+SUM(_xlfn._xlws.FILTER(AX15:AX17,(AY15:AY17="")*(AZ15:AZ17="")))+SUMIFS(BA15:BA17,AZ15:AZ17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(AW15:AW17)</f>
-        <v>0</v>
-      </c>
-      <c r="AX11" s="98"/>
-      <c r="AY11" s="98"/>
-      <c r="AZ11" s="98"/>
-      <c r="BA11" s="99"/>
-      <c r="BB11" s="97" cm="1">
-        <f t="array" ref="BB11">SUM(BE15:BE17)+SUM(_xlfn._xlws.FILTER(BD15:BD17,BE15:BE17=""))+SUM(_xlfn._xlws.FILTER(BC15:BC17,(BD15:BD17="")*(BE15:BE17="")))+SUMIFS(BF15:BF17,BE15:BE17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(BB15:BB17)</f>
-        <v>0</v>
-      </c>
-      <c r="BC11" s="98"/>
-      <c r="BD11" s="98"/>
-      <c r="BE11" s="98"/>
-      <c r="BF11" s="99"/>
-      <c r="BG11" s="97" cm="1">
-        <f t="array" ref="BG11">SUM(BJ15:BJ17)+SUM(_xlfn._xlws.FILTER(BI15:BI17,BJ15:BJ17=""))+SUM(_xlfn._xlws.FILTER(BH15:BH17,(BI15:BI17="")*(BJ15:BJ17="")))+SUMIFS(BK15:BK17,BJ15:BJ17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(BG15:BG17)</f>
-        <v>0</v>
-      </c>
-      <c r="BH11" s="98"/>
-      <c r="BI11" s="98"/>
-      <c r="BJ11" s="98"/>
-      <c r="BK11" s="99"/>
-      <c r="BL11" s="97" cm="1">
-        <f t="array" ref="BL11">SUM(BO15:BO17)+SUM(_xlfn._xlws.FILTER(BN15:BN17,BO15:BO17=""))+SUM(_xlfn._xlws.FILTER(BM15:BM17,(BN15:BN17="")*(BO15:BO17="")))+SUMIFS(BP15:BP17,BO15:BO17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(BL15:BL17)</f>
-        <v>0</v>
-      </c>
-      <c r="BM11" s="98"/>
-      <c r="BN11" s="98"/>
-      <c r="BO11" s="98"/>
-      <c r="BP11" s="99"/>
-      <c r="BQ11" s="97" cm="1">
-        <f t="array" ref="BQ11">SUM(BT15:BT17)+SUM(_xlfn._xlws.FILTER(BS15:BS17,BT15:BT17=""))+SUM(_xlfn._xlws.FILTER(BR15:BR17,(BS15:BS17="")*(BT15:BT17="")))+SUMIFS(BU15:BU17,BT15:BT17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(BQ15:BQ17)</f>
-        <v>0</v>
-      </c>
-      <c r="BR11" s="98"/>
-      <c r="BS11" s="98"/>
-      <c r="BT11" s="98"/>
-      <c r="BU11" s="99"/>
+      <c r="M11" s="114"/>
+      <c r="N11" s="105" cm="1">
+        <f t="array" ref="N11">SUM(Q15:Q65)+SUM(_xlfn._xlws.FILTER(P15:P65,Q15:Q65=""))+SUM(_xlfn._xlws.FILTER(O15:O65,(P15:P65="")*(Q15:Q65="")))+SUMIFS(R15:R65,Q15:Q65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(N15:N65)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="106"/>
+      <c r="P11" s="106"/>
+      <c r="Q11" s="106"/>
+      <c r="R11" s="107"/>
+      <c r="S11" s="105" cm="1">
+        <f t="array" ref="S11">SUM(V15:V65)+SUM(_xlfn._xlws.FILTER(U15:U65,V15:V65=""))+SUM(_xlfn._xlws.FILTER(T15:T65,(U15:U65="")*(V15:V65="")))+SUMIFS(W15:W65,V15:V65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(S15:S65)</f>
+        <v>0</v>
+      </c>
+      <c r="T11" s="106"/>
+      <c r="U11" s="106"/>
+      <c r="V11" s="106"/>
+      <c r="W11" s="107"/>
+      <c r="X11" s="105" cm="1">
+        <f t="array" ref="X11">SUM(AA15:AA65)+SUM(_xlfn._xlws.FILTER(Z15:Z65,AA15:AA65=""))+SUM(_xlfn._xlws.FILTER(Y15:Y65,(Z15:Z65="")*(AA15:AA65="")))+SUMIFS(AB15:AB65,AA15:AA65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(X15:X65)</f>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="106"/>
+      <c r="Z11" s="106"/>
+      <c r="AA11" s="106"/>
+      <c r="AB11" s="107"/>
+      <c r="AC11" s="105" cm="1">
+        <f t="array" ref="AC11">SUM(AF15:AF65)+SUM(_xlfn._xlws.FILTER(AE15:AE65,AF15:AF65=""))+SUM(_xlfn._xlws.FILTER(AD15:AD65,(AE15:AE65="")*(AF15:AF65="")))+SUMIFS(AG15:AG65,AF15:AF65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AC15:AC65)</f>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="106"/>
+      <c r="AE11" s="106"/>
+      <c r="AF11" s="106"/>
+      <c r="AG11" s="107"/>
+      <c r="AH11" s="105" cm="1">
+        <f t="array" ref="AH11">SUM(AK15:AK65)+SUM(_xlfn._xlws.FILTER(AJ15:AJ65,AK15:AK65=""))+SUM(_xlfn._xlws.FILTER(AI15:AI65,(AJ15:AJ65="")*(AK15:AK65="")))+SUMIFS(AL15:AL65,AK15:AK65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AH15:AH65)</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="106"/>
+      <c r="AJ11" s="106"/>
+      <c r="AK11" s="106"/>
+      <c r="AL11" s="107"/>
+      <c r="AM11" s="105" cm="1">
+        <f t="array" ref="AM11">SUM(AP15:AP65)+SUM(_xlfn._xlws.FILTER(AO15:AO65,AP15:AP65=""))+SUM(_xlfn._xlws.FILTER(AN15:AN65,(AO15:AO65="")*(AP15:AP65="")))+SUMIFS(AQ15:AQ65,AP15:AP65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AM15:AM65)</f>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="106"/>
+      <c r="AO11" s="106"/>
+      <c r="AP11" s="106"/>
+      <c r="AQ11" s="107"/>
+      <c r="AR11" s="105" cm="1">
+        <f t="array" ref="AR11">SUM(AU15:AU65)+SUM(_xlfn._xlws.FILTER(AT15:AT65,AU15:AU65=""))+SUM(_xlfn._xlws.FILTER(AS15:AS65,(AT15:AT65="")*(AU15:AU65="")))+SUMIFS(AV15:AV65,AU15:AU65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AR15:AR65)</f>
+        <v>0</v>
+      </c>
+      <c r="AS11" s="106"/>
+      <c r="AT11" s="106"/>
+      <c r="AU11" s="106"/>
+      <c r="AV11" s="107"/>
+      <c r="AW11" s="105" cm="1">
+        <f t="array" ref="AW11">SUM(AZ15:AZ65)+SUM(_xlfn._xlws.FILTER(AY15:AY65,AZ15:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX15:AX65,(AY15:AY65="")*(AZ15:AZ65="")))+SUMIFS(BA15:BA65,AZ15:AZ65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AW15:AW65)</f>
+        <v>0</v>
+      </c>
+      <c r="AX11" s="106"/>
+      <c r="AY11" s="106"/>
+      <c r="AZ11" s="106"/>
+      <c r="BA11" s="107"/>
+      <c r="BB11" s="105" cm="1">
+        <f t="array" ref="BB11">SUM(BE15:BE65)+SUM(_xlfn._xlws.FILTER(BD15:BD65,BE15:BE65=""))+SUM(_xlfn._xlws.FILTER(BC15:BC65,(BD15:BD65="")*(BE15:BE65="")))+SUMIFS(BF15:BF65,BE15:BE65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BB15:BB65)</f>
+        <v>0</v>
+      </c>
+      <c r="BC11" s="106"/>
+      <c r="BD11" s="106"/>
+      <c r="BE11" s="106"/>
+      <c r="BF11" s="107"/>
+      <c r="BG11" s="105" cm="1">
+        <f t="array" ref="BG11">SUM(BJ15:BJ65)+SUM(_xlfn._xlws.FILTER(BI15:BI65,BJ15:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH15:BH65,(BI15:BI65="")*(BJ15:BJ65="")))+SUMIFS(BK15:BK65,BJ15:BJ65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BG15:BG65)</f>
+        <v>0</v>
+      </c>
+      <c r="BH11" s="106"/>
+      <c r="BI11" s="106"/>
+      <c r="BJ11" s="106"/>
+      <c r="BK11" s="107"/>
+      <c r="BL11" s="105" cm="1">
+        <f t="array" ref="BL11">SUM(BO15:BO65)+SUM(_xlfn._xlws.FILTER(BN15:BN65,BO15:BO65=""))+SUM(_xlfn._xlws.FILTER(BM15:BM65,(BN15:BN65="")*(BO15:BO65="")))+SUMIFS(BP15:BP65,BO15:BO65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BL15:BL65)</f>
+        <v>0</v>
+      </c>
+      <c r="BM11" s="106"/>
+      <c r="BN11" s="106"/>
+      <c r="BO11" s="106"/>
+      <c r="BP11" s="107"/>
+      <c r="BQ11" s="105" cm="1">
+        <f t="array" ref="BQ11">SUM(BT15:BT65)+SUM(_xlfn._xlws.FILTER(BS15:BS65,BT15:BT65=""))+SUM(_xlfn._xlws.FILTER(BR15:BR65,(BS15:BS65="")*(BT15:BT65="")))+SUMIFS(BU15:BU65,BT15:BT65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BQ15:BQ65)</f>
+        <v>0</v>
+      </c>
+      <c r="BR11" s="106"/>
+      <c r="BS11" s="106"/>
+      <c r="BT11" s="106"/>
+      <c r="BU11" s="107"/>
       <c r="BV11" s="4" t="s">
         <v>14</v>
       </c>
@@ -2114,106 +2489,106 @@
       <c r="K12" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="L12" s="107" t="s">
+      <c r="L12" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="108"/>
-      <c r="N12" s="97" cm="1">
-        <f t="array" ref="N12">SUM(Q15:Q17)+SUM(_xlfn._xlws.FILTER(P15:P17,Q15:Q17=""))+SUM(_xlfn._xlws.FILTER(O15:O17,(P15:P17="")*(Q15:Q17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="O12" s="98"/>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="99"/>
-      <c r="S12" s="97" cm="1">
-        <f t="array" ref="S12">SUM(V15:V17)+SUM(_xlfn._xlws.FILTER(U15:U17,V15:V17=""))+SUM(_xlfn._xlws.FILTER(T15:T17,(U15:U17="")*(V15:V17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="T12" s="98"/>
-      <c r="U12" s="98"/>
-      <c r="V12" s="98"/>
-      <c r="W12" s="99"/>
-      <c r="X12" s="97" cm="1">
-        <f t="array" ref="X12">SUM(AA15:AA17)+SUM(_xlfn._xlws.FILTER(Z15:Z17,AA15:AA17=""))+SUM(_xlfn._xlws.FILTER(Y15:Y17,(Z15:Z17="")*(AA15:AA17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="98"/>
-      <c r="Z12" s="98"/>
-      <c r="AA12" s="98"/>
-      <c r="AB12" s="99"/>
-      <c r="AC12" s="97" cm="1">
-        <f t="array" ref="AC12">SUM(AF15:AF17)+SUM(_xlfn._xlws.FILTER(AE15:AE17,AF15:AF17=""))+SUM(_xlfn._xlws.FILTER(AD15:AD17,(AE15:AE17="")*(AF15:AF17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="98"/>
-      <c r="AE12" s="98"/>
-      <c r="AF12" s="98"/>
-      <c r="AG12" s="99"/>
-      <c r="AH12" s="97" cm="1">
-        <f t="array" ref="AH12">SUM(AK15:AK17)+SUM(_xlfn._xlws.FILTER(AJ15:AJ17,AK15:AK17=""))+SUM(_xlfn._xlws.FILTER(AI15:AI17,(AJ15:AJ17="")*(AK15:AK17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="AI12" s="98"/>
-      <c r="AJ12" s="98"/>
-      <c r="AK12" s="98"/>
-      <c r="AL12" s="99"/>
-      <c r="AM12" s="97" cm="1">
-        <f t="array" ref="AM12">SUM(AP15:AP17)+SUM(_xlfn._xlws.FILTER(AO15:AO17,AP15:AP17=""))+SUM(_xlfn._xlws.FILTER(AN15:AN17,(AO15:AO17="")*(AP15:AP17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="AN12" s="98"/>
-      <c r="AO12" s="98"/>
-      <c r="AP12" s="98"/>
-      <c r="AQ12" s="99"/>
-      <c r="AR12" s="97" cm="1">
-        <f t="array" ref="AR12">SUM(AU15:AU17)+SUM(_xlfn._xlws.FILTER(AT15:AT17,AU15:AU17=""))+SUM(_xlfn._xlws.FILTER(AS15:AS17,(AT15:AT17="")*(AU15:AU17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="AS12" s="98"/>
-      <c r="AT12" s="98"/>
-      <c r="AU12" s="98"/>
-      <c r="AV12" s="99"/>
-      <c r="AW12" s="97" cm="1">
-        <f t="array" ref="AW12">SUM(AZ15:AZ17)+SUM(_xlfn._xlws.FILTER(AY15:AY17,AZ15:AZ17=""))+SUM(_xlfn._xlws.FILTER(AX15:AX17,(AY15:AY17="")*(AZ15:AZ17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="AX12" s="98"/>
-      <c r="AY12" s="98"/>
-      <c r="AZ12" s="98"/>
-      <c r="BA12" s="99"/>
-      <c r="BB12" s="97" cm="1">
-        <f t="array" ref="BB12">SUM(BE15:BE17)+SUM(_xlfn._xlws.FILTER(BD15:BD17,BE15:BE17=""))+SUM(_xlfn._xlws.FILTER(BC15:BC17,(BD15:BD17="")*(BE15:BE17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="BC12" s="98"/>
-      <c r="BD12" s="98"/>
-      <c r="BE12" s="98"/>
-      <c r="BF12" s="99"/>
-      <c r="BG12" s="97" cm="1">
-        <f t="array" ref="BG12">SUM(BJ15:BJ17)+SUM(_xlfn._xlws.FILTER(BI15:BI17,BJ15:BJ17=""))+SUM(_xlfn._xlws.FILTER(BH15:BH17,(BI15:BI17="")*(BJ15:BJ17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="BH12" s="98"/>
-      <c r="BI12" s="98"/>
-      <c r="BJ12" s="98"/>
-      <c r="BK12" s="99"/>
-      <c r="BL12" s="97" cm="1">
-        <f t="array" ref="BL12">SUM(BO15:BO17)+SUM(_xlfn._xlws.FILTER(BN15:BN17,BO15:BO17=""))+SUM(_xlfn._xlws.FILTER(BM15:BM17,(BN15:BN17="")*(BO15:BO17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="BM12" s="98"/>
-      <c r="BN12" s="98"/>
-      <c r="BO12" s="98"/>
-      <c r="BP12" s="99"/>
-      <c r="BQ12" s="97" cm="1">
-        <f t="array" ref="BQ12">SUM(BT15:BT17)+SUM(_xlfn._xlws.FILTER(BS15:BS17,BT15:BT17=""))+SUM(_xlfn._xlws.FILTER(BR15:BR17,(BS15:BS17="")*(BT15:BT17="")))</f>
-        <v>0</v>
-      </c>
-      <c r="BR12" s="98"/>
-      <c r="BS12" s="98"/>
-      <c r="BT12" s="98"/>
-      <c r="BU12" s="99"/>
+      <c r="M12" s="116"/>
+      <c r="N12" s="105" cm="1">
+        <f t="array" ref="N12">SUM(Q15:Q65)+SUM(_xlfn._xlws.FILTER(P15:P65,Q15:Q65=""))+SUM(_xlfn._xlws.FILTER(O15:O65,(P15:P65="")*(Q15:Q65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="106"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="106"/>
+      <c r="R12" s="107"/>
+      <c r="S12" s="105" cm="1">
+        <f t="array" ref="S12">SUM(V15:V65)+SUM(_xlfn._xlws.FILTER(U15:U65,V15:V65=""))+SUM(_xlfn._xlws.FILTER(T15:T65,(U15:U65="")*(V15:V65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="106"/>
+      <c r="U12" s="106"/>
+      <c r="V12" s="106"/>
+      <c r="W12" s="107"/>
+      <c r="X12" s="105" cm="1">
+        <f t="array" ref="X12">SUM(AA15:AA65)+SUM(_xlfn._xlws.FILTER(Z15:Z65,AA15:AA65=""))+SUM(_xlfn._xlws.FILTER(Y15:Y65,(Z15:Z65="")*(AA15:AA65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="106"/>
+      <c r="Z12" s="106"/>
+      <c r="AA12" s="106"/>
+      <c r="AB12" s="107"/>
+      <c r="AC12" s="105" cm="1">
+        <f t="array" ref="AC12">SUM(AF15:AF65)+SUM(_xlfn._xlws.FILTER(AE15:AE65,AF15:AF65=""))+SUM(_xlfn._xlws.FILTER(AD15:AD65,(AE15:AE65="")*(AF15:AF65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="106"/>
+      <c r="AE12" s="106"/>
+      <c r="AF12" s="106"/>
+      <c r="AG12" s="107"/>
+      <c r="AH12" s="105" cm="1">
+        <f t="array" ref="AH12">SUM(AK15:AK65)+SUM(_xlfn._xlws.FILTER(AJ15:AJ65,AK15:AK65=""))+SUM(_xlfn._xlws.FILTER(AI15:AI65,(AJ15:AJ65="")*(AK15:AK65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="106"/>
+      <c r="AJ12" s="106"/>
+      <c r="AK12" s="106"/>
+      <c r="AL12" s="107"/>
+      <c r="AM12" s="105" cm="1">
+        <f t="array" ref="AM12">SUM(AP15:AP65)+SUM(_xlfn._xlws.FILTER(AO15:AO65,AP15:AP65=""))+SUM(_xlfn._xlws.FILTER(AN15:AN65,(AO15:AO65="")*(AP15:AP65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AN12" s="106"/>
+      <c r="AO12" s="106"/>
+      <c r="AP12" s="106"/>
+      <c r="AQ12" s="107"/>
+      <c r="AR12" s="105" cm="1">
+        <f t="array" ref="AR12">SUM(AU15:AU65)+SUM(_xlfn._xlws.FILTER(AT15:AT65,AU15:AU65=""))+SUM(_xlfn._xlws.FILTER(AS15:AS65,(AT15:AT65="")*(AU15:AU65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AS12" s="106"/>
+      <c r="AT12" s="106"/>
+      <c r="AU12" s="106"/>
+      <c r="AV12" s="107"/>
+      <c r="AW12" s="105" cm="1">
+        <f t="array" ref="AW12">SUM(AZ15:AZ65)+SUM(_xlfn._xlws.FILTER(AY15:AY65,AZ15:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX15:AX65,(AY15:AY65="")*(AZ15:AZ65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AX12" s="106"/>
+      <c r="AY12" s="106"/>
+      <c r="AZ12" s="106"/>
+      <c r="BA12" s="107"/>
+      <c r="BB12" s="105" cm="1">
+        <f t="array" ref="BB12">SUM(BE15:BE65)+SUM(_xlfn._xlws.FILTER(BD15:BD65,BE15:BE65=""))+SUM(_xlfn._xlws.FILTER(BC15:BC65,(BD15:BD65="")*(BE15:BE65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BC12" s="106"/>
+      <c r="BD12" s="106"/>
+      <c r="BE12" s="106"/>
+      <c r="BF12" s="107"/>
+      <c r="BG12" s="105" cm="1">
+        <f t="array" ref="BG12">SUM(BJ15:BJ65)+SUM(_xlfn._xlws.FILTER(BI15:BI65,BJ15:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH15:BH65,(BI15:BI65="")*(BJ15:BJ65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BH12" s="106"/>
+      <c r="BI12" s="106"/>
+      <c r="BJ12" s="106"/>
+      <c r="BK12" s="107"/>
+      <c r="BL12" s="105" cm="1">
+        <f t="array" ref="BL12">SUM(BO15:BO65)+SUM(_xlfn._xlws.FILTER(BN15:BN65,BO15:BO65=""))+SUM(_xlfn._xlws.FILTER(BM15:BM65,(BN15:BN65="")*(BO15:BO65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BM12" s="106"/>
+      <c r="BN12" s="106"/>
+      <c r="BO12" s="106"/>
+      <c r="BP12" s="107"/>
+      <c r="BQ12" s="105" cm="1">
+        <f t="array" ref="BQ12">SUM(BT15:BT65)+SUM(_xlfn._xlws.FILTER(BS15:BS65,BT15:BT65=""))+SUM(_xlfn._xlws.FILTER(BR15:BR65,(BS15:BS65="")*(BT15:BT65="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BR12" s="106"/>
+      <c r="BS12" s="106"/>
+      <c r="BT12" s="106"/>
+      <c r="BU12" s="107"/>
       <c r="BV12" s="4"/>
       <c r="BW12" s="5"/>
     </row>
@@ -2226,120 +2601,120 @@
       <c r="J13" s="6"/>
       <c r="K13" s="54">
         <f>SUBTOTAL(9,K15:K16)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="107" t="s">
+        <v>190781</v>
+      </c>
+      <c r="L13" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="M13" s="108"/>
-      <c r="N13" s="100">
+      <c r="M13" s="116"/>
+      <c r="N13" s="108">
         <v>46053</v>
       </c>
-      <c r="O13" s="101" t="s">
+      <c r="O13" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="P13" s="101"/>
-      <c r="Q13" s="101"/>
-      <c r="R13" s="101"/>
-      <c r="S13" s="100">
+      <c r="P13" s="109"/>
+      <c r="Q13" s="109"/>
+      <c r="R13" s="109"/>
+      <c r="S13" s="108">
         <v>46054</v>
       </c>
-      <c r="T13" s="101"/>
-      <c r="U13" s="101"/>
-      <c r="V13" s="101"/>
-      <c r="W13" s="102"/>
-      <c r="X13" s="100">
+      <c r="T13" s="109"/>
+      <c r="U13" s="109"/>
+      <c r="V13" s="109"/>
+      <c r="W13" s="110"/>
+      <c r="X13" s="108">
         <v>46112</v>
       </c>
-      <c r="Y13" s="101" t="s">
+      <c r="Y13" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="Z13" s="101"/>
-      <c r="AA13" s="101"/>
-      <c r="AB13" s="102"/>
-      <c r="AC13" s="100">
+      <c r="Z13" s="109"/>
+      <c r="AA13" s="109"/>
+      <c r="AB13" s="110"/>
+      <c r="AC13" s="108">
         <v>46142</v>
       </c>
-      <c r="AD13" s="101" t="s">
+      <c r="AD13" s="109" t="s">
         <v>22</v>
       </c>
-      <c r="AE13" s="101"/>
-      <c r="AF13" s="101"/>
-      <c r="AG13" s="102"/>
-      <c r="AH13" s="100">
+      <c r="AE13" s="109"/>
+      <c r="AF13" s="109"/>
+      <c r="AG13" s="110"/>
+      <c r="AH13" s="108">
         <v>46173</v>
       </c>
-      <c r="AI13" s="101" t="s">
+      <c r="AI13" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="AJ13" s="101"/>
-      <c r="AK13" s="101"/>
-      <c r="AL13" s="102"/>
-      <c r="AM13" s="100">
+      <c r="AJ13" s="109"/>
+      <c r="AK13" s="109"/>
+      <c r="AL13" s="110"/>
+      <c r="AM13" s="108">
         <v>46203</v>
       </c>
-      <c r="AN13" s="101" t="s">
+      <c r="AN13" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="AO13" s="101"/>
-      <c r="AP13" s="101"/>
-      <c r="AQ13" s="102"/>
-      <c r="AR13" s="100">
+      <c r="AO13" s="109"/>
+      <c r="AP13" s="109"/>
+      <c r="AQ13" s="110"/>
+      <c r="AR13" s="108">
         <v>46234</v>
       </c>
-      <c r="AS13" s="101" t="s">
+      <c r="AS13" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="AT13" s="101"/>
-      <c r="AU13" s="101"/>
-      <c r="AV13" s="102"/>
-      <c r="AW13" s="100">
+      <c r="AT13" s="109"/>
+      <c r="AU13" s="109"/>
+      <c r="AV13" s="110"/>
+      <c r="AW13" s="108">
         <v>46265</v>
       </c>
-      <c r="AX13" s="101" t="s">
+      <c r="AX13" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="AY13" s="101"/>
-      <c r="AZ13" s="101"/>
-      <c r="BA13" s="102"/>
-      <c r="BB13" s="100">
+      <c r="AY13" s="109"/>
+      <c r="AZ13" s="109"/>
+      <c r="BA13" s="110"/>
+      <c r="BB13" s="108">
         <v>46295</v>
       </c>
-      <c r="BC13" s="101" t="s">
+      <c r="BC13" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="BD13" s="101"/>
-      <c r="BE13" s="101"/>
-      <c r="BF13" s="102"/>
-      <c r="BG13" s="100">
+      <c r="BD13" s="109"/>
+      <c r="BE13" s="109"/>
+      <c r="BF13" s="110"/>
+      <c r="BG13" s="108">
         <v>46326</v>
       </c>
-      <c r="BH13" s="101" t="s">
+      <c r="BH13" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="BI13" s="101"/>
-      <c r="BJ13" s="101"/>
-      <c r="BK13" s="102"/>
-      <c r="BL13" s="100">
+      <c r="BI13" s="109"/>
+      <c r="BJ13" s="109"/>
+      <c r="BK13" s="110"/>
+      <c r="BL13" s="108">
         <v>46356</v>
       </c>
-      <c r="BM13" s="101" t="s">
+      <c r="BM13" s="109" t="s">
         <v>29</v>
       </c>
-      <c r="BN13" s="101"/>
-      <c r="BO13" s="101"/>
-      <c r="BP13" s="102"/>
-      <c r="BQ13" s="100">
+      <c r="BN13" s="109"/>
+      <c r="BO13" s="109"/>
+      <c r="BP13" s="110"/>
+      <c r="BQ13" s="108">
         <v>46387</v>
       </c>
-      <c r="BR13" s="101" t="s">
+      <c r="BR13" s="109" t="s">
         <v>30</v>
       </c>
-      <c r="BS13" s="101"/>
-      <c r="BT13" s="101"/>
-      <c r="BU13" s="102"/>
+      <c r="BS13" s="109"/>
+      <c r="BT13" s="109"/>
+      <c r="BU13" s="110"/>
       <c r="BV13" s="7">
-        <f>SUM(BV15:BV17)</f>
+        <f>SUM(BV15:BV65)</f>
         <v>0</v>
       </c>
       <c r="BW13" s="8"/>
@@ -2576,122 +2951,146 @@
       </c>
     </row>
     <row r="15" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A15" s="79"/>
-      <c r="B15" s="109">
-        <v>9500879389</v>
-      </c>
-      <c r="C15" s="80"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="82"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="86"/>
-      <c r="P15" s="86"/>
-      <c r="Q15" s="87"/>
-      <c r="R15" s="87">
+      <c r="A15" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="94">
+        <v>9501133449</v>
+      </c>
+      <c r="C15" s="96">
+        <v>45993</v>
+      </c>
+      <c r="D15" s="96">
+        <v>46173</v>
+      </c>
+      <c r="E15" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" s="80" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="80">
+        <v>41500000</v>
+      </c>
+      <c r="H15" s="80">
+        <v>3840</v>
+      </c>
+      <c r="I15" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="J15" s="80">
+        <v>2430238</v>
+      </c>
+      <c r="K15" s="97">
+        <v>66363</v>
+      </c>
+      <c r="L15" s="100" t="s">
+        <v>165</v>
+      </c>
+      <c r="M15" s="101" t="s">
+        <v>166</v>
+      </c>
+      <c r="N15" s="82"/>
+      <c r="O15" s="83"/>
+      <c r="P15" s="83"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84">
         <f>P15-Q15</f>
         <v>0</v>
       </c>
-      <c r="S15" s="88"/>
-      <c r="T15" s="86"/>
-      <c r="U15" s="86"/>
-      <c r="V15" s="87"/>
-      <c r="W15" s="89">
+      <c r="S15" s="85"/>
+      <c r="T15" s="83"/>
+      <c r="U15" s="83"/>
+      <c r="V15" s="84"/>
+      <c r="W15" s="86">
         <f>U15-V15</f>
         <v>0</v>
       </c>
-      <c r="X15" s="90"/>
-      <c r="Y15" s="86"/>
-      <c r="Z15" s="86"/>
-      <c r="AA15" s="87"/>
-      <c r="AB15" s="89">
+      <c r="X15" s="87"/>
+      <c r="Y15" s="83"/>
+      <c r="Z15" s="83"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="86">
         <f>Z15-AA15</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="90"/>
-      <c r="AD15" s="86"/>
-      <c r="AE15" s="86"/>
-      <c r="AF15" s="86"/>
-      <c r="AG15" s="89">
+      <c r="AC15" s="87"/>
+      <c r="AD15" s="83"/>
+      <c r="AE15" s="83"/>
+      <c r="AF15" s="83"/>
+      <c r="AG15" s="86">
         <f>AE15-AF15</f>
         <v>0</v>
       </c>
-      <c r="AH15" s="90"/>
-      <c r="AI15" s="86"/>
-      <c r="AJ15" s="86"/>
-      <c r="AK15" s="86"/>
-      <c r="AL15" s="89">
+      <c r="AH15" s="87"/>
+      <c r="AI15" s="83"/>
+      <c r="AJ15" s="83"/>
+      <c r="AK15" s="83"/>
+      <c r="AL15" s="86">
         <f>AJ15-AK15</f>
         <v>0</v>
       </c>
-      <c r="AM15" s="90"/>
-      <c r="AN15" s="86"/>
-      <c r="AO15" s="86"/>
-      <c r="AP15" s="86"/>
-      <c r="AQ15" s="89">
+      <c r="AM15" s="87"/>
+      <c r="AN15" s="83"/>
+      <c r="AO15" s="83"/>
+      <c r="AP15" s="83"/>
+      <c r="AQ15" s="86">
         <f>AO15-AP15</f>
         <v>0</v>
       </c>
-      <c r="AR15" s="90"/>
-      <c r="AS15" s="86"/>
-      <c r="AT15" s="86"/>
-      <c r="AU15" s="86"/>
-      <c r="AV15" s="89">
+      <c r="AR15" s="87"/>
+      <c r="AS15" s="83"/>
+      <c r="AT15" s="83"/>
+      <c r="AU15" s="83"/>
+      <c r="AV15" s="86">
         <f>AT15-AU15</f>
         <v>0</v>
       </c>
-      <c r="AW15" s="90"/>
-      <c r="AX15" s="86"/>
-      <c r="AY15" s="86"/>
-      <c r="AZ15" s="86"/>
-      <c r="BA15" s="89">
+      <c r="AW15" s="87"/>
+      <c r="AX15" s="83"/>
+      <c r="AY15" s="83"/>
+      <c r="AZ15" s="83"/>
+      <c r="BA15" s="86">
         <f>AY15-AZ15</f>
         <v>0</v>
       </c>
-      <c r="BB15" s="90"/>
-      <c r="BC15" s="86"/>
-      <c r="BD15" s="86"/>
-      <c r="BE15" s="86"/>
-      <c r="BF15" s="89">
+      <c r="BB15" s="87"/>
+      <c r="BC15" s="83"/>
+      <c r="BD15" s="83"/>
+      <c r="BE15" s="83"/>
+      <c r="BF15" s="86">
         <f>BD15-BE15</f>
         <v>0</v>
       </c>
-      <c r="BG15" s="90"/>
-      <c r="BH15" s="86"/>
-      <c r="BI15" s="86"/>
-      <c r="BJ15" s="86"/>
-      <c r="BK15" s="89">
+      <c r="BG15" s="87"/>
+      <c r="BH15" s="83"/>
+      <c r="BI15" s="83"/>
+      <c r="BJ15" s="83"/>
+      <c r="BK15" s="86">
         <f>BI15-BJ15</f>
         <v>0</v>
       </c>
-      <c r="BL15" s="90"/>
-      <c r="BM15" s="86"/>
-      <c r="BN15" s="86"/>
-      <c r="BO15" s="86"/>
-      <c r="BP15" s="89">
+      <c r="BL15" s="87"/>
+      <c r="BM15" s="83"/>
+      <c r="BN15" s="83"/>
+      <c r="BO15" s="83"/>
+      <c r="BP15" s="86">
         <f>BN15-BO15</f>
         <v>0</v>
       </c>
-      <c r="BQ15" s="90"/>
-      <c r="BR15" s="86"/>
-      <c r="BS15" s="86"/>
-      <c r="BT15" s="86"/>
-      <c r="BU15" s="89">
+      <c r="BQ15" s="87"/>
+      <c r="BR15" s="83"/>
+      <c r="BS15" s="83"/>
+      <c r="BT15" s="83"/>
+      <c r="BU15" s="86">
         <f>BS15-BT15</f>
         <v>0</v>
       </c>
-      <c r="BV15" s="91">
-        <v>0</v>
-      </c>
-      <c r="BW15" s="92"/>
-      <c r="BX15" s="93"/>
+      <c r="BV15" s="88">
+        <v>0</v>
+      </c>
+      <c r="BW15" s="89"/>
+      <c r="BX15" s="90"/>
       <c r="BY15" s="78"/>
       <c r="BZ15" s="78"/>
       <c r="CA15" s="78"/>
@@ -2757,122 +3156,146 @@
       <c r="EI15" s="78"/>
     </row>
     <row r="16" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A16" s="94"/>
-      <c r="B16" s="86">
-        <v>9500882917</v>
-      </c>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="85"/>
-      <c r="O16" s="86"/>
-      <c r="P16" s="86"/>
-      <c r="Q16" s="87"/>
-      <c r="R16" s="87">
+      <c r="A16" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="83">
+        <v>9501133442</v>
+      </c>
+      <c r="C16" s="98">
+        <v>45993</v>
+      </c>
+      <c r="D16" s="98">
+        <v>46356</v>
+      </c>
+      <c r="E16" s="92" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="92" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H16" s="92">
+        <v>3840</v>
+      </c>
+      <c r="I16" s="92" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="92">
+        <v>2430238</v>
+      </c>
+      <c r="K16" s="99">
+        <v>124418</v>
+      </c>
+      <c r="L16" s="102" t="s">
+        <v>167</v>
+      </c>
+      <c r="M16" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N16" s="82"/>
+      <c r="O16" s="83"/>
+      <c r="P16" s="83"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="84">
         <f>P16-Q16</f>
         <v>0</v>
       </c>
-      <c r="S16" s="88"/>
-      <c r="T16" s="86"/>
-      <c r="U16" s="86"/>
-      <c r="V16" s="87"/>
-      <c r="W16" s="89">
+      <c r="S16" s="85"/>
+      <c r="T16" s="83"/>
+      <c r="U16" s="83"/>
+      <c r="V16" s="84"/>
+      <c r="W16" s="86">
         <f>U16-V16</f>
         <v>0</v>
       </c>
-      <c r="X16" s="90"/>
-      <c r="Y16" s="86"/>
-      <c r="Z16" s="86"/>
-      <c r="AA16" s="87"/>
-      <c r="AB16" s="89">
+      <c r="X16" s="87"/>
+      <c r="Y16" s="83"/>
+      <c r="Z16" s="83"/>
+      <c r="AA16" s="84"/>
+      <c r="AB16" s="86">
         <f>Z16-AA16</f>
         <v>0</v>
       </c>
-      <c r="AC16" s="90"/>
-      <c r="AD16" s="86"/>
-      <c r="AE16" s="86"/>
-      <c r="AF16" s="87"/>
-      <c r="AG16" s="89">
+      <c r="AC16" s="87"/>
+      <c r="AD16" s="83"/>
+      <c r="AE16" s="83"/>
+      <c r="AF16" s="84"/>
+      <c r="AG16" s="86">
         <f>AE16-AF16</f>
         <v>0</v>
       </c>
-      <c r="AH16" s="90"/>
-      <c r="AI16" s="86"/>
-      <c r="AJ16" s="86"/>
-      <c r="AK16" s="87"/>
-      <c r="AL16" s="89">
+      <c r="AH16" s="87"/>
+      <c r="AI16" s="83"/>
+      <c r="AJ16" s="83"/>
+      <c r="AK16" s="84"/>
+      <c r="AL16" s="86">
         <f>AJ16-AK16</f>
         <v>0</v>
       </c>
-      <c r="AM16" s="90"/>
-      <c r="AN16" s="86"/>
-      <c r="AO16" s="86"/>
-      <c r="AP16" s="87"/>
-      <c r="AQ16" s="89">
+      <c r="AM16" s="87"/>
+      <c r="AN16" s="83"/>
+      <c r="AO16" s="83"/>
+      <c r="AP16" s="84"/>
+      <c r="AQ16" s="86">
         <f>AO16-AP16</f>
         <v>0</v>
       </c>
-      <c r="AR16" s="90"/>
-      <c r="AS16" s="86"/>
-      <c r="AT16" s="86"/>
-      <c r="AU16" s="87"/>
-      <c r="AV16" s="89">
+      <c r="AR16" s="87"/>
+      <c r="AS16" s="83"/>
+      <c r="AT16" s="83"/>
+      <c r="AU16" s="84"/>
+      <c r="AV16" s="86">
         <f>AT16-AU16</f>
         <v>0</v>
       </c>
-      <c r="AW16" s="90"/>
-      <c r="AX16" s="86"/>
-      <c r="AY16" s="86"/>
-      <c r="AZ16" s="87"/>
-      <c r="BA16" s="89">
+      <c r="AW16" s="87"/>
+      <c r="AX16" s="83"/>
+      <c r="AY16" s="83"/>
+      <c r="AZ16" s="84"/>
+      <c r="BA16" s="86">
         <f>AY16-AZ16</f>
         <v>0</v>
       </c>
-      <c r="BB16" s="90"/>
-      <c r="BC16" s="86"/>
-      <c r="BD16" s="86"/>
-      <c r="BE16" s="87"/>
-      <c r="BF16" s="89">
+      <c r="BB16" s="87"/>
+      <c r="BC16" s="83"/>
+      <c r="BD16" s="83"/>
+      <c r="BE16" s="84"/>
+      <c r="BF16" s="86">
         <f>BD16-BE16</f>
         <v>0</v>
       </c>
-      <c r="BG16" s="90"/>
-      <c r="BH16" s="86"/>
-      <c r="BI16" s="86"/>
-      <c r="BJ16" s="87"/>
-      <c r="BK16" s="89">
+      <c r="BG16" s="87"/>
+      <c r="BH16" s="83"/>
+      <c r="BI16" s="83"/>
+      <c r="BJ16" s="84"/>
+      <c r="BK16" s="86">
         <f>BI16-BJ16</f>
         <v>0</v>
       </c>
-      <c r="BL16" s="90"/>
-      <c r="BM16" s="86"/>
-      <c r="BN16" s="86"/>
-      <c r="BO16" s="87"/>
-      <c r="BP16" s="89">
+      <c r="BL16" s="87"/>
+      <c r="BM16" s="83"/>
+      <c r="BN16" s="83"/>
+      <c r="BO16" s="84"/>
+      <c r="BP16" s="86">
         <f>BN16-BO16</f>
         <v>0</v>
       </c>
-      <c r="BQ16" s="90"/>
-      <c r="BR16" s="86"/>
-      <c r="BS16" s="86"/>
-      <c r="BT16" s="87"/>
-      <c r="BU16" s="89">
+      <c r="BQ16" s="87"/>
+      <c r="BR16" s="83"/>
+      <c r="BS16" s="83"/>
+      <c r="BT16" s="84"/>
+      <c r="BU16" s="86">
         <f>BS16-BT16</f>
         <v>0</v>
       </c>
-      <c r="BV16" s="88">
-        <v>0</v>
-      </c>
-      <c r="BW16" s="92"/>
-      <c r="BX16" s="93"/>
+      <c r="BV16" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW16" s="89"/>
+      <c r="BX16" s="90"/>
       <c r="BY16" s="78"/>
       <c r="BZ16" s="78"/>
       <c r="CA16" s="78"/>
@@ -2937,187 +3360,6297 @@
       <c r="EH16" s="78"/>
       <c r="EI16" s="78"/>
     </row>
-    <row r="17" spans="1:139" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="66" t="s">
+    <row r="17" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="83">
+        <v>9100561560</v>
+      </c>
+      <c r="C17" s="98">
+        <v>46137</v>
+      </c>
+      <c r="D17" s="98">
+        <v>46501</v>
+      </c>
+      <c r="E17" s="92" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="92" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="92">
+        <v>61010000</v>
+      </c>
+      <c r="H17" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I17" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J17" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K17" s="99">
+        <v>21098.22</v>
+      </c>
+      <c r="L17" s="104" t="s">
+        <v>168</v>
+      </c>
+      <c r="M17" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N17" s="82"/>
+      <c r="O17" s="83"/>
+      <c r="P17" s="83"/>
+      <c r="Q17" s="84"/>
+      <c r="R17" s="84">
+        <f t="shared" ref="R17:R24" si="0">P17-Q17</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="85"/>
+      <c r="T17" s="83"/>
+      <c r="U17" s="83"/>
+      <c r="V17" s="84"/>
+      <c r="W17" s="86">
+        <f t="shared" ref="W17:W24" si="1">U17-V17</f>
+        <v>0</v>
+      </c>
+      <c r="X17" s="87"/>
+      <c r="Y17" s="83"/>
+      <c r="Z17" s="83"/>
+      <c r="AA17" s="84"/>
+      <c r="AB17" s="86">
+        <f t="shared" ref="AB17:AB24" si="2">Z17-AA17</f>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="87"/>
+      <c r="AD17" s="83"/>
+      <c r="AE17" s="83"/>
+      <c r="AF17" s="84"/>
+      <c r="AG17" s="86">
+        <f t="shared" ref="AG17:AG24" si="3">AE17-AF17</f>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="87"/>
+      <c r="AI17" s="83"/>
+      <c r="AJ17" s="83"/>
+      <c r="AK17" s="84"/>
+      <c r="AL17" s="86">
+        <f t="shared" ref="AL17:AL24" si="4">AJ17-AK17</f>
+        <v>0</v>
+      </c>
+      <c r="AM17" s="87"/>
+      <c r="AN17" s="83"/>
+      <c r="AO17" s="83"/>
+      <c r="AP17" s="84"/>
+      <c r="AQ17" s="86">
+        <f t="shared" ref="AQ17:AQ24" si="5">AO17-AP17</f>
+        <v>0</v>
+      </c>
+      <c r="AR17" s="87"/>
+      <c r="AS17" s="83"/>
+      <c r="AT17" s="83"/>
+      <c r="AU17" s="84"/>
+      <c r="AV17" s="86">
+        <f t="shared" ref="AV17:AV24" si="6">AT17-AU17</f>
+        <v>0</v>
+      </c>
+      <c r="AW17" s="87"/>
+      <c r="AX17" s="83"/>
+      <c r="AY17" s="83"/>
+      <c r="AZ17" s="84"/>
+      <c r="BA17" s="86">
+        <f t="shared" ref="BA17:BA24" si="7">AY17-AZ17</f>
+        <v>0</v>
+      </c>
+      <c r="BB17" s="87"/>
+      <c r="BC17" s="83"/>
+      <c r="BD17" s="83"/>
+      <c r="BE17" s="84"/>
+      <c r="BF17" s="86">
+        <f t="shared" ref="BF17:BF24" si="8">BD17-BE17</f>
+        <v>0</v>
+      </c>
+      <c r="BG17" s="87"/>
+      <c r="BH17" s="83"/>
+      <c r="BI17" s="83"/>
+      <c r="BJ17" s="84"/>
+      <c r="BK17" s="86">
+        <f t="shared" ref="BK17:BK24" si="9">BI17-BJ17</f>
+        <v>0</v>
+      </c>
+      <c r="BL17" s="87"/>
+      <c r="BM17" s="83"/>
+      <c r="BN17" s="83"/>
+      <c r="BO17" s="84"/>
+      <c r="BP17" s="86">
+        <f t="shared" ref="BP17:BP24" si="10">BN17-BO17</f>
+        <v>0</v>
+      </c>
+      <c r="BQ17" s="87"/>
+      <c r="BR17" s="83"/>
+      <c r="BS17" s="83"/>
+      <c r="BT17" s="84"/>
+      <c r="BU17" s="86">
+        <f t="shared" ref="BU17:BU24" si="11">BS17-BT17</f>
+        <v>0</v>
+      </c>
+      <c r="BV17" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW17" s="89"/>
+      <c r="BX17" s="90"/>
+    </row>
+    <row r="18" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A18" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" s="83">
+        <v>9501079958</v>
+      </c>
+      <c r="C18" s="98">
+        <v>45931</v>
+      </c>
+      <c r="D18" s="98">
+        <v>46265</v>
+      </c>
+      <c r="E18" s="92" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="92"/>
+      <c r="G18" s="92"/>
+      <c r="H18" s="92"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="93"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="82"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="83"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="84">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="85"/>
+      <c r="T18" s="83"/>
+      <c r="U18" s="83"/>
+      <c r="V18" s="84"/>
+      <c r="W18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="87"/>
+      <c r="Y18" s="83"/>
+      <c r="Z18" s="83"/>
+      <c r="AA18" s="84"/>
+      <c r="AB18" s="86">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="87"/>
+      <c r="AD18" s="83"/>
+      <c r="AE18" s="83"/>
+      <c r="AF18" s="84"/>
+      <c r="AG18" s="86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="87"/>
+      <c r="AI18" s="83"/>
+      <c r="AJ18" s="83"/>
+      <c r="AK18" s="84"/>
+      <c r="AL18" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AM18" s="87"/>
+      <c r="AN18" s="83"/>
+      <c r="AO18" s="83"/>
+      <c r="AP18" s="84"/>
+      <c r="AQ18" s="86">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AR18" s="87"/>
+      <c r="AS18" s="83"/>
+      <c r="AT18" s="83"/>
+      <c r="AU18" s="84"/>
+      <c r="AV18" s="86">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AW18" s="87"/>
+      <c r="AX18" s="83"/>
+      <c r="AY18" s="83"/>
+      <c r="AZ18" s="84"/>
+      <c r="BA18" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BB18" s="87"/>
+      <c r="BC18" s="83"/>
+      <c r="BD18" s="83"/>
+      <c r="BE18" s="84"/>
+      <c r="BF18" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BG18" s="87"/>
+      <c r="BH18" s="83"/>
+      <c r="BI18" s="83"/>
+      <c r="BJ18" s="84"/>
+      <c r="BK18" s="86">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BL18" s="87"/>
+      <c r="BM18" s="83"/>
+      <c r="BN18" s="83"/>
+      <c r="BO18" s="84"/>
+      <c r="BP18" s="86">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BQ18" s="87"/>
+      <c r="BR18" s="83"/>
+      <c r="BS18" s="83"/>
+      <c r="BT18" s="84"/>
+      <c r="BU18" s="86">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BV18" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW18" s="89"/>
+      <c r="BX18" s="90"/>
+    </row>
+    <row r="19" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A19" s="91" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="83">
+        <v>9501215650</v>
+      </c>
+      <c r="C19" s="98">
+        <v>46065</v>
+      </c>
+      <c r="D19" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E19" s="92" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H19" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I19" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" s="92">
+        <v>2340693</v>
+      </c>
+      <c r="K19" s="99">
+        <v>54880</v>
+      </c>
+      <c r="L19" s="104" t="s">
+        <v>169</v>
+      </c>
+      <c r="M19" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N19" s="82"/>
+      <c r="O19" s="83"/>
+      <c r="P19" s="83"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="85"/>
+      <c r="T19" s="83"/>
+      <c r="U19" s="83"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="87"/>
+      <c r="Y19" s="83"/>
+      <c r="Z19" s="83"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="86">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="87"/>
+      <c r="AD19" s="83"/>
+      <c r="AE19" s="83"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="87"/>
+      <c r="AI19" s="83"/>
+      <c r="AJ19" s="83"/>
+      <c r="AK19" s="84"/>
+      <c r="AL19" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="87"/>
+      <c r="AN19" s="83"/>
+      <c r="AO19" s="83"/>
+      <c r="AP19" s="84"/>
+      <c r="AQ19" s="86">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AR19" s="87"/>
+      <c r="AS19" s="83"/>
+      <c r="AT19" s="83"/>
+      <c r="AU19" s="84"/>
+      <c r="AV19" s="86">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AW19" s="87"/>
+      <c r="AX19" s="83"/>
+      <c r="AY19" s="83"/>
+      <c r="AZ19" s="84"/>
+      <c r="BA19" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BB19" s="87"/>
+      <c r="BC19" s="83"/>
+      <c r="BD19" s="83"/>
+      <c r="BE19" s="84"/>
+      <c r="BF19" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BG19" s="87"/>
+      <c r="BH19" s="83"/>
+      <c r="BI19" s="83"/>
+      <c r="BJ19" s="84"/>
+      <c r="BK19" s="86">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BL19" s="87"/>
+      <c r="BM19" s="83"/>
+      <c r="BN19" s="83"/>
+      <c r="BO19" s="84"/>
+      <c r="BP19" s="86">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BQ19" s="87"/>
+      <c r="BR19" s="83"/>
+      <c r="BS19" s="83"/>
+      <c r="BT19" s="84"/>
+      <c r="BU19" s="86">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BV19" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW19" s="89"/>
+      <c r="BX19" s="90"/>
+    </row>
+    <row r="20" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="91"/>
+      <c r="B20" s="83" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="92"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="92"/>
+      <c r="H20" s="92"/>
+      <c r="I20" s="92"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="99">
+        <v>150000</v>
+      </c>
+      <c r="L20" s="102" t="s">
+        <v>170</v>
+      </c>
+      <c r="M20" s="103"/>
+      <c r="N20" s="82"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="84">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="85"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="84"/>
+      <c r="W20" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="87"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="84"/>
+      <c r="AB20" s="86">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC20" s="87"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="84"/>
+      <c r="AG20" s="86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH20" s="87"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="84"/>
+      <c r="AL20" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AM20" s="87"/>
+      <c r="AN20" s="83"/>
+      <c r="AO20" s="83"/>
+      <c r="AP20" s="84"/>
+      <c r="AQ20" s="86">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AR20" s="87"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="84"/>
+      <c r="AV20" s="86">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AW20" s="87"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="84"/>
+      <c r="BA20" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BB20" s="87"/>
+      <c r="BC20" s="83"/>
+      <c r="BD20" s="83"/>
+      <c r="BE20" s="84"/>
+      <c r="BF20" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BG20" s="87"/>
+      <c r="BH20" s="83"/>
+      <c r="BI20" s="83"/>
+      <c r="BJ20" s="84"/>
+      <c r="BK20" s="86">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BL20" s="87"/>
+      <c r="BM20" s="83"/>
+      <c r="BN20" s="83"/>
+      <c r="BO20" s="84"/>
+      <c r="BP20" s="86">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BQ20" s="87"/>
+      <c r="BR20" s="83"/>
+      <c r="BS20" s="83"/>
+      <c r="BT20" s="84"/>
+      <c r="BU20" s="86">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BV20" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW20" s="89"/>
+      <c r="BX20" s="90"/>
+    </row>
+    <row r="21" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A21" s="91" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="83"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="92" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H21" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I21" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J21" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K21" s="93"/>
+      <c r="L21" s="102" t="s">
+        <v>171</v>
+      </c>
+      <c r="M21" s="103"/>
+      <c r="N21" s="82"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="84"/>
+      <c r="R21" s="84">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="85"/>
+      <c r="T21" s="83"/>
+      <c r="U21" s="83"/>
+      <c r="V21" s="84"/>
+      <c r="W21" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="87"/>
+      <c r="Y21" s="83"/>
+      <c r="Z21" s="83"/>
+      <c r="AA21" s="84"/>
+      <c r="AB21" s="86">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC21" s="87"/>
+      <c r="AD21" s="83"/>
+      <c r="AE21" s="83"/>
+      <c r="AF21" s="84"/>
+      <c r="AG21" s="86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH21" s="87"/>
+      <c r="AI21" s="83"/>
+      <c r="AJ21" s="83"/>
+      <c r="AK21" s="84"/>
+      <c r="AL21" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AM21" s="87"/>
+      <c r="AN21" s="83"/>
+      <c r="AO21" s="83"/>
+      <c r="AP21" s="84"/>
+      <c r="AQ21" s="86">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AR21" s="87"/>
+      <c r="AS21" s="83"/>
+      <c r="AT21" s="83"/>
+      <c r="AU21" s="84"/>
+      <c r="AV21" s="86">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AW21" s="87"/>
+      <c r="AX21" s="83"/>
+      <c r="AY21" s="83"/>
+      <c r="AZ21" s="84"/>
+      <c r="BA21" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BB21" s="87"/>
+      <c r="BC21" s="83"/>
+      <c r="BD21" s="83"/>
+      <c r="BE21" s="84"/>
+      <c r="BF21" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BG21" s="87"/>
+      <c r="BH21" s="83"/>
+      <c r="BI21" s="83"/>
+      <c r="BJ21" s="84"/>
+      <c r="BK21" s="86">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BL21" s="87"/>
+      <c r="BM21" s="83"/>
+      <c r="BN21" s="83"/>
+      <c r="BO21" s="84"/>
+      <c r="BP21" s="86">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BQ21" s="87"/>
+      <c r="BR21" s="83"/>
+      <c r="BS21" s="83"/>
+      <c r="BT21" s="84"/>
+      <c r="BU21" s="86">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BV21" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW21" s="89"/>
+      <c r="BX21" s="90"/>
+    </row>
+    <row r="22" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="91"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="92"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="102" t="s">
+        <v>172</v>
+      </c>
+      <c r="M22" s="103"/>
+      <c r="N22" s="82"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="83"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="84">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="85"/>
+      <c r="T22" s="83"/>
+      <c r="U22" s="83"/>
+      <c r="V22" s="84"/>
+      <c r="W22" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="87"/>
+      <c r="Y22" s="83"/>
+      <c r="Z22" s="83"/>
+      <c r="AA22" s="84"/>
+      <c r="AB22" s="86">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="87"/>
+      <c r="AD22" s="83"/>
+      <c r="AE22" s="83"/>
+      <c r="AF22" s="84"/>
+      <c r="AG22" s="86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="87"/>
+      <c r="AI22" s="83"/>
+      <c r="AJ22" s="83"/>
+      <c r="AK22" s="84"/>
+      <c r="AL22" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AM22" s="87"/>
+      <c r="AN22" s="83"/>
+      <c r="AO22" s="83"/>
+      <c r="AP22" s="84"/>
+      <c r="AQ22" s="86">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AR22" s="87"/>
+      <c r="AS22" s="83"/>
+      <c r="AT22" s="83"/>
+      <c r="AU22" s="84"/>
+      <c r="AV22" s="86">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AW22" s="87"/>
+      <c r="AX22" s="83"/>
+      <c r="AY22" s="83"/>
+      <c r="AZ22" s="84"/>
+      <c r="BA22" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BB22" s="87"/>
+      <c r="BC22" s="83"/>
+      <c r="BD22" s="83"/>
+      <c r="BE22" s="84"/>
+      <c r="BF22" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BG22" s="87"/>
+      <c r="BH22" s="83"/>
+      <c r="BI22" s="83"/>
+      <c r="BJ22" s="84"/>
+      <c r="BK22" s="86">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BL22" s="87"/>
+      <c r="BM22" s="83"/>
+      <c r="BN22" s="83"/>
+      <c r="BO22" s="84"/>
+      <c r="BP22" s="86">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BQ22" s="87"/>
+      <c r="BR22" s="83"/>
+      <c r="BS22" s="83"/>
+      <c r="BT22" s="84"/>
+      <c r="BU22" s="86">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BV22" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW22" s="89"/>
+      <c r="BX22" s="90"/>
+    </row>
+    <row r="23" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="91"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="102" t="s">
+        <v>173</v>
+      </c>
+      <c r="M23" s="103"/>
+      <c r="N23" s="82"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="84"/>
+      <c r="R23" s="84">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="85"/>
+      <c r="T23" s="83"/>
+      <c r="U23" s="83"/>
+      <c r="V23" s="84"/>
+      <c r="W23" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="87"/>
+      <c r="Y23" s="83"/>
+      <c r="Z23" s="83"/>
+      <c r="AA23" s="84"/>
+      <c r="AB23" s="86">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="87"/>
+      <c r="AD23" s="83"/>
+      <c r="AE23" s="83"/>
+      <c r="AF23" s="84"/>
+      <c r="AG23" s="86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH23" s="87"/>
+      <c r="AI23" s="83"/>
+      <c r="AJ23" s="83"/>
+      <c r="AK23" s="84"/>
+      <c r="AL23" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AM23" s="87"/>
+      <c r="AN23" s="83"/>
+      <c r="AO23" s="83"/>
+      <c r="AP23" s="84"/>
+      <c r="AQ23" s="86">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AR23" s="87"/>
+      <c r="AS23" s="83"/>
+      <c r="AT23" s="83"/>
+      <c r="AU23" s="84"/>
+      <c r="AV23" s="86">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AW23" s="87"/>
+      <c r="AX23" s="83"/>
+      <c r="AY23" s="83"/>
+      <c r="AZ23" s="84"/>
+      <c r="BA23" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BB23" s="87"/>
+      <c r="BC23" s="83"/>
+      <c r="BD23" s="83"/>
+      <c r="BE23" s="84"/>
+      <c r="BF23" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BG23" s="87"/>
+      <c r="BH23" s="83"/>
+      <c r="BI23" s="83"/>
+      <c r="BJ23" s="84"/>
+      <c r="BK23" s="86">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BL23" s="87"/>
+      <c r="BM23" s="83"/>
+      <c r="BN23" s="83"/>
+      <c r="BO23" s="84"/>
+      <c r="BP23" s="86">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BQ23" s="87"/>
+      <c r="BR23" s="83"/>
+      <c r="BS23" s="83"/>
+      <c r="BT23" s="84"/>
+      <c r="BU23" s="86">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BV23" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW23" s="89"/>
+      <c r="BX23" s="90"/>
+    </row>
+    <row r="24" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="91"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="92" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" s="92"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="102" t="s">
+        <v>174</v>
+      </c>
+      <c r="M24" s="103"/>
+      <c r="N24" s="82"/>
+      <c r="O24" s="83"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="84"/>
+      <c r="R24" s="84">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="85"/>
+      <c r="T24" s="83"/>
+      <c r="U24" s="83"/>
+      <c r="V24" s="84"/>
+      <c r="W24" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="87"/>
+      <c r="Y24" s="83"/>
+      <c r="Z24" s="83"/>
+      <c r="AA24" s="84"/>
+      <c r="AB24" s="86">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="87"/>
+      <c r="AD24" s="83"/>
+      <c r="AE24" s="83"/>
+      <c r="AF24" s="84"/>
+      <c r="AG24" s="86">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH24" s="87"/>
+      <c r="AI24" s="83"/>
+      <c r="AJ24" s="83"/>
+      <c r="AK24" s="84"/>
+      <c r="AL24" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AM24" s="87"/>
+      <c r="AN24" s="83"/>
+      <c r="AO24" s="83"/>
+      <c r="AP24" s="84"/>
+      <c r="AQ24" s="86">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AR24" s="87"/>
+      <c r="AS24" s="83"/>
+      <c r="AT24" s="83"/>
+      <c r="AU24" s="84"/>
+      <c r="AV24" s="86">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AW24" s="87"/>
+      <c r="AX24" s="83"/>
+      <c r="AY24" s="83"/>
+      <c r="AZ24" s="84"/>
+      <c r="BA24" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BB24" s="87"/>
+      <c r="BC24" s="83"/>
+      <c r="BD24" s="83"/>
+      <c r="BE24" s="84"/>
+      <c r="BF24" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BG24" s="87"/>
+      <c r="BH24" s="83"/>
+      <c r="BI24" s="83"/>
+      <c r="BJ24" s="84"/>
+      <c r="BK24" s="86">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BL24" s="87"/>
+      <c r="BM24" s="83"/>
+      <c r="BN24" s="83"/>
+      <c r="BO24" s="84"/>
+      <c r="BP24" s="86">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BQ24" s="87"/>
+      <c r="BR24" s="83"/>
+      <c r="BS24" s="83"/>
+      <c r="BT24" s="84"/>
+      <c r="BU24" s="86">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BV24" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW24" s="89"/>
+      <c r="BX24" s="90"/>
+    </row>
+    <row r="25" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="91"/>
+      <c r="B25" s="83"/>
+      <c r="C25" s="92"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="92" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" s="92"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="102" t="s">
+        <v>175</v>
+      </c>
+      <c r="M25" s="103"/>
+      <c r="N25" s="82"/>
+      <c r="O25" s="83"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="84"/>
+      <c r="R25" s="84">
+        <f t="shared" ref="R25:R29" si="12">P25-Q25</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="85"/>
+      <c r="T25" s="83"/>
+      <c r="U25" s="83"/>
+      <c r="V25" s="84"/>
+      <c r="W25" s="86">
+        <f t="shared" ref="W25:W29" si="13">U25-V25</f>
+        <v>0</v>
+      </c>
+      <c r="X25" s="87"/>
+      <c r="Y25" s="83"/>
+      <c r="Z25" s="83"/>
+      <c r="AA25" s="84"/>
+      <c r="AB25" s="86">
+        <f t="shared" ref="AB25:AB29" si="14">Z25-AA25</f>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="83"/>
+      <c r="AE25" s="83"/>
+      <c r="AF25" s="84"/>
+      <c r="AG25" s="86">
+        <f t="shared" ref="AG25:AG29" si="15">AE25-AF25</f>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="87"/>
+      <c r="AI25" s="83"/>
+      <c r="AJ25" s="83"/>
+      <c r="AK25" s="84"/>
+      <c r="AL25" s="86">
+        <f t="shared" ref="AL25:AL29" si="16">AJ25-AK25</f>
+        <v>0</v>
+      </c>
+      <c r="AM25" s="87"/>
+      <c r="AN25" s="83"/>
+      <c r="AO25" s="83"/>
+      <c r="AP25" s="84"/>
+      <c r="AQ25" s="86">
+        <f t="shared" ref="AQ25:AQ29" si="17">AO25-AP25</f>
+        <v>0</v>
+      </c>
+      <c r="AR25" s="87"/>
+      <c r="AS25" s="83"/>
+      <c r="AT25" s="83"/>
+      <c r="AU25" s="84"/>
+      <c r="AV25" s="86">
+        <f t="shared" ref="AV25:AV29" si="18">AT25-AU25</f>
+        <v>0</v>
+      </c>
+      <c r="AW25" s="87"/>
+      <c r="AX25" s="83"/>
+      <c r="AY25" s="83"/>
+      <c r="AZ25" s="84"/>
+      <c r="BA25" s="86">
+        <f t="shared" ref="BA25:BA29" si="19">AY25-AZ25</f>
+        <v>0</v>
+      </c>
+      <c r="BB25" s="87"/>
+      <c r="BC25" s="83"/>
+      <c r="BD25" s="83"/>
+      <c r="BE25" s="84"/>
+      <c r="BF25" s="86">
+        <f t="shared" ref="BF25:BF29" si="20">BD25-BE25</f>
+        <v>0</v>
+      </c>
+      <c r="BG25" s="87"/>
+      <c r="BH25" s="83"/>
+      <c r="BI25" s="83"/>
+      <c r="BJ25" s="84"/>
+      <c r="BK25" s="86">
+        <f t="shared" ref="BK25:BK29" si="21">BI25-BJ25</f>
+        <v>0</v>
+      </c>
+      <c r="BL25" s="87"/>
+      <c r="BM25" s="83"/>
+      <c r="BN25" s="83"/>
+      <c r="BO25" s="84"/>
+      <c r="BP25" s="86">
+        <f t="shared" ref="BP25:BP29" si="22">BN25-BO25</f>
+        <v>0</v>
+      </c>
+      <c r="BQ25" s="87"/>
+      <c r="BR25" s="83"/>
+      <c r="BS25" s="83"/>
+      <c r="BT25" s="84"/>
+      <c r="BU25" s="86">
+        <f t="shared" ref="BU25:BU29" si="23">BS25-BT25</f>
+        <v>0</v>
+      </c>
+      <c r="BV25" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW25" s="89"/>
+      <c r="BX25" s="90"/>
+    </row>
+    <row r="26" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A26" s="91"/>
+      <c r="B26" s="83"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="93"/>
+      <c r="L26" s="102" t="s">
+        <v>176</v>
+      </c>
+      <c r="M26" s="103"/>
+      <c r="N26" s="82"/>
+      <c r="O26" s="83"/>
+      <c r="P26" s="83"/>
+      <c r="Q26" s="84"/>
+      <c r="R26" s="84">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="85"/>
+      <c r="T26" s="83"/>
+      <c r="U26" s="83"/>
+      <c r="V26" s="84"/>
+      <c r="W26" s="86">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="87"/>
+      <c r="Y26" s="83"/>
+      <c r="Z26" s="83"/>
+      <c r="AA26" s="84"/>
+      <c r="AB26" s="86">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AC26" s="87"/>
+      <c r="AD26" s="83"/>
+      <c r="AE26" s="83"/>
+      <c r="AF26" s="84"/>
+      <c r="AG26" s="86">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH26" s="87"/>
+      <c r="AI26" s="83"/>
+      <c r="AJ26" s="83"/>
+      <c r="AK26" s="84"/>
+      <c r="AL26" s="86">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AM26" s="87"/>
+      <c r="AN26" s="83"/>
+      <c r="AO26" s="83"/>
+      <c r="AP26" s="84"/>
+      <c r="AQ26" s="86">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AR26" s="87"/>
+      <c r="AS26" s="83"/>
+      <c r="AT26" s="83"/>
+      <c r="AU26" s="84"/>
+      <c r="AV26" s="86">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AW26" s="87"/>
+      <c r="AX26" s="83"/>
+      <c r="AY26" s="83"/>
+      <c r="AZ26" s="84"/>
+      <c r="BA26" s="86">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BB26" s="87"/>
+      <c r="BC26" s="83"/>
+      <c r="BD26" s="83"/>
+      <c r="BE26" s="84"/>
+      <c r="BF26" s="86">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BG26" s="87"/>
+      <c r="BH26" s="83"/>
+      <c r="BI26" s="83"/>
+      <c r="BJ26" s="84"/>
+      <c r="BK26" s="86">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BL26" s="87"/>
+      <c r="BM26" s="83"/>
+      <c r="BN26" s="83"/>
+      <c r="BO26" s="84"/>
+      <c r="BP26" s="86">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BQ26" s="87"/>
+      <c r="BR26" s="83"/>
+      <c r="BS26" s="83"/>
+      <c r="BT26" s="84"/>
+      <c r="BU26" s="86">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BV26" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW26" s="89"/>
+      <c r="BX26" s="90"/>
+    </row>
+    <row r="27" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="91"/>
+      <c r="B27" s="83"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92" t="s">
+        <v>118</v>
+      </c>
+      <c r="G27" s="92"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="102" t="s">
+        <v>177</v>
+      </c>
+      <c r="M27" s="103"/>
+      <c r="N27" s="82"/>
+      <c r="O27" s="83"/>
+      <c r="P27" s="83"/>
+      <c r="Q27" s="84"/>
+      <c r="R27" s="84">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="85"/>
+      <c r="T27" s="83"/>
+      <c r="U27" s="83"/>
+      <c r="V27" s="84"/>
+      <c r="W27" s="86">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="87"/>
+      <c r="Y27" s="83"/>
+      <c r="Z27" s="83"/>
+      <c r="AA27" s="84"/>
+      <c r="AB27" s="86">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AC27" s="87"/>
+      <c r="AD27" s="83"/>
+      <c r="AE27" s="83"/>
+      <c r="AF27" s="84"/>
+      <c r="AG27" s="86">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH27" s="87"/>
+      <c r="AI27" s="83"/>
+      <c r="AJ27" s="83"/>
+      <c r="AK27" s="84"/>
+      <c r="AL27" s="86">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AM27" s="87"/>
+      <c r="AN27" s="83"/>
+      <c r="AO27" s="83"/>
+      <c r="AP27" s="84"/>
+      <c r="AQ27" s="86">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AR27" s="87"/>
+      <c r="AS27" s="83"/>
+      <c r="AT27" s="83"/>
+      <c r="AU27" s="84"/>
+      <c r="AV27" s="86">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AW27" s="87"/>
+      <c r="AX27" s="83"/>
+      <c r="AY27" s="83"/>
+      <c r="AZ27" s="84"/>
+      <c r="BA27" s="86">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BB27" s="87"/>
+      <c r="BC27" s="83"/>
+      <c r="BD27" s="83"/>
+      <c r="BE27" s="84"/>
+      <c r="BF27" s="86">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BG27" s="87"/>
+      <c r="BH27" s="83"/>
+      <c r="BI27" s="83"/>
+      <c r="BJ27" s="84"/>
+      <c r="BK27" s="86">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BL27" s="87"/>
+      <c r="BM27" s="83"/>
+      <c r="BN27" s="83"/>
+      <c r="BO27" s="84"/>
+      <c r="BP27" s="86">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BQ27" s="87"/>
+      <c r="BR27" s="83"/>
+      <c r="BS27" s="83"/>
+      <c r="BT27" s="84"/>
+      <c r="BU27" s="86">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BV27" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW27" s="89"/>
+      <c r="BX27" s="90"/>
+    </row>
+    <row r="28" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A28" s="91"/>
+      <c r="B28" s="83"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="92" t="s">
+        <v>119</v>
+      </c>
+      <c r="G28" s="92"/>
+      <c r="H28" s="92"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="92"/>
+      <c r="K28" s="93"/>
+      <c r="L28" s="102" t="s">
+        <v>178</v>
+      </c>
+      <c r="M28" s="103"/>
+      <c r="N28" s="82"/>
+      <c r="O28" s="83"/>
+      <c r="P28" s="83"/>
+      <c r="Q28" s="84"/>
+      <c r="R28" s="84">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="85"/>
+      <c r="T28" s="83"/>
+      <c r="U28" s="83"/>
+      <c r="V28" s="84"/>
+      <c r="W28" s="86">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="87"/>
+      <c r="Y28" s="83"/>
+      <c r="Z28" s="83"/>
+      <c r="AA28" s="84"/>
+      <c r="AB28" s="86">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AC28" s="87"/>
+      <c r="AD28" s="83"/>
+      <c r="AE28" s="83"/>
+      <c r="AF28" s="84"/>
+      <c r="AG28" s="86">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH28" s="87"/>
+      <c r="AI28" s="83"/>
+      <c r="AJ28" s="83"/>
+      <c r="AK28" s="84"/>
+      <c r="AL28" s="86">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AM28" s="87"/>
+      <c r="AN28" s="83"/>
+      <c r="AO28" s="83"/>
+      <c r="AP28" s="84"/>
+      <c r="AQ28" s="86">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AR28" s="87"/>
+      <c r="AS28" s="83"/>
+      <c r="AT28" s="83"/>
+      <c r="AU28" s="84"/>
+      <c r="AV28" s="86">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AW28" s="87"/>
+      <c r="AX28" s="83"/>
+      <c r="AY28" s="83"/>
+      <c r="AZ28" s="84"/>
+      <c r="BA28" s="86">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BB28" s="87"/>
+      <c r="BC28" s="83"/>
+      <c r="BD28" s="83"/>
+      <c r="BE28" s="84"/>
+      <c r="BF28" s="86">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BG28" s="87"/>
+      <c r="BH28" s="83"/>
+      <c r="BI28" s="83"/>
+      <c r="BJ28" s="84"/>
+      <c r="BK28" s="86">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BL28" s="87"/>
+      <c r="BM28" s="83"/>
+      <c r="BN28" s="83"/>
+      <c r="BO28" s="84"/>
+      <c r="BP28" s="86">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BQ28" s="87"/>
+      <c r="BR28" s="83"/>
+      <c r="BS28" s="83"/>
+      <c r="BT28" s="84"/>
+      <c r="BU28" s="86">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BV28" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW28" s="89"/>
+      <c r="BX28" s="90"/>
+    </row>
+    <row r="29" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A29" s="91"/>
+      <c r="B29" s="83"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92" t="s">
+        <v>120</v>
+      </c>
+      <c r="G29" s="92"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="92"/>
+      <c r="J29" s="92"/>
+      <c r="K29" s="93"/>
+      <c r="L29" s="102" t="s">
+        <v>178</v>
+      </c>
+      <c r="M29" s="103"/>
+      <c r="N29" s="82"/>
+      <c r="O29" s="83"/>
+      <c r="P29" s="83"/>
+      <c r="Q29" s="84"/>
+      <c r="R29" s="84">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="85"/>
+      <c r="T29" s="83"/>
+      <c r="U29" s="83"/>
+      <c r="V29" s="84"/>
+      <c r="W29" s="86">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="87"/>
+      <c r="Y29" s="83"/>
+      <c r="Z29" s="83"/>
+      <c r="AA29" s="84"/>
+      <c r="AB29" s="86">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AC29" s="87"/>
+      <c r="AD29" s="83"/>
+      <c r="AE29" s="83"/>
+      <c r="AF29" s="84"/>
+      <c r="AG29" s="86">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH29" s="87"/>
+      <c r="AI29" s="83"/>
+      <c r="AJ29" s="83"/>
+      <c r="AK29" s="84"/>
+      <c r="AL29" s="86">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AM29" s="87"/>
+      <c r="AN29" s="83"/>
+      <c r="AO29" s="83"/>
+      <c r="AP29" s="84"/>
+      <c r="AQ29" s="86">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AR29" s="87"/>
+      <c r="AS29" s="83"/>
+      <c r="AT29" s="83"/>
+      <c r="AU29" s="84"/>
+      <c r="AV29" s="86">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AW29" s="87"/>
+      <c r="AX29" s="83"/>
+      <c r="AY29" s="83"/>
+      <c r="AZ29" s="84"/>
+      <c r="BA29" s="86">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BB29" s="87"/>
+      <c r="BC29" s="83"/>
+      <c r="BD29" s="83"/>
+      <c r="BE29" s="84"/>
+      <c r="BF29" s="86">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BG29" s="87"/>
+      <c r="BH29" s="83"/>
+      <c r="BI29" s="83"/>
+      <c r="BJ29" s="84"/>
+      <c r="BK29" s="86">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BL29" s="87"/>
+      <c r="BM29" s="83"/>
+      <c r="BN29" s="83"/>
+      <c r="BO29" s="84"/>
+      <c r="BP29" s="86">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BQ29" s="87"/>
+      <c r="BR29" s="83"/>
+      <c r="BS29" s="83"/>
+      <c r="BT29" s="84"/>
+      <c r="BU29" s="86">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BV29" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW29" s="89"/>
+      <c r="BX29" s="90"/>
+    </row>
+    <row r="30" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="91"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" s="92"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="92"/>
+      <c r="J30" s="92"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="102" t="s">
+        <v>179</v>
+      </c>
+      <c r="M30" s="103"/>
+      <c r="N30" s="82"/>
+      <c r="O30" s="83"/>
+      <c r="P30" s="83"/>
+      <c r="Q30" s="84"/>
+      <c r="R30" s="84">
+        <f t="shared" ref="R30:R64" si="24">P30-Q30</f>
+        <v>0</v>
+      </c>
+      <c r="S30" s="85"/>
+      <c r="T30" s="83"/>
+      <c r="U30" s="83"/>
+      <c r="V30" s="84"/>
+      <c r="W30" s="86">
+        <f t="shared" ref="W30:W64" si="25">U30-V30</f>
+        <v>0</v>
+      </c>
+      <c r="X30" s="87"/>
+      <c r="Y30" s="83"/>
+      <c r="Z30" s="83"/>
+      <c r="AA30" s="84"/>
+      <c r="AB30" s="86">
+        <f t="shared" ref="AB30:AB64" si="26">Z30-AA30</f>
+        <v>0</v>
+      </c>
+      <c r="AC30" s="87"/>
+      <c r="AD30" s="83"/>
+      <c r="AE30" s="83"/>
+      <c r="AF30" s="84"/>
+      <c r="AG30" s="86">
+        <f t="shared" ref="AG30:AG64" si="27">AE30-AF30</f>
+        <v>0</v>
+      </c>
+      <c r="AH30" s="87"/>
+      <c r="AI30" s="83"/>
+      <c r="AJ30" s="83"/>
+      <c r="AK30" s="84"/>
+      <c r="AL30" s="86">
+        <f t="shared" ref="AL30:AL64" si="28">AJ30-AK30</f>
+        <v>0</v>
+      </c>
+      <c r="AM30" s="87"/>
+      <c r="AN30" s="83"/>
+      <c r="AO30" s="83"/>
+      <c r="AP30" s="84"/>
+      <c r="AQ30" s="86">
+        <f t="shared" ref="AQ30:AQ64" si="29">AO30-AP30</f>
+        <v>0</v>
+      </c>
+      <c r="AR30" s="87"/>
+      <c r="AS30" s="83"/>
+      <c r="AT30" s="83"/>
+      <c r="AU30" s="84"/>
+      <c r="AV30" s="86">
+        <f t="shared" ref="AV30:AV64" si="30">AT30-AU30</f>
+        <v>0</v>
+      </c>
+      <c r="AW30" s="87"/>
+      <c r="AX30" s="83"/>
+      <c r="AY30" s="83"/>
+      <c r="AZ30" s="84"/>
+      <c r="BA30" s="86">
+        <f t="shared" ref="BA30:BA64" si="31">AY30-AZ30</f>
+        <v>0</v>
+      </c>
+      <c r="BB30" s="87"/>
+      <c r="BC30" s="83"/>
+      <c r="BD30" s="83"/>
+      <c r="BE30" s="84"/>
+      <c r="BF30" s="86">
+        <f t="shared" ref="BF30:BF64" si="32">BD30-BE30</f>
+        <v>0</v>
+      </c>
+      <c r="BG30" s="87"/>
+      <c r="BH30" s="83"/>
+      <c r="BI30" s="83"/>
+      <c r="BJ30" s="84"/>
+      <c r="BK30" s="86">
+        <f t="shared" ref="BK30:BK64" si="33">BI30-BJ30</f>
+        <v>0</v>
+      </c>
+      <c r="BL30" s="87"/>
+      <c r="BM30" s="83"/>
+      <c r="BN30" s="83"/>
+      <c r="BO30" s="84"/>
+      <c r="BP30" s="86">
+        <f t="shared" ref="BP30:BP64" si="34">BN30-BO30</f>
+        <v>0</v>
+      </c>
+      <c r="BQ30" s="87"/>
+      <c r="BR30" s="83"/>
+      <c r="BS30" s="83"/>
+      <c r="BT30" s="84"/>
+      <c r="BU30" s="86">
+        <f t="shared" ref="BU30:BU64" si="35">BS30-BT30</f>
+        <v>0</v>
+      </c>
+      <c r="BV30" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW30" s="89"/>
+      <c r="BX30" s="90"/>
+    </row>
+    <row r="31" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="91"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92" t="s">
+        <v>122</v>
+      </c>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="92"/>
+      <c r="K31" s="93"/>
+      <c r="L31" s="102" t="s">
+        <v>180</v>
+      </c>
+      <c r="M31" s="103"/>
+      <c r="N31" s="82"/>
+      <c r="O31" s="83"/>
+      <c r="P31" s="83"/>
+      <c r="Q31" s="84"/>
+      <c r="R31" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="85"/>
+      <c r="T31" s="83"/>
+      <c r="U31" s="83"/>
+      <c r="V31" s="84"/>
+      <c r="W31" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="87"/>
+      <c r="Y31" s="83"/>
+      <c r="Z31" s="83"/>
+      <c r="AA31" s="84"/>
+      <c r="AB31" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC31" s="87"/>
+      <c r="AD31" s="83"/>
+      <c r="AE31" s="83"/>
+      <c r="AF31" s="84"/>
+      <c r="AG31" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH31" s="87"/>
+      <c r="AI31" s="83"/>
+      <c r="AJ31" s="83"/>
+      <c r="AK31" s="84"/>
+      <c r="AL31" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM31" s="87"/>
+      <c r="AN31" s="83"/>
+      <c r="AO31" s="83"/>
+      <c r="AP31" s="84"/>
+      <c r="AQ31" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR31" s="87"/>
+      <c r="AS31" s="83"/>
+      <c r="AT31" s="83"/>
+      <c r="AU31" s="84"/>
+      <c r="AV31" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW31" s="87"/>
+      <c r="AX31" s="83"/>
+      <c r="AY31" s="83"/>
+      <c r="AZ31" s="84"/>
+      <c r="BA31" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB31" s="87"/>
+      <c r="BC31" s="83"/>
+      <c r="BD31" s="83"/>
+      <c r="BE31" s="84"/>
+      <c r="BF31" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG31" s="87"/>
+      <c r="BH31" s="83"/>
+      <c r="BI31" s="83"/>
+      <c r="BJ31" s="84"/>
+      <c r="BK31" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL31" s="87"/>
+      <c r="BM31" s="83"/>
+      <c r="BN31" s="83"/>
+      <c r="BO31" s="84"/>
+      <c r="BP31" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ31" s="87"/>
+      <c r="BR31" s="83"/>
+      <c r="BS31" s="83"/>
+      <c r="BT31" s="84"/>
+      <c r="BU31" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV31" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW31" s="89"/>
+      <c r="BX31" s="90"/>
+    </row>
+    <row r="32" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="91"/>
+      <c r="B32" s="83"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92" t="s">
+        <v>123</v>
+      </c>
+      <c r="G32" s="92"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="92"/>
+      <c r="J32" s="92"/>
+      <c r="K32" s="93"/>
+      <c r="L32" s="102" t="s">
+        <v>181</v>
+      </c>
+      <c r="M32" s="103"/>
+      <c r="N32" s="82"/>
+      <c r="O32" s="83"/>
+      <c r="P32" s="83"/>
+      <c r="Q32" s="84"/>
+      <c r="R32" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="85"/>
+      <c r="T32" s="83"/>
+      <c r="U32" s="83"/>
+      <c r="V32" s="84"/>
+      <c r="W32" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="87"/>
+      <c r="Y32" s="83"/>
+      <c r="Z32" s="83"/>
+      <c r="AA32" s="84"/>
+      <c r="AB32" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC32" s="87"/>
+      <c r="AD32" s="83"/>
+      <c r="AE32" s="83"/>
+      <c r="AF32" s="84"/>
+      <c r="AG32" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH32" s="87"/>
+      <c r="AI32" s="83"/>
+      <c r="AJ32" s="83"/>
+      <c r="AK32" s="84"/>
+      <c r="AL32" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM32" s="87"/>
+      <c r="AN32" s="83"/>
+      <c r="AO32" s="83"/>
+      <c r="AP32" s="84"/>
+      <c r="AQ32" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR32" s="87"/>
+      <c r="AS32" s="83"/>
+      <c r="AT32" s="83"/>
+      <c r="AU32" s="84"/>
+      <c r="AV32" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW32" s="87"/>
+      <c r="AX32" s="83"/>
+      <c r="AY32" s="83"/>
+      <c r="AZ32" s="84"/>
+      <c r="BA32" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB32" s="87"/>
+      <c r="BC32" s="83"/>
+      <c r="BD32" s="83"/>
+      <c r="BE32" s="84"/>
+      <c r="BF32" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG32" s="87"/>
+      <c r="BH32" s="83"/>
+      <c r="BI32" s="83"/>
+      <c r="BJ32" s="84"/>
+      <c r="BK32" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL32" s="87"/>
+      <c r="BM32" s="83"/>
+      <c r="BN32" s="83"/>
+      <c r="BO32" s="84"/>
+      <c r="BP32" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ32" s="87"/>
+      <c r="BR32" s="83"/>
+      <c r="BS32" s="83"/>
+      <c r="BT32" s="84"/>
+      <c r="BU32" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV32" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW32" s="89"/>
+      <c r="BX32" s="90"/>
+    </row>
+    <row r="33" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A33" s="91"/>
+      <c r="B33" s="83"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92" t="s">
+        <v>124</v>
+      </c>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="93"/>
+      <c r="L33" s="102" t="s">
+        <v>182</v>
+      </c>
+      <c r="M33" s="103"/>
+      <c r="N33" s="82"/>
+      <c r="O33" s="83"/>
+      <c r="P33" s="83"/>
+      <c r="Q33" s="84"/>
+      <c r="R33" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="85"/>
+      <c r="T33" s="83"/>
+      <c r="U33" s="83"/>
+      <c r="V33" s="84"/>
+      <c r="W33" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="87"/>
+      <c r="Y33" s="83"/>
+      <c r="Z33" s="83"/>
+      <c r="AA33" s="84"/>
+      <c r="AB33" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC33" s="87"/>
+      <c r="AD33" s="83"/>
+      <c r="AE33" s="83"/>
+      <c r="AF33" s="84"/>
+      <c r="AG33" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH33" s="87"/>
+      <c r="AI33" s="83"/>
+      <c r="AJ33" s="83"/>
+      <c r="AK33" s="84"/>
+      <c r="AL33" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM33" s="87"/>
+      <c r="AN33" s="83"/>
+      <c r="AO33" s="83"/>
+      <c r="AP33" s="84"/>
+      <c r="AQ33" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR33" s="87"/>
+      <c r="AS33" s="83"/>
+      <c r="AT33" s="83"/>
+      <c r="AU33" s="84"/>
+      <c r="AV33" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW33" s="87"/>
+      <c r="AX33" s="83"/>
+      <c r="AY33" s="83"/>
+      <c r="AZ33" s="84"/>
+      <c r="BA33" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB33" s="87"/>
+      <c r="BC33" s="83"/>
+      <c r="BD33" s="83"/>
+      <c r="BE33" s="84"/>
+      <c r="BF33" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG33" s="87"/>
+      <c r="BH33" s="83"/>
+      <c r="BI33" s="83"/>
+      <c r="BJ33" s="84"/>
+      <c r="BK33" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL33" s="87"/>
+      <c r="BM33" s="83"/>
+      <c r="BN33" s="83"/>
+      <c r="BO33" s="84"/>
+      <c r="BP33" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ33" s="87"/>
+      <c r="BR33" s="83"/>
+      <c r="BS33" s="83"/>
+      <c r="BT33" s="84"/>
+      <c r="BU33" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV33" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW33" s="89"/>
+      <c r="BX33" s="90"/>
+    </row>
+    <row r="34" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="91"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92" t="s">
+        <v>125</v>
+      </c>
+      <c r="G34" s="92"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="92"/>
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="102" t="s">
+        <v>183</v>
+      </c>
+      <c r="M34" s="103"/>
+      <c r="N34" s="82"/>
+      <c r="O34" s="83"/>
+      <c r="P34" s="83"/>
+      <c r="Q34" s="84"/>
+      <c r="R34" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="85"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="83"/>
+      <c r="V34" s="84"/>
+      <c r="W34" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="87"/>
+      <c r="Y34" s="83"/>
+      <c r="Z34" s="83"/>
+      <c r="AA34" s="84"/>
+      <c r="AB34" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC34" s="87"/>
+      <c r="AD34" s="83"/>
+      <c r="AE34" s="83"/>
+      <c r="AF34" s="84"/>
+      <c r="AG34" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH34" s="87"/>
+      <c r="AI34" s="83"/>
+      <c r="AJ34" s="83"/>
+      <c r="AK34" s="84"/>
+      <c r="AL34" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM34" s="87"/>
+      <c r="AN34" s="83"/>
+      <c r="AO34" s="83"/>
+      <c r="AP34" s="84"/>
+      <c r="AQ34" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR34" s="87"/>
+      <c r="AS34" s="83"/>
+      <c r="AT34" s="83"/>
+      <c r="AU34" s="84"/>
+      <c r="AV34" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW34" s="87"/>
+      <c r="AX34" s="83"/>
+      <c r="AY34" s="83"/>
+      <c r="AZ34" s="84"/>
+      <c r="BA34" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB34" s="87"/>
+      <c r="BC34" s="83"/>
+      <c r="BD34" s="83"/>
+      <c r="BE34" s="84"/>
+      <c r="BF34" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG34" s="87"/>
+      <c r="BH34" s="83"/>
+      <c r="BI34" s="83"/>
+      <c r="BJ34" s="84"/>
+      <c r="BK34" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL34" s="87"/>
+      <c r="BM34" s="83"/>
+      <c r="BN34" s="83"/>
+      <c r="BO34" s="84"/>
+      <c r="BP34" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ34" s="87"/>
+      <c r="BR34" s="83"/>
+      <c r="BS34" s="83"/>
+      <c r="BT34" s="84"/>
+      <c r="BU34" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV34" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW34" s="89"/>
+      <c r="BX34" s="90"/>
+    </row>
+    <row r="35" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A35" s="91"/>
+      <c r="B35" s="83"/>
+      <c r="C35" s="92"/>
+      <c r="D35" s="92"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92" t="s">
+        <v>126</v>
+      </c>
+      <c r="G35" s="92"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="93"/>
+      <c r="L35" s="102" t="s">
+        <v>184</v>
+      </c>
+      <c r="M35" s="103"/>
+      <c r="N35" s="82"/>
+      <c r="O35" s="83"/>
+      <c r="P35" s="83"/>
+      <c r="Q35" s="84"/>
+      <c r="R35" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="85"/>
+      <c r="T35" s="83"/>
+      <c r="U35" s="83"/>
+      <c r="V35" s="84"/>
+      <c r="W35" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="87"/>
+      <c r="Y35" s="83"/>
+      <c r="Z35" s="83"/>
+      <c r="AA35" s="84"/>
+      <c r="AB35" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC35" s="87"/>
+      <c r="AD35" s="83"/>
+      <c r="AE35" s="83"/>
+      <c r="AF35" s="84"/>
+      <c r="AG35" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH35" s="87"/>
+      <c r="AI35" s="83"/>
+      <c r="AJ35" s="83"/>
+      <c r="AK35" s="84"/>
+      <c r="AL35" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM35" s="87"/>
+      <c r="AN35" s="83"/>
+      <c r="AO35" s="83"/>
+      <c r="AP35" s="84"/>
+      <c r="AQ35" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR35" s="87"/>
+      <c r="AS35" s="83"/>
+      <c r="AT35" s="83"/>
+      <c r="AU35" s="84"/>
+      <c r="AV35" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW35" s="87"/>
+      <c r="AX35" s="83"/>
+      <c r="AY35" s="83"/>
+      <c r="AZ35" s="84"/>
+      <c r="BA35" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB35" s="87"/>
+      <c r="BC35" s="83"/>
+      <c r="BD35" s="83"/>
+      <c r="BE35" s="84"/>
+      <c r="BF35" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG35" s="87"/>
+      <c r="BH35" s="83"/>
+      <c r="BI35" s="83"/>
+      <c r="BJ35" s="84"/>
+      <c r="BK35" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL35" s="87"/>
+      <c r="BM35" s="83"/>
+      <c r="BN35" s="83"/>
+      <c r="BO35" s="84"/>
+      <c r="BP35" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ35" s="87"/>
+      <c r="BR35" s="83"/>
+      <c r="BS35" s="83"/>
+      <c r="BT35" s="84"/>
+      <c r="BU35" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV35" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW35" s="89"/>
+      <c r="BX35" s="90"/>
+    </row>
+    <row r="36" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A36" s="91"/>
+      <c r="B36" s="83"/>
+      <c r="C36" s="92"/>
+      <c r="D36" s="92"/>
+      <c r="E36" s="92"/>
+      <c r="F36" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="92"/>
+      <c r="H36" s="92"/>
+      <c r="I36" s="92"/>
+      <c r="J36" s="92"/>
+      <c r="K36" s="93"/>
+      <c r="L36" s="102" t="s">
+        <v>185</v>
+      </c>
+      <c r="M36" s="103"/>
+      <c r="N36" s="82"/>
+      <c r="O36" s="83"/>
+      <c r="P36" s="83"/>
+      <c r="Q36" s="84"/>
+      <c r="R36" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="85"/>
+      <c r="T36" s="83"/>
+      <c r="U36" s="83"/>
+      <c r="V36" s="84"/>
+      <c r="W36" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="87"/>
+      <c r="Y36" s="83"/>
+      <c r="Z36" s="83"/>
+      <c r="AA36" s="84"/>
+      <c r="AB36" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC36" s="87"/>
+      <c r="AD36" s="83"/>
+      <c r="AE36" s="83"/>
+      <c r="AF36" s="84"/>
+      <c r="AG36" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH36" s="87"/>
+      <c r="AI36" s="83"/>
+      <c r="AJ36" s="83"/>
+      <c r="AK36" s="84"/>
+      <c r="AL36" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM36" s="87"/>
+      <c r="AN36" s="83"/>
+      <c r="AO36" s="83"/>
+      <c r="AP36" s="84"/>
+      <c r="AQ36" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR36" s="87"/>
+      <c r="AS36" s="83"/>
+      <c r="AT36" s="83"/>
+      <c r="AU36" s="84"/>
+      <c r="AV36" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW36" s="87"/>
+      <c r="AX36" s="83"/>
+      <c r="AY36" s="83"/>
+      <c r="AZ36" s="84"/>
+      <c r="BA36" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB36" s="87"/>
+      <c r="BC36" s="83"/>
+      <c r="BD36" s="83"/>
+      <c r="BE36" s="84"/>
+      <c r="BF36" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG36" s="87"/>
+      <c r="BH36" s="83"/>
+      <c r="BI36" s="83"/>
+      <c r="BJ36" s="84"/>
+      <c r="BK36" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL36" s="87"/>
+      <c r="BM36" s="83"/>
+      <c r="BN36" s="83"/>
+      <c r="BO36" s="84"/>
+      <c r="BP36" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ36" s="87"/>
+      <c r="BR36" s="83"/>
+      <c r="BS36" s="83"/>
+      <c r="BT36" s="84"/>
+      <c r="BU36" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV36" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW36" s="89"/>
+      <c r="BX36" s="90"/>
+    </row>
+    <row r="37" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A37" s="91"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92" t="s">
+        <v>128</v>
+      </c>
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="92"/>
+      <c r="K37" s="93"/>
+      <c r="L37" s="102" t="s">
+        <v>186</v>
+      </c>
+      <c r="M37" s="103"/>
+      <c r="N37" s="82"/>
+      <c r="O37" s="83"/>
+      <c r="P37" s="83"/>
+      <c r="Q37" s="84"/>
+      <c r="R37" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="85"/>
+      <c r="T37" s="83"/>
+      <c r="U37" s="83"/>
+      <c r="V37" s="84"/>
+      <c r="W37" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="87"/>
+      <c r="Y37" s="83"/>
+      <c r="Z37" s="83"/>
+      <c r="AA37" s="84"/>
+      <c r="AB37" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC37" s="87"/>
+      <c r="AD37" s="83"/>
+      <c r="AE37" s="83"/>
+      <c r="AF37" s="84"/>
+      <c r="AG37" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH37" s="87"/>
+      <c r="AI37" s="83"/>
+      <c r="AJ37" s="83"/>
+      <c r="AK37" s="84"/>
+      <c r="AL37" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM37" s="87"/>
+      <c r="AN37" s="83"/>
+      <c r="AO37" s="83"/>
+      <c r="AP37" s="84"/>
+      <c r="AQ37" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR37" s="87"/>
+      <c r="AS37" s="83"/>
+      <c r="AT37" s="83"/>
+      <c r="AU37" s="84"/>
+      <c r="AV37" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW37" s="87"/>
+      <c r="AX37" s="83"/>
+      <c r="AY37" s="83"/>
+      <c r="AZ37" s="84"/>
+      <c r="BA37" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB37" s="87"/>
+      <c r="BC37" s="83"/>
+      <c r="BD37" s="83"/>
+      <c r="BE37" s="84"/>
+      <c r="BF37" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG37" s="87"/>
+      <c r="BH37" s="83"/>
+      <c r="BI37" s="83"/>
+      <c r="BJ37" s="84"/>
+      <c r="BK37" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL37" s="87"/>
+      <c r="BM37" s="83"/>
+      <c r="BN37" s="83"/>
+      <c r="BO37" s="84"/>
+      <c r="BP37" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ37" s="87"/>
+      <c r="BR37" s="83"/>
+      <c r="BS37" s="83"/>
+      <c r="BT37" s="84"/>
+      <c r="BU37" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV37" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW37" s="89"/>
+      <c r="BX37" s="90"/>
+    </row>
+    <row r="38" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A38" s="91"/>
+      <c r="B38" s="83"/>
+      <c r="C38" s="92"/>
+      <c r="D38" s="92"/>
+      <c r="E38" s="92"/>
+      <c r="F38" s="92" t="s">
+        <v>104</v>
+      </c>
+      <c r="G38" s="92"/>
+      <c r="H38" s="92"/>
+      <c r="I38" s="92"/>
+      <c r="J38" s="92"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="102" t="s">
+        <v>187</v>
+      </c>
+      <c r="M38" s="103"/>
+      <c r="N38" s="82"/>
+      <c r="O38" s="83"/>
+      <c r="P38" s="83"/>
+      <c r="Q38" s="84"/>
+      <c r="R38" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="85"/>
+      <c r="T38" s="83"/>
+      <c r="U38" s="83"/>
+      <c r="V38" s="84"/>
+      <c r="W38" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X38" s="87"/>
+      <c r="Y38" s="83"/>
+      <c r="Z38" s="83"/>
+      <c r="AA38" s="84"/>
+      <c r="AB38" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC38" s="87"/>
+      <c r="AD38" s="83"/>
+      <c r="AE38" s="83"/>
+      <c r="AF38" s="84"/>
+      <c r="AG38" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH38" s="87"/>
+      <c r="AI38" s="83"/>
+      <c r="AJ38" s="83"/>
+      <c r="AK38" s="84"/>
+      <c r="AL38" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM38" s="87"/>
+      <c r="AN38" s="83"/>
+      <c r="AO38" s="83"/>
+      <c r="AP38" s="84"/>
+      <c r="AQ38" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR38" s="87"/>
+      <c r="AS38" s="83"/>
+      <c r="AT38" s="83"/>
+      <c r="AU38" s="84"/>
+      <c r="AV38" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW38" s="87"/>
+      <c r="AX38" s="83"/>
+      <c r="AY38" s="83"/>
+      <c r="AZ38" s="84"/>
+      <c r="BA38" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB38" s="87"/>
+      <c r="BC38" s="83"/>
+      <c r="BD38" s="83"/>
+      <c r="BE38" s="84"/>
+      <c r="BF38" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG38" s="87"/>
+      <c r="BH38" s="83"/>
+      <c r="BI38" s="83"/>
+      <c r="BJ38" s="84"/>
+      <c r="BK38" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL38" s="87"/>
+      <c r="BM38" s="83"/>
+      <c r="BN38" s="83"/>
+      <c r="BO38" s="84"/>
+      <c r="BP38" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ38" s="87"/>
+      <c r="BR38" s="83"/>
+      <c r="BS38" s="83"/>
+      <c r="BT38" s="84"/>
+      <c r="BU38" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV38" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW38" s="89"/>
+      <c r="BX38" s="90"/>
+    </row>
+    <row r="39" spans="1:76" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" s="91"/>
+      <c r="B39" s="83"/>
+      <c r="C39" s="92"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="G39" s="92"/>
+      <c r="H39" s="92"/>
+      <c r="I39" s="92"/>
+      <c r="J39" s="92"/>
+      <c r="K39" s="93"/>
+      <c r="L39" s="102" t="s">
+        <v>188</v>
+      </c>
+      <c r="M39" s="103"/>
+      <c r="N39" s="82"/>
+      <c r="O39" s="83"/>
+      <c r="P39" s="83"/>
+      <c r="Q39" s="84"/>
+      <c r="R39" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="85"/>
+      <c r="T39" s="83"/>
+      <c r="U39" s="83"/>
+      <c r="V39" s="84"/>
+      <c r="W39" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X39" s="87"/>
+      <c r="Y39" s="83"/>
+      <c r="Z39" s="83"/>
+      <c r="AA39" s="84"/>
+      <c r="AB39" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC39" s="87"/>
+      <c r="AD39" s="83"/>
+      <c r="AE39" s="83"/>
+      <c r="AF39" s="84"/>
+      <c r="AG39" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH39" s="87"/>
+      <c r="AI39" s="83"/>
+      <c r="AJ39" s="83"/>
+      <c r="AK39" s="84"/>
+      <c r="AL39" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM39" s="87"/>
+      <c r="AN39" s="83"/>
+      <c r="AO39" s="83"/>
+      <c r="AP39" s="84"/>
+      <c r="AQ39" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR39" s="87"/>
+      <c r="AS39" s="83"/>
+      <c r="AT39" s="83"/>
+      <c r="AU39" s="84"/>
+      <c r="AV39" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW39" s="87"/>
+      <c r="AX39" s="83"/>
+      <c r="AY39" s="83"/>
+      <c r="AZ39" s="84"/>
+      <c r="BA39" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB39" s="87"/>
+      <c r="BC39" s="83"/>
+      <c r="BD39" s="83"/>
+      <c r="BE39" s="84"/>
+      <c r="BF39" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG39" s="87"/>
+      <c r="BH39" s="83"/>
+      <c r="BI39" s="83"/>
+      <c r="BJ39" s="84"/>
+      <c r="BK39" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL39" s="87"/>
+      <c r="BM39" s="83"/>
+      <c r="BN39" s="83"/>
+      <c r="BO39" s="84"/>
+      <c r="BP39" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ39" s="87"/>
+      <c r="BR39" s="83"/>
+      <c r="BS39" s="83"/>
+      <c r="BT39" s="84"/>
+      <c r="BU39" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV39" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW39" s="89"/>
+      <c r="BX39" s="90"/>
+    </row>
+    <row r="40" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="91"/>
+      <c r="B40" s="83"/>
+      <c r="C40" s="92"/>
+      <c r="D40" s="92"/>
+      <c r="E40" s="92"/>
+      <c r="F40" s="92" t="s">
+        <v>130</v>
+      </c>
+      <c r="G40" s="92"/>
+      <c r="H40" s="92"/>
+      <c r="I40" s="92"/>
+      <c r="J40" s="92"/>
+      <c r="K40" s="93"/>
+      <c r="L40" s="102" t="s">
+        <v>189</v>
+      </c>
+      <c r="M40" s="103"/>
+      <c r="N40" s="82"/>
+      <c r="O40" s="83"/>
+      <c r="P40" s="83"/>
+      <c r="Q40" s="84"/>
+      <c r="R40" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="85"/>
+      <c r="T40" s="83"/>
+      <c r="U40" s="83"/>
+      <c r="V40" s="84"/>
+      <c r="W40" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="87"/>
+      <c r="Y40" s="83"/>
+      <c r="Z40" s="83"/>
+      <c r="AA40" s="84"/>
+      <c r="AB40" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC40" s="87"/>
+      <c r="AD40" s="83"/>
+      <c r="AE40" s="83"/>
+      <c r="AF40" s="84"/>
+      <c r="AG40" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH40" s="87"/>
+      <c r="AI40" s="83"/>
+      <c r="AJ40" s="83"/>
+      <c r="AK40" s="84"/>
+      <c r="AL40" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM40" s="87"/>
+      <c r="AN40" s="83"/>
+      <c r="AO40" s="83"/>
+      <c r="AP40" s="84"/>
+      <c r="AQ40" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR40" s="87"/>
+      <c r="AS40" s="83"/>
+      <c r="AT40" s="83"/>
+      <c r="AU40" s="84"/>
+      <c r="AV40" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW40" s="87"/>
+      <c r="AX40" s="83"/>
+      <c r="AY40" s="83"/>
+      <c r="AZ40" s="84"/>
+      <c r="BA40" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB40" s="87"/>
+      <c r="BC40" s="83"/>
+      <c r="BD40" s="83"/>
+      <c r="BE40" s="84"/>
+      <c r="BF40" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG40" s="87"/>
+      <c r="BH40" s="83"/>
+      <c r="BI40" s="83"/>
+      <c r="BJ40" s="84"/>
+      <c r="BK40" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL40" s="87"/>
+      <c r="BM40" s="83"/>
+      <c r="BN40" s="83"/>
+      <c r="BO40" s="84"/>
+      <c r="BP40" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ40" s="87"/>
+      <c r="BR40" s="83"/>
+      <c r="BS40" s="83"/>
+      <c r="BT40" s="84"/>
+      <c r="BU40" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV40" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW40" s="89"/>
+      <c r="BX40" s="90"/>
+    </row>
+    <row r="41" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="91"/>
+      <c r="B41" s="83"/>
+      <c r="C41" s="92"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92" t="s">
+        <v>131</v>
+      </c>
+      <c r="G41" s="92"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="102" t="s">
+        <v>190</v>
+      </c>
+      <c r="M41" s="103"/>
+      <c r="N41" s="82"/>
+      <c r="O41" s="83"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="84"/>
+      <c r="R41" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="85"/>
+      <c r="T41" s="83"/>
+      <c r="U41" s="83"/>
+      <c r="V41" s="84"/>
+      <c r="W41" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X41" s="87"/>
+      <c r="Y41" s="83"/>
+      <c r="Z41" s="83"/>
+      <c r="AA41" s="84"/>
+      <c r="AB41" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC41" s="87"/>
+      <c r="AD41" s="83"/>
+      <c r="AE41" s="83"/>
+      <c r="AF41" s="84"/>
+      <c r="AG41" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH41" s="87"/>
+      <c r="AI41" s="83"/>
+      <c r="AJ41" s="83"/>
+      <c r="AK41" s="84"/>
+      <c r="AL41" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM41" s="87"/>
+      <c r="AN41" s="83"/>
+      <c r="AO41" s="83"/>
+      <c r="AP41" s="84"/>
+      <c r="AQ41" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR41" s="87"/>
+      <c r="AS41" s="83"/>
+      <c r="AT41" s="83"/>
+      <c r="AU41" s="84"/>
+      <c r="AV41" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW41" s="87"/>
+      <c r="AX41" s="83"/>
+      <c r="AY41" s="83"/>
+      <c r="AZ41" s="84"/>
+      <c r="BA41" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB41" s="87"/>
+      <c r="BC41" s="83"/>
+      <c r="BD41" s="83"/>
+      <c r="BE41" s="84"/>
+      <c r="BF41" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG41" s="87"/>
+      <c r="BH41" s="83"/>
+      <c r="BI41" s="83"/>
+      <c r="BJ41" s="84"/>
+      <c r="BK41" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL41" s="87"/>
+      <c r="BM41" s="83"/>
+      <c r="BN41" s="83"/>
+      <c r="BO41" s="84"/>
+      <c r="BP41" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ41" s="87"/>
+      <c r="BR41" s="83"/>
+      <c r="BS41" s="83"/>
+      <c r="BT41" s="84"/>
+      <c r="BU41" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV41" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW41" s="89"/>
+      <c r="BX41" s="90"/>
+    </row>
+    <row r="42" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="91" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" s="83"/>
+      <c r="C42" s="92"/>
+      <c r="D42" s="92"/>
+      <c r="E42" s="92"/>
+      <c r="F42" s="92" t="s">
+        <v>133</v>
+      </c>
+      <c r="G42" s="92"/>
+      <c r="H42" s="92"/>
+      <c r="I42" s="92"/>
+      <c r="J42" s="92"/>
+      <c r="K42" s="93"/>
+      <c r="L42" s="102" t="s">
+        <v>191</v>
+      </c>
+      <c r="M42" s="103"/>
+      <c r="N42" s="82"/>
+      <c r="O42" s="83"/>
+      <c r="P42" s="83"/>
+      <c r="Q42" s="84"/>
+      <c r="R42" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="85"/>
+      <c r="T42" s="83"/>
+      <c r="U42" s="83"/>
+      <c r="V42" s="84"/>
+      <c r="W42" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X42" s="87"/>
+      <c r="Y42" s="83"/>
+      <c r="Z42" s="83"/>
+      <c r="AA42" s="84"/>
+      <c r="AB42" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC42" s="87"/>
+      <c r="AD42" s="83"/>
+      <c r="AE42" s="83"/>
+      <c r="AF42" s="84"/>
+      <c r="AG42" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH42" s="87"/>
+      <c r="AI42" s="83"/>
+      <c r="AJ42" s="83"/>
+      <c r="AK42" s="84"/>
+      <c r="AL42" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM42" s="87"/>
+      <c r="AN42" s="83"/>
+      <c r="AO42" s="83"/>
+      <c r="AP42" s="84"/>
+      <c r="AQ42" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR42" s="87"/>
+      <c r="AS42" s="83"/>
+      <c r="AT42" s="83"/>
+      <c r="AU42" s="84"/>
+      <c r="AV42" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW42" s="87"/>
+      <c r="AX42" s="83"/>
+      <c r="AY42" s="83"/>
+      <c r="AZ42" s="84"/>
+      <c r="BA42" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB42" s="87"/>
+      <c r="BC42" s="83"/>
+      <c r="BD42" s="83"/>
+      <c r="BE42" s="84"/>
+      <c r="BF42" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG42" s="87"/>
+      <c r="BH42" s="83"/>
+      <c r="BI42" s="83"/>
+      <c r="BJ42" s="84"/>
+      <c r="BK42" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL42" s="87"/>
+      <c r="BM42" s="83"/>
+      <c r="BN42" s="83"/>
+      <c r="BO42" s="84"/>
+      <c r="BP42" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ42" s="87"/>
+      <c r="BR42" s="83"/>
+      <c r="BS42" s="83"/>
+      <c r="BT42" s="84"/>
+      <c r="BU42" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV42" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW42" s="89"/>
+      <c r="BX42" s="90"/>
+    </row>
+    <row r="43" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="91" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="83"/>
+      <c r="C43" s="92"/>
+      <c r="D43" s="92"/>
+      <c r="E43" s="92"/>
+      <c r="F43" s="92" t="s">
+        <v>135</v>
+      </c>
+      <c r="G43" s="92"/>
+      <c r="H43" s="92"/>
+      <c r="I43" s="92"/>
+      <c r="J43" s="92"/>
+      <c r="K43" s="93"/>
+      <c r="L43" s="102" t="s">
+        <v>192</v>
+      </c>
+      <c r="M43" s="103"/>
+      <c r="N43" s="82"/>
+      <c r="O43" s="83"/>
+      <c r="P43" s="83"/>
+      <c r="Q43" s="84"/>
+      <c r="R43" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="85"/>
+      <c r="T43" s="83"/>
+      <c r="U43" s="83"/>
+      <c r="V43" s="84"/>
+      <c r="W43" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X43" s="87"/>
+      <c r="Y43" s="83"/>
+      <c r="Z43" s="83"/>
+      <c r="AA43" s="84"/>
+      <c r="AB43" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC43" s="87"/>
+      <c r="AD43" s="83"/>
+      <c r="AE43" s="83"/>
+      <c r="AF43" s="84"/>
+      <c r="AG43" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH43" s="87"/>
+      <c r="AI43" s="83"/>
+      <c r="AJ43" s="83"/>
+      <c r="AK43" s="84"/>
+      <c r="AL43" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM43" s="87"/>
+      <c r="AN43" s="83"/>
+      <c r="AO43" s="83"/>
+      <c r="AP43" s="84"/>
+      <c r="AQ43" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR43" s="87"/>
+      <c r="AS43" s="83"/>
+      <c r="AT43" s="83"/>
+      <c r="AU43" s="84"/>
+      <c r="AV43" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW43" s="87"/>
+      <c r="AX43" s="83"/>
+      <c r="AY43" s="83"/>
+      <c r="AZ43" s="84"/>
+      <c r="BA43" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB43" s="87"/>
+      <c r="BC43" s="83"/>
+      <c r="BD43" s="83"/>
+      <c r="BE43" s="84"/>
+      <c r="BF43" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG43" s="87"/>
+      <c r="BH43" s="83"/>
+      <c r="BI43" s="83"/>
+      <c r="BJ43" s="84"/>
+      <c r="BK43" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL43" s="87"/>
+      <c r="BM43" s="83"/>
+      <c r="BN43" s="83"/>
+      <c r="BO43" s="84"/>
+      <c r="BP43" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ43" s="87"/>
+      <c r="BR43" s="83"/>
+      <c r="BS43" s="83"/>
+      <c r="BT43" s="84"/>
+      <c r="BU43" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV43" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW43" s="89"/>
+      <c r="BX43" s="90"/>
+    </row>
+    <row r="44" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A44" s="91"/>
+      <c r="B44" s="83"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
+      <c r="F44" s="92" t="s">
+        <v>136</v>
+      </c>
+      <c r="G44" s="92"/>
+      <c r="H44" s="92"/>
+      <c r="I44" s="92"/>
+      <c r="J44" s="92"/>
+      <c r="K44" s="93"/>
+      <c r="L44" s="102" t="s">
+        <v>193</v>
+      </c>
+      <c r="M44" s="103"/>
+      <c r="N44" s="82"/>
+      <c r="O44" s="83"/>
+      <c r="P44" s="83"/>
+      <c r="Q44" s="84"/>
+      <c r="R44" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="85"/>
+      <c r="T44" s="83"/>
+      <c r="U44" s="83"/>
+      <c r="V44" s="84"/>
+      <c r="W44" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X44" s="87"/>
+      <c r="Y44" s="83"/>
+      <c r="Z44" s="83"/>
+      <c r="AA44" s="84"/>
+      <c r="AB44" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC44" s="87"/>
+      <c r="AD44" s="83"/>
+      <c r="AE44" s="83"/>
+      <c r="AF44" s="84"/>
+      <c r="AG44" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH44" s="87"/>
+      <c r="AI44" s="83"/>
+      <c r="AJ44" s="83"/>
+      <c r="AK44" s="84"/>
+      <c r="AL44" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM44" s="87"/>
+      <c r="AN44" s="83"/>
+      <c r="AO44" s="83"/>
+      <c r="AP44" s="84"/>
+      <c r="AQ44" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR44" s="87"/>
+      <c r="AS44" s="83"/>
+      <c r="AT44" s="83"/>
+      <c r="AU44" s="84"/>
+      <c r="AV44" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW44" s="87"/>
+      <c r="AX44" s="83"/>
+      <c r="AY44" s="83"/>
+      <c r="AZ44" s="84"/>
+      <c r="BA44" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB44" s="87"/>
+      <c r="BC44" s="83"/>
+      <c r="BD44" s="83"/>
+      <c r="BE44" s="84"/>
+      <c r="BF44" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG44" s="87"/>
+      <c r="BH44" s="83"/>
+      <c r="BI44" s="83"/>
+      <c r="BJ44" s="84"/>
+      <c r="BK44" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL44" s="87"/>
+      <c r="BM44" s="83"/>
+      <c r="BN44" s="83"/>
+      <c r="BO44" s="84"/>
+      <c r="BP44" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ44" s="87"/>
+      <c r="BR44" s="83"/>
+      <c r="BS44" s="83"/>
+      <c r="BT44" s="84"/>
+      <c r="BU44" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV44" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW44" s="89"/>
+      <c r="BX44" s="90"/>
+    </row>
+    <row r="45" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A45" s="91"/>
+      <c r="B45" s="83"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="92" t="s">
+        <v>137</v>
+      </c>
+      <c r="G45" s="92"/>
+      <c r="H45" s="92"/>
+      <c r="I45" s="92"/>
+      <c r="J45" s="92"/>
+      <c r="K45" s="93"/>
+      <c r="L45" s="102" t="s">
+        <v>194</v>
+      </c>
+      <c r="M45" s="103"/>
+      <c r="N45" s="82"/>
+      <c r="O45" s="83"/>
+      <c r="P45" s="83"/>
+      <c r="Q45" s="84"/>
+      <c r="R45" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="85"/>
+      <c r="T45" s="83"/>
+      <c r="U45" s="83"/>
+      <c r="V45" s="84"/>
+      <c r="W45" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X45" s="87"/>
+      <c r="Y45" s="83"/>
+      <c r="Z45" s="83"/>
+      <c r="AA45" s="84"/>
+      <c r="AB45" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC45" s="87"/>
+      <c r="AD45" s="83"/>
+      <c r="AE45" s="83"/>
+      <c r="AF45" s="84"/>
+      <c r="AG45" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH45" s="87"/>
+      <c r="AI45" s="83"/>
+      <c r="AJ45" s="83"/>
+      <c r="AK45" s="84"/>
+      <c r="AL45" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM45" s="87"/>
+      <c r="AN45" s="83"/>
+      <c r="AO45" s="83"/>
+      <c r="AP45" s="84"/>
+      <c r="AQ45" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR45" s="87"/>
+      <c r="AS45" s="83"/>
+      <c r="AT45" s="83"/>
+      <c r="AU45" s="84"/>
+      <c r="AV45" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW45" s="87"/>
+      <c r="AX45" s="83"/>
+      <c r="AY45" s="83"/>
+      <c r="AZ45" s="84"/>
+      <c r="BA45" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB45" s="87"/>
+      <c r="BC45" s="83"/>
+      <c r="BD45" s="83"/>
+      <c r="BE45" s="84"/>
+      <c r="BF45" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG45" s="87"/>
+      <c r="BH45" s="83"/>
+      <c r="BI45" s="83"/>
+      <c r="BJ45" s="84"/>
+      <c r="BK45" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL45" s="87"/>
+      <c r="BM45" s="83"/>
+      <c r="BN45" s="83"/>
+      <c r="BO45" s="84"/>
+      <c r="BP45" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ45" s="87"/>
+      <c r="BR45" s="83"/>
+      <c r="BS45" s="83"/>
+      <c r="BT45" s="84"/>
+      <c r="BU45" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV45" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW45" s="89"/>
+      <c r="BX45" s="90"/>
+    </row>
+    <row r="46" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="91" t="s">
+        <v>138</v>
+      </c>
+      <c r="B46" s="83">
+        <v>9501137831</v>
+      </c>
+      <c r="C46" s="98">
+        <v>45992</v>
+      </c>
+      <c r="D46" s="98">
+        <v>46356</v>
+      </c>
+      <c r="E46" s="92" t="s">
+        <v>139</v>
+      </c>
+      <c r="F46" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="G46" s="92">
+        <v>41010100</v>
+      </c>
+      <c r="H46" s="92">
+        <v>7280</v>
+      </c>
+      <c r="I46" s="92" t="s">
+        <v>141</v>
+      </c>
+      <c r="J46" s="92">
+        <v>2662855</v>
+      </c>
+      <c r="K46" s="99">
+        <v>38005</v>
+      </c>
+      <c r="L46" s="102" t="s">
+        <v>195</v>
+      </c>
+      <c r="M46" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N46" s="82"/>
+      <c r="O46" s="83"/>
+      <c r="P46" s="83"/>
+      <c r="Q46" s="84"/>
+      <c r="R46" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="85"/>
+      <c r="T46" s="83"/>
+      <c r="U46" s="83"/>
+      <c r="V46" s="84"/>
+      <c r="W46" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X46" s="87"/>
+      <c r="Y46" s="83"/>
+      <c r="Z46" s="83"/>
+      <c r="AA46" s="84"/>
+      <c r="AB46" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC46" s="87"/>
+      <c r="AD46" s="83"/>
+      <c r="AE46" s="83"/>
+      <c r="AF46" s="84"/>
+      <c r="AG46" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH46" s="87"/>
+      <c r="AI46" s="83"/>
+      <c r="AJ46" s="83"/>
+      <c r="AK46" s="84"/>
+      <c r="AL46" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM46" s="87"/>
+      <c r="AN46" s="83"/>
+      <c r="AO46" s="83"/>
+      <c r="AP46" s="84"/>
+      <c r="AQ46" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR46" s="87"/>
+      <c r="AS46" s="83"/>
+      <c r="AT46" s="83"/>
+      <c r="AU46" s="84"/>
+      <c r="AV46" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW46" s="87"/>
+      <c r="AX46" s="83"/>
+      <c r="AY46" s="83"/>
+      <c r="AZ46" s="84"/>
+      <c r="BA46" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB46" s="87"/>
+      <c r="BC46" s="83"/>
+      <c r="BD46" s="83"/>
+      <c r="BE46" s="84"/>
+      <c r="BF46" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG46" s="87"/>
+      <c r="BH46" s="83"/>
+      <c r="BI46" s="83"/>
+      <c r="BJ46" s="84"/>
+      <c r="BK46" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL46" s="87"/>
+      <c r="BM46" s="83"/>
+      <c r="BN46" s="83"/>
+      <c r="BO46" s="84"/>
+      <c r="BP46" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ46" s="87"/>
+      <c r="BR46" s="83"/>
+      <c r="BS46" s="83"/>
+      <c r="BT46" s="84"/>
+      <c r="BU46" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV46" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW46" s="89"/>
+      <c r="BX46" s="90"/>
+    </row>
+    <row r="47" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="83">
+        <v>9501137269</v>
+      </c>
+      <c r="C47" s="98">
+        <v>45992</v>
+      </c>
+      <c r="D47" s="98">
+        <v>46356</v>
+      </c>
+      <c r="E47" s="92" t="s">
+        <v>142</v>
+      </c>
+      <c r="F47" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="G47" s="92">
+        <v>41010100</v>
+      </c>
+      <c r="H47" s="92">
+        <v>7280</v>
+      </c>
+      <c r="I47" s="92" t="s">
+        <v>141</v>
+      </c>
+      <c r="J47" s="92">
+        <v>2662855</v>
+      </c>
+      <c r="K47" s="99">
+        <v>9980</v>
+      </c>
+      <c r="L47" s="102" t="s">
+        <v>196</v>
+      </c>
+      <c r="M47" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N47" s="82"/>
+      <c r="O47" s="83"/>
+      <c r="P47" s="83"/>
+      <c r="Q47" s="84"/>
+      <c r="R47" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="85"/>
+      <c r="T47" s="83"/>
+      <c r="U47" s="83"/>
+      <c r="V47" s="84"/>
+      <c r="W47" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="87"/>
+      <c r="Y47" s="83"/>
+      <c r="Z47" s="83"/>
+      <c r="AA47" s="84"/>
+      <c r="AB47" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC47" s="87"/>
+      <c r="AD47" s="83"/>
+      <c r="AE47" s="83"/>
+      <c r="AF47" s="84"/>
+      <c r="AG47" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH47" s="87"/>
+      <c r="AI47" s="83"/>
+      <c r="AJ47" s="83"/>
+      <c r="AK47" s="84"/>
+      <c r="AL47" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM47" s="87"/>
+      <c r="AN47" s="83"/>
+      <c r="AO47" s="83"/>
+      <c r="AP47" s="84"/>
+      <c r="AQ47" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR47" s="87"/>
+      <c r="AS47" s="83"/>
+      <c r="AT47" s="83"/>
+      <c r="AU47" s="84"/>
+      <c r="AV47" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW47" s="87"/>
+      <c r="AX47" s="83"/>
+      <c r="AY47" s="83"/>
+      <c r="AZ47" s="84"/>
+      <c r="BA47" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB47" s="87"/>
+      <c r="BC47" s="83"/>
+      <c r="BD47" s="83"/>
+      <c r="BE47" s="84"/>
+      <c r="BF47" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG47" s="87"/>
+      <c r="BH47" s="83"/>
+      <c r="BI47" s="83"/>
+      <c r="BJ47" s="84"/>
+      <c r="BK47" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL47" s="87"/>
+      <c r="BM47" s="83"/>
+      <c r="BN47" s="83"/>
+      <c r="BO47" s="84"/>
+      <c r="BP47" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ47" s="87"/>
+      <c r="BR47" s="83"/>
+      <c r="BS47" s="83"/>
+      <c r="BT47" s="84"/>
+      <c r="BU47" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV47" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW47" s="89"/>
+      <c r="BX47" s="90"/>
+    </row>
+    <row r="48" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="91"/>
+      <c r="B48" s="83"/>
+      <c r="C48" s="92"/>
+      <c r="D48" s="92"/>
+      <c r="E48" s="92"/>
+      <c r="F48" s="92" t="s">
+        <v>144</v>
+      </c>
+      <c r="G48" s="92"/>
+      <c r="H48" s="92"/>
+      <c r="I48" s="92"/>
+      <c r="J48" s="92"/>
+      <c r="K48" s="99">
+        <v>12000</v>
+      </c>
+      <c r="L48" s="102" t="s">
+        <v>197</v>
+      </c>
+      <c r="M48" s="103"/>
+      <c r="N48" s="82"/>
+      <c r="O48" s="83"/>
+      <c r="P48" s="83"/>
+      <c r="Q48" s="84"/>
+      <c r="R48" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="85"/>
+      <c r="T48" s="83"/>
+      <c r="U48" s="83"/>
+      <c r="V48" s="84"/>
+      <c r="W48" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X48" s="87"/>
+      <c r="Y48" s="83"/>
+      <c r="Z48" s="83"/>
+      <c r="AA48" s="84"/>
+      <c r="AB48" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC48" s="87"/>
+      <c r="AD48" s="83"/>
+      <c r="AE48" s="83"/>
+      <c r="AF48" s="84"/>
+      <c r="AG48" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH48" s="87"/>
+      <c r="AI48" s="83"/>
+      <c r="AJ48" s="83"/>
+      <c r="AK48" s="84"/>
+      <c r="AL48" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM48" s="87"/>
+      <c r="AN48" s="83"/>
+      <c r="AO48" s="83"/>
+      <c r="AP48" s="84"/>
+      <c r="AQ48" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR48" s="87"/>
+      <c r="AS48" s="83"/>
+      <c r="AT48" s="83"/>
+      <c r="AU48" s="84"/>
+      <c r="AV48" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW48" s="87"/>
+      <c r="AX48" s="83"/>
+      <c r="AY48" s="83"/>
+      <c r="AZ48" s="84"/>
+      <c r="BA48" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB48" s="87"/>
+      <c r="BC48" s="83"/>
+      <c r="BD48" s="83"/>
+      <c r="BE48" s="84"/>
+      <c r="BF48" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG48" s="87"/>
+      <c r="BH48" s="83"/>
+      <c r="BI48" s="83"/>
+      <c r="BJ48" s="84"/>
+      <c r="BK48" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL48" s="87"/>
+      <c r="BM48" s="83"/>
+      <c r="BN48" s="83"/>
+      <c r="BO48" s="84"/>
+      <c r="BP48" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ48" s="87"/>
+      <c r="BR48" s="83"/>
+      <c r="BS48" s="83"/>
+      <c r="BT48" s="84"/>
+      <c r="BU48" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV48" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW48" s="89"/>
+      <c r="BX48" s="90"/>
+    </row>
+    <row r="49" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="91"/>
+      <c r="B49" s="83"/>
+      <c r="C49" s="92"/>
+      <c r="D49" s="92"/>
+      <c r="E49" s="92"/>
+      <c r="F49" s="92" t="s">
+        <v>145</v>
+      </c>
+      <c r="G49" s="92"/>
+      <c r="H49" s="92"/>
+      <c r="I49" s="92"/>
+      <c r="J49" s="92"/>
+      <c r="K49" s="99">
+        <v>0</v>
+      </c>
+      <c r="L49" s="102" t="s">
+        <v>198</v>
+      </c>
+      <c r="M49" s="103"/>
+      <c r="N49" s="82"/>
+      <c r="O49" s="83"/>
+      <c r="P49" s="83"/>
+      <c r="Q49" s="84"/>
+      <c r="R49" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="85"/>
+      <c r="T49" s="83"/>
+      <c r="U49" s="83"/>
+      <c r="V49" s="84"/>
+      <c r="W49" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X49" s="87"/>
+      <c r="Y49" s="83"/>
+      <c r="Z49" s="83"/>
+      <c r="AA49" s="84"/>
+      <c r="AB49" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC49" s="87"/>
+      <c r="AD49" s="83"/>
+      <c r="AE49" s="83"/>
+      <c r="AF49" s="84"/>
+      <c r="AG49" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH49" s="87"/>
+      <c r="AI49" s="83"/>
+      <c r="AJ49" s="83"/>
+      <c r="AK49" s="84"/>
+      <c r="AL49" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM49" s="87"/>
+      <c r="AN49" s="83"/>
+      <c r="AO49" s="83"/>
+      <c r="AP49" s="84"/>
+      <c r="AQ49" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR49" s="87"/>
+      <c r="AS49" s="83"/>
+      <c r="AT49" s="83"/>
+      <c r="AU49" s="84"/>
+      <c r="AV49" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW49" s="87"/>
+      <c r="AX49" s="83"/>
+      <c r="AY49" s="83"/>
+      <c r="AZ49" s="84"/>
+      <c r="BA49" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB49" s="87"/>
+      <c r="BC49" s="83"/>
+      <c r="BD49" s="83"/>
+      <c r="BE49" s="84"/>
+      <c r="BF49" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG49" s="87"/>
+      <c r="BH49" s="83"/>
+      <c r="BI49" s="83"/>
+      <c r="BJ49" s="84"/>
+      <c r="BK49" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL49" s="87"/>
+      <c r="BM49" s="83"/>
+      <c r="BN49" s="83"/>
+      <c r="BO49" s="84"/>
+      <c r="BP49" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ49" s="87"/>
+      <c r="BR49" s="83"/>
+      <c r="BS49" s="83"/>
+      <c r="BT49" s="84"/>
+      <c r="BU49" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV49" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW49" s="89"/>
+      <c r="BX49" s="90"/>
+    </row>
+    <row r="50" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" s="83">
+        <v>9501166164</v>
+      </c>
+      <c r="C50" s="98">
+        <v>46023</v>
+      </c>
+      <c r="D50" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E50" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="F50" s="92" t="s">
+        <v>147</v>
+      </c>
+      <c r="G50" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H50" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I50" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J50" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K50" s="99">
+        <v>4651600</v>
+      </c>
+      <c r="L50" s="102" t="s">
+        <v>199</v>
+      </c>
+      <c r="M50" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N50" s="82"/>
+      <c r="O50" s="83"/>
+      <c r="P50" s="83"/>
+      <c r="Q50" s="84"/>
+      <c r="R50" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="85"/>
+      <c r="T50" s="83"/>
+      <c r="U50" s="83"/>
+      <c r="V50" s="84"/>
+      <c r="W50" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="87"/>
+      <c r="Y50" s="83"/>
+      <c r="Z50" s="83"/>
+      <c r="AA50" s="84"/>
+      <c r="AB50" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC50" s="87"/>
+      <c r="AD50" s="83"/>
+      <c r="AE50" s="83"/>
+      <c r="AF50" s="84"/>
+      <c r="AG50" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH50" s="87"/>
+      <c r="AI50" s="83"/>
+      <c r="AJ50" s="83"/>
+      <c r="AK50" s="84"/>
+      <c r="AL50" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM50" s="87"/>
+      <c r="AN50" s="83"/>
+      <c r="AO50" s="83"/>
+      <c r="AP50" s="84"/>
+      <c r="AQ50" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR50" s="87"/>
+      <c r="AS50" s="83"/>
+      <c r="AT50" s="83"/>
+      <c r="AU50" s="84"/>
+      <c r="AV50" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW50" s="87"/>
+      <c r="AX50" s="83"/>
+      <c r="AY50" s="83"/>
+      <c r="AZ50" s="84"/>
+      <c r="BA50" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB50" s="87"/>
+      <c r="BC50" s="83"/>
+      <c r="BD50" s="83"/>
+      <c r="BE50" s="84"/>
+      <c r="BF50" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG50" s="87"/>
+      <c r="BH50" s="83"/>
+      <c r="BI50" s="83"/>
+      <c r="BJ50" s="84"/>
+      <c r="BK50" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL50" s="87"/>
+      <c r="BM50" s="83"/>
+      <c r="BN50" s="83"/>
+      <c r="BO50" s="84"/>
+      <c r="BP50" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ50" s="87"/>
+      <c r="BR50" s="83"/>
+      <c r="BS50" s="83"/>
+      <c r="BT50" s="84"/>
+      <c r="BU50" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV50" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW50" s="89"/>
+      <c r="BX50" s="90"/>
+    </row>
+    <row r="51" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" s="83">
+        <v>9501190667</v>
+      </c>
+      <c r="C51" s="98">
+        <v>45992</v>
+      </c>
+      <c r="D51" s="98">
+        <v>46296</v>
+      </c>
+      <c r="E51" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="F51" s="92" t="s">
+        <v>147</v>
+      </c>
+      <c r="G51" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H51" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I51" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J51" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K51" s="99">
+        <v>62500</v>
+      </c>
+      <c r="L51" s="102" t="s">
+        <v>200</v>
+      </c>
+      <c r="M51" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N51" s="82"/>
+      <c r="O51" s="83"/>
+      <c r="P51" s="83"/>
+      <c r="Q51" s="84"/>
+      <c r="R51" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="85"/>
+      <c r="T51" s="83"/>
+      <c r="U51" s="83"/>
+      <c r="V51" s="84"/>
+      <c r="W51" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="87"/>
+      <c r="Y51" s="83"/>
+      <c r="Z51" s="83"/>
+      <c r="AA51" s="84"/>
+      <c r="AB51" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC51" s="87"/>
+      <c r="AD51" s="83"/>
+      <c r="AE51" s="83"/>
+      <c r="AF51" s="84"/>
+      <c r="AG51" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH51" s="87"/>
+      <c r="AI51" s="83"/>
+      <c r="AJ51" s="83"/>
+      <c r="AK51" s="84"/>
+      <c r="AL51" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM51" s="87"/>
+      <c r="AN51" s="83"/>
+      <c r="AO51" s="83"/>
+      <c r="AP51" s="84"/>
+      <c r="AQ51" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR51" s="87"/>
+      <c r="AS51" s="83"/>
+      <c r="AT51" s="83"/>
+      <c r="AU51" s="84"/>
+      <c r="AV51" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW51" s="87"/>
+      <c r="AX51" s="83"/>
+      <c r="AY51" s="83"/>
+      <c r="AZ51" s="84"/>
+      <c r="BA51" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB51" s="87"/>
+      <c r="BC51" s="83"/>
+      <c r="BD51" s="83"/>
+      <c r="BE51" s="84"/>
+      <c r="BF51" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG51" s="87"/>
+      <c r="BH51" s="83"/>
+      <c r="BI51" s="83"/>
+      <c r="BJ51" s="84"/>
+      <c r="BK51" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL51" s="87"/>
+      <c r="BM51" s="83"/>
+      <c r="BN51" s="83"/>
+      <c r="BO51" s="84"/>
+      <c r="BP51" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ51" s="87"/>
+      <c r="BR51" s="83"/>
+      <c r="BS51" s="83"/>
+      <c r="BT51" s="84"/>
+      <c r="BU51" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV51" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW51" s="89"/>
+      <c r="BX51" s="90"/>
+    </row>
+    <row r="52" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A52" s="91" t="s">
+        <v>148</v>
+      </c>
+      <c r="B52" s="83">
+        <v>9501199822</v>
+      </c>
+      <c r="C52" s="98">
+        <v>46023</v>
+      </c>
+      <c r="D52" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E52" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="F52" s="92" t="s">
+        <v>149</v>
+      </c>
+      <c r="G52" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H52" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I52" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J52" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K52" s="99">
+        <v>1058400</v>
+      </c>
+      <c r="L52" s="102" t="s">
+        <v>201</v>
+      </c>
+      <c r="M52" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N52" s="82"/>
+      <c r="O52" s="83"/>
+      <c r="P52" s="83"/>
+      <c r="Q52" s="84"/>
+      <c r="R52" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="85"/>
+      <c r="T52" s="83"/>
+      <c r="U52" s="83"/>
+      <c r="V52" s="84"/>
+      <c r="W52" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X52" s="87"/>
+      <c r="Y52" s="83"/>
+      <c r="Z52" s="83"/>
+      <c r="AA52" s="84"/>
+      <c r="AB52" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC52" s="87"/>
+      <c r="AD52" s="83"/>
+      <c r="AE52" s="83"/>
+      <c r="AF52" s="84"/>
+      <c r="AG52" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH52" s="87"/>
+      <c r="AI52" s="83"/>
+      <c r="AJ52" s="83"/>
+      <c r="AK52" s="84"/>
+      <c r="AL52" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM52" s="87"/>
+      <c r="AN52" s="83"/>
+      <c r="AO52" s="83"/>
+      <c r="AP52" s="84"/>
+      <c r="AQ52" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR52" s="87"/>
+      <c r="AS52" s="83"/>
+      <c r="AT52" s="83"/>
+      <c r="AU52" s="84"/>
+      <c r="AV52" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW52" s="87"/>
+      <c r="AX52" s="83"/>
+      <c r="AY52" s="83"/>
+      <c r="AZ52" s="84"/>
+      <c r="BA52" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB52" s="87"/>
+      <c r="BC52" s="83"/>
+      <c r="BD52" s="83"/>
+      <c r="BE52" s="84"/>
+      <c r="BF52" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG52" s="87"/>
+      <c r="BH52" s="83"/>
+      <c r="BI52" s="83"/>
+      <c r="BJ52" s="84"/>
+      <c r="BK52" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL52" s="87"/>
+      <c r="BM52" s="83"/>
+      <c r="BN52" s="83"/>
+      <c r="BO52" s="84"/>
+      <c r="BP52" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ52" s="87"/>
+      <c r="BR52" s="83"/>
+      <c r="BS52" s="83"/>
+      <c r="BT52" s="84"/>
+      <c r="BU52" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV52" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW52" s="89"/>
+      <c r="BX52" s="90"/>
+    </row>
+    <row r="53" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A53" s="91" t="s">
+        <v>150</v>
+      </c>
+      <c r="B53" s="83">
+        <v>9501199827</v>
+      </c>
+      <c r="C53" s="98">
+        <v>46023</v>
+      </c>
+      <c r="D53" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E53" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" s="92" t="s">
+        <v>149</v>
+      </c>
+      <c r="G53" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H53" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I53" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J53" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K53" s="99">
+        <v>577400</v>
+      </c>
+      <c r="L53" s="102" t="s">
+        <v>202</v>
+      </c>
+      <c r="M53" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N53" s="82"/>
+      <c r="O53" s="83"/>
+      <c r="P53" s="83"/>
+      <c r="Q53" s="84"/>
+      <c r="R53" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="85"/>
+      <c r="T53" s="83"/>
+      <c r="U53" s="83"/>
+      <c r="V53" s="84"/>
+      <c r="W53" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X53" s="87"/>
+      <c r="Y53" s="83"/>
+      <c r="Z53" s="83"/>
+      <c r="AA53" s="84"/>
+      <c r="AB53" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC53" s="87"/>
+      <c r="AD53" s="83"/>
+      <c r="AE53" s="83"/>
+      <c r="AF53" s="84"/>
+      <c r="AG53" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH53" s="87"/>
+      <c r="AI53" s="83"/>
+      <c r="AJ53" s="83"/>
+      <c r="AK53" s="84"/>
+      <c r="AL53" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM53" s="87"/>
+      <c r="AN53" s="83"/>
+      <c r="AO53" s="83"/>
+      <c r="AP53" s="84"/>
+      <c r="AQ53" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR53" s="87"/>
+      <c r="AS53" s="83"/>
+      <c r="AT53" s="83"/>
+      <c r="AU53" s="84"/>
+      <c r="AV53" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW53" s="87"/>
+      <c r="AX53" s="83"/>
+      <c r="AY53" s="83"/>
+      <c r="AZ53" s="84"/>
+      <c r="BA53" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB53" s="87"/>
+      <c r="BC53" s="83"/>
+      <c r="BD53" s="83"/>
+      <c r="BE53" s="84"/>
+      <c r="BF53" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG53" s="87"/>
+      <c r="BH53" s="83"/>
+      <c r="BI53" s="83"/>
+      <c r="BJ53" s="84"/>
+      <c r="BK53" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL53" s="87"/>
+      <c r="BM53" s="83"/>
+      <c r="BN53" s="83"/>
+      <c r="BO53" s="84"/>
+      <c r="BP53" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ53" s="87"/>
+      <c r="BR53" s="83"/>
+      <c r="BS53" s="83"/>
+      <c r="BT53" s="84"/>
+      <c r="BU53" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV53" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW53" s="89"/>
+      <c r="BX53" s="90"/>
+    </row>
+    <row r="54" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A54" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="83">
+        <v>9501195328</v>
+      </c>
+      <c r="C54" s="98">
+        <v>46023</v>
+      </c>
+      <c r="D54" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E54" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="F54" s="92" t="s">
+        <v>151</v>
+      </c>
+      <c r="G54" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H54" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I54" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J54" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K54" s="99">
+        <v>36000</v>
+      </c>
+      <c r="L54" s="102" t="s">
+        <v>203</v>
+      </c>
+      <c r="M54" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N54" s="82"/>
+      <c r="O54" s="83"/>
+      <c r="P54" s="83"/>
+      <c r="Q54" s="84"/>
+      <c r="R54" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="85"/>
+      <c r="T54" s="83"/>
+      <c r="U54" s="83"/>
+      <c r="V54" s="84"/>
+      <c r="W54" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X54" s="87"/>
+      <c r="Y54" s="83"/>
+      <c r="Z54" s="83"/>
+      <c r="AA54" s="84"/>
+      <c r="AB54" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC54" s="87"/>
+      <c r="AD54" s="83"/>
+      <c r="AE54" s="83"/>
+      <c r="AF54" s="84"/>
+      <c r="AG54" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH54" s="87"/>
+      <c r="AI54" s="83"/>
+      <c r="AJ54" s="83"/>
+      <c r="AK54" s="84"/>
+      <c r="AL54" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM54" s="87"/>
+      <c r="AN54" s="83"/>
+      <c r="AO54" s="83"/>
+      <c r="AP54" s="84"/>
+      <c r="AQ54" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR54" s="87"/>
+      <c r="AS54" s="83"/>
+      <c r="AT54" s="83"/>
+      <c r="AU54" s="84"/>
+      <c r="AV54" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW54" s="87"/>
+      <c r="AX54" s="83"/>
+      <c r="AY54" s="83"/>
+      <c r="AZ54" s="84"/>
+      <c r="BA54" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB54" s="87"/>
+      <c r="BC54" s="83"/>
+      <c r="BD54" s="83"/>
+      <c r="BE54" s="84"/>
+      <c r="BF54" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG54" s="87"/>
+      <c r="BH54" s="83"/>
+      <c r="BI54" s="83"/>
+      <c r="BJ54" s="84"/>
+      <c r="BK54" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL54" s="87"/>
+      <c r="BM54" s="83"/>
+      <c r="BN54" s="83"/>
+      <c r="BO54" s="84"/>
+      <c r="BP54" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ54" s="87"/>
+      <c r="BR54" s="83"/>
+      <c r="BS54" s="83"/>
+      <c r="BT54" s="84"/>
+      <c r="BU54" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV54" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW54" s="89"/>
+      <c r="BX54" s="90"/>
+    </row>
+    <row r="55" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A55" s="91"/>
+      <c r="B55" s="83"/>
+      <c r="C55" s="92"/>
+      <c r="D55" s="92"/>
+      <c r="E55" s="92"/>
+      <c r="F55" s="92" t="s">
+        <v>152</v>
+      </c>
+      <c r="G55" s="92"/>
+      <c r="H55" s="92"/>
+      <c r="I55" s="92"/>
+      <c r="J55" s="92"/>
+      <c r="K55" s="93"/>
+      <c r="L55" s="102" t="s">
+        <v>204</v>
+      </c>
+      <c r="M55" s="103"/>
+      <c r="N55" s="82"/>
+      <c r="O55" s="83"/>
+      <c r="P55" s="83"/>
+      <c r="Q55" s="84"/>
+      <c r="R55" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="85"/>
+      <c r="T55" s="83"/>
+      <c r="U55" s="83"/>
+      <c r="V55" s="84"/>
+      <c r="W55" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X55" s="87"/>
+      <c r="Y55" s="83"/>
+      <c r="Z55" s="83"/>
+      <c r="AA55" s="84"/>
+      <c r="AB55" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC55" s="87"/>
+      <c r="AD55" s="83"/>
+      <c r="AE55" s="83"/>
+      <c r="AF55" s="84"/>
+      <c r="AG55" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH55" s="87"/>
+      <c r="AI55" s="83"/>
+      <c r="AJ55" s="83"/>
+      <c r="AK55" s="84"/>
+      <c r="AL55" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM55" s="87"/>
+      <c r="AN55" s="83"/>
+      <c r="AO55" s="83"/>
+      <c r="AP55" s="84"/>
+      <c r="AQ55" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR55" s="87"/>
+      <c r="AS55" s="83"/>
+      <c r="AT55" s="83"/>
+      <c r="AU55" s="84"/>
+      <c r="AV55" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW55" s="87"/>
+      <c r="AX55" s="83"/>
+      <c r="AY55" s="83"/>
+      <c r="AZ55" s="84"/>
+      <c r="BA55" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB55" s="87"/>
+      <c r="BC55" s="83"/>
+      <c r="BD55" s="83"/>
+      <c r="BE55" s="84"/>
+      <c r="BF55" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG55" s="87"/>
+      <c r="BH55" s="83"/>
+      <c r="BI55" s="83"/>
+      <c r="BJ55" s="84"/>
+      <c r="BK55" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL55" s="87"/>
+      <c r="BM55" s="83"/>
+      <c r="BN55" s="83"/>
+      <c r="BO55" s="84"/>
+      <c r="BP55" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ55" s="87"/>
+      <c r="BR55" s="83"/>
+      <c r="BS55" s="83"/>
+      <c r="BT55" s="84"/>
+      <c r="BU55" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV55" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW55" s="89"/>
+      <c r="BX55" s="90"/>
+    </row>
+    <row r="56" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A56" s="91"/>
+      <c r="B56" s="83"/>
+      <c r="C56" s="92"/>
+      <c r="D56" s="92"/>
+      <c r="E56" s="92"/>
+      <c r="F56" s="92" t="s">
+        <v>153</v>
+      </c>
+      <c r="G56" s="92"/>
+      <c r="H56" s="92"/>
+      <c r="I56" s="92"/>
+      <c r="J56" s="92"/>
+      <c r="K56" s="93"/>
+      <c r="L56" s="102" t="s">
+        <v>205</v>
+      </c>
+      <c r="M56" s="103"/>
+      <c r="N56" s="82"/>
+      <c r="O56" s="83"/>
+      <c r="P56" s="83"/>
+      <c r="Q56" s="84"/>
+      <c r="R56" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="85"/>
+      <c r="T56" s="83"/>
+      <c r="U56" s="83"/>
+      <c r="V56" s="84"/>
+      <c r="W56" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X56" s="87"/>
+      <c r="Y56" s="83"/>
+      <c r="Z56" s="83"/>
+      <c r="AA56" s="84"/>
+      <c r="AB56" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC56" s="87"/>
+      <c r="AD56" s="83"/>
+      <c r="AE56" s="83"/>
+      <c r="AF56" s="84"/>
+      <c r="AG56" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH56" s="87"/>
+      <c r="AI56" s="83"/>
+      <c r="AJ56" s="83"/>
+      <c r="AK56" s="84"/>
+      <c r="AL56" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM56" s="87"/>
+      <c r="AN56" s="83"/>
+      <c r="AO56" s="83"/>
+      <c r="AP56" s="84"/>
+      <c r="AQ56" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR56" s="87"/>
+      <c r="AS56" s="83"/>
+      <c r="AT56" s="83"/>
+      <c r="AU56" s="84"/>
+      <c r="AV56" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW56" s="87"/>
+      <c r="AX56" s="83"/>
+      <c r="AY56" s="83"/>
+      <c r="AZ56" s="84"/>
+      <c r="BA56" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB56" s="87"/>
+      <c r="BC56" s="83"/>
+      <c r="BD56" s="83"/>
+      <c r="BE56" s="84"/>
+      <c r="BF56" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG56" s="87"/>
+      <c r="BH56" s="83"/>
+      <c r="BI56" s="83"/>
+      <c r="BJ56" s="84"/>
+      <c r="BK56" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL56" s="87"/>
+      <c r="BM56" s="83"/>
+      <c r="BN56" s="83"/>
+      <c r="BO56" s="84"/>
+      <c r="BP56" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ56" s="87"/>
+      <c r="BR56" s="83"/>
+      <c r="BS56" s="83"/>
+      <c r="BT56" s="84"/>
+      <c r="BU56" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV56" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW56" s="89"/>
+      <c r="BX56" s="90"/>
+    </row>
+    <row r="57" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A57" s="91" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" s="83">
+        <v>9501212179</v>
+      </c>
+      <c r="C57" s="98">
+        <v>46023</v>
+      </c>
+      <c r="D57" s="92" t="s">
+        <v>154</v>
+      </c>
+      <c r="E57" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="F57" s="92" t="s">
+        <v>155</v>
+      </c>
+      <c r="G57" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H57" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I57" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J57" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K57" s="99">
+        <v>334732.5</v>
+      </c>
+      <c r="L57" s="102" t="s">
+        <v>206</v>
+      </c>
+      <c r="M57" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N57" s="82"/>
+      <c r="O57" s="83"/>
+      <c r="P57" s="83"/>
+      <c r="Q57" s="84"/>
+      <c r="R57" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="85"/>
+      <c r="T57" s="83"/>
+      <c r="U57" s="83"/>
+      <c r="V57" s="84"/>
+      <c r="W57" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X57" s="87"/>
+      <c r="Y57" s="83"/>
+      <c r="Z57" s="83"/>
+      <c r="AA57" s="84"/>
+      <c r="AB57" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC57" s="87"/>
+      <c r="AD57" s="83"/>
+      <c r="AE57" s="83"/>
+      <c r="AF57" s="84"/>
+      <c r="AG57" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH57" s="87"/>
+      <c r="AI57" s="83"/>
+      <c r="AJ57" s="83"/>
+      <c r="AK57" s="84"/>
+      <c r="AL57" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM57" s="87"/>
+      <c r="AN57" s="83"/>
+      <c r="AO57" s="83"/>
+      <c r="AP57" s="84"/>
+      <c r="AQ57" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR57" s="87"/>
+      <c r="AS57" s="83"/>
+      <c r="AT57" s="83"/>
+      <c r="AU57" s="84"/>
+      <c r="AV57" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW57" s="87"/>
+      <c r="AX57" s="83"/>
+      <c r="AY57" s="83"/>
+      <c r="AZ57" s="84"/>
+      <c r="BA57" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB57" s="87"/>
+      <c r="BC57" s="83"/>
+      <c r="BD57" s="83"/>
+      <c r="BE57" s="84"/>
+      <c r="BF57" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG57" s="87"/>
+      <c r="BH57" s="83"/>
+      <c r="BI57" s="83"/>
+      <c r="BJ57" s="84"/>
+      <c r="BK57" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL57" s="87"/>
+      <c r="BM57" s="83"/>
+      <c r="BN57" s="83"/>
+      <c r="BO57" s="84"/>
+      <c r="BP57" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ57" s="87"/>
+      <c r="BR57" s="83"/>
+      <c r="BS57" s="83"/>
+      <c r="BT57" s="84"/>
+      <c r="BU57" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV57" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW57" s="89"/>
+      <c r="BX57" s="90"/>
+    </row>
+    <row r="58" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B58" s="83">
+        <v>9501196824</v>
+      </c>
+      <c r="C58" s="98">
+        <v>46023</v>
+      </c>
+      <c r="D58" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E58" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="F58" s="92" t="s">
+        <v>156</v>
+      </c>
+      <c r="G58" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H58" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I58" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J58" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K58" s="99">
+        <v>433000</v>
+      </c>
+      <c r="L58" s="102" t="s">
+        <v>207</v>
+      </c>
+      <c r="M58" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N58" s="82"/>
+      <c r="O58" s="83"/>
+      <c r="P58" s="83"/>
+      <c r="Q58" s="84"/>
+      <c r="R58" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="85"/>
+      <c r="T58" s="83"/>
+      <c r="U58" s="83"/>
+      <c r="V58" s="84"/>
+      <c r="W58" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X58" s="87"/>
+      <c r="Y58" s="83"/>
+      <c r="Z58" s="83"/>
+      <c r="AA58" s="84"/>
+      <c r="AB58" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC58" s="87"/>
+      <c r="AD58" s="83"/>
+      <c r="AE58" s="83"/>
+      <c r="AF58" s="84"/>
+      <c r="AG58" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH58" s="87"/>
+      <c r="AI58" s="83"/>
+      <c r="AJ58" s="83"/>
+      <c r="AK58" s="84"/>
+      <c r="AL58" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM58" s="87"/>
+      <c r="AN58" s="83"/>
+      <c r="AO58" s="83"/>
+      <c r="AP58" s="84"/>
+      <c r="AQ58" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR58" s="87"/>
+      <c r="AS58" s="83"/>
+      <c r="AT58" s="83"/>
+      <c r="AU58" s="84"/>
+      <c r="AV58" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW58" s="87"/>
+      <c r="AX58" s="83"/>
+      <c r="AY58" s="83"/>
+      <c r="AZ58" s="84"/>
+      <c r="BA58" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB58" s="87"/>
+      <c r="BC58" s="83"/>
+      <c r="BD58" s="83"/>
+      <c r="BE58" s="84"/>
+      <c r="BF58" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG58" s="87"/>
+      <c r="BH58" s="83"/>
+      <c r="BI58" s="83"/>
+      <c r="BJ58" s="84"/>
+      <c r="BK58" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL58" s="87"/>
+      <c r="BM58" s="83"/>
+      <c r="BN58" s="83"/>
+      <c r="BO58" s="84"/>
+      <c r="BP58" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ58" s="87"/>
+      <c r="BR58" s="83"/>
+      <c r="BS58" s="83"/>
+      <c r="BT58" s="84"/>
+      <c r="BU58" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV58" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW58" s="89"/>
+      <c r="BX58" s="90"/>
+    </row>
+    <row r="59" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="91" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59" s="83">
+        <v>9501196865</v>
+      </c>
+      <c r="C59" s="98">
+        <v>46023</v>
+      </c>
+      <c r="D59" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E59" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" s="92" t="s">
+        <v>158</v>
+      </c>
+      <c r="G59" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H59" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I59" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J59" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K59" s="99">
+        <v>335904</v>
+      </c>
+      <c r="L59" s="102" t="s">
+        <v>208</v>
+      </c>
+      <c r="M59" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N59" s="82"/>
+      <c r="O59" s="83"/>
+      <c r="P59" s="83"/>
+      <c r="Q59" s="84"/>
+      <c r="R59" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="85"/>
+      <c r="T59" s="83"/>
+      <c r="U59" s="83"/>
+      <c r="V59" s="84"/>
+      <c r="W59" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X59" s="87"/>
+      <c r="Y59" s="83"/>
+      <c r="Z59" s="83"/>
+      <c r="AA59" s="84"/>
+      <c r="AB59" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC59" s="87"/>
+      <c r="AD59" s="83"/>
+      <c r="AE59" s="83"/>
+      <c r="AF59" s="84"/>
+      <c r="AG59" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH59" s="87"/>
+      <c r="AI59" s="83"/>
+      <c r="AJ59" s="83"/>
+      <c r="AK59" s="84"/>
+      <c r="AL59" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM59" s="87"/>
+      <c r="AN59" s="83"/>
+      <c r="AO59" s="83"/>
+      <c r="AP59" s="84"/>
+      <c r="AQ59" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR59" s="87"/>
+      <c r="AS59" s="83"/>
+      <c r="AT59" s="83"/>
+      <c r="AU59" s="84"/>
+      <c r="AV59" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW59" s="87"/>
+      <c r="AX59" s="83"/>
+      <c r="AY59" s="83"/>
+      <c r="AZ59" s="84"/>
+      <c r="BA59" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB59" s="87"/>
+      <c r="BC59" s="83"/>
+      <c r="BD59" s="83"/>
+      <c r="BE59" s="84"/>
+      <c r="BF59" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG59" s="87"/>
+      <c r="BH59" s="83"/>
+      <c r="BI59" s="83"/>
+      <c r="BJ59" s="84"/>
+      <c r="BK59" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL59" s="87"/>
+      <c r="BM59" s="83"/>
+      <c r="BN59" s="83"/>
+      <c r="BO59" s="84"/>
+      <c r="BP59" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ59" s="87"/>
+      <c r="BR59" s="83"/>
+      <c r="BS59" s="83"/>
+      <c r="BT59" s="84"/>
+      <c r="BU59" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV59" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW59" s="89"/>
+      <c r="BX59" s="90"/>
+    </row>
+    <row r="60" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B60" s="83">
+        <v>9501158806</v>
+      </c>
+      <c r="C60" s="98">
+        <v>46023</v>
+      </c>
+      <c r="D60" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E60" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="F60" s="92" t="s">
+        <v>159</v>
+      </c>
+      <c r="G60" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H60" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I60" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J60" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K60" s="99">
+        <v>376200</v>
+      </c>
+      <c r="L60" s="102" t="s">
+        <v>209</v>
+      </c>
+      <c r="M60" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N60" s="82"/>
+      <c r="O60" s="83"/>
+      <c r="P60" s="83"/>
+      <c r="Q60" s="84"/>
+      <c r="R60" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S60" s="85"/>
+      <c r="T60" s="83"/>
+      <c r="U60" s="83"/>
+      <c r="V60" s="84"/>
+      <c r="W60" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X60" s="87"/>
+      <c r="Y60" s="83"/>
+      <c r="Z60" s="83"/>
+      <c r="AA60" s="84"/>
+      <c r="AB60" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC60" s="87"/>
+      <c r="AD60" s="83"/>
+      <c r="AE60" s="83"/>
+      <c r="AF60" s="84"/>
+      <c r="AG60" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH60" s="87"/>
+      <c r="AI60" s="83"/>
+      <c r="AJ60" s="83"/>
+      <c r="AK60" s="84"/>
+      <c r="AL60" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM60" s="87"/>
+      <c r="AN60" s="83"/>
+      <c r="AO60" s="83"/>
+      <c r="AP60" s="84"/>
+      <c r="AQ60" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR60" s="87"/>
+      <c r="AS60" s="83"/>
+      <c r="AT60" s="83"/>
+      <c r="AU60" s="84"/>
+      <c r="AV60" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW60" s="87"/>
+      <c r="AX60" s="83"/>
+      <c r="AY60" s="83"/>
+      <c r="AZ60" s="84"/>
+      <c r="BA60" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB60" s="87"/>
+      <c r="BC60" s="83"/>
+      <c r="BD60" s="83"/>
+      <c r="BE60" s="84"/>
+      <c r="BF60" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG60" s="87"/>
+      <c r="BH60" s="83"/>
+      <c r="BI60" s="83"/>
+      <c r="BJ60" s="84"/>
+      <c r="BK60" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL60" s="87"/>
+      <c r="BM60" s="83"/>
+      <c r="BN60" s="83"/>
+      <c r="BO60" s="84"/>
+      <c r="BP60" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ60" s="87"/>
+      <c r="BR60" s="83"/>
+      <c r="BS60" s="83"/>
+      <c r="BT60" s="84"/>
+      <c r="BU60" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV60" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW60" s="89"/>
+      <c r="BX60" s="90"/>
+    </row>
+    <row r="61" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="91" t="s">
+        <v>160</v>
+      </c>
+      <c r="B61" s="83">
+        <v>9501159633</v>
+      </c>
+      <c r="C61" s="98">
+        <v>46023</v>
+      </c>
+      <c r="D61" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E61" s="92" t="s">
+        <v>161</v>
+      </c>
+      <c r="F61" s="92" t="s">
+        <v>162</v>
+      </c>
+      <c r="G61" s="92">
+        <v>61010000</v>
+      </c>
+      <c r="H61" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I61" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J61" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K61" s="99">
+        <v>146493</v>
+      </c>
+      <c r="L61" s="102" t="s">
+        <v>210</v>
+      </c>
+      <c r="M61" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N61" s="82"/>
+      <c r="O61" s="83"/>
+      <c r="P61" s="83"/>
+      <c r="Q61" s="84"/>
+      <c r="R61" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S61" s="85"/>
+      <c r="T61" s="83"/>
+      <c r="U61" s="83"/>
+      <c r="V61" s="84"/>
+      <c r="W61" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X61" s="87"/>
+      <c r="Y61" s="83"/>
+      <c r="Z61" s="83"/>
+      <c r="AA61" s="84"/>
+      <c r="AB61" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC61" s="87"/>
+      <c r="AD61" s="83"/>
+      <c r="AE61" s="83"/>
+      <c r="AF61" s="84"/>
+      <c r="AG61" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH61" s="87"/>
+      <c r="AI61" s="83"/>
+      <c r="AJ61" s="83"/>
+      <c r="AK61" s="84"/>
+      <c r="AL61" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM61" s="87"/>
+      <c r="AN61" s="83"/>
+      <c r="AO61" s="83"/>
+      <c r="AP61" s="84"/>
+      <c r="AQ61" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR61" s="87"/>
+      <c r="AS61" s="83"/>
+      <c r="AT61" s="83"/>
+      <c r="AU61" s="84"/>
+      <c r="AV61" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW61" s="87"/>
+      <c r="AX61" s="83"/>
+      <c r="AY61" s="83"/>
+      <c r="AZ61" s="84"/>
+      <c r="BA61" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB61" s="87"/>
+      <c r="BC61" s="83"/>
+      <c r="BD61" s="83"/>
+      <c r="BE61" s="84"/>
+      <c r="BF61" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG61" s="87"/>
+      <c r="BH61" s="83"/>
+      <c r="BI61" s="83"/>
+      <c r="BJ61" s="84"/>
+      <c r="BK61" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL61" s="87"/>
+      <c r="BM61" s="83"/>
+      <c r="BN61" s="83"/>
+      <c r="BO61" s="84"/>
+      <c r="BP61" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ61" s="87"/>
+      <c r="BR61" s="83"/>
+      <c r="BS61" s="83"/>
+      <c r="BT61" s="84"/>
+      <c r="BU61" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV61" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW61" s="89"/>
+      <c r="BX61" s="90"/>
+    </row>
+    <row r="62" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="91" t="s">
+        <v>163</v>
+      </c>
+      <c r="B62" s="83">
+        <v>9501199250</v>
+      </c>
+      <c r="C62" s="98">
+        <v>46054</v>
+      </c>
+      <c r="D62" s="98">
+        <v>46418</v>
+      </c>
+      <c r="E62" s="92" t="s">
+        <v>139</v>
+      </c>
+      <c r="F62" s="92" t="s">
+        <v>164</v>
+      </c>
+      <c r="G62" s="92">
+        <v>41010100</v>
+      </c>
+      <c r="H62" s="92">
+        <v>7280</v>
+      </c>
+      <c r="I62" s="92" t="s">
+        <v>141</v>
+      </c>
+      <c r="J62" s="92">
+        <v>2662855</v>
+      </c>
+      <c r="K62" s="99">
+        <v>69429</v>
+      </c>
+      <c r="L62" s="102" t="s">
+        <v>211</v>
+      </c>
+      <c r="M62" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="N62" s="82"/>
+      <c r="O62" s="83"/>
+      <c r="P62" s="83"/>
+      <c r="Q62" s="84"/>
+      <c r="R62" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S62" s="85"/>
+      <c r="T62" s="83"/>
+      <c r="U62" s="83"/>
+      <c r="V62" s="84"/>
+      <c r="W62" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X62" s="87"/>
+      <c r="Y62" s="83"/>
+      <c r="Z62" s="83"/>
+      <c r="AA62" s="84"/>
+      <c r="AB62" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC62" s="87"/>
+      <c r="AD62" s="83"/>
+      <c r="AE62" s="83"/>
+      <c r="AF62" s="84"/>
+      <c r="AG62" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH62" s="87"/>
+      <c r="AI62" s="83"/>
+      <c r="AJ62" s="83"/>
+      <c r="AK62" s="84"/>
+      <c r="AL62" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM62" s="87"/>
+      <c r="AN62" s="83"/>
+      <c r="AO62" s="83"/>
+      <c r="AP62" s="84"/>
+      <c r="AQ62" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR62" s="87"/>
+      <c r="AS62" s="83"/>
+      <c r="AT62" s="83"/>
+      <c r="AU62" s="84"/>
+      <c r="AV62" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW62" s="87"/>
+      <c r="AX62" s="83"/>
+      <c r="AY62" s="83"/>
+      <c r="AZ62" s="84"/>
+      <c r="BA62" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB62" s="87"/>
+      <c r="BC62" s="83"/>
+      <c r="BD62" s="83"/>
+      <c r="BE62" s="84"/>
+      <c r="BF62" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG62" s="87"/>
+      <c r="BH62" s="83"/>
+      <c r="BI62" s="83"/>
+      <c r="BJ62" s="84"/>
+      <c r="BK62" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL62" s="87"/>
+      <c r="BM62" s="83"/>
+      <c r="BN62" s="83"/>
+      <c r="BO62" s="84"/>
+      <c r="BP62" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ62" s="87"/>
+      <c r="BR62" s="83"/>
+      <c r="BS62" s="83"/>
+      <c r="BT62" s="84"/>
+      <c r="BU62" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV62" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW62" s="89"/>
+      <c r="BX62" s="90"/>
+    </row>
+    <row r="63" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A63" s="91"/>
+      <c r="B63" s="83"/>
+      <c r="C63" s="92"/>
+      <c r="D63" s="92"/>
+      <c r="E63" s="92"/>
+      <c r="F63" s="92"/>
+      <c r="G63" s="92"/>
+      <c r="H63" s="92"/>
+      <c r="I63" s="92"/>
+      <c r="J63" s="92"/>
+      <c r="K63" s="93"/>
+      <c r="L63" s="92"/>
+      <c r="M63" s="90"/>
+      <c r="N63" s="82"/>
+      <c r="O63" s="83"/>
+      <c r="P63" s="83"/>
+      <c r="Q63" s="84"/>
+      <c r="R63" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S63" s="85"/>
+      <c r="T63" s="83"/>
+      <c r="U63" s="83"/>
+      <c r="V63" s="84"/>
+      <c r="W63" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X63" s="87"/>
+      <c r="Y63" s="83"/>
+      <c r="Z63" s="83"/>
+      <c r="AA63" s="84"/>
+      <c r="AB63" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC63" s="87"/>
+      <c r="AD63" s="83"/>
+      <c r="AE63" s="83"/>
+      <c r="AF63" s="84"/>
+      <c r="AG63" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH63" s="87"/>
+      <c r="AI63" s="83"/>
+      <c r="AJ63" s="83"/>
+      <c r="AK63" s="84"/>
+      <c r="AL63" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM63" s="87"/>
+      <c r="AN63" s="83"/>
+      <c r="AO63" s="83"/>
+      <c r="AP63" s="84"/>
+      <c r="AQ63" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR63" s="87"/>
+      <c r="AS63" s="83"/>
+      <c r="AT63" s="83"/>
+      <c r="AU63" s="84"/>
+      <c r="AV63" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW63" s="87"/>
+      <c r="AX63" s="83"/>
+      <c r="AY63" s="83"/>
+      <c r="AZ63" s="84"/>
+      <c r="BA63" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB63" s="87"/>
+      <c r="BC63" s="83"/>
+      <c r="BD63" s="83"/>
+      <c r="BE63" s="84"/>
+      <c r="BF63" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG63" s="87"/>
+      <c r="BH63" s="83"/>
+      <c r="BI63" s="83"/>
+      <c r="BJ63" s="84"/>
+      <c r="BK63" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL63" s="87"/>
+      <c r="BM63" s="83"/>
+      <c r="BN63" s="83"/>
+      <c r="BO63" s="84"/>
+      <c r="BP63" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ63" s="87"/>
+      <c r="BR63" s="83"/>
+      <c r="BS63" s="83"/>
+      <c r="BT63" s="84"/>
+      <c r="BU63" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV63" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW63" s="89"/>
+      <c r="BX63" s="90"/>
+    </row>
+    <row r="64" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A64" s="91"/>
+      <c r="B64" s="83"/>
+      <c r="C64" s="92"/>
+      <c r="D64" s="92"/>
+      <c r="E64" s="92"/>
+      <c r="F64" s="92"/>
+      <c r="G64" s="92"/>
+      <c r="H64" s="92"/>
+      <c r="I64" s="92"/>
+      <c r="J64" s="92"/>
+      <c r="K64" s="93"/>
+      <c r="L64" s="92"/>
+      <c r="M64" s="90"/>
+      <c r="N64" s="82"/>
+      <c r="O64" s="83"/>
+      <c r="P64" s="83"/>
+      <c r="Q64" s="84"/>
+      <c r="R64" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S64" s="85"/>
+      <c r="T64" s="83"/>
+      <c r="U64" s="83"/>
+      <c r="V64" s="84"/>
+      <c r="W64" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X64" s="87"/>
+      <c r="Y64" s="83"/>
+      <c r="Z64" s="83"/>
+      <c r="AA64" s="84"/>
+      <c r="AB64" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC64" s="87"/>
+      <c r="AD64" s="83"/>
+      <c r="AE64" s="83"/>
+      <c r="AF64" s="84"/>
+      <c r="AG64" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH64" s="87"/>
+      <c r="AI64" s="83"/>
+      <c r="AJ64" s="83"/>
+      <c r="AK64" s="84"/>
+      <c r="AL64" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM64" s="87"/>
+      <c r="AN64" s="83"/>
+      <c r="AO64" s="83"/>
+      <c r="AP64" s="84"/>
+      <c r="AQ64" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR64" s="87"/>
+      <c r="AS64" s="83"/>
+      <c r="AT64" s="83"/>
+      <c r="AU64" s="84"/>
+      <c r="AV64" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW64" s="87"/>
+      <c r="AX64" s="83"/>
+      <c r="AY64" s="83"/>
+      <c r="AZ64" s="84"/>
+      <c r="BA64" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB64" s="87"/>
+      <c r="BC64" s="83"/>
+      <c r="BD64" s="83"/>
+      <c r="BE64" s="84"/>
+      <c r="BF64" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG64" s="87"/>
+      <c r="BH64" s="83"/>
+      <c r="BI64" s="83"/>
+      <c r="BJ64" s="84"/>
+      <c r="BK64" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL64" s="87"/>
+      <c r="BM64" s="83"/>
+      <c r="BN64" s="83"/>
+      <c r="BO64" s="84"/>
+      <c r="BP64" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ64" s="87"/>
+      <c r="BR64" s="83"/>
+      <c r="BS64" s="83"/>
+      <c r="BT64" s="84"/>
+      <c r="BU64" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV64" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW64" s="89"/>
+      <c r="BX64" s="90"/>
+    </row>
+    <row r="65" spans="1:139" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="73"/>
-      <c r="P17" s="73"/>
-      <c r="Q17" s="74"/>
-      <c r="R17" s="74" t="str">
-        <f>IF(OR(P17="",Q17=""),"",P17-Q17)</f>
+      <c r="B65" s="67"/>
+      <c r="C65" s="68"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="69"/>
+      <c r="F65" s="69"/>
+      <c r="G65" s="69"/>
+      <c r="H65" s="69"/>
+      <c r="I65" s="69"/>
+      <c r="J65" s="69"/>
+      <c r="K65" s="70"/>
+      <c r="L65" s="69"/>
+      <c r="M65" s="71"/>
+      <c r="N65" s="72"/>
+      <c r="O65" s="73"/>
+      <c r="P65" s="73"/>
+      <c r="Q65" s="74"/>
+      <c r="R65" s="74" t="str">
+        <f>IF(OR(P65="",Q65=""),"",P65-Q65)</f>
         <v/>
       </c>
-      <c r="S17" s="75"/>
-      <c r="T17" s="73"/>
-      <c r="U17" s="73"/>
-      <c r="V17" s="74"/>
-      <c r="W17" s="76"/>
-      <c r="X17" s="77"/>
-      <c r="Y17" s="73"/>
-      <c r="Z17" s="73"/>
-      <c r="AA17" s="74"/>
-      <c r="AB17" s="76"/>
-      <c r="AC17" s="77"/>
-      <c r="AD17" s="73"/>
-      <c r="AE17" s="73"/>
-      <c r="AF17" s="74"/>
-      <c r="AG17" s="76" t="str">
-        <f t="shared" ref="AG17" si="0">IF(OR(AE17="",AF17=""),"",AE17-AF17)</f>
+      <c r="S65" s="75"/>
+      <c r="T65" s="73"/>
+      <c r="U65" s="73"/>
+      <c r="V65" s="74"/>
+      <c r="W65" s="76"/>
+      <c r="X65" s="77"/>
+      <c r="Y65" s="73"/>
+      <c r="Z65" s="73"/>
+      <c r="AA65" s="74"/>
+      <c r="AB65" s="76"/>
+      <c r="AC65" s="77"/>
+      <c r="AD65" s="73"/>
+      <c r="AE65" s="73"/>
+      <c r="AF65" s="74"/>
+      <c r="AG65" s="76" t="str">
+        <f t="shared" ref="AG65" si="36">IF(OR(AE65="",AF65=""),"",AE65-AF65)</f>
         <v/>
       </c>
-      <c r="AH17" s="77"/>
-      <c r="AI17" s="73"/>
-      <c r="AJ17" s="73"/>
-      <c r="AK17" s="74"/>
-      <c r="AL17" s="76" t="str">
-        <f t="shared" ref="AL17" si="1">IF(OR(AJ17="",AK17=""),"",AJ17-AK17)</f>
+      <c r="AH65" s="77"/>
+      <c r="AI65" s="73"/>
+      <c r="AJ65" s="73"/>
+      <c r="AK65" s="74"/>
+      <c r="AL65" s="76" t="str">
+        <f t="shared" ref="AL65" si="37">IF(OR(AJ65="",AK65=""),"",AJ65-AK65)</f>
         <v/>
       </c>
-      <c r="AM17" s="77"/>
-      <c r="AN17" s="73"/>
-      <c r="AO17" s="73"/>
-      <c r="AP17" s="74"/>
-      <c r="AQ17" s="76" t="str">
-        <f t="shared" ref="AQ17" si="2">IF(OR(AO17="",AP17=""),"",AO17-AP17)</f>
+      <c r="AM65" s="77"/>
+      <c r="AN65" s="73"/>
+      <c r="AO65" s="73"/>
+      <c r="AP65" s="74"/>
+      <c r="AQ65" s="76" t="str">
+        <f t="shared" ref="AQ65" si="38">IF(OR(AO65="",AP65=""),"",AO65-AP65)</f>
         <v/>
       </c>
-      <c r="AR17" s="77"/>
-      <c r="AS17" s="73"/>
-      <c r="AT17" s="73"/>
-      <c r="AU17" s="74"/>
-      <c r="AV17" s="76" t="str">
-        <f t="shared" ref="AV17" si="3">IF(OR(AT17="",AU17=""),"",AT17-AU17)</f>
+      <c r="AR65" s="77"/>
+      <c r="AS65" s="73"/>
+      <c r="AT65" s="73"/>
+      <c r="AU65" s="74"/>
+      <c r="AV65" s="76" t="str">
+        <f t="shared" ref="AV65" si="39">IF(OR(AT65="",AU65=""),"",AT65-AU65)</f>
         <v/>
       </c>
-      <c r="AW17" s="77"/>
-      <c r="AX17" s="73"/>
-      <c r="AY17" s="73"/>
-      <c r="AZ17" s="74"/>
-      <c r="BA17" s="76" t="str">
-        <f t="shared" ref="BA17" si="4">IF(OR(AY17="",AZ17=""),"",AY17-AZ17)</f>
+      <c r="AW65" s="77"/>
+      <c r="AX65" s="73"/>
+      <c r="AY65" s="73"/>
+      <c r="AZ65" s="74"/>
+      <c r="BA65" s="76" t="str">
+        <f t="shared" ref="BA65" si="40">IF(OR(AY65="",AZ65=""),"",AY65-AZ65)</f>
         <v/>
       </c>
-      <c r="BB17" s="77"/>
-      <c r="BC17" s="73"/>
-      <c r="BD17" s="73"/>
-      <c r="BE17" s="74"/>
-      <c r="BF17" s="76" t="str">
-        <f t="shared" ref="BF17" si="5">IF(OR(BD17="",BE17=""),"",BD17-BE17)</f>
+      <c r="BB65" s="77"/>
+      <c r="BC65" s="73"/>
+      <c r="BD65" s="73"/>
+      <c r="BE65" s="74"/>
+      <c r="BF65" s="76" t="str">
+        <f t="shared" ref="BF65" si="41">IF(OR(BD65="",BE65=""),"",BD65-BE65)</f>
         <v/>
       </c>
-      <c r="BG17" s="77"/>
-      <c r="BH17" s="73"/>
-      <c r="BI17" s="73"/>
-      <c r="BJ17" s="74"/>
-      <c r="BK17" s="76" t="str">
-        <f t="shared" ref="BK17" si="6">IF(OR(BI17="",BJ17=""),"",BI17-BJ17)</f>
+      <c r="BG65" s="77"/>
+      <c r="BH65" s="73"/>
+      <c r="BI65" s="73"/>
+      <c r="BJ65" s="74"/>
+      <c r="BK65" s="76" t="str">
+        <f t="shared" ref="BK65" si="42">IF(OR(BI65="",BJ65=""),"",BI65-BJ65)</f>
         <v/>
       </c>
-      <c r="BL17" s="77"/>
-      <c r="BM17" s="73"/>
-      <c r="BN17" s="73"/>
-      <c r="BO17" s="74"/>
-      <c r="BP17" s="76" t="str">
-        <f t="shared" ref="BP17" si="7">IF(OR(BN17="",BO17=""),"",BN17-BO17)</f>
+      <c r="BL65" s="77"/>
+      <c r="BM65" s="73"/>
+      <c r="BN65" s="73"/>
+      <c r="BO65" s="74"/>
+      <c r="BP65" s="76" t="str">
+        <f t="shared" ref="BP65" si="43">IF(OR(BN65="",BO65=""),"",BN65-BO65)</f>
         <v/>
       </c>
-      <c r="BQ17" s="77"/>
-      <c r="BR17" s="73"/>
-      <c r="BS17" s="73"/>
-      <c r="BT17" s="74"/>
-      <c r="BU17" s="76" t="str">
-        <f t="shared" ref="BU17" si="8">IF(OR(BS17="",BT17=""),"",BS17-BT17)</f>
+      <c r="BQ65" s="77"/>
+      <c r="BR65" s="73"/>
+      <c r="BS65" s="73"/>
+      <c r="BT65" s="74"/>
+      <c r="BU65" s="76" t="str">
+        <f t="shared" ref="BU65" si="44">IF(OR(BS65="",BT65=""),"",BS65-BT65)</f>
         <v/>
       </c>
-      <c r="BV17" s="75">
-        <f t="shared" ref="BV17" si="9">SUM(IF(Q17&lt;&gt;"",Q17,IF(P17&lt;&gt;"",P17,O17)),IF(V17&lt;&gt;"",V17,IF(U17&lt;&gt;"",U17,T17)),IF(AA17&lt;&gt;"",AA17,IF(Z17&lt;&gt;"",Z17,Y17)),IF(AF17&lt;&gt;"",AF17,IF(AE17&lt;&gt;"",AE17,AD17)),IF(AK17&lt;&gt;"",AK17,IF(AJ17&lt;&gt;"",AJ17,AI17)),IF(AP17&lt;&gt;"",AP17,IF(AO17&lt;&gt;"",AO17,AN17)),IF(AU17&lt;&gt;"",AU17,IF(AT17&lt;&gt;"",AT17,AS17)),IF(AZ17&lt;&gt;"",AZ17,IF(AY17&lt;&gt;"",AY17,AX17)),IF(BE17&lt;&gt;"",BE17,IF(BD17&lt;&gt;"",BD17,BC17)),IF(BJ17&lt;&gt;"",BJ17,IF(BI17&lt;&gt;"",BI17,BH17)),IF(BO17&lt;&gt;"",BO17,IF(BN17&lt;&gt;"",BN17,BM17)),IF(BT17&lt;&gt;"",BT17,IF(BS17&lt;&gt;"",BS17,BR17)))</f>
-        <v>0</v>
-      </c>
-      <c r="BW17" s="53"/>
-      <c r="BX17" s="49"/>
-      <c r="BY17"/>
-      <c r="BZ17"/>
-      <c r="CA17"/>
-      <c r="CB17"/>
-      <c r="CC17"/>
-      <c r="CD17"/>
-      <c r="CE17"/>
-      <c r="CF17"/>
-      <c r="CG17"/>
-      <c r="CH17"/>
-      <c r="CI17"/>
-      <c r="CJ17"/>
-      <c r="CK17"/>
-      <c r="CL17"/>
-      <c r="CM17"/>
-      <c r="CN17"/>
-      <c r="CO17"/>
-      <c r="CP17"/>
-      <c r="CQ17"/>
-      <c r="CR17"/>
-      <c r="CS17"/>
-      <c r="CT17"/>
-      <c r="CU17"/>
-      <c r="CV17"/>
-      <c r="CW17"/>
-      <c r="CX17"/>
-      <c r="CY17"/>
-      <c r="CZ17"/>
-      <c r="DA17"/>
-      <c r="DB17"/>
-      <c r="DC17"/>
-      <c r="DD17"/>
-      <c r="DE17"/>
-      <c r="DF17"/>
-      <c r="DG17"/>
-      <c r="DH17"/>
-      <c r="DI17"/>
-      <c r="DJ17"/>
-      <c r="DK17"/>
-      <c r="DL17"/>
-      <c r="DM17"/>
-      <c r="DN17"/>
-      <c r="DO17"/>
-      <c r="DP17"/>
-      <c r="DQ17"/>
-      <c r="DR17"/>
-      <c r="DS17"/>
-      <c r="DT17"/>
-      <c r="DU17"/>
-      <c r="DV17"/>
-      <c r="DW17"/>
-      <c r="DX17"/>
-      <c r="DY17"/>
-      <c r="DZ17"/>
-      <c r="EA17"/>
-      <c r="EB17"/>
-      <c r="EC17"/>
-      <c r="ED17"/>
-      <c r="EE17"/>
-      <c r="EF17"/>
-      <c r="EG17"/>
-      <c r="EH17"/>
-      <c r="EI17"/>
+      <c r="BV65" s="75"/>
+      <c r="BW65" s="53"/>
+      <c r="BX65" s="49"/>
+      <c r="BY65"/>
+      <c r="BZ65"/>
+      <c r="CA65"/>
+      <c r="CB65"/>
+      <c r="CC65"/>
+      <c r="CD65"/>
+      <c r="CE65"/>
+      <c r="CF65"/>
+      <c r="CG65"/>
+      <c r="CH65"/>
+      <c r="CI65"/>
+      <c r="CJ65"/>
+      <c r="CK65"/>
+      <c r="CL65"/>
+      <c r="CM65"/>
+      <c r="CN65"/>
+      <c r="CO65"/>
+      <c r="CP65"/>
+      <c r="CQ65"/>
+      <c r="CR65"/>
+      <c r="CS65"/>
+      <c r="CT65"/>
+      <c r="CU65"/>
+      <c r="CV65"/>
+      <c r="CW65"/>
+      <c r="CX65"/>
+      <c r="CY65"/>
+      <c r="CZ65"/>
+      <c r="DA65"/>
+      <c r="DB65"/>
+      <c r="DC65"/>
+      <c r="DD65"/>
+      <c r="DE65"/>
+      <c r="DF65"/>
+      <c r="DG65"/>
+      <c r="DH65"/>
+      <c r="DI65"/>
+      <c r="DJ65"/>
+      <c r="DK65"/>
+      <c r="DL65"/>
+      <c r="DM65"/>
+      <c r="DN65"/>
+      <c r="DO65"/>
+      <c r="DP65"/>
+      <c r="DQ65"/>
+      <c r="DR65"/>
+      <c r="DS65"/>
+      <c r="DT65"/>
+      <c r="DU65"/>
+      <c r="DV65"/>
+      <c r="DW65"/>
+      <c r="DX65"/>
+      <c r="DY65"/>
+      <c r="DZ65"/>
+      <c r="EA65"/>
+      <c r="EB65"/>
+      <c r="EC65"/>
+      <c r="ED65"/>
+      <c r="EE65"/>
+      <c r="EF65"/>
+      <c r="EG65"/>
+      <c r="EH65"/>
+      <c r="EI65"/>
     </row>
-    <row r="18" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="66" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>96</v>
       </c>
-      <c r="AA18" s="3"/>
+      <c r="AA66" s="3"/>
+      <c r="BV66" s="95"/>
     </row>
   </sheetData>
   <autoFilter ref="A14:BY18" xr:uid="{177F1DEB-197D-49C6-A2E3-152C1AC7B373}"/>
@@ -3163,12 +9696,12 @@
     <mergeCell ref="N13:R13"/>
     <mergeCell ref="X13:AB13"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q17 V17 AA17 AF17 AK17 AP17 AU17 AZ17 BE17 BJ17 BO17 BT17">
+  <conditionalFormatting sqref="Q65 V65 AA65 AF65 AK65 AP65 AU65 AZ65 BE65 BJ65 BO65 BT65">
     <cfRule type="expression" dxfId="2" priority="8">
-      <formula>IF(AND(P17&gt;0,Q17=0),TRUE,FALSE)</formula>
+      <formula>IF(AND(P65&gt;0,Q65=0),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT10 V17:X17 AB17:AC17 AG17:AH17 AL17:AM17 AQ17:AR17 AV17:AW17 BA17:BB17 BF17:BG17 BK17:BL17 BP17:BQ17 BU17">
+  <conditionalFormatting sqref="BT10 V65:X65 AB65:AC65 AG65:AH65 AL65:AM65 AQ65:AR65 AV65:AW65 BA65:BB65 BF65:BG65 BK65:BL65 BP65:BQ65 BU65">
     <cfRule type="expression" dxfId="1" priority="9">
       <formula>IF(AND(U10&lt;&gt;"",V10="",TODAY()&gt;DATE(YEAR(TODAY()),MONTH(DATEVALUE("1-"&amp;LEFT(#REF!,3)&amp;"-1900")),20)),TRUE,FALSE)</formula>
     </cfRule>

--- a/data/templates/financial_template_v2_2026.xlsx
+++ b/data/templates/financial_template_v2_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pfizer-my.sharepoint.com/personal/hoveyo_pfizer_com/Documents/financial-automation-project/data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="8_{783183DD-73AE-4283-AD85-EEFD805851D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74C06533-0487-4308-94B4-599F809304B1}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="8_{783183DD-73AE-4283-AD85-EEFD805851D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67E8D884-7862-41E5-98D0-4F52412DF91E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" tabRatio="590" xr2:uid="{0996C49B-04E6-42AE-AA83-2F64BE89A626}"/>
   </bookViews>
@@ -1807,6 +1807,12 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1815,21 +1821,6 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1842,6 +1833,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2315,10 +2315,10 @@
     </row>
     <row r="8" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="112"/>
+      <c r="B9" s="106"/>
       <c r="D9" s="55" t="s">
         <v>8</v>
       </c>
@@ -2364,106 +2364,106 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="44"/>
-      <c r="L11" s="113" t="s">
+      <c r="L11" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="114"/>
-      <c r="N11" s="105" cm="1">
+      <c r="M11" s="111"/>
+      <c r="N11" s="107" cm="1">
         <f t="array" ref="N11">SUM(Q15:Q65)+SUM(_xlfn._xlws.FILTER(P15:P65,Q15:Q65=""))+SUM(_xlfn._xlws.FILTER(O15:O65,(P15:P65="")*(Q15:Q65="")))+SUMIFS(R15:R65,Q15:Q65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(N15:N65)</f>
         <v>0</v>
       </c>
-      <c r="O11" s="106"/>
-      <c r="P11" s="106"/>
-      <c r="Q11" s="106"/>
-      <c r="R11" s="107"/>
-      <c r="S11" s="105" cm="1">
+      <c r="O11" s="108"/>
+      <c r="P11" s="108"/>
+      <c r="Q11" s="108"/>
+      <c r="R11" s="109"/>
+      <c r="S11" s="107" cm="1">
         <f t="array" ref="S11">SUM(V15:V65)+SUM(_xlfn._xlws.FILTER(U15:U65,V15:V65=""))+SUM(_xlfn._xlws.FILTER(T15:T65,(U15:U65="")*(V15:V65="")))+SUMIFS(W15:W65,V15:V65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(S15:S65)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="106"/>
-      <c r="U11" s="106"/>
-      <c r="V11" s="106"/>
-      <c r="W11" s="107"/>
-      <c r="X11" s="105" cm="1">
+      <c r="T11" s="108"/>
+      <c r="U11" s="108"/>
+      <c r="V11" s="108"/>
+      <c r="W11" s="109"/>
+      <c r="X11" s="107" cm="1">
         <f t="array" ref="X11">SUM(AA15:AA65)+SUM(_xlfn._xlws.FILTER(Z15:Z65,AA15:AA65=""))+SUM(_xlfn._xlws.FILTER(Y15:Y65,(Z15:Z65="")*(AA15:AA65="")))+SUMIFS(AB15:AB65,AA15:AA65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(X15:X65)</f>
         <v>0</v>
       </c>
-      <c r="Y11" s="106"/>
-      <c r="Z11" s="106"/>
-      <c r="AA11" s="106"/>
-      <c r="AB11" s="107"/>
-      <c r="AC11" s="105" cm="1">
+      <c r="Y11" s="108"/>
+      <c r="Z11" s="108"/>
+      <c r="AA11" s="108"/>
+      <c r="AB11" s="109"/>
+      <c r="AC11" s="107" cm="1">
         <f t="array" ref="AC11">SUM(AF15:AF65)+SUM(_xlfn._xlws.FILTER(AE15:AE65,AF15:AF65=""))+SUM(_xlfn._xlws.FILTER(AD15:AD65,(AE15:AE65="")*(AF15:AF65="")))+SUMIFS(AG15:AG65,AF15:AF65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AC15:AC65)</f>
         <v>0</v>
       </c>
-      <c r="AD11" s="106"/>
-      <c r="AE11" s="106"/>
-      <c r="AF11" s="106"/>
-      <c r="AG11" s="107"/>
-      <c r="AH11" s="105" cm="1">
+      <c r="AD11" s="108"/>
+      <c r="AE11" s="108"/>
+      <c r="AF11" s="108"/>
+      <c r="AG11" s="109"/>
+      <c r="AH11" s="107" cm="1">
         <f t="array" ref="AH11">SUM(AK15:AK65)+SUM(_xlfn._xlws.FILTER(AJ15:AJ65,AK15:AK65=""))+SUM(_xlfn._xlws.FILTER(AI15:AI65,(AJ15:AJ65="")*(AK15:AK65="")))+SUMIFS(AL15:AL65,AK15:AK65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AH15:AH65)</f>
         <v>0</v>
       </c>
-      <c r="AI11" s="106"/>
-      <c r="AJ11" s="106"/>
-      <c r="AK11" s="106"/>
-      <c r="AL11" s="107"/>
-      <c r="AM11" s="105" cm="1">
+      <c r="AI11" s="108"/>
+      <c r="AJ11" s="108"/>
+      <c r="AK11" s="108"/>
+      <c r="AL11" s="109"/>
+      <c r="AM11" s="107" cm="1">
         <f t="array" ref="AM11">SUM(AP15:AP65)+SUM(_xlfn._xlws.FILTER(AO15:AO65,AP15:AP65=""))+SUM(_xlfn._xlws.FILTER(AN15:AN65,(AO15:AO65="")*(AP15:AP65="")))+SUMIFS(AQ15:AQ65,AP15:AP65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AM15:AM65)</f>
         <v>0</v>
       </c>
-      <c r="AN11" s="106"/>
-      <c r="AO11" s="106"/>
-      <c r="AP11" s="106"/>
-      <c r="AQ11" s="107"/>
-      <c r="AR11" s="105" cm="1">
+      <c r="AN11" s="108"/>
+      <c r="AO11" s="108"/>
+      <c r="AP11" s="108"/>
+      <c r="AQ11" s="109"/>
+      <c r="AR11" s="107" cm="1">
         <f t="array" ref="AR11">SUM(AU15:AU65)+SUM(_xlfn._xlws.FILTER(AT15:AT65,AU15:AU65=""))+SUM(_xlfn._xlws.FILTER(AS15:AS65,(AT15:AT65="")*(AU15:AU65="")))+SUMIFS(AV15:AV65,AU15:AU65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AR15:AR65)</f>
         <v>0</v>
       </c>
-      <c r="AS11" s="106"/>
-      <c r="AT11" s="106"/>
-      <c r="AU11" s="106"/>
-      <c r="AV11" s="107"/>
-      <c r="AW11" s="105" cm="1">
+      <c r="AS11" s="108"/>
+      <c r="AT11" s="108"/>
+      <c r="AU11" s="108"/>
+      <c r="AV11" s="109"/>
+      <c r="AW11" s="107" cm="1">
         <f t="array" ref="AW11">SUM(AZ15:AZ65)+SUM(_xlfn._xlws.FILTER(AY15:AY65,AZ15:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX15:AX65,(AY15:AY65="")*(AZ15:AZ65="")))+SUMIFS(BA15:BA65,AZ15:AZ65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AW15:AW65)</f>
         <v>0</v>
       </c>
-      <c r="AX11" s="106"/>
-      <c r="AY11" s="106"/>
-      <c r="AZ11" s="106"/>
-      <c r="BA11" s="107"/>
-      <c r="BB11" s="105" cm="1">
+      <c r="AX11" s="108"/>
+      <c r="AY11" s="108"/>
+      <c r="AZ11" s="108"/>
+      <c r="BA11" s="109"/>
+      <c r="BB11" s="107" cm="1">
         <f t="array" ref="BB11">SUM(BE15:BE65)+SUM(_xlfn._xlws.FILTER(BD15:BD65,BE15:BE65=""))+SUM(_xlfn._xlws.FILTER(BC15:BC65,(BD15:BD65="")*(BE15:BE65="")))+SUMIFS(BF15:BF65,BE15:BE65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BB15:BB65)</f>
         <v>0</v>
       </c>
-      <c r="BC11" s="106"/>
-      <c r="BD11" s="106"/>
-      <c r="BE11" s="106"/>
-      <c r="BF11" s="107"/>
-      <c r="BG11" s="105" cm="1">
+      <c r="BC11" s="108"/>
+      <c r="BD11" s="108"/>
+      <c r="BE11" s="108"/>
+      <c r="BF11" s="109"/>
+      <c r="BG11" s="107" cm="1">
         <f t="array" ref="BG11">SUM(BJ15:BJ65)+SUM(_xlfn._xlws.FILTER(BI15:BI65,BJ15:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH15:BH65,(BI15:BI65="")*(BJ15:BJ65="")))+SUMIFS(BK15:BK65,BJ15:BJ65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BG15:BG65)</f>
         <v>0</v>
       </c>
-      <c r="BH11" s="106"/>
-      <c r="BI11" s="106"/>
-      <c r="BJ11" s="106"/>
-      <c r="BK11" s="107"/>
-      <c r="BL11" s="105" cm="1">
+      <c r="BH11" s="108"/>
+      <c r="BI11" s="108"/>
+      <c r="BJ11" s="108"/>
+      <c r="BK11" s="109"/>
+      <c r="BL11" s="107" cm="1">
         <f t="array" ref="BL11">SUM(BO15:BO65)+SUM(_xlfn._xlws.FILTER(BN15:BN65,BO15:BO65=""))+SUM(_xlfn._xlws.FILTER(BM15:BM65,(BN15:BN65="")*(BO15:BO65="")))+SUMIFS(BP15:BP65,BO15:BO65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BL15:BL65)</f>
         <v>0</v>
       </c>
-      <c r="BM11" s="106"/>
-      <c r="BN11" s="106"/>
-      <c r="BO11" s="106"/>
-      <c r="BP11" s="107"/>
-      <c r="BQ11" s="105" cm="1">
+      <c r="BM11" s="108"/>
+      <c r="BN11" s="108"/>
+      <c r="BO11" s="108"/>
+      <c r="BP11" s="109"/>
+      <c r="BQ11" s="107" cm="1">
         <f t="array" ref="BQ11">SUM(BT15:BT65)+SUM(_xlfn._xlws.FILTER(BS15:BS65,BT15:BT65=""))+SUM(_xlfn._xlws.FILTER(BR15:BR65,(BS15:BS65="")*(BT15:BT65="")))+SUMIFS(BU15:BU65,BT15:BT65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BQ15:BQ65)</f>
         <v>0</v>
       </c>
-      <c r="BR11" s="106"/>
-      <c r="BS11" s="106"/>
-      <c r="BT11" s="106"/>
-      <c r="BU11" s="107"/>
+      <c r="BR11" s="108"/>
+      <c r="BS11" s="108"/>
+      <c r="BT11" s="108"/>
+      <c r="BU11" s="109"/>
       <c r="BV11" s="4" t="s">
         <v>14</v>
       </c>
@@ -2489,106 +2489,106 @@
       <c r="K12" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="L12" s="115" t="s">
+      <c r="L12" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="116"/>
-      <c r="N12" s="105" cm="1">
+      <c r="M12" s="113"/>
+      <c r="N12" s="107" cm="1">
         <f t="array" ref="N12">SUM(Q15:Q65)+SUM(_xlfn._xlws.FILTER(P15:P65,Q15:Q65=""))+SUM(_xlfn._xlws.FILTER(O15:O65,(P15:P65="")*(Q15:Q65="")))</f>
         <v>0</v>
       </c>
-      <c r="O12" s="106"/>
-      <c r="P12" s="106"/>
-      <c r="Q12" s="106"/>
-      <c r="R12" s="107"/>
-      <c r="S12" s="105" cm="1">
+      <c r="O12" s="108"/>
+      <c r="P12" s="108"/>
+      <c r="Q12" s="108"/>
+      <c r="R12" s="109"/>
+      <c r="S12" s="107" cm="1">
         <f t="array" ref="S12">SUM(V15:V65)+SUM(_xlfn._xlws.FILTER(U15:U65,V15:V65=""))+SUM(_xlfn._xlws.FILTER(T15:T65,(U15:U65="")*(V15:V65="")))</f>
         <v>0</v>
       </c>
-      <c r="T12" s="106"/>
-      <c r="U12" s="106"/>
-      <c r="V12" s="106"/>
-      <c r="W12" s="107"/>
-      <c r="X12" s="105" cm="1">
+      <c r="T12" s="108"/>
+      <c r="U12" s="108"/>
+      <c r="V12" s="108"/>
+      <c r="W12" s="109"/>
+      <c r="X12" s="107" cm="1">
         <f t="array" ref="X12">SUM(AA15:AA65)+SUM(_xlfn._xlws.FILTER(Z15:Z65,AA15:AA65=""))+SUM(_xlfn._xlws.FILTER(Y15:Y65,(Z15:Z65="")*(AA15:AA65="")))</f>
         <v>0</v>
       </c>
-      <c r="Y12" s="106"/>
-      <c r="Z12" s="106"/>
-      <c r="AA12" s="106"/>
-      <c r="AB12" s="107"/>
-      <c r="AC12" s="105" cm="1">
+      <c r="Y12" s="108"/>
+      <c r="Z12" s="108"/>
+      <c r="AA12" s="108"/>
+      <c r="AB12" s="109"/>
+      <c r="AC12" s="107" cm="1">
         <f t="array" ref="AC12">SUM(AF15:AF65)+SUM(_xlfn._xlws.FILTER(AE15:AE65,AF15:AF65=""))+SUM(_xlfn._xlws.FILTER(AD15:AD65,(AE15:AE65="")*(AF15:AF65="")))</f>
         <v>0</v>
       </c>
-      <c r="AD12" s="106"/>
-      <c r="AE12" s="106"/>
-      <c r="AF12" s="106"/>
-      <c r="AG12" s="107"/>
-      <c r="AH12" s="105" cm="1">
+      <c r="AD12" s="108"/>
+      <c r="AE12" s="108"/>
+      <c r="AF12" s="108"/>
+      <c r="AG12" s="109"/>
+      <c r="AH12" s="107" cm="1">
         <f t="array" ref="AH12">SUM(AK15:AK65)+SUM(_xlfn._xlws.FILTER(AJ15:AJ65,AK15:AK65=""))+SUM(_xlfn._xlws.FILTER(AI15:AI65,(AJ15:AJ65="")*(AK15:AK65="")))</f>
         <v>0</v>
       </c>
-      <c r="AI12" s="106"/>
-      <c r="AJ12" s="106"/>
-      <c r="AK12" s="106"/>
-      <c r="AL12" s="107"/>
-      <c r="AM12" s="105" cm="1">
+      <c r="AI12" s="108"/>
+      <c r="AJ12" s="108"/>
+      <c r="AK12" s="108"/>
+      <c r="AL12" s="109"/>
+      <c r="AM12" s="107" cm="1">
         <f t="array" ref="AM12">SUM(AP15:AP65)+SUM(_xlfn._xlws.FILTER(AO15:AO65,AP15:AP65=""))+SUM(_xlfn._xlws.FILTER(AN15:AN65,(AO15:AO65="")*(AP15:AP65="")))</f>
         <v>0</v>
       </c>
-      <c r="AN12" s="106"/>
-      <c r="AO12" s="106"/>
-      <c r="AP12" s="106"/>
-      <c r="AQ12" s="107"/>
-      <c r="AR12" s="105" cm="1">
+      <c r="AN12" s="108"/>
+      <c r="AO12" s="108"/>
+      <c r="AP12" s="108"/>
+      <c r="AQ12" s="109"/>
+      <c r="AR12" s="107" cm="1">
         <f t="array" ref="AR12">SUM(AU15:AU65)+SUM(_xlfn._xlws.FILTER(AT15:AT65,AU15:AU65=""))+SUM(_xlfn._xlws.FILTER(AS15:AS65,(AT15:AT65="")*(AU15:AU65="")))</f>
         <v>0</v>
       </c>
-      <c r="AS12" s="106"/>
-      <c r="AT12" s="106"/>
-      <c r="AU12" s="106"/>
-      <c r="AV12" s="107"/>
-      <c r="AW12" s="105" cm="1">
+      <c r="AS12" s="108"/>
+      <c r="AT12" s="108"/>
+      <c r="AU12" s="108"/>
+      <c r="AV12" s="109"/>
+      <c r="AW12" s="107" cm="1">
         <f t="array" ref="AW12">SUM(AZ15:AZ65)+SUM(_xlfn._xlws.FILTER(AY15:AY65,AZ15:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX15:AX65,(AY15:AY65="")*(AZ15:AZ65="")))</f>
         <v>0</v>
       </c>
-      <c r="AX12" s="106"/>
-      <c r="AY12" s="106"/>
-      <c r="AZ12" s="106"/>
-      <c r="BA12" s="107"/>
-      <c r="BB12" s="105" cm="1">
+      <c r="AX12" s="108"/>
+      <c r="AY12" s="108"/>
+      <c r="AZ12" s="108"/>
+      <c r="BA12" s="109"/>
+      <c r="BB12" s="107" cm="1">
         <f t="array" ref="BB12">SUM(BE15:BE65)+SUM(_xlfn._xlws.FILTER(BD15:BD65,BE15:BE65=""))+SUM(_xlfn._xlws.FILTER(BC15:BC65,(BD15:BD65="")*(BE15:BE65="")))</f>
         <v>0</v>
       </c>
-      <c r="BC12" s="106"/>
-      <c r="BD12" s="106"/>
-      <c r="BE12" s="106"/>
-      <c r="BF12" s="107"/>
-      <c r="BG12" s="105" cm="1">
+      <c r="BC12" s="108"/>
+      <c r="BD12" s="108"/>
+      <c r="BE12" s="108"/>
+      <c r="BF12" s="109"/>
+      <c r="BG12" s="107" cm="1">
         <f t="array" ref="BG12">SUM(BJ15:BJ65)+SUM(_xlfn._xlws.FILTER(BI15:BI65,BJ15:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH15:BH65,(BI15:BI65="")*(BJ15:BJ65="")))</f>
         <v>0</v>
       </c>
-      <c r="BH12" s="106"/>
-      <c r="BI12" s="106"/>
-      <c r="BJ12" s="106"/>
-      <c r="BK12" s="107"/>
-      <c r="BL12" s="105" cm="1">
+      <c r="BH12" s="108"/>
+      <c r="BI12" s="108"/>
+      <c r="BJ12" s="108"/>
+      <c r="BK12" s="109"/>
+      <c r="BL12" s="107" cm="1">
         <f t="array" ref="BL12">SUM(BO15:BO65)+SUM(_xlfn._xlws.FILTER(BN15:BN65,BO15:BO65=""))+SUM(_xlfn._xlws.FILTER(BM15:BM65,(BN15:BN65="")*(BO15:BO65="")))</f>
         <v>0</v>
       </c>
-      <c r="BM12" s="106"/>
-      <c r="BN12" s="106"/>
-      <c r="BO12" s="106"/>
-      <c r="BP12" s="107"/>
-      <c r="BQ12" s="105" cm="1">
+      <c r="BM12" s="108"/>
+      <c r="BN12" s="108"/>
+      <c r="BO12" s="108"/>
+      <c r="BP12" s="109"/>
+      <c r="BQ12" s="107" cm="1">
         <f t="array" ref="BQ12">SUM(BT15:BT65)+SUM(_xlfn._xlws.FILTER(BS15:BS65,BT15:BT65=""))+SUM(_xlfn._xlws.FILTER(BR15:BR65,(BS15:BS65="")*(BT15:BT65="")))</f>
         <v>0</v>
       </c>
-      <c r="BR12" s="106"/>
-      <c r="BS12" s="106"/>
-      <c r="BT12" s="106"/>
-      <c r="BU12" s="107"/>
+      <c r="BR12" s="108"/>
+      <c r="BS12" s="108"/>
+      <c r="BT12" s="108"/>
+      <c r="BU12" s="109"/>
       <c r="BV12" s="4"/>
       <c r="BW12" s="5"/>
     </row>
@@ -2603,116 +2603,116 @@
         <f>SUBTOTAL(9,K15:K16)</f>
         <v>190781</v>
       </c>
-      <c r="L13" s="115" t="s">
+      <c r="L13" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="M13" s="116"/>
-      <c r="N13" s="108">
+      <c r="M13" s="113"/>
+      <c r="N13" s="114">
         <v>46053</v>
       </c>
-      <c r="O13" s="109" t="s">
+      <c r="O13" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="P13" s="109"/>
-      <c r="Q13" s="109"/>
-      <c r="R13" s="109"/>
-      <c r="S13" s="108">
+      <c r="P13" s="115"/>
+      <c r="Q13" s="115"/>
+      <c r="R13" s="115"/>
+      <c r="S13" s="114">
         <v>46054</v>
       </c>
-      <c r="T13" s="109"/>
-      <c r="U13" s="109"/>
-      <c r="V13" s="109"/>
-      <c r="W13" s="110"/>
-      <c r="X13" s="108">
+      <c r="T13" s="115"/>
+      <c r="U13" s="115"/>
+      <c r="V13" s="115"/>
+      <c r="W13" s="116"/>
+      <c r="X13" s="114">
         <v>46112</v>
       </c>
-      <c r="Y13" s="109" t="s">
+      <c r="Y13" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="Z13" s="109"/>
-      <c r="AA13" s="109"/>
-      <c r="AB13" s="110"/>
-      <c r="AC13" s="108">
+      <c r="Z13" s="115"/>
+      <c r="AA13" s="115"/>
+      <c r="AB13" s="116"/>
+      <c r="AC13" s="114">
         <v>46142</v>
       </c>
-      <c r="AD13" s="109" t="s">
+      <c r="AD13" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="AE13" s="109"/>
-      <c r="AF13" s="109"/>
-      <c r="AG13" s="110"/>
-      <c r="AH13" s="108">
+      <c r="AE13" s="115"/>
+      <c r="AF13" s="115"/>
+      <c r="AG13" s="116"/>
+      <c r="AH13" s="114">
         <v>46173</v>
       </c>
-      <c r="AI13" s="109" t="s">
+      <c r="AI13" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="AJ13" s="109"/>
-      <c r="AK13" s="109"/>
-      <c r="AL13" s="110"/>
-      <c r="AM13" s="108">
+      <c r="AJ13" s="115"/>
+      <c r="AK13" s="115"/>
+      <c r="AL13" s="116"/>
+      <c r="AM13" s="114">
         <v>46203</v>
       </c>
-      <c r="AN13" s="109" t="s">
+      <c r="AN13" s="115" t="s">
         <v>24</v>
       </c>
-      <c r="AO13" s="109"/>
-      <c r="AP13" s="109"/>
-      <c r="AQ13" s="110"/>
-      <c r="AR13" s="108">
+      <c r="AO13" s="115"/>
+      <c r="AP13" s="115"/>
+      <c r="AQ13" s="116"/>
+      <c r="AR13" s="114">
         <v>46234</v>
       </c>
-      <c r="AS13" s="109" t="s">
+      <c r="AS13" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="AT13" s="109"/>
-      <c r="AU13" s="109"/>
-      <c r="AV13" s="110"/>
-      <c r="AW13" s="108">
+      <c r="AT13" s="115"/>
+      <c r="AU13" s="115"/>
+      <c r="AV13" s="116"/>
+      <c r="AW13" s="114">
         <v>46265</v>
       </c>
-      <c r="AX13" s="109" t="s">
+      <c r="AX13" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="AY13" s="109"/>
-      <c r="AZ13" s="109"/>
-      <c r="BA13" s="110"/>
-      <c r="BB13" s="108">
+      <c r="AY13" s="115"/>
+      <c r="AZ13" s="115"/>
+      <c r="BA13" s="116"/>
+      <c r="BB13" s="114">
         <v>46295</v>
       </c>
-      <c r="BC13" s="109" t="s">
+      <c r="BC13" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="BD13" s="109"/>
-      <c r="BE13" s="109"/>
-      <c r="BF13" s="110"/>
-      <c r="BG13" s="108">
+      <c r="BD13" s="115"/>
+      <c r="BE13" s="115"/>
+      <c r="BF13" s="116"/>
+      <c r="BG13" s="114">
         <v>46326</v>
       </c>
-      <c r="BH13" s="109" t="s">
+      <c r="BH13" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="BI13" s="109"/>
-      <c r="BJ13" s="109"/>
-      <c r="BK13" s="110"/>
-      <c r="BL13" s="108">
+      <c r="BI13" s="115"/>
+      <c r="BJ13" s="115"/>
+      <c r="BK13" s="116"/>
+      <c r="BL13" s="114">
         <v>46356</v>
       </c>
-      <c r="BM13" s="109" t="s">
+      <c r="BM13" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="BN13" s="109"/>
-      <c r="BO13" s="109"/>
-      <c r="BP13" s="110"/>
-      <c r="BQ13" s="108">
+      <c r="BN13" s="115"/>
+      <c r="BO13" s="115"/>
+      <c r="BP13" s="116"/>
+      <c r="BQ13" s="114">
         <v>46387</v>
       </c>
-      <c r="BR13" s="109" t="s">
+      <c r="BR13" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="BS13" s="109"/>
-      <c r="BT13" s="109"/>
-      <c r="BU13" s="110"/>
+      <c r="BS13" s="115"/>
+      <c r="BT13" s="115"/>
+      <c r="BU13" s="116"/>
       <c r="BV13" s="7">
         <f>SUM(BV15:BV65)</f>
         <v>0</v>
@@ -9655,6 +9655,30 @@
   </sheetData>
   <autoFilter ref="A14:BY18" xr:uid="{177F1DEB-197D-49C6-A2E3-152C1AC7B373}"/>
   <mergeCells count="40">
+    <mergeCell ref="BQ11:BU11"/>
+    <mergeCell ref="BQ13:BU13"/>
+    <mergeCell ref="S11:W11"/>
+    <mergeCell ref="N11:R11"/>
+    <mergeCell ref="X11:AB11"/>
+    <mergeCell ref="AC11:AG11"/>
+    <mergeCell ref="AH11:AL11"/>
+    <mergeCell ref="AM11:AQ11"/>
+    <mergeCell ref="AR11:AV11"/>
+    <mergeCell ref="AW11:BA11"/>
+    <mergeCell ref="BB11:BF11"/>
+    <mergeCell ref="BG11:BK11"/>
+    <mergeCell ref="BL11:BP11"/>
+    <mergeCell ref="S13:W13"/>
+    <mergeCell ref="N13:R13"/>
+    <mergeCell ref="X13:AB13"/>
+    <mergeCell ref="BB12:BF12"/>
+    <mergeCell ref="BG12:BK12"/>
+    <mergeCell ref="BL12:BP12"/>
+    <mergeCell ref="AC13:AG13"/>
+    <mergeCell ref="AH13:AL13"/>
+    <mergeCell ref="AM13:AQ13"/>
+    <mergeCell ref="AR13:AV13"/>
+    <mergeCell ref="AW13:BA13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="BQ12:BU12"/>
     <mergeCell ref="L11:M11"/>
@@ -9671,30 +9695,6 @@
     <mergeCell ref="AM12:AQ12"/>
     <mergeCell ref="AR12:AV12"/>
     <mergeCell ref="AW12:BA12"/>
-    <mergeCell ref="BB12:BF12"/>
-    <mergeCell ref="BG12:BK12"/>
-    <mergeCell ref="BL12:BP12"/>
-    <mergeCell ref="AC13:AG13"/>
-    <mergeCell ref="AH13:AL13"/>
-    <mergeCell ref="AM13:AQ13"/>
-    <mergeCell ref="AR13:AV13"/>
-    <mergeCell ref="AW13:BA13"/>
-    <mergeCell ref="BQ11:BU11"/>
-    <mergeCell ref="BQ13:BU13"/>
-    <mergeCell ref="S11:W11"/>
-    <mergeCell ref="N11:R11"/>
-    <mergeCell ref="X11:AB11"/>
-    <mergeCell ref="AC11:AG11"/>
-    <mergeCell ref="AH11:AL11"/>
-    <mergeCell ref="AM11:AQ11"/>
-    <mergeCell ref="AR11:AV11"/>
-    <mergeCell ref="AW11:BA11"/>
-    <mergeCell ref="BB11:BF11"/>
-    <mergeCell ref="BG11:BK11"/>
-    <mergeCell ref="BL11:BP11"/>
-    <mergeCell ref="S13:W13"/>
-    <mergeCell ref="N13:R13"/>
-    <mergeCell ref="X13:AB13"/>
   </mergeCells>
   <conditionalFormatting sqref="Q65 V65 AA65 AF65 AK65 AP65 AU65 AZ65 BE65 BJ65 BO65 BT65">
     <cfRule type="expression" dxfId="2" priority="8">
@@ -9717,6 +9717,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19b1ad6d-7bbd-4338-adb0-a51e11e836c7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002B3B1E9AF76D8540A21B723585178CF2" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9038a3d09b9201f70a536d69b3ffdde9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="19b1ad6d-7bbd-4338-adb0-a51e11e836c7" xmlns:ns3="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9f1b7b0d1eaccac7f713200a7ec3f32" ns2:_="" ns3:_="">
     <xsd:import namespace="19b1ad6d-7bbd-4338-adb0-a51e11e836c7"/>
@@ -9959,27 +9979,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC2B212-31BA-49FB-B215-9E14B2C60948}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09"/>
+    <ds:schemaRef ds:uri="19b1ad6d-7bbd-4338-adb0-a51e11e836c7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19b1ad6d-7bbd-4338-adb0-a51e11e836c7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3614A8F8-9AED-4C02-B640-81A3A1FEB080}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B6774AE-0D33-4944-9922-507715E1B0E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9996,23 +10015,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3614A8F8-9AED-4C02-B640-81A3A1FEB080}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC2B212-31BA-49FB-B215-9E14B2C60948}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09"/>
-    <ds:schemaRef ds:uri="19b1ad6d-7bbd-4338-adb0-a51e11e836c7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/templates/financial_template_v2_2026.xlsx
+++ b/data/templates/financial_template_v2_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pfizer-my.sharepoint.com/personal/hoveyo_pfizer_com/Documents/financial-automation-project/data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="8_{783183DD-73AE-4283-AD85-EEFD805851D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67E8D884-7862-41E5-98D0-4F52412DF91E}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="8_{783183DD-73AE-4283-AD85-EEFD805851D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2275B3F8-8E5A-4910-A117-4523E2FD9255}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" tabRatio="590" xr2:uid="{0996C49B-04E6-42AE-AA83-2F64BE89A626}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Template" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Template!$A$14:$BY$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Template!$A$15:$BY$15</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1613,7 +1613,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1822,6 +1822,15 @@
     <xf numFmtId="3" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1834,14 +1843,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1850,7 +1853,35 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 2" xfId="3" xr:uid="{EFDA3BDD-7E2C-4F3B-BEB7-091BB23895D4}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2182,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177F1DEB-197D-49C6-A2E3-152C1AC7B373}">
-  <dimension ref="A1:EI66"/>
+  <dimension ref="A1:EI67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -2202,137 +2233,151 @@
     <col min="76" max="76" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A1" s="13"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+    </row>
     <row r="2" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
+      <c r="A2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="34">
+        <v>2026</v>
+      </c>
+      <c r="F2" s="34"/>
+      <c r="G2" s="35">
+        <f>C2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:139" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="33">
+        <v>0</v>
+      </c>
+      <c r="D3" s="34">
+        <v>2321511</v>
       </c>
       <c r="E3" s="34">
         <v>2026</v>
       </c>
       <c r="F3" s="34"/>
       <c r="G3" s="35">
-        <f>C3</f>
         <v>0</v>
       </c>
       <c r="H3" s="46"/>
       <c r="I3" s="46"/>
       <c r="J3" s="46"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
     </row>
     <row r="4" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="33">
-        <v>0</v>
-      </c>
-      <c r="D4" s="34">
-        <v>2321511</v>
-      </c>
-      <c r="E4" s="34">
-        <v>2026</v>
-      </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="35">
-        <v>0</v>
-      </c>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
+      <c r="A4" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
     </row>
     <row r="5" spans="1:139" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="30"/>
+        <v>5</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>6</v>
+      </c>
       <c r="C5" s="37"/>
       <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-    </row>
-    <row r="6" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="40" t="str">
+      <c r="E5" s="40" t="str">
         <f>IF(SUMIFS(BV:BV,A:A,"Contingency")&gt;0,"Contingency is "&amp;TEXT(SUMIFS(BV:BV,A:A,"Contingency"),"$#,##"),IF(SUMIFS(BV:BV,A:A,"Contingency")&lt;0,"Overspent by "&amp;TEXT(SUMIFS(BV:BV,A:A,"Contingency"),"$#,##"),"No contingency"))</f>
         <v>No contingency</v>
       </c>
-      <c r="F6" s="40"/>
-      <c r="G6" s="17"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+    </row>
+    <row r="6" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="22"/>
       <c r="H6" s="37"/>
       <c r="I6" s="37"/>
       <c r="J6" s="37"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A8" s="105" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="106"/>
+      <c r="D8" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+    </row>
     <row r="9" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A9" s="105" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="106"/>
-      <c r="D9" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="43"/>
+      <c r="A9" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
-        <v>9</v>
+    <row r="10" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>12</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>10</v>
@@ -2344,16 +2389,13 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
-      <c r="K10" s="44"/>
-      <c r="BW10" s="9" t="s">
-        <v>11</v>
-      </c>
+      <c r="K10" s="43"/>
     </row>
-    <row r="11" spans="1:139" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="23" t="s">
+    <row r="11" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="24" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="11"/>
@@ -2364,137 +2406,18 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="44"/>
-      <c r="L11" s="110" t="s">
+      <c r="BW11" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:139" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="44"/>
+      <c r="L12" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="111"/>
-      <c r="N11" s="107" cm="1">
-        <f t="array" ref="N11">SUM(Q15:Q65)+SUM(_xlfn._xlws.FILTER(P15:P65,Q15:Q65=""))+SUM(_xlfn._xlws.FILTER(O15:O65,(P15:P65="")*(Q15:Q65="")))+SUMIFS(R15:R65,Q15:Q65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(N15:N65)</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="108"/>
-      <c r="P11" s="108"/>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="109"/>
-      <c r="S11" s="107" cm="1">
-        <f t="array" ref="S11">SUM(V15:V65)+SUM(_xlfn._xlws.FILTER(U15:U65,V15:V65=""))+SUM(_xlfn._xlws.FILTER(T15:T65,(U15:U65="")*(V15:V65="")))+SUMIFS(W15:W65,V15:V65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(S15:S65)</f>
-        <v>0</v>
-      </c>
-      <c r="T11" s="108"/>
-      <c r="U11" s="108"/>
-      <c r="V11" s="108"/>
-      <c r="W11" s="109"/>
-      <c r="X11" s="107" cm="1">
-        <f t="array" ref="X11">SUM(AA15:AA65)+SUM(_xlfn._xlws.FILTER(Z15:Z65,AA15:AA65=""))+SUM(_xlfn._xlws.FILTER(Y15:Y65,(Z15:Z65="")*(AA15:AA65="")))+SUMIFS(AB15:AB65,AA15:AA65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(X15:X65)</f>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="108"/>
-      <c r="Z11" s="108"/>
-      <c r="AA11" s="108"/>
-      <c r="AB11" s="109"/>
-      <c r="AC11" s="107" cm="1">
-        <f t="array" ref="AC11">SUM(AF15:AF65)+SUM(_xlfn._xlws.FILTER(AE15:AE65,AF15:AF65=""))+SUM(_xlfn._xlws.FILTER(AD15:AD65,(AE15:AE65="")*(AF15:AF65="")))+SUMIFS(AG15:AG65,AF15:AF65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AC15:AC65)</f>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="108"/>
-      <c r="AE11" s="108"/>
-      <c r="AF11" s="108"/>
-      <c r="AG11" s="109"/>
-      <c r="AH11" s="107" cm="1">
-        <f t="array" ref="AH11">SUM(AK15:AK65)+SUM(_xlfn._xlws.FILTER(AJ15:AJ65,AK15:AK65=""))+SUM(_xlfn._xlws.FILTER(AI15:AI65,(AJ15:AJ65="")*(AK15:AK65="")))+SUMIFS(AL15:AL65,AK15:AK65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AH15:AH65)</f>
-        <v>0</v>
-      </c>
-      <c r="AI11" s="108"/>
-      <c r="AJ11" s="108"/>
-      <c r="AK11" s="108"/>
-      <c r="AL11" s="109"/>
-      <c r="AM11" s="107" cm="1">
-        <f t="array" ref="AM11">SUM(AP15:AP65)+SUM(_xlfn._xlws.FILTER(AO15:AO65,AP15:AP65=""))+SUM(_xlfn._xlws.FILTER(AN15:AN65,(AO15:AO65="")*(AP15:AP65="")))+SUMIFS(AQ15:AQ65,AP15:AP65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AM15:AM65)</f>
-        <v>0</v>
-      </c>
-      <c r="AN11" s="108"/>
-      <c r="AO11" s="108"/>
-      <c r="AP11" s="108"/>
-      <c r="AQ11" s="109"/>
-      <c r="AR11" s="107" cm="1">
-        <f t="array" ref="AR11">SUM(AU15:AU65)+SUM(_xlfn._xlws.FILTER(AT15:AT65,AU15:AU65=""))+SUM(_xlfn._xlws.FILTER(AS15:AS65,(AT15:AT65="")*(AU15:AU65="")))+SUMIFS(AV15:AV65,AU15:AU65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AR15:AR65)</f>
-        <v>0</v>
-      </c>
-      <c r="AS11" s="108"/>
-      <c r="AT11" s="108"/>
-      <c r="AU11" s="108"/>
-      <c r="AV11" s="109"/>
-      <c r="AW11" s="107" cm="1">
-        <f t="array" ref="AW11">SUM(AZ15:AZ65)+SUM(_xlfn._xlws.FILTER(AY15:AY65,AZ15:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX15:AX65,(AY15:AY65="")*(AZ15:AZ65="")))+SUMIFS(BA15:BA65,AZ15:AZ65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(AW15:AW65)</f>
-        <v>0</v>
-      </c>
-      <c r="AX11" s="108"/>
-      <c r="AY11" s="108"/>
-      <c r="AZ11" s="108"/>
-      <c r="BA11" s="109"/>
-      <c r="BB11" s="107" cm="1">
-        <f t="array" ref="BB11">SUM(BE15:BE65)+SUM(_xlfn._xlws.FILTER(BD15:BD65,BE15:BE65=""))+SUM(_xlfn._xlws.FILTER(BC15:BC65,(BD15:BD65="")*(BE15:BE65="")))+SUMIFS(BF15:BF65,BE15:BE65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BB15:BB65)</f>
-        <v>0</v>
-      </c>
-      <c r="BC11" s="108"/>
-      <c r="BD11" s="108"/>
-      <c r="BE11" s="108"/>
-      <c r="BF11" s="109"/>
-      <c r="BG11" s="107" cm="1">
-        <f t="array" ref="BG11">SUM(BJ15:BJ65)+SUM(_xlfn._xlws.FILTER(BI15:BI65,BJ15:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH15:BH65,(BI15:BI65="")*(BJ15:BJ65="")))+SUMIFS(BK15:BK65,BJ15:BJ65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BG15:BG65)</f>
-        <v>0</v>
-      </c>
-      <c r="BH11" s="108"/>
-      <c r="BI11" s="108"/>
-      <c r="BJ11" s="108"/>
-      <c r="BK11" s="109"/>
-      <c r="BL11" s="107" cm="1">
-        <f t="array" ref="BL11">SUM(BO15:BO65)+SUM(_xlfn._xlws.FILTER(BN15:BN65,BO15:BO65=""))+SUM(_xlfn._xlws.FILTER(BM15:BM65,(BN15:BN65="")*(BO15:BO65="")))+SUMIFS(BP15:BP65,BO15:BO65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BL15:BL65)</f>
-        <v>0</v>
-      </c>
-      <c r="BM11" s="108"/>
-      <c r="BN11" s="108"/>
-      <c r="BO11" s="108"/>
-      <c r="BP11" s="109"/>
-      <c r="BQ11" s="107" cm="1">
-        <f t="array" ref="BQ11">SUM(BT15:BT65)+SUM(_xlfn._xlws.FILTER(BS15:BS65,BT15:BT65=""))+SUM(_xlfn._xlws.FILTER(BR15:BR65,(BS15:BS65="")*(BT15:BT65="")))+SUMIFS(BU15:BU65,BT15:BT65,"&lt;&gt;"&amp;"",$P$15:$P$65,"&lt;&gt;"&amp;"")+SUM(BQ15:BQ65)</f>
-        <v>0</v>
-      </c>
-      <c r="BR11" s="108"/>
-      <c r="BS11" s="108"/>
-      <c r="BT11" s="108"/>
-      <c r="BU11" s="109"/>
-      <c r="BV11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="BW11" s="5">
-        <f>BW13-BV13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="112" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" s="113"/>
+      <c r="M12" s="114"/>
       <c r="N12" s="107" cm="1">
-        <f t="array" ref="N12">SUM(Q15:Q65)+SUM(_xlfn._xlws.FILTER(P15:P65,Q15:Q65=""))+SUM(_xlfn._xlws.FILTER(O15:O65,(P15:P65="")*(Q15:Q65="")))</f>
+        <f t="array" ref="N12">SUM(Q16:Q66)+SUM(_xlfn._xlws.FILTER(P16:P66,Q16:Q66=""))+SUM(_xlfn._xlws.FILTER(O16:O66,(P16:P66="")*(Q16:Q66="")))+SUMIFS(R16:R66,Q16:Q66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(N16:N66)</f>
         <v>0</v>
       </c>
       <c r="O12" s="108"/>
@@ -2502,7 +2425,7 @@
       <c r="Q12" s="108"/>
       <c r="R12" s="109"/>
       <c r="S12" s="107" cm="1">
-        <f t="array" ref="S12">SUM(V15:V65)+SUM(_xlfn._xlws.FILTER(U15:U65,V15:V65=""))+SUM(_xlfn._xlws.FILTER(T15:T65,(U15:U65="")*(V15:V65="")))</f>
+        <f t="array" ref="S12">SUM(V16:V66)+SUM(_xlfn._xlws.FILTER(U16:U66,V16:V66=""))+SUM(_xlfn._xlws.FILTER(T16:T66,(U16:U66="")*(V16:V66="")))+SUMIFS(W16:W66,V16:V66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(S16:S66)</f>
         <v>0</v>
       </c>
       <c r="T12" s="108"/>
@@ -2510,7 +2433,7 @@
       <c r="V12" s="108"/>
       <c r="W12" s="109"/>
       <c r="X12" s="107" cm="1">
-        <f t="array" ref="X12">SUM(AA15:AA65)+SUM(_xlfn._xlws.FILTER(Z15:Z65,AA15:AA65=""))+SUM(_xlfn._xlws.FILTER(Y15:Y65,(Z15:Z65="")*(AA15:AA65="")))</f>
+        <f t="array" ref="X12">SUM(AA16:AA66)+SUM(_xlfn._xlws.FILTER(Z16:Z66,AA16:AA66=""))+SUM(_xlfn._xlws.FILTER(Y16:Y66,(Z16:Z66="")*(AA16:AA66="")))+SUMIFS(AB16:AB66,AA16:AA66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(X16:X66)</f>
         <v>0</v>
       </c>
       <c r="Y12" s="108"/>
@@ -2518,7 +2441,7 @@
       <c r="AA12" s="108"/>
       <c r="AB12" s="109"/>
       <c r="AC12" s="107" cm="1">
-        <f t="array" ref="AC12">SUM(AF15:AF65)+SUM(_xlfn._xlws.FILTER(AE15:AE65,AF15:AF65=""))+SUM(_xlfn._xlws.FILTER(AD15:AD65,(AE15:AE65="")*(AF15:AF65="")))</f>
+        <f t="array" ref="AC12">SUM(AF16:AF66)+SUM(_xlfn._xlws.FILTER(AE16:AE66,AF16:AF66=""))+SUM(_xlfn._xlws.FILTER(AD16:AD66,(AE16:AE66="")*(AF16:AF66="")))+SUMIFS(AG16:AG66,AF16:AF66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(AC16:AC66)</f>
         <v>0</v>
       </c>
       <c r="AD12" s="108"/>
@@ -2526,7 +2449,7 @@
       <c r="AF12" s="108"/>
       <c r="AG12" s="109"/>
       <c r="AH12" s="107" cm="1">
-        <f t="array" ref="AH12">SUM(AK15:AK65)+SUM(_xlfn._xlws.FILTER(AJ15:AJ65,AK15:AK65=""))+SUM(_xlfn._xlws.FILTER(AI15:AI65,(AJ15:AJ65="")*(AK15:AK65="")))</f>
+        <f t="array" ref="AH12">SUM(AK16:AK66)+SUM(_xlfn._xlws.FILTER(AJ16:AJ66,AK16:AK66=""))+SUM(_xlfn._xlws.FILTER(AI16:AI66,(AJ16:AJ66="")*(AK16:AK66="")))+SUMIFS(AL16:AL66,AK16:AK66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(AH16:AH66)</f>
         <v>0</v>
       </c>
       <c r="AI12" s="108"/>
@@ -2534,7 +2457,7 @@
       <c r="AK12" s="108"/>
       <c r="AL12" s="109"/>
       <c r="AM12" s="107" cm="1">
-        <f t="array" ref="AM12">SUM(AP15:AP65)+SUM(_xlfn._xlws.FILTER(AO15:AO65,AP15:AP65=""))+SUM(_xlfn._xlws.FILTER(AN15:AN65,(AO15:AO65="")*(AP15:AP65="")))</f>
+        <f t="array" ref="AM12">SUM(AP16:AP66)+SUM(_xlfn._xlws.FILTER(AO16:AO66,AP16:AP66=""))+SUM(_xlfn._xlws.FILTER(AN16:AN66,(AO16:AO66="")*(AP16:AP66="")))+SUMIFS(AQ16:AQ66,AP16:AP66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(AM16:AM66)</f>
         <v>0</v>
       </c>
       <c r="AN12" s="108"/>
@@ -2542,7 +2465,7 @@
       <c r="AP12" s="108"/>
       <c r="AQ12" s="109"/>
       <c r="AR12" s="107" cm="1">
-        <f t="array" ref="AR12">SUM(AU15:AU65)+SUM(_xlfn._xlws.FILTER(AT15:AT65,AU15:AU65=""))+SUM(_xlfn._xlws.FILTER(AS15:AS65,(AT15:AT65="")*(AU15:AU65="")))</f>
+        <f t="array" ref="AR12">SUM(AU16:AU66)+SUM(_xlfn._xlws.FILTER(AT16:AT66,AU16:AU66=""))+SUM(_xlfn._xlws.FILTER(AS16:AS66,(AT16:AT66="")*(AU16:AU66="")))+SUMIFS(AV16:AV66,AU16:AU66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(AR16:AR66)</f>
         <v>0</v>
       </c>
       <c r="AS12" s="108"/>
@@ -2550,7 +2473,7 @@
       <c r="AU12" s="108"/>
       <c r="AV12" s="109"/>
       <c r="AW12" s="107" cm="1">
-        <f t="array" ref="AW12">SUM(AZ15:AZ65)+SUM(_xlfn._xlws.FILTER(AY15:AY65,AZ15:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX15:AX65,(AY15:AY65="")*(AZ15:AZ65="")))</f>
+        <f t="array" ref="AW12">SUM(AZ16:AZ66)+SUM(_xlfn._xlws.FILTER(AY16:AY66,AZ16:AZ66=""))+SUM(_xlfn._xlws.FILTER(AX16:AX66,(AY16:AY66="")*(AZ16:AZ66="")))+SUMIFS(BA16:BA66,AZ16:AZ66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(AW16:AW66)</f>
         <v>0</v>
       </c>
       <c r="AX12" s="108"/>
@@ -2558,7 +2481,7 @@
       <c r="AZ12" s="108"/>
       <c r="BA12" s="109"/>
       <c r="BB12" s="107" cm="1">
-        <f t="array" ref="BB12">SUM(BE15:BE65)+SUM(_xlfn._xlws.FILTER(BD15:BD65,BE15:BE65=""))+SUM(_xlfn._xlws.FILTER(BC15:BC65,(BD15:BD65="")*(BE15:BE65="")))</f>
+        <f t="array" ref="BB12">SUM(BE16:BE66)+SUM(_xlfn._xlws.FILTER(BD16:BD66,BE16:BE66=""))+SUM(_xlfn._xlws.FILTER(BC16:BC66,(BD16:BD66="")*(BE16:BE66="")))+SUMIFS(BF16:BF66,BE16:BE66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(BB16:BB66)</f>
         <v>0</v>
       </c>
       <c r="BC12" s="108"/>
@@ -2566,7 +2489,7 @@
       <c r="BE12" s="108"/>
       <c r="BF12" s="109"/>
       <c r="BG12" s="107" cm="1">
-        <f t="array" ref="BG12">SUM(BJ15:BJ65)+SUM(_xlfn._xlws.FILTER(BI15:BI65,BJ15:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH15:BH65,(BI15:BI65="")*(BJ15:BJ65="")))</f>
+        <f t="array" ref="BG12">SUM(BJ16:BJ66)+SUM(_xlfn._xlws.FILTER(BI16:BI66,BJ16:BJ66=""))+SUM(_xlfn._xlws.FILTER(BH16:BH66,(BI16:BI66="")*(BJ16:BJ66="")))+SUMIFS(BK16:BK66,BJ16:BJ66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(BG16:BG66)</f>
         <v>0</v>
       </c>
       <c r="BH12" s="108"/>
@@ -2574,7 +2497,7 @@
       <c r="BJ12" s="108"/>
       <c r="BK12" s="109"/>
       <c r="BL12" s="107" cm="1">
-        <f t="array" ref="BL12">SUM(BO15:BO65)+SUM(_xlfn._xlws.FILTER(BN15:BN65,BO15:BO65=""))+SUM(_xlfn._xlws.FILTER(BM15:BM65,(BN15:BN65="")*(BO15:BO65="")))</f>
+        <f t="array" ref="BL12">SUM(BO16:BO66)+SUM(_xlfn._xlws.FILTER(BN16:BN66,BO16:BO66=""))+SUM(_xlfn._xlws.FILTER(BM16:BM66,(BN16:BN66="")*(BO16:BO66="")))+SUMIFS(BP16:BP66,BO16:BO66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(BL16:BL66)</f>
         <v>0</v>
       </c>
       <c r="BM12" s="108"/>
@@ -2582,617 +2505,524 @@
       <c r="BO12" s="108"/>
       <c r="BP12" s="109"/>
       <c r="BQ12" s="107" cm="1">
-        <f t="array" ref="BQ12">SUM(BT15:BT65)+SUM(_xlfn._xlws.FILTER(BS15:BS65,BT15:BT65=""))+SUM(_xlfn._xlws.FILTER(BR15:BR65,(BS15:BS65="")*(BT15:BT65="")))</f>
+        <f t="array" ref="BQ12">SUM(BT16:BT66)+SUM(_xlfn._xlws.FILTER(BS16:BS66,BT16:BT66=""))+SUM(_xlfn._xlws.FILTER(BR16:BR66,(BS16:BS66="")*(BT16:BT66="")))+SUMIFS(BU16:BU66,BT16:BT66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(BQ16:BQ66)</f>
         <v>0</v>
       </c>
       <c r="BR12" s="108"/>
       <c r="BS12" s="108"/>
       <c r="BT12" s="108"/>
       <c r="BU12" s="109"/>
-      <c r="BV12" s="4"/>
-      <c r="BW12" s="5"/>
+      <c r="BV12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="BW12" s="5">
+        <f>BW14-BV14</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:139" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="117" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13" s="116"/>
+      <c r="N13" s="107" cm="1">
+        <f t="array" ref="N13">SUM(Q16:Q66)+SUM(_xlfn._xlws.FILTER(P16:P66,Q16:Q66=""))+SUM(_xlfn._xlws.FILTER(O16:O66,(P16:P66="")*(Q16:Q66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="108"/>
+      <c r="P13" s="108"/>
+      <c r="Q13" s="108"/>
+      <c r="R13" s="109"/>
+      <c r="S13" s="107" cm="1">
+        <f t="array" ref="S13">SUM(V16:V66)+SUM(_xlfn._xlws.FILTER(U16:U66,V16:V66=""))+SUM(_xlfn._xlws.FILTER(T16:T66,(U16:U66="")*(V16:V66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="108"/>
+      <c r="U13" s="108"/>
+      <c r="V13" s="108"/>
+      <c r="W13" s="109"/>
+      <c r="X13" s="107" cm="1">
+        <f t="array" ref="X13">SUM(AA16:AA66)+SUM(_xlfn._xlws.FILTER(Z16:Z66,AA16:AA66=""))+SUM(_xlfn._xlws.FILTER(Y16:Y66,(Z16:Z66="")*(AA16:AA66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="108"/>
+      <c r="Z13" s="108"/>
+      <c r="AA13" s="108"/>
+      <c r="AB13" s="109"/>
+      <c r="AC13" s="107" cm="1">
+        <f t="array" ref="AC13">SUM(AF16:AF66)+SUM(_xlfn._xlws.FILTER(AE16:AE66,AF16:AF66=""))+SUM(_xlfn._xlws.FILTER(AD16:AD66,(AE16:AE66="")*(AF16:AF66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="108"/>
+      <c r="AE13" s="108"/>
+      <c r="AF13" s="108"/>
+      <c r="AG13" s="109"/>
+      <c r="AH13" s="107" cm="1">
+        <f t="array" ref="AH13">SUM(AK16:AK66)+SUM(_xlfn._xlws.FILTER(AJ16:AJ66,AK16:AK66=""))+SUM(_xlfn._xlws.FILTER(AI16:AI66,(AJ16:AJ66="")*(AK16:AK66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AI13" s="108"/>
+      <c r="AJ13" s="108"/>
+      <c r="AK13" s="108"/>
+      <c r="AL13" s="109"/>
+      <c r="AM13" s="107" cm="1">
+        <f t="array" ref="AM13">SUM(AP16:AP66)+SUM(_xlfn._xlws.FILTER(AO16:AO66,AP16:AP66=""))+SUM(_xlfn._xlws.FILTER(AN16:AN66,(AO16:AO66="")*(AP16:AP66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AN13" s="108"/>
+      <c r="AO13" s="108"/>
+      <c r="AP13" s="108"/>
+      <c r="AQ13" s="109"/>
+      <c r="AR13" s="107" cm="1">
+        <f t="array" ref="AR13">SUM(AU16:AU66)+SUM(_xlfn._xlws.FILTER(AT16:AT66,AU16:AU66=""))+SUM(_xlfn._xlws.FILTER(AS16:AS66,(AT16:AT66="")*(AU16:AU66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AS13" s="108"/>
+      <c r="AT13" s="108"/>
+      <c r="AU13" s="108"/>
+      <c r="AV13" s="109"/>
+      <c r="AW13" s="107" cm="1">
+        <f t="array" ref="AW13">SUM(AZ16:AZ66)+SUM(_xlfn._xlws.FILTER(AY16:AY66,AZ16:AZ66=""))+SUM(_xlfn._xlws.FILTER(AX16:AX66,(AY16:AY66="")*(AZ16:AZ66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AX13" s="108"/>
+      <c r="AY13" s="108"/>
+      <c r="AZ13" s="108"/>
+      <c r="BA13" s="109"/>
+      <c r="BB13" s="107" cm="1">
+        <f t="array" ref="BB13">SUM(BE16:BE66)+SUM(_xlfn._xlws.FILTER(BD16:BD66,BE16:BE66=""))+SUM(_xlfn._xlws.FILTER(BC16:BC66,(BD16:BD66="")*(BE16:BE66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BC13" s="108"/>
+      <c r="BD13" s="108"/>
+      <c r="BE13" s="108"/>
+      <c r="BF13" s="109"/>
+      <c r="BG13" s="107" cm="1">
+        <f t="array" ref="BG13">SUM(BJ16:BJ66)+SUM(_xlfn._xlws.FILTER(BI16:BI66,BJ16:BJ66=""))+SUM(_xlfn._xlws.FILTER(BH16:BH66,(BI16:BI66="")*(BJ16:BJ66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BH13" s="108"/>
+      <c r="BI13" s="108"/>
+      <c r="BJ13" s="108"/>
+      <c r="BK13" s="109"/>
+      <c r="BL13" s="107" cm="1">
+        <f t="array" ref="BL13">SUM(BO16:BO66)+SUM(_xlfn._xlws.FILTER(BN16:BN66,BO16:BO66=""))+SUM(_xlfn._xlws.FILTER(BM16:BM66,(BN16:BN66="")*(BO16:BO66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BM13" s="108"/>
+      <c r="BN13" s="108"/>
+      <c r="BO13" s="108"/>
+      <c r="BP13" s="109"/>
+      <c r="BQ13" s="107" cm="1">
+        <f t="array" ref="BQ13">SUM(BT16:BT66)+SUM(_xlfn._xlws.FILTER(BS16:BS66,BT16:BT66=""))+SUM(_xlfn._xlws.FILTER(BR16:BR66,(BS16:BS66="")*(BT16:BT66="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BR13" s="108"/>
+      <c r="BS13" s="108"/>
+      <c r="BT13" s="108"/>
+      <c r="BU13" s="109"/>
+      <c r="BV13" s="4"/>
+      <c r="BW13" s="5"/>
+    </row>
+    <row r="14" spans="1:139" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="54">
-        <f>SUBTOTAL(9,K15:K16)</f>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="54">
+        <f>SUBTOTAL(9,K16:K17)</f>
         <v>190781</v>
       </c>
-      <c r="L13" s="112" t="s">
+      <c r="L14" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="M13" s="113"/>
-      <c r="N13" s="114">
+      <c r="M14" s="116"/>
+      <c r="N14" s="110">
         <v>46053</v>
       </c>
-      <c r="O13" s="115" t="s">
+      <c r="O14" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="P13" s="115"/>
-      <c r="Q13" s="115"/>
-      <c r="R13" s="115"/>
-      <c r="S13" s="114">
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="111"/>
+      <c r="S14" s="110">
         <v>46054</v>
       </c>
-      <c r="T13" s="115"/>
-      <c r="U13" s="115"/>
-      <c r="V13" s="115"/>
-      <c r="W13" s="116"/>
-      <c r="X13" s="114">
+      <c r="T14" s="111"/>
+      <c r="U14" s="111"/>
+      <c r="V14" s="111"/>
+      <c r="W14" s="112"/>
+      <c r="X14" s="110">
         <v>46112</v>
       </c>
-      <c r="Y13" s="115" t="s">
+      <c r="Y14" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="Z13" s="115"/>
-      <c r="AA13" s="115"/>
-      <c r="AB13" s="116"/>
-      <c r="AC13" s="114">
+      <c r="Z14" s="111"/>
+      <c r="AA14" s="111"/>
+      <c r="AB14" s="112"/>
+      <c r="AC14" s="110">
         <v>46142</v>
       </c>
-      <c r="AD13" s="115" t="s">
+      <c r="AD14" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="AE13" s="115"/>
-      <c r="AF13" s="115"/>
-      <c r="AG13" s="116"/>
-      <c r="AH13" s="114">
+      <c r="AE14" s="111"/>
+      <c r="AF14" s="111"/>
+      <c r="AG14" s="112"/>
+      <c r="AH14" s="110">
         <v>46173</v>
       </c>
-      <c r="AI13" s="115" t="s">
+      <c r="AI14" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="AJ13" s="115"/>
-      <c r="AK13" s="115"/>
-      <c r="AL13" s="116"/>
-      <c r="AM13" s="114">
+      <c r="AJ14" s="111"/>
+      <c r="AK14" s="111"/>
+      <c r="AL14" s="112"/>
+      <c r="AM14" s="110">
         <v>46203</v>
       </c>
-      <c r="AN13" s="115" t="s">
+      <c r="AN14" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="AO13" s="115"/>
-      <c r="AP13" s="115"/>
-      <c r="AQ13" s="116"/>
-      <c r="AR13" s="114">
+      <c r="AO14" s="111"/>
+      <c r="AP14" s="111"/>
+      <c r="AQ14" s="112"/>
+      <c r="AR14" s="110">
         <v>46234</v>
       </c>
-      <c r="AS13" s="115" t="s">
+      <c r="AS14" s="111" t="s">
         <v>25</v>
       </c>
-      <c r="AT13" s="115"/>
-      <c r="AU13" s="115"/>
-      <c r="AV13" s="116"/>
-      <c r="AW13" s="114">
+      <c r="AT14" s="111"/>
+      <c r="AU14" s="111"/>
+      <c r="AV14" s="112"/>
+      <c r="AW14" s="110">
         <v>46265</v>
       </c>
-      <c r="AX13" s="115" t="s">
+      <c r="AX14" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="AY13" s="115"/>
-      <c r="AZ13" s="115"/>
-      <c r="BA13" s="116"/>
-      <c r="BB13" s="114">
+      <c r="AY14" s="111"/>
+      <c r="AZ14" s="111"/>
+      <c r="BA14" s="112"/>
+      <c r="BB14" s="110">
         <v>46295</v>
       </c>
-      <c r="BC13" s="115" t="s">
+      <c r="BC14" s="111" t="s">
         <v>27</v>
       </c>
-      <c r="BD13" s="115"/>
-      <c r="BE13" s="115"/>
-      <c r="BF13" s="116"/>
-      <c r="BG13" s="114">
+      <c r="BD14" s="111"/>
+      <c r="BE14" s="111"/>
+      <c r="BF14" s="112"/>
+      <c r="BG14" s="110">
         <v>46326</v>
       </c>
-      <c r="BH13" s="115" t="s">
+      <c r="BH14" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="BI13" s="115"/>
-      <c r="BJ13" s="115"/>
-      <c r="BK13" s="116"/>
-      <c r="BL13" s="114">
+      <c r="BI14" s="111"/>
+      <c r="BJ14" s="111"/>
+      <c r="BK14" s="112"/>
+      <c r="BL14" s="110">
         <v>46356</v>
       </c>
-      <c r="BM13" s="115" t="s">
+      <c r="BM14" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="BN13" s="115"/>
-      <c r="BO13" s="115"/>
-      <c r="BP13" s="116"/>
-      <c r="BQ13" s="114">
+      <c r="BN14" s="111"/>
+      <c r="BO14" s="111"/>
+      <c r="BP14" s="112"/>
+      <c r="BQ14" s="110">
         <v>46387</v>
       </c>
-      <c r="BR13" s="115" t="s">
+      <c r="BR14" s="111" t="s">
         <v>30</v>
       </c>
-      <c r="BS13" s="115"/>
-      <c r="BT13" s="115"/>
-      <c r="BU13" s="116"/>
-      <c r="BV13" s="7">
-        <f>SUM(BV15:BV65)</f>
-        <v>0</v>
-      </c>
-      <c r="BW13" s="8"/>
-      <c r="BY13" s="3"/>
+      <c r="BS14" s="111"/>
+      <c r="BT14" s="111"/>
+      <c r="BU14" s="112"/>
+      <c r="BV14" s="7">
+        <f>SUM(BV16:BV66)</f>
+        <v>0</v>
+      </c>
+      <c r="BW14" s="8"/>
+      <c r="BY14" s="3"/>
     </row>
-    <row r="14" spans="1:139" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="56" t="s">
+    <row r="15" spans="1:139" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B15" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C15" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="D15" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="60" t="s">
+      <c r="E15" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="60" t="s">
+      <c r="F15" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="58" t="s">
+      <c r="G15" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="58" t="s">
+      <c r="H15" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="I14" s="58" t="s">
+      <c r="I15" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="58" t="s">
+      <c r="J15" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K14" s="61" t="s">
+      <c r="K15" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="L14" s="62" t="s">
+      <c r="L15" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="M14" s="48" t="s">
+      <c r="M15" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="N14" s="51" t="s">
+      <c r="N15" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="O14" s="52" t="s">
+      <c r="O15" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="P14" s="52" t="s">
+      <c r="P15" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="Q14" s="52" t="s">
+      <c r="Q15" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="R14" s="50" t="s">
+      <c r="R15" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="S14" s="63" t="s">
+      <c r="S15" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="T14" s="52" t="s">
+      <c r="T15" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="U14" s="52" t="s">
+      <c r="U15" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="V14" s="64" t="s">
+      <c r="V15" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="W14" s="65" t="s">
+      <c r="W15" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="X14" s="63" t="s">
+      <c r="X15" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="Y14" s="52" t="s">
+      <c r="Y15" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Z14" s="52" t="s">
+      <c r="Z15" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="AA14" s="64" t="s">
+      <c r="AA15" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="AB14" s="65" t="s">
+      <c r="AB15" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AC14" s="63" t="s">
+      <c r="AC15" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AD14" s="52" t="s">
+      <c r="AD15" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="AE14" s="52" t="s">
+      <c r="AE15" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="AF14" s="64" t="s">
+      <c r="AF15" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="AG14" s="65" t="s">
+      <c r="AG15" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AH14" s="63" t="s">
+      <c r="AH15" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="AI14" s="52" t="s">
+      <c r="AI15" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="AJ14" s="52" t="s">
+      <c r="AJ15" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="AK14" s="64" t="s">
+      <c r="AK15" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="AL14" s="65" t="s">
+      <c r="AL15" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AM14" s="63" t="s">
+      <c r="AM15" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="AN14" s="52" t="s">
+      <c r="AN15" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="AO14" s="52" t="s">
+      <c r="AO15" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="AP14" s="64" t="s">
+      <c r="AP15" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="AQ14" s="65" t="s">
+      <c r="AQ15" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AR14" s="63" t="s">
+      <c r="AR15" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="AS14" s="52" t="s">
+      <c r="AS15" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="AT14" s="52" t="s">
+      <c r="AT15" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="AU14" s="64" t="s">
+      <c r="AU15" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="AV14" s="65" t="s">
+      <c r="AV15" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AW14" s="63" t="s">
+      <c r="AW15" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="AX14" s="52" t="s">
+      <c r="AX15" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="AY14" s="52" t="s">
+      <c r="AY15" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="AZ14" s="64" t="s">
+      <c r="AZ15" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="BA14" s="65" t="s">
+      <c r="BA15" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="BB14" s="63" t="s">
+      <c r="BB15" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="BC14" s="52" t="s">
+      <c r="BC15" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="BD14" s="52" t="s">
+      <c r="BD15" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="BE14" s="64" t="s">
+      <c r="BE15" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="BF14" s="65" t="s">
+      <c r="BF15" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="BG14" s="63" t="s">
+      <c r="BG15" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="BH14" s="52" t="s">
+      <c r="BH15" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="BI14" s="52" t="s">
+      <c r="BI15" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="BJ14" s="64" t="s">
+      <c r="BJ15" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="BK14" s="65" t="s">
+      <c r="BK15" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="BL14" s="63" t="s">
+      <c r="BL15" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="BM14" s="52" t="s">
+      <c r="BM15" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="BN14" s="52" t="s">
+      <c r="BN15" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="BO14" s="64" t="s">
+      <c r="BO15" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="BP14" s="65" t="s">
+      <c r="BP15" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="BQ14" s="63" t="s">
+      <c r="BQ15" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="BR14" s="52" t="s">
+      <c r="BR15" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="BS14" s="52" t="s">
+      <c r="BS15" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="BT14" s="64" t="s">
+      <c r="BT15" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="BU14" s="65" t="s">
+      <c r="BU15" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="BV14" s="51" t="s">
+      <c r="BV15" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="BW14" s="52" t="s">
+      <c r="BW15" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="BX14" s="48" t="s">
+      <c r="BX15" s="48" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="15" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A15" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="94">
-        <v>9501133449</v>
-      </c>
-      <c r="C15" s="96">
-        <v>45993</v>
-      </c>
-      <c r="D15" s="96">
-        <v>46173</v>
-      </c>
-      <c r="E15" s="81" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="80" t="s">
-        <v>99</v>
-      </c>
-      <c r="G15" s="80">
-        <v>41500000</v>
-      </c>
-      <c r="H15" s="80">
-        <v>3840</v>
-      </c>
-      <c r="I15" s="80" t="s">
-        <v>100</v>
-      </c>
-      <c r="J15" s="80">
-        <v>2430238</v>
-      </c>
-      <c r="K15" s="97">
-        <v>66363</v>
-      </c>
-      <c r="L15" s="100" t="s">
-        <v>165</v>
-      </c>
-      <c r="M15" s="101" t="s">
-        <v>166</v>
-      </c>
-      <c r="N15" s="82"/>
-      <c r="O15" s="83"/>
-      <c r="P15" s="83"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84">
-        <f>P15-Q15</f>
-        <v>0</v>
-      </c>
-      <c r="S15" s="85"/>
-      <c r="T15" s="83"/>
-      <c r="U15" s="83"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="86">
-        <f>U15-V15</f>
-        <v>0</v>
-      </c>
-      <c r="X15" s="87"/>
-      <c r="Y15" s="83"/>
-      <c r="Z15" s="83"/>
-      <c r="AA15" s="84"/>
-      <c r="AB15" s="86">
-        <f>Z15-AA15</f>
-        <v>0</v>
-      </c>
-      <c r="AC15" s="87"/>
-      <c r="AD15" s="83"/>
-      <c r="AE15" s="83"/>
-      <c r="AF15" s="83"/>
-      <c r="AG15" s="86">
-        <f>AE15-AF15</f>
-        <v>0</v>
-      </c>
-      <c r="AH15" s="87"/>
-      <c r="AI15" s="83"/>
-      <c r="AJ15" s="83"/>
-      <c r="AK15" s="83"/>
-      <c r="AL15" s="86">
-        <f>AJ15-AK15</f>
-        <v>0</v>
-      </c>
-      <c r="AM15" s="87"/>
-      <c r="AN15" s="83"/>
-      <c r="AO15" s="83"/>
-      <c r="AP15" s="83"/>
-      <c r="AQ15" s="86">
-        <f>AO15-AP15</f>
-        <v>0</v>
-      </c>
-      <c r="AR15" s="87"/>
-      <c r="AS15" s="83"/>
-      <c r="AT15" s="83"/>
-      <c r="AU15" s="83"/>
-      <c r="AV15" s="86">
-        <f>AT15-AU15</f>
-        <v>0</v>
-      </c>
-      <c r="AW15" s="87"/>
-      <c r="AX15" s="83"/>
-      <c r="AY15" s="83"/>
-      <c r="AZ15" s="83"/>
-      <c r="BA15" s="86">
-        <f>AY15-AZ15</f>
-        <v>0</v>
-      </c>
-      <c r="BB15" s="87"/>
-      <c r="BC15" s="83"/>
-      <c r="BD15" s="83"/>
-      <c r="BE15" s="83"/>
-      <c r="BF15" s="86">
-        <f>BD15-BE15</f>
-        <v>0</v>
-      </c>
-      <c r="BG15" s="87"/>
-      <c r="BH15" s="83"/>
-      <c r="BI15" s="83"/>
-      <c r="BJ15" s="83"/>
-      <c r="BK15" s="86">
-        <f>BI15-BJ15</f>
-        <v>0</v>
-      </c>
-      <c r="BL15" s="87"/>
-      <c r="BM15" s="83"/>
-      <c r="BN15" s="83"/>
-      <c r="BO15" s="83"/>
-      <c r="BP15" s="86">
-        <f>BN15-BO15</f>
-        <v>0</v>
-      </c>
-      <c r="BQ15" s="87"/>
-      <c r="BR15" s="83"/>
-      <c r="BS15" s="83"/>
-      <c r="BT15" s="83"/>
-      <c r="BU15" s="86">
-        <f>BS15-BT15</f>
-        <v>0</v>
-      </c>
-      <c r="BV15" s="88">
-        <v>0</v>
-      </c>
-      <c r="BW15" s="89"/>
-      <c r="BX15" s="90"/>
-      <c r="BY15" s="78"/>
-      <c r="BZ15" s="78"/>
-      <c r="CA15" s="78"/>
-      <c r="CB15" s="78"/>
-      <c r="CC15" s="78"/>
-      <c r="CD15" s="78"/>
-      <c r="CE15" s="78"/>
-      <c r="CF15" s="78"/>
-      <c r="CG15" s="78"/>
-      <c r="CH15" s="78"/>
-      <c r="CI15" s="78"/>
-      <c r="CJ15" s="78"/>
-      <c r="CK15" s="78"/>
-      <c r="CL15" s="78"/>
-      <c r="CM15" s="78"/>
-      <c r="CN15" s="78"/>
-      <c r="CO15" s="78"/>
-      <c r="CP15" s="78"/>
-      <c r="CQ15" s="78"/>
-      <c r="CR15" s="78"/>
-      <c r="CS15" s="78"/>
-      <c r="CT15" s="78"/>
-      <c r="CU15" s="78"/>
-      <c r="CV15" s="78"/>
-      <c r="CW15" s="78"/>
-      <c r="CX15" s="78"/>
-      <c r="CY15" s="78"/>
-      <c r="CZ15" s="78"/>
-      <c r="DA15" s="78"/>
-      <c r="DB15" s="78"/>
-      <c r="DC15" s="78"/>
-      <c r="DD15" s="78"/>
-      <c r="DE15" s="78"/>
-      <c r="DF15" s="78"/>
-      <c r="DG15" s="78"/>
-      <c r="DH15" s="78"/>
-      <c r="DI15" s="78"/>
-      <c r="DJ15" s="78"/>
-      <c r="DK15" s="78"/>
-      <c r="DL15" s="78"/>
-      <c r="DM15" s="78"/>
-      <c r="DN15" s="78"/>
-      <c r="DO15" s="78"/>
-      <c r="DP15" s="78"/>
-      <c r="DQ15" s="78"/>
-      <c r="DR15" s="78"/>
-      <c r="DS15" s="78"/>
-      <c r="DT15" s="78"/>
-      <c r="DU15" s="78"/>
-      <c r="DV15" s="78"/>
-      <c r="DW15" s="78"/>
-      <c r="DX15" s="78"/>
-      <c r="DY15" s="78"/>
-      <c r="DZ15" s="78"/>
-      <c r="EA15" s="78"/>
-      <c r="EB15" s="78"/>
-      <c r="EC15" s="78"/>
-      <c r="ED15" s="78"/>
-      <c r="EE15" s="78"/>
-      <c r="EF15" s="78"/>
-      <c r="EG15" s="78"/>
-      <c r="EH15" s="78"/>
-      <c r="EI15" s="78"/>
     </row>
     <row r="16" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="79" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="83">
-        <v>9501133442</v>
-      </c>
-      <c r="C16" s="98">
+      <c r="B16" s="94">
+        <v>9501133449</v>
+      </c>
+      <c r="C16" s="96">
         <v>45993</v>
       </c>
-      <c r="D16" s="98">
-        <v>46356</v>
-      </c>
-      <c r="E16" s="92" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="92" t="s">
-        <v>102</v>
-      </c>
-      <c r="G16" s="92">
+      <c r="D16" s="96">
+        <v>46173</v>
+      </c>
+      <c r="E16" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="80" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="80">
         <v>41500000</v>
       </c>
-      <c r="H16" s="92">
+      <c r="H16" s="80">
         <v>3840</v>
       </c>
-      <c r="I16" s="92" t="s">
+      <c r="I16" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="J16" s="92">
+      <c r="J16" s="80">
         <v>2430238</v>
       </c>
-      <c r="K16" s="99">
-        <v>124418</v>
-      </c>
-      <c r="L16" s="102" t="s">
-        <v>167</v>
-      </c>
-      <c r="M16" s="103" t="s">
+      <c r="K16" s="97">
+        <v>66363</v>
+      </c>
+      <c r="L16" s="100" t="s">
+        <v>165</v>
+      </c>
+      <c r="M16" s="101" t="s">
         <v>166</v>
       </c>
       <c r="N16" s="82"/>
@@ -3222,7 +3052,7 @@
       <c r="AC16" s="87"/>
       <c r="AD16" s="83"/>
       <c r="AE16" s="83"/>
-      <c r="AF16" s="84"/>
+      <c r="AF16" s="83"/>
       <c r="AG16" s="86">
         <f>AE16-AF16</f>
         <v>0</v>
@@ -3230,7 +3060,7 @@
       <c r="AH16" s="87"/>
       <c r="AI16" s="83"/>
       <c r="AJ16" s="83"/>
-      <c r="AK16" s="84"/>
+      <c r="AK16" s="83"/>
       <c r="AL16" s="86">
         <f>AJ16-AK16</f>
         <v>0</v>
@@ -3238,7 +3068,7 @@
       <c r="AM16" s="87"/>
       <c r="AN16" s="83"/>
       <c r="AO16" s="83"/>
-      <c r="AP16" s="84"/>
+      <c r="AP16" s="83"/>
       <c r="AQ16" s="86">
         <f>AO16-AP16</f>
         <v>0</v>
@@ -3246,7 +3076,7 @@
       <c r="AR16" s="87"/>
       <c r="AS16" s="83"/>
       <c r="AT16" s="83"/>
-      <c r="AU16" s="84"/>
+      <c r="AU16" s="83"/>
       <c r="AV16" s="86">
         <f>AT16-AU16</f>
         <v>0</v>
@@ -3254,7 +3084,7 @@
       <c r="AW16" s="87"/>
       <c r="AX16" s="83"/>
       <c r="AY16" s="83"/>
-      <c r="AZ16" s="84"/>
+      <c r="AZ16" s="83"/>
       <c r="BA16" s="86">
         <f>AY16-AZ16</f>
         <v>0</v>
@@ -3262,7 +3092,7 @@
       <c r="BB16" s="87"/>
       <c r="BC16" s="83"/>
       <c r="BD16" s="83"/>
-      <c r="BE16" s="84"/>
+      <c r="BE16" s="83"/>
       <c r="BF16" s="86">
         <f>BD16-BE16</f>
         <v>0</v>
@@ -3270,7 +3100,7 @@
       <c r="BG16" s="87"/>
       <c r="BH16" s="83"/>
       <c r="BI16" s="83"/>
-      <c r="BJ16" s="84"/>
+      <c r="BJ16" s="83"/>
       <c r="BK16" s="86">
         <f>BI16-BJ16</f>
         <v>0</v>
@@ -3278,7 +3108,7 @@
       <c r="BL16" s="87"/>
       <c r="BM16" s="83"/>
       <c r="BN16" s="83"/>
-      <c r="BO16" s="84"/>
+      <c r="BO16" s="83"/>
       <c r="BP16" s="86">
         <f>BN16-BO16</f>
         <v>0</v>
@@ -3286,12 +3116,12 @@
       <c r="BQ16" s="87"/>
       <c r="BR16" s="83"/>
       <c r="BS16" s="83"/>
-      <c r="BT16" s="84"/>
+      <c r="BT16" s="83"/>
       <c r="BU16" s="86">
         <f>BS16-BT16</f>
         <v>0</v>
       </c>
-      <c r="BV16" s="85">
+      <c r="BV16" s="88">
         <v>0</v>
       </c>
       <c r="BW16" s="89"/>
@@ -3360,42 +3190,42 @@
       <c r="EH16" s="78"/>
       <c r="EI16" s="78"/>
     </row>
-    <row r="17" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:139" x14ac:dyDescent="0.25">
       <c r="A17" s="91" t="s">
         <v>97</v>
       </c>
       <c r="B17" s="83">
-        <v>9100561560</v>
+        <v>9501133442</v>
       </c>
       <c r="C17" s="98">
-        <v>46137</v>
+        <v>45993</v>
       </c>
       <c r="D17" s="98">
-        <v>46501</v>
+        <v>46356</v>
       </c>
       <c r="E17" s="92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F17" s="92" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G17" s="92">
-        <v>61010000</v>
+        <v>41500000</v>
       </c>
       <c r="H17" s="92">
-        <v>1400</v>
+        <v>3840</v>
       </c>
       <c r="I17" s="92" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J17" s="92">
-        <v>2321403</v>
+        <v>2430238</v>
       </c>
       <c r="K17" s="99">
-        <v>21098.22</v>
-      </c>
-      <c r="L17" s="104" t="s">
-        <v>168</v>
+        <v>124418</v>
+      </c>
+      <c r="L17" s="102" t="s">
+        <v>167</v>
       </c>
       <c r="M17" s="103" t="s">
         <v>166</v>
@@ -3405,7 +3235,7 @@
       <c r="P17" s="83"/>
       <c r="Q17" s="84"/>
       <c r="R17" s="84">
-        <f t="shared" ref="R17:R24" si="0">P17-Q17</f>
+        <f>P17-Q17</f>
         <v>0</v>
       </c>
       <c r="S17" s="85"/>
@@ -3413,7 +3243,7 @@
       <c r="U17" s="83"/>
       <c r="V17" s="84"/>
       <c r="W17" s="86">
-        <f t="shared" ref="W17:W24" si="1">U17-V17</f>
+        <f>U17-V17</f>
         <v>0</v>
       </c>
       <c r="X17" s="87"/>
@@ -3421,7 +3251,7 @@
       <c r="Z17" s="83"/>
       <c r="AA17" s="84"/>
       <c r="AB17" s="86">
-        <f t="shared" ref="AB17:AB24" si="2">Z17-AA17</f>
+        <f>Z17-AA17</f>
         <v>0</v>
       </c>
       <c r="AC17" s="87"/>
@@ -3429,7 +3259,7 @@
       <c r="AE17" s="83"/>
       <c r="AF17" s="84"/>
       <c r="AG17" s="86">
-        <f t="shared" ref="AG17:AG24" si="3">AE17-AF17</f>
+        <f>AE17-AF17</f>
         <v>0</v>
       </c>
       <c r="AH17" s="87"/>
@@ -3437,7 +3267,7 @@
       <c r="AJ17" s="83"/>
       <c r="AK17" s="84"/>
       <c r="AL17" s="86">
-        <f t="shared" ref="AL17:AL24" si="4">AJ17-AK17</f>
+        <f>AJ17-AK17</f>
         <v>0</v>
       </c>
       <c r="AM17" s="87"/>
@@ -3445,7 +3275,7 @@
       <c r="AO17" s="83"/>
       <c r="AP17" s="84"/>
       <c r="AQ17" s="86">
-        <f t="shared" ref="AQ17:AQ24" si="5">AO17-AP17</f>
+        <f>AO17-AP17</f>
         <v>0</v>
       </c>
       <c r="AR17" s="87"/>
@@ -3453,7 +3283,7 @@
       <c r="AT17" s="83"/>
       <c r="AU17" s="84"/>
       <c r="AV17" s="86">
-        <f t="shared" ref="AV17:AV24" si="6">AT17-AU17</f>
+        <f>AT17-AU17</f>
         <v>0</v>
       </c>
       <c r="AW17" s="87"/>
@@ -3461,7 +3291,7 @@
       <c r="AY17" s="83"/>
       <c r="AZ17" s="84"/>
       <c r="BA17" s="86">
-        <f t="shared" ref="BA17:BA24" si="7">AY17-AZ17</f>
+        <f>AY17-AZ17</f>
         <v>0</v>
       </c>
       <c r="BB17" s="87"/>
@@ -3469,7 +3299,7 @@
       <c r="BD17" s="83"/>
       <c r="BE17" s="84"/>
       <c r="BF17" s="86">
-        <f t="shared" ref="BF17:BF24" si="8">BD17-BE17</f>
+        <f>BD17-BE17</f>
         <v>0</v>
       </c>
       <c r="BG17" s="87"/>
@@ -3477,7 +3307,7 @@
       <c r="BI17" s="83"/>
       <c r="BJ17" s="84"/>
       <c r="BK17" s="86">
-        <f t="shared" ref="BK17:BK24" si="9">BI17-BJ17</f>
+        <f>BI17-BJ17</f>
         <v>0</v>
       </c>
       <c r="BL17" s="87"/>
@@ -3485,7 +3315,7 @@
       <c r="BN17" s="83"/>
       <c r="BO17" s="84"/>
       <c r="BP17" s="86">
-        <f t="shared" ref="BP17:BP24" si="10">BN17-BO17</f>
+        <f>BN17-BO17</f>
         <v>0</v>
       </c>
       <c r="BQ17" s="87"/>
@@ -3493,7 +3323,7 @@
       <c r="BS17" s="83"/>
       <c r="BT17" s="84"/>
       <c r="BU17" s="86">
-        <f t="shared" ref="BU17:BU24" si="11">BS17-BT17</f>
+        <f>BS17-BT17</f>
         <v>0</v>
       </c>
       <c r="BV17" s="85">
@@ -3501,37 +3331,116 @@
       </c>
       <c r="BW17" s="89"/>
       <c r="BX17" s="90"/>
+      <c r="BY17" s="78"/>
+      <c r="BZ17" s="78"/>
+      <c r="CA17" s="78"/>
+      <c r="CB17" s="78"/>
+      <c r="CC17" s="78"/>
+      <c r="CD17" s="78"/>
+      <c r="CE17" s="78"/>
+      <c r="CF17" s="78"/>
+      <c r="CG17" s="78"/>
+      <c r="CH17" s="78"/>
+      <c r="CI17" s="78"/>
+      <c r="CJ17" s="78"/>
+      <c r="CK17" s="78"/>
+      <c r="CL17" s="78"/>
+      <c r="CM17" s="78"/>
+      <c r="CN17" s="78"/>
+      <c r="CO17" s="78"/>
+      <c r="CP17" s="78"/>
+      <c r="CQ17" s="78"/>
+      <c r="CR17" s="78"/>
+      <c r="CS17" s="78"/>
+      <c r="CT17" s="78"/>
+      <c r="CU17" s="78"/>
+      <c r="CV17" s="78"/>
+      <c r="CW17" s="78"/>
+      <c r="CX17" s="78"/>
+      <c r="CY17" s="78"/>
+      <c r="CZ17" s="78"/>
+      <c r="DA17" s="78"/>
+      <c r="DB17" s="78"/>
+      <c r="DC17" s="78"/>
+      <c r="DD17" s="78"/>
+      <c r="DE17" s="78"/>
+      <c r="DF17" s="78"/>
+      <c r="DG17" s="78"/>
+      <c r="DH17" s="78"/>
+      <c r="DI17" s="78"/>
+      <c r="DJ17" s="78"/>
+      <c r="DK17" s="78"/>
+      <c r="DL17" s="78"/>
+      <c r="DM17" s="78"/>
+      <c r="DN17" s="78"/>
+      <c r="DO17" s="78"/>
+      <c r="DP17" s="78"/>
+      <c r="DQ17" s="78"/>
+      <c r="DR17" s="78"/>
+      <c r="DS17" s="78"/>
+      <c r="DT17" s="78"/>
+      <c r="DU17" s="78"/>
+      <c r="DV17" s="78"/>
+      <c r="DW17" s="78"/>
+      <c r="DX17" s="78"/>
+      <c r="DY17" s="78"/>
+      <c r="DZ17" s="78"/>
+      <c r="EA17" s="78"/>
+      <c r="EB17" s="78"/>
+      <c r="EC17" s="78"/>
+      <c r="ED17" s="78"/>
+      <c r="EE17" s="78"/>
+      <c r="EF17" s="78"/>
+      <c r="EG17" s="78"/>
+      <c r="EH17" s="78"/>
+      <c r="EI17" s="78"/>
     </row>
-    <row r="18" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:139" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="91" t="s">
         <v>97</v>
       </c>
       <c r="B18" s="83">
-        <v>9501079958</v>
+        <v>9100561560</v>
       </c>
       <c r="C18" s="98">
-        <v>45931</v>
+        <v>46137</v>
       </c>
       <c r="D18" s="98">
-        <v>46265</v>
+        <v>46501</v>
       </c>
       <c r="E18" s="92" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" s="92"/>
-      <c r="G18" s="92"/>
-      <c r="H18" s="92"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="93"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="103"/>
+        <v>103</v>
+      </c>
+      <c r="F18" s="92" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="92">
+        <v>61010000</v>
+      </c>
+      <c r="H18" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I18" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J18" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K18" s="99">
+        <v>21098.22</v>
+      </c>
+      <c r="L18" s="104" t="s">
+        <v>168</v>
+      </c>
+      <c r="M18" s="103" t="s">
+        <v>166</v>
+      </c>
       <c r="N18" s="82"/>
       <c r="O18" s="83"/>
       <c r="P18" s="83"/>
       <c r="Q18" s="84"/>
       <c r="R18" s="84">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="R18:R25" si="0">P18-Q18</f>
         <v>0</v>
       </c>
       <c r="S18" s="85"/>
@@ -3539,7 +3448,7 @@
       <c r="U18" s="83"/>
       <c r="V18" s="84"/>
       <c r="W18" s="86">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="W18:W25" si="1">U18-V18</f>
         <v>0</v>
       </c>
       <c r="X18" s="87"/>
@@ -3547,7 +3456,7 @@
       <c r="Z18" s="83"/>
       <c r="AA18" s="84"/>
       <c r="AB18" s="86">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AB18:AB25" si="2">Z18-AA18</f>
         <v>0</v>
       </c>
       <c r="AC18" s="87"/>
@@ -3555,7 +3464,7 @@
       <c r="AE18" s="83"/>
       <c r="AF18" s="84"/>
       <c r="AG18" s="86">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="AG18:AG25" si="3">AE18-AF18</f>
         <v>0</v>
       </c>
       <c r="AH18" s="87"/>
@@ -3563,7 +3472,7 @@
       <c r="AJ18" s="83"/>
       <c r="AK18" s="84"/>
       <c r="AL18" s="86">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="AL18:AL25" si="4">AJ18-AK18</f>
         <v>0</v>
       </c>
       <c r="AM18" s="87"/>
@@ -3571,7 +3480,7 @@
       <c r="AO18" s="83"/>
       <c r="AP18" s="84"/>
       <c r="AQ18" s="86">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="AQ18:AQ25" si="5">AO18-AP18</f>
         <v>0</v>
       </c>
       <c r="AR18" s="87"/>
@@ -3579,7 +3488,7 @@
       <c r="AT18" s="83"/>
       <c r="AU18" s="84"/>
       <c r="AV18" s="86">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="AV18:AV25" si="6">AT18-AU18</f>
         <v>0</v>
       </c>
       <c r="AW18" s="87"/>
@@ -3587,7 +3496,7 @@
       <c r="AY18" s="83"/>
       <c r="AZ18" s="84"/>
       <c r="BA18" s="86">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="BA18:BA25" si="7">AY18-AZ18</f>
         <v>0</v>
       </c>
       <c r="BB18" s="87"/>
@@ -3595,7 +3504,7 @@
       <c r="BD18" s="83"/>
       <c r="BE18" s="84"/>
       <c r="BF18" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="BF18:BF25" si="8">BD18-BE18</f>
         <v>0</v>
       </c>
       <c r="BG18" s="87"/>
@@ -3603,7 +3512,7 @@
       <c r="BI18" s="83"/>
       <c r="BJ18" s="84"/>
       <c r="BK18" s="86">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="BK18:BK25" si="9">BI18-BJ18</f>
         <v>0</v>
       </c>
       <c r="BL18" s="87"/>
@@ -3611,7 +3520,7 @@
       <c r="BN18" s="83"/>
       <c r="BO18" s="84"/>
       <c r="BP18" s="86">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="BP18:BP25" si="10">BN18-BO18</f>
         <v>0</v>
       </c>
       <c r="BQ18" s="87"/>
@@ -3619,7 +3528,7 @@
       <c r="BS18" s="83"/>
       <c r="BT18" s="84"/>
       <c r="BU18" s="86">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="BU18:BU25" si="11">BS18-BT18</f>
         <v>0</v>
       </c>
       <c r="BV18" s="85">
@@ -3628,46 +3537,30 @@
       <c r="BW18" s="89"/>
       <c r="BX18" s="90"/>
     </row>
-    <row r="19" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:139" x14ac:dyDescent="0.25">
       <c r="A19" s="91" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B19" s="83">
-        <v>9501215650</v>
+        <v>9501079958</v>
       </c>
       <c r="C19" s="98">
-        <v>46065</v>
+        <v>45931</v>
       </c>
       <c r="D19" s="98">
-        <v>46387</v>
+        <v>46265</v>
       </c>
       <c r="E19" s="92" t="s">
-        <v>108</v>
-      </c>
-      <c r="F19" s="92" t="s">
-        <v>109</v>
-      </c>
-      <c r="G19" s="92">
-        <v>41500000</v>
-      </c>
-      <c r="H19" s="92">
-        <v>1400</v>
-      </c>
-      <c r="I19" s="92" t="s">
-        <v>105</v>
-      </c>
-      <c r="J19" s="92">
-        <v>2340693</v>
-      </c>
-      <c r="K19" s="99">
-        <v>54880</v>
-      </c>
-      <c r="L19" s="104" t="s">
-        <v>169</v>
-      </c>
-      <c r="M19" s="103" t="s">
-        <v>166</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="103"/>
       <c r="N19" s="82"/>
       <c r="O19" s="83"/>
       <c r="P19" s="83"/>
@@ -3770,28 +3663,46 @@
       <c r="BW19" s="89"/>
       <c r="BX19" s="90"/>
     </row>
-    <row r="20" spans="1:76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="91"/>
-      <c r="B20" s="83" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="92"/>
-      <c r="D20" s="92"/>
-      <c r="E20" s="92"/>
+    <row r="20" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A20" s="91" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" s="83">
+        <v>9501215650</v>
+      </c>
+      <c r="C20" s="98">
+        <v>46065</v>
+      </c>
+      <c r="D20" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E20" s="92" t="s">
+        <v>108</v>
+      </c>
       <c r="F20" s="92" t="s">
-        <v>111</v>
-      </c>
-      <c r="G20" s="92"/>
-      <c r="H20" s="92"/>
-      <c r="I20" s="92"/>
-      <c r="J20" s="92"/>
+        <v>109</v>
+      </c>
+      <c r="G20" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H20" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I20" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J20" s="92">
+        <v>2340693</v>
+      </c>
       <c r="K20" s="99">
-        <v>150000</v>
-      </c>
-      <c r="L20" s="102" t="s">
-        <v>170</v>
-      </c>
-      <c r="M20" s="103"/>
+        <v>54880</v>
+      </c>
+      <c r="L20" s="104" t="s">
+        <v>169</v>
+      </c>
+      <c r="M20" s="103" t="s">
+        <v>166</v>
+      </c>
       <c r="N20" s="82"/>
       <c r="O20" s="83"/>
       <c r="P20" s="83"/>
@@ -3894,34 +3805,26 @@
       <c r="BW20" s="89"/>
       <c r="BX20" s="90"/>
     </row>
-    <row r="21" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A21" s="91" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="83"/>
+    <row r="21" spans="1:139" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="91"/>
+      <c r="B21" s="83" t="s">
+        <v>110</v>
+      </c>
       <c r="C21" s="92"/>
       <c r="D21" s="92"/>
-      <c r="E21" s="92" t="s">
-        <v>101</v>
-      </c>
+      <c r="E21" s="92"/>
       <c r="F21" s="92" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="92">
-        <v>41500000</v>
-      </c>
-      <c r="H21" s="92">
-        <v>1400</v>
-      </c>
-      <c r="I21" s="92" t="s">
-        <v>105</v>
-      </c>
-      <c r="J21" s="92">
-        <v>2321403</v>
-      </c>
-      <c r="K21" s="93"/>
+        <v>111</v>
+      </c>
+      <c r="G21" s="92"/>
+      <c r="H21" s="92"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="99">
+        <v>150000</v>
+      </c>
       <c r="L21" s="102" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M21" s="103"/>
       <c r="N21" s="82"/>
@@ -4026,22 +3929,34 @@
       <c r="BW21" s="89"/>
       <c r="BX21" s="90"/>
     </row>
-    <row r="22" spans="1:76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="91"/>
+    <row r="22" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A22" s="91" t="s">
+        <v>112</v>
+      </c>
       <c r="B22" s="83"/>
       <c r="C22" s="92"/>
       <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
+      <c r="E22" s="92" t="s">
+        <v>101</v>
+      </c>
       <c r="F22" s="92" t="s">
-        <v>113</v>
-      </c>
-      <c r="G22" s="92"/>
-      <c r="H22" s="92"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="92"/>
+        <v>102</v>
+      </c>
+      <c r="G22" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H22" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I22" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="92">
+        <v>2321403</v>
+      </c>
       <c r="K22" s="93"/>
       <c r="L22" s="102" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M22" s="103"/>
       <c r="N22" s="82"/>
@@ -4146,14 +4061,14 @@
       <c r="BW22" s="89"/>
       <c r="BX22" s="90"/>
     </row>
-    <row r="23" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:139" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="91"/>
       <c r="B23" s="83"/>
       <c r="C23" s="92"/>
       <c r="D23" s="92"/>
       <c r="E23" s="92"/>
       <c r="F23" s="92" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G23" s="92"/>
       <c r="H23" s="92"/>
@@ -4161,7 +4076,7 @@
       <c r="J23" s="92"/>
       <c r="K23" s="93"/>
       <c r="L23" s="102" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M23" s="103"/>
       <c r="N23" s="82"/>
@@ -4266,14 +4181,14 @@
       <c r="BW23" s="89"/>
       <c r="BX23" s="90"/>
     </row>
-    <row r="24" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:139" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="91"/>
       <c r="B24" s="83"/>
       <c r="C24" s="92"/>
       <c r="D24" s="92"/>
       <c r="E24" s="92"/>
       <c r="F24" s="92" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G24" s="92"/>
       <c r="H24" s="92"/>
@@ -4281,7 +4196,7 @@
       <c r="J24" s="92"/>
       <c r="K24" s="93"/>
       <c r="L24" s="102" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M24" s="103"/>
       <c r="N24" s="82"/>
@@ -4386,14 +4301,14 @@
       <c r="BW24" s="89"/>
       <c r="BX24" s="90"/>
     </row>
-    <row r="25" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:139" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="91"/>
       <c r="B25" s="83"/>
       <c r="C25" s="92"/>
       <c r="D25" s="92"/>
       <c r="E25" s="92"/>
       <c r="F25" s="92" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G25" s="92"/>
       <c r="H25" s="92"/>
@@ -4401,7 +4316,7 @@
       <c r="J25" s="92"/>
       <c r="K25" s="93"/>
       <c r="L25" s="102" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M25" s="103"/>
       <c r="N25" s="82"/>
@@ -4409,7 +4324,7 @@
       <c r="P25" s="83"/>
       <c r="Q25" s="84"/>
       <c r="R25" s="84">
-        <f t="shared" ref="R25:R29" si="12">P25-Q25</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S25" s="85"/>
@@ -4417,7 +4332,7 @@
       <c r="U25" s="83"/>
       <c r="V25" s="84"/>
       <c r="W25" s="86">
-        <f t="shared" ref="W25:W29" si="13">U25-V25</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X25" s="87"/>
@@ -4425,7 +4340,7 @@
       <c r="Z25" s="83"/>
       <c r="AA25" s="84"/>
       <c r="AB25" s="86">
-        <f t="shared" ref="AB25:AB29" si="14">Z25-AA25</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC25" s="87"/>
@@ -4433,7 +4348,7 @@
       <c r="AE25" s="83"/>
       <c r="AF25" s="84"/>
       <c r="AG25" s="86">
-        <f t="shared" ref="AG25:AG29" si="15">AE25-AF25</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH25" s="87"/>
@@ -4441,7 +4356,7 @@
       <c r="AJ25" s="83"/>
       <c r="AK25" s="84"/>
       <c r="AL25" s="86">
-        <f t="shared" ref="AL25:AL29" si="16">AJ25-AK25</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AM25" s="87"/>
@@ -4449,7 +4364,7 @@
       <c r="AO25" s="83"/>
       <c r="AP25" s="84"/>
       <c r="AQ25" s="86">
-        <f t="shared" ref="AQ25:AQ29" si="17">AO25-AP25</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AR25" s="87"/>
@@ -4457,7 +4372,7 @@
       <c r="AT25" s="83"/>
       <c r="AU25" s="84"/>
       <c r="AV25" s="86">
-        <f t="shared" ref="AV25:AV29" si="18">AT25-AU25</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW25" s="87"/>
@@ -4465,7 +4380,7 @@
       <c r="AY25" s="83"/>
       <c r="AZ25" s="84"/>
       <c r="BA25" s="86">
-        <f t="shared" ref="BA25:BA29" si="19">AY25-AZ25</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BB25" s="87"/>
@@ -4473,7 +4388,7 @@
       <c r="BD25" s="83"/>
       <c r="BE25" s="84"/>
       <c r="BF25" s="86">
-        <f t="shared" ref="BF25:BF29" si="20">BD25-BE25</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BG25" s="87"/>
@@ -4481,7 +4396,7 @@
       <c r="BI25" s="83"/>
       <c r="BJ25" s="84"/>
       <c r="BK25" s="86">
-        <f t="shared" ref="BK25:BK29" si="21">BI25-BJ25</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BL25" s="87"/>
@@ -4489,7 +4404,7 @@
       <c r="BN25" s="83"/>
       <c r="BO25" s="84"/>
       <c r="BP25" s="86">
-        <f t="shared" ref="BP25:BP29" si="22">BN25-BO25</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BQ25" s="87"/>
@@ -4497,7 +4412,7 @@
       <c r="BS25" s="83"/>
       <c r="BT25" s="84"/>
       <c r="BU25" s="86">
-        <f t="shared" ref="BU25:BU29" si="23">BS25-BT25</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BV25" s="85">
@@ -4506,14 +4421,14 @@
       <c r="BW25" s="89"/>
       <c r="BX25" s="90"/>
     </row>
-    <row r="26" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:139" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="91"/>
       <c r="B26" s="83"/>
       <c r="C26" s="92"/>
       <c r="D26" s="92"/>
       <c r="E26" s="92"/>
       <c r="F26" s="92" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G26" s="92"/>
       <c r="H26" s="92"/>
@@ -4521,7 +4436,7 @@
       <c r="J26" s="92"/>
       <c r="K26" s="93"/>
       <c r="L26" s="102" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M26" s="103"/>
       <c r="N26" s="82"/>
@@ -4529,7 +4444,7 @@
       <c r="P26" s="83"/>
       <c r="Q26" s="84"/>
       <c r="R26" s="84">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="R26:R30" si="12">P26-Q26</f>
         <v>0</v>
       </c>
       <c r="S26" s="85"/>
@@ -4537,7 +4452,7 @@
       <c r="U26" s="83"/>
       <c r="V26" s="84"/>
       <c r="W26" s="86">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="W26:W30" si="13">U26-V26</f>
         <v>0</v>
       </c>
       <c r="X26" s="87"/>
@@ -4545,7 +4460,7 @@
       <c r="Z26" s="83"/>
       <c r="AA26" s="84"/>
       <c r="AB26" s="86">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="AB26:AB30" si="14">Z26-AA26</f>
         <v>0</v>
       </c>
       <c r="AC26" s="87"/>
@@ -4553,7 +4468,7 @@
       <c r="AE26" s="83"/>
       <c r="AF26" s="84"/>
       <c r="AG26" s="86">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="AG26:AG30" si="15">AE26-AF26</f>
         <v>0</v>
       </c>
       <c r="AH26" s="87"/>
@@ -4561,7 +4476,7 @@
       <c r="AJ26" s="83"/>
       <c r="AK26" s="84"/>
       <c r="AL26" s="86">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="AL26:AL30" si="16">AJ26-AK26</f>
         <v>0</v>
       </c>
       <c r="AM26" s="87"/>
@@ -4569,7 +4484,7 @@
       <c r="AO26" s="83"/>
       <c r="AP26" s="84"/>
       <c r="AQ26" s="86">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="AQ26:AQ30" si="17">AO26-AP26</f>
         <v>0</v>
       </c>
       <c r="AR26" s="87"/>
@@ -4577,7 +4492,7 @@
       <c r="AT26" s="83"/>
       <c r="AU26" s="84"/>
       <c r="AV26" s="86">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="AV26:AV30" si="18">AT26-AU26</f>
         <v>0</v>
       </c>
       <c r="AW26" s="87"/>
@@ -4585,7 +4500,7 @@
       <c r="AY26" s="83"/>
       <c r="AZ26" s="84"/>
       <c r="BA26" s="86">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="BA26:BA30" si="19">AY26-AZ26</f>
         <v>0</v>
       </c>
       <c r="BB26" s="87"/>
@@ -4593,7 +4508,7 @@
       <c r="BD26" s="83"/>
       <c r="BE26" s="84"/>
       <c r="BF26" s="86">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="BF26:BF30" si="20">BD26-BE26</f>
         <v>0</v>
       </c>
       <c r="BG26" s="87"/>
@@ -4601,7 +4516,7 @@
       <c r="BI26" s="83"/>
       <c r="BJ26" s="84"/>
       <c r="BK26" s="86">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="BK26:BK30" si="21">BI26-BJ26</f>
         <v>0</v>
       </c>
       <c r="BL26" s="87"/>
@@ -4609,7 +4524,7 @@
       <c r="BN26" s="83"/>
       <c r="BO26" s="84"/>
       <c r="BP26" s="86">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="BP26:BP30" si="22">BN26-BO26</f>
         <v>0</v>
       </c>
       <c r="BQ26" s="87"/>
@@ -4617,7 +4532,7 @@
       <c r="BS26" s="83"/>
       <c r="BT26" s="84"/>
       <c r="BU26" s="86">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="BU26:BU30" si="23">BS26-BT26</f>
         <v>0</v>
       </c>
       <c r="BV26" s="85">
@@ -4626,14 +4541,14 @@
       <c r="BW26" s="89"/>
       <c r="BX26" s="90"/>
     </row>
-    <row r="27" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:139" x14ac:dyDescent="0.25">
       <c r="A27" s="91"/>
       <c r="B27" s="83"/>
       <c r="C27" s="92"/>
       <c r="D27" s="92"/>
       <c r="E27" s="92"/>
       <c r="F27" s="92" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G27" s="92"/>
       <c r="H27" s="92"/>
@@ -4641,7 +4556,7 @@
       <c r="J27" s="92"/>
       <c r="K27" s="93"/>
       <c r="L27" s="102" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M27" s="103"/>
       <c r="N27" s="82"/>
@@ -4746,14 +4661,14 @@
       <c r="BW27" s="89"/>
       <c r="BX27" s="90"/>
     </row>
-    <row r="28" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:139" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="91"/>
       <c r="B28" s="83"/>
       <c r="C28" s="92"/>
       <c r="D28" s="92"/>
       <c r="E28" s="92"/>
       <c r="F28" s="92" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G28" s="92"/>
       <c r="H28" s="92"/>
@@ -4761,7 +4676,7 @@
       <c r="J28" s="92"/>
       <c r="K28" s="93"/>
       <c r="L28" s="102" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M28" s="103"/>
       <c r="N28" s="82"/>
@@ -4866,14 +4781,14 @@
       <c r="BW28" s="89"/>
       <c r="BX28" s="90"/>
     </row>
-    <row r="29" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:139" x14ac:dyDescent="0.25">
       <c r="A29" s="91"/>
       <c r="B29" s="83"/>
       <c r="C29" s="92"/>
       <c r="D29" s="92"/>
       <c r="E29" s="92"/>
       <c r="F29" s="92" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G29" s="92"/>
       <c r="H29" s="92"/>
@@ -4986,14 +4901,14 @@
       <c r="BW29" s="89"/>
       <c r="BX29" s="90"/>
     </row>
-    <row r="30" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:139" x14ac:dyDescent="0.25">
       <c r="A30" s="91"/>
       <c r="B30" s="83"/>
       <c r="C30" s="92"/>
       <c r="D30" s="92"/>
       <c r="E30" s="92"/>
       <c r="F30" s="92" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G30" s="92"/>
       <c r="H30" s="92"/>
@@ -5001,7 +4916,7 @@
       <c r="J30" s="92"/>
       <c r="K30" s="93"/>
       <c r="L30" s="102" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M30" s="103"/>
       <c r="N30" s="82"/>
@@ -5009,7 +4924,7 @@
       <c r="P30" s="83"/>
       <c r="Q30" s="84"/>
       <c r="R30" s="84">
-        <f t="shared" ref="R30:R64" si="24">P30-Q30</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S30" s="85"/>
@@ -5017,7 +4932,7 @@
       <c r="U30" s="83"/>
       <c r="V30" s="84"/>
       <c r="W30" s="86">
-        <f t="shared" ref="W30:W64" si="25">U30-V30</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="X30" s="87"/>
@@ -5025,7 +4940,7 @@
       <c r="Z30" s="83"/>
       <c r="AA30" s="84"/>
       <c r="AB30" s="86">
-        <f t="shared" ref="AB30:AB64" si="26">Z30-AA30</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC30" s="87"/>
@@ -5033,7 +4948,7 @@
       <c r="AE30" s="83"/>
       <c r="AF30" s="84"/>
       <c r="AG30" s="86">
-        <f t="shared" ref="AG30:AG64" si="27">AE30-AF30</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH30" s="87"/>
@@ -5041,7 +4956,7 @@
       <c r="AJ30" s="83"/>
       <c r="AK30" s="84"/>
       <c r="AL30" s="86">
-        <f t="shared" ref="AL30:AL64" si="28">AJ30-AK30</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AM30" s="87"/>
@@ -5049,7 +4964,7 @@
       <c r="AO30" s="83"/>
       <c r="AP30" s="84"/>
       <c r="AQ30" s="86">
-        <f t="shared" ref="AQ30:AQ64" si="29">AO30-AP30</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AR30" s="87"/>
@@ -5057,7 +4972,7 @@
       <c r="AT30" s="83"/>
       <c r="AU30" s="84"/>
       <c r="AV30" s="86">
-        <f t="shared" ref="AV30:AV64" si="30">AT30-AU30</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AW30" s="87"/>
@@ -5065,7 +4980,7 @@
       <c r="AY30" s="83"/>
       <c r="AZ30" s="84"/>
       <c r="BA30" s="86">
-        <f t="shared" ref="BA30:BA64" si="31">AY30-AZ30</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB30" s="87"/>
@@ -5073,7 +4988,7 @@
       <c r="BD30" s="83"/>
       <c r="BE30" s="84"/>
       <c r="BF30" s="86">
-        <f t="shared" ref="BF30:BF64" si="32">BD30-BE30</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BG30" s="87"/>
@@ -5081,7 +4996,7 @@
       <c r="BI30" s="83"/>
       <c r="BJ30" s="84"/>
       <c r="BK30" s="86">
-        <f t="shared" ref="BK30:BK64" si="33">BI30-BJ30</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BL30" s="87"/>
@@ -5089,7 +5004,7 @@
       <c r="BN30" s="83"/>
       <c r="BO30" s="84"/>
       <c r="BP30" s="86">
-        <f t="shared" ref="BP30:BP64" si="34">BN30-BO30</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BQ30" s="87"/>
@@ -5097,7 +5012,7 @@
       <c r="BS30" s="83"/>
       <c r="BT30" s="84"/>
       <c r="BU30" s="86">
-        <f t="shared" ref="BU30:BU64" si="35">BS30-BT30</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BV30" s="85">
@@ -5106,14 +5021,14 @@
       <c r="BW30" s="89"/>
       <c r="BX30" s="90"/>
     </row>
-    <row r="31" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:139" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="91"/>
       <c r="B31" s="83"/>
       <c r="C31" s="92"/>
       <c r="D31" s="92"/>
       <c r="E31" s="92"/>
       <c r="F31" s="92" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G31" s="92"/>
       <c r="H31" s="92"/>
@@ -5121,7 +5036,7 @@
       <c r="J31" s="92"/>
       <c r="K31" s="93"/>
       <c r="L31" s="102" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M31" s="103"/>
       <c r="N31" s="82"/>
@@ -5129,7 +5044,7 @@
       <c r="P31" s="83"/>
       <c r="Q31" s="84"/>
       <c r="R31" s="84">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="R31:R65" si="24">P31-Q31</f>
         <v>0</v>
       </c>
       <c r="S31" s="85"/>
@@ -5137,7 +5052,7 @@
       <c r="U31" s="83"/>
       <c r="V31" s="84"/>
       <c r="W31" s="86">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="W31:W65" si="25">U31-V31</f>
         <v>0</v>
       </c>
       <c r="X31" s="87"/>
@@ -5145,7 +5060,7 @@
       <c r="Z31" s="83"/>
       <c r="AA31" s="84"/>
       <c r="AB31" s="86">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="AB31:AB65" si="26">Z31-AA31</f>
         <v>0</v>
       </c>
       <c r="AC31" s="87"/>
@@ -5153,7 +5068,7 @@
       <c r="AE31" s="83"/>
       <c r="AF31" s="84"/>
       <c r="AG31" s="86">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="AG31:AG65" si="27">AE31-AF31</f>
         <v>0</v>
       </c>
       <c r="AH31" s="87"/>
@@ -5161,7 +5076,7 @@
       <c r="AJ31" s="83"/>
       <c r="AK31" s="84"/>
       <c r="AL31" s="86">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="AL31:AL65" si="28">AJ31-AK31</f>
         <v>0</v>
       </c>
       <c r="AM31" s="87"/>
@@ -5169,7 +5084,7 @@
       <c r="AO31" s="83"/>
       <c r="AP31" s="84"/>
       <c r="AQ31" s="86">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="AQ31:AQ65" si="29">AO31-AP31</f>
         <v>0</v>
       </c>
       <c r="AR31" s="87"/>
@@ -5177,7 +5092,7 @@
       <c r="AT31" s="83"/>
       <c r="AU31" s="84"/>
       <c r="AV31" s="86">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="AV31:AV65" si="30">AT31-AU31</f>
         <v>0</v>
       </c>
       <c r="AW31" s="87"/>
@@ -5185,7 +5100,7 @@
       <c r="AY31" s="83"/>
       <c r="AZ31" s="84"/>
       <c r="BA31" s="86">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="BA31:BA65" si="31">AY31-AZ31</f>
         <v>0</v>
       </c>
       <c r="BB31" s="87"/>
@@ -5193,7 +5108,7 @@
       <c r="BD31" s="83"/>
       <c r="BE31" s="84"/>
       <c r="BF31" s="86">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="BF31:BF65" si="32">BD31-BE31</f>
         <v>0</v>
       </c>
       <c r="BG31" s="87"/>
@@ -5201,7 +5116,7 @@
       <c r="BI31" s="83"/>
       <c r="BJ31" s="84"/>
       <c r="BK31" s="86">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="BK31:BK65" si="33">BI31-BJ31</f>
         <v>0</v>
       </c>
       <c r="BL31" s="87"/>
@@ -5209,7 +5124,7 @@
       <c r="BN31" s="83"/>
       <c r="BO31" s="84"/>
       <c r="BP31" s="86">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="BP31:BP65" si="34">BN31-BO31</f>
         <v>0</v>
       </c>
       <c r="BQ31" s="87"/>
@@ -5217,7 +5132,7 @@
       <c r="BS31" s="83"/>
       <c r="BT31" s="84"/>
       <c r="BU31" s="86">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="BU31:BU65" si="35">BS31-BT31</f>
         <v>0</v>
       </c>
       <c r="BV31" s="85">
@@ -5226,14 +5141,14 @@
       <c r="BW31" s="89"/>
       <c r="BX31" s="90"/>
     </row>
-    <row r="32" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:139" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="91"/>
       <c r="B32" s="83"/>
       <c r="C32" s="92"/>
       <c r="D32" s="92"/>
       <c r="E32" s="92"/>
       <c r="F32" s="92" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G32" s="92"/>
       <c r="H32" s="92"/>
@@ -5241,7 +5156,7 @@
       <c r="J32" s="92"/>
       <c r="K32" s="93"/>
       <c r="L32" s="102" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M32" s="103"/>
       <c r="N32" s="82"/>
@@ -5346,14 +5261,14 @@
       <c r="BW32" s="89"/>
       <c r="BX32" s="90"/>
     </row>
-    <row r="33" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:76" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="91"/>
       <c r="B33" s="83"/>
       <c r="C33" s="92"/>
       <c r="D33" s="92"/>
       <c r="E33" s="92"/>
       <c r="F33" s="92" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G33" s="92"/>
       <c r="H33" s="92"/>
@@ -5361,7 +5276,7 @@
       <c r="J33" s="92"/>
       <c r="K33" s="93"/>
       <c r="L33" s="102" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M33" s="103"/>
       <c r="N33" s="82"/>
@@ -5466,14 +5381,14 @@
       <c r="BW33" s="89"/>
       <c r="BX33" s="90"/>
     </row>
-    <row r="34" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A34" s="91"/>
       <c r="B34" s="83"/>
       <c r="C34" s="92"/>
       <c r="D34" s="92"/>
       <c r="E34" s="92"/>
       <c r="F34" s="92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G34" s="92"/>
       <c r="H34" s="92"/>
@@ -5481,7 +5396,7 @@
       <c r="J34" s="92"/>
       <c r="K34" s="93"/>
       <c r="L34" s="102" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M34" s="103"/>
       <c r="N34" s="82"/>
@@ -5586,14 +5501,14 @@
       <c r="BW34" s="89"/>
       <c r="BX34" s="90"/>
     </row>
-    <row r="35" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="91"/>
       <c r="B35" s="83"/>
       <c r="C35" s="92"/>
       <c r="D35" s="92"/>
       <c r="E35" s="92"/>
       <c r="F35" s="92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G35" s="92"/>
       <c r="H35" s="92"/>
@@ -5601,7 +5516,7 @@
       <c r="J35" s="92"/>
       <c r="K35" s="93"/>
       <c r="L35" s="102" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M35" s="103"/>
       <c r="N35" s="82"/>
@@ -5713,7 +5628,7 @@
       <c r="D36" s="92"/>
       <c r="E36" s="92"/>
       <c r="F36" s="92" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G36" s="92"/>
       <c r="H36" s="92"/>
@@ -5721,7 +5636,7 @@
       <c r="J36" s="92"/>
       <c r="K36" s="93"/>
       <c r="L36" s="102" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M36" s="103"/>
       <c r="N36" s="82"/>
@@ -5833,7 +5748,7 @@
       <c r="D37" s="92"/>
       <c r="E37" s="92"/>
       <c r="F37" s="92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G37" s="92"/>
       <c r="H37" s="92"/>
@@ -5841,7 +5756,7 @@
       <c r="J37" s="92"/>
       <c r="K37" s="93"/>
       <c r="L37" s="102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M37" s="103"/>
       <c r="N37" s="82"/>
@@ -5953,7 +5868,7 @@
       <c r="D38" s="92"/>
       <c r="E38" s="92"/>
       <c r="F38" s="92" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="G38" s="92"/>
       <c r="H38" s="92"/>
@@ -5961,7 +5876,7 @@
       <c r="J38" s="92"/>
       <c r="K38" s="93"/>
       <c r="L38" s="102" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M38" s="103"/>
       <c r="N38" s="82"/>
@@ -6066,14 +5981,14 @@
       <c r="BW38" s="89"/>
       <c r="BX38" s="90"/>
     </row>
-    <row r="39" spans="1:76" ht="60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A39" s="91"/>
       <c r="B39" s="83"/>
       <c r="C39" s="92"/>
       <c r="D39" s="92"/>
       <c r="E39" s="92"/>
       <c r="F39" s="92" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="G39" s="92"/>
       <c r="H39" s="92"/>
@@ -6081,7 +5996,7 @@
       <c r="J39" s="92"/>
       <c r="K39" s="93"/>
       <c r="L39" s="102" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M39" s="103"/>
       <c r="N39" s="82"/>
@@ -6186,14 +6101,14 @@
       <c r="BW39" s="89"/>
       <c r="BX39" s="90"/>
     </row>
-    <row r="40" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:76" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="91"/>
       <c r="B40" s="83"/>
       <c r="C40" s="92"/>
       <c r="D40" s="92"/>
       <c r="E40" s="92"/>
       <c r="F40" s="92" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G40" s="92"/>
       <c r="H40" s="92"/>
@@ -6201,7 +6116,7 @@
       <c r="J40" s="92"/>
       <c r="K40" s="93"/>
       <c r="L40" s="102" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M40" s="103"/>
       <c r="N40" s="82"/>
@@ -6306,14 +6221,14 @@
       <c r="BW40" s="89"/>
       <c r="BX40" s="90"/>
     </row>
-    <row r="41" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="91"/>
       <c r="B41" s="83"/>
       <c r="C41" s="92"/>
       <c r="D41" s="92"/>
       <c r="E41" s="92"/>
       <c r="F41" s="92" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G41" s="92"/>
       <c r="H41" s="92"/>
@@ -6321,7 +6236,7 @@
       <c r="J41" s="92"/>
       <c r="K41" s="93"/>
       <c r="L41" s="102" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M41" s="103"/>
       <c r="N41" s="82"/>
@@ -6426,16 +6341,14 @@
       <c r="BW41" s="89"/>
       <c r="BX41" s="90"/>
     </row>
-    <row r="42" spans="1:76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="91" t="s">
-        <v>132</v>
-      </c>
+    <row r="42" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="91"/>
       <c r="B42" s="83"/>
       <c r="C42" s="92"/>
       <c r="D42" s="92"/>
       <c r="E42" s="92"/>
       <c r="F42" s="92" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G42" s="92"/>
       <c r="H42" s="92"/>
@@ -6443,7 +6356,7 @@
       <c r="J42" s="92"/>
       <c r="K42" s="93"/>
       <c r="L42" s="102" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M42" s="103"/>
       <c r="N42" s="82"/>
@@ -6550,14 +6463,14 @@
     </row>
     <row r="43" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="91" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B43" s="83"/>
       <c r="C43" s="92"/>
       <c r="D43" s="92"/>
       <c r="E43" s="92"/>
       <c r="F43" s="92" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G43" s="92"/>
       <c r="H43" s="92"/>
@@ -6565,7 +6478,7 @@
       <c r="J43" s="92"/>
       <c r="K43" s="93"/>
       <c r="L43" s="102" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M43" s="103"/>
       <c r="N43" s="82"/>
@@ -6670,14 +6583,16 @@
       <c r="BW43" s="89"/>
       <c r="BX43" s="90"/>
     </row>
-    <row r="44" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A44" s="91"/>
+    <row r="44" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="91" t="s">
+        <v>134</v>
+      </c>
       <c r="B44" s="83"/>
       <c r="C44" s="92"/>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
       <c r="F44" s="92" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G44" s="92"/>
       <c r="H44" s="92"/>
@@ -6685,7 +6600,7 @@
       <c r="J44" s="92"/>
       <c r="K44" s="93"/>
       <c r="L44" s="102" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M44" s="103"/>
       <c r="N44" s="82"/>
@@ -6797,7 +6712,7 @@
       <c r="D45" s="92"/>
       <c r="E45" s="92"/>
       <c r="F45" s="92" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G45" s="92"/>
       <c r="H45" s="92"/>
@@ -6805,7 +6720,7 @@
       <c r="J45" s="92"/>
       <c r="K45" s="93"/>
       <c r="L45" s="102" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M45" s="103"/>
       <c r="N45" s="82"/>
@@ -6910,46 +6825,24 @@
       <c r="BW45" s="89"/>
       <c r="BX45" s="90"/>
     </row>
-    <row r="46" spans="1:76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="91" t="s">
-        <v>138</v>
-      </c>
-      <c r="B46" s="83">
-        <v>9501137831</v>
-      </c>
-      <c r="C46" s="98">
-        <v>45992</v>
-      </c>
-      <c r="D46" s="98">
-        <v>46356</v>
-      </c>
-      <c r="E46" s="92" t="s">
-        <v>139</v>
-      </c>
+    <row r="46" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A46" s="91"/>
+      <c r="B46" s="83"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="92"/>
+      <c r="E46" s="92"/>
       <c r="F46" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="G46" s="92">
-        <v>41010100</v>
-      </c>
-      <c r="H46" s="92">
-        <v>7280</v>
-      </c>
-      <c r="I46" s="92" t="s">
-        <v>141</v>
-      </c>
-      <c r="J46" s="92">
-        <v>2662855</v>
-      </c>
-      <c r="K46" s="99">
-        <v>38005</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="G46" s="92"/>
+      <c r="H46" s="92"/>
+      <c r="I46" s="92"/>
+      <c r="J46" s="92"/>
+      <c r="K46" s="93"/>
       <c r="L46" s="102" t="s">
-        <v>195</v>
-      </c>
-      <c r="M46" s="103" t="s">
-        <v>166</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="M46" s="103"/>
       <c r="N46" s="82"/>
       <c r="O46" s="83"/>
       <c r="P46" s="83"/>
@@ -7052,12 +6945,12 @@
       <c r="BW46" s="89"/>
       <c r="BX46" s="90"/>
     </row>
-    <row r="47" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="91" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="B47" s="83">
-        <v>9501137269</v>
+        <v>9501137831</v>
       </c>
       <c r="C47" s="98">
         <v>45992</v>
@@ -7066,10 +6959,10 @@
         <v>46356</v>
       </c>
       <c r="E47" s="92" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F47" s="92" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G47" s="92">
         <v>41010100</v>
@@ -7084,10 +6977,10 @@
         <v>2662855</v>
       </c>
       <c r="K47" s="99">
-        <v>9980</v>
+        <v>38005</v>
       </c>
       <c r="L47" s="102" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M47" s="103" t="s">
         <v>166</v>
@@ -7194,26 +7087,46 @@
       <c r="BW47" s="89"/>
       <c r="BX47" s="90"/>
     </row>
-    <row r="48" spans="1:76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="91"/>
-      <c r="B48" s="83"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="92"/>
-      <c r="E48" s="92"/>
+    <row r="48" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" s="83">
+        <v>9501137269</v>
+      </c>
+      <c r="C48" s="98">
+        <v>45992</v>
+      </c>
+      <c r="D48" s="98">
+        <v>46356</v>
+      </c>
+      <c r="E48" s="92" t="s">
+        <v>142</v>
+      </c>
       <c r="F48" s="92" t="s">
-        <v>144</v>
-      </c>
-      <c r="G48" s="92"/>
-      <c r="H48" s="92"/>
-      <c r="I48" s="92"/>
-      <c r="J48" s="92"/>
+        <v>143</v>
+      </c>
+      <c r="G48" s="92">
+        <v>41010100</v>
+      </c>
+      <c r="H48" s="92">
+        <v>7280</v>
+      </c>
+      <c r="I48" s="92" t="s">
+        <v>141</v>
+      </c>
+      <c r="J48" s="92">
+        <v>2662855</v>
+      </c>
       <c r="K48" s="99">
-        <v>12000</v>
+        <v>9980</v>
       </c>
       <c r="L48" s="102" t="s">
-        <v>197</v>
-      </c>
-      <c r="M48" s="103"/>
+        <v>196</v>
+      </c>
+      <c r="M48" s="103" t="s">
+        <v>166</v>
+      </c>
       <c r="N48" s="82"/>
       <c r="O48" s="83"/>
       <c r="P48" s="83"/>
@@ -7316,24 +7229,24 @@
       <c r="BW48" s="89"/>
       <c r="BX48" s="90"/>
     </row>
-    <row r="49" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="91"/>
       <c r="B49" s="83"/>
       <c r="C49" s="92"/>
       <c r="D49" s="92"/>
       <c r="E49" s="92"/>
       <c r="F49" s="92" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G49" s="92"/>
       <c r="H49" s="92"/>
       <c r="I49" s="92"/>
       <c r="J49" s="92"/>
       <c r="K49" s="99">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="L49" s="102" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M49" s="103"/>
       <c r="N49" s="82"/>
@@ -7438,46 +7351,26 @@
       <c r="BW49" s="89"/>
       <c r="BX49" s="90"/>
     </row>
-    <row r="50" spans="1:76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="91" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" s="83">
-        <v>9501166164</v>
-      </c>
-      <c r="C50" s="98">
-        <v>46023</v>
-      </c>
-      <c r="D50" s="98">
-        <v>46387</v>
-      </c>
-      <c r="E50" s="92" t="s">
-        <v>146</v>
-      </c>
+    <row r="50" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A50" s="91"/>
+      <c r="B50" s="83"/>
+      <c r="C50" s="92"/>
+      <c r="D50" s="92"/>
+      <c r="E50" s="92"/>
       <c r="F50" s="92" t="s">
-        <v>147</v>
-      </c>
-      <c r="G50" s="92">
-        <v>41500000</v>
-      </c>
-      <c r="H50" s="92">
-        <v>1400</v>
-      </c>
-      <c r="I50" s="92" t="s">
-        <v>105</v>
-      </c>
-      <c r="J50" s="92">
-        <v>2321403</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="G50" s="92"/>
+      <c r="H50" s="92"/>
+      <c r="I50" s="92"/>
+      <c r="J50" s="92"/>
       <c r="K50" s="99">
-        <v>4651600</v>
+        <v>0</v>
       </c>
       <c r="L50" s="102" t="s">
-        <v>199</v>
-      </c>
-      <c r="M50" s="103" t="s">
-        <v>166</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="M50" s="103"/>
       <c r="N50" s="82"/>
       <c r="O50" s="83"/>
       <c r="P50" s="83"/>
@@ -7580,18 +7473,18 @@
       <c r="BW50" s="89"/>
       <c r="BX50" s="90"/>
     </row>
-    <row r="51" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="91" t="s">
         <v>97</v>
       </c>
       <c r="B51" s="83">
-        <v>9501190667</v>
+        <v>9501166164</v>
       </c>
       <c r="C51" s="98">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="D51" s="98">
-        <v>46296</v>
+        <v>46387</v>
       </c>
       <c r="E51" s="92" t="s">
         <v>146</v>
@@ -7612,10 +7505,10 @@
         <v>2321403</v>
       </c>
       <c r="K51" s="99">
-        <v>62500</v>
+        <v>4651600</v>
       </c>
       <c r="L51" s="102" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M51" s="103" t="s">
         <v>166</v>
@@ -7724,22 +7617,22 @@
     </row>
     <row r="52" spans="1:76" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="91" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="B52" s="83">
-        <v>9501199822</v>
+        <v>9501190667</v>
       </c>
       <c r="C52" s="98">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="D52" s="98">
-        <v>46387</v>
+        <v>46296</v>
       </c>
       <c r="E52" s="92" t="s">
         <v>146</v>
       </c>
       <c r="F52" s="92" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G52" s="92">
         <v>41500000</v>
@@ -7754,10 +7647,10 @@
         <v>2321403</v>
       </c>
       <c r="K52" s="99">
-        <v>1058400</v>
+        <v>62500</v>
       </c>
       <c r="L52" s="102" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M52" s="103" t="s">
         <v>166</v>
@@ -7866,10 +7759,10 @@
     </row>
     <row r="53" spans="1:76" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="91" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B53" s="83">
-        <v>9501199827</v>
+        <v>9501199822</v>
       </c>
       <c r="C53" s="98">
         <v>46023</v>
@@ -7896,10 +7789,10 @@
         <v>2321403</v>
       </c>
       <c r="K53" s="99">
-        <v>577400</v>
+        <v>1058400</v>
       </c>
       <c r="L53" s="102" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M53" s="103" t="s">
         <v>166</v>
@@ -8006,12 +7899,12 @@
       <c r="BW53" s="89"/>
       <c r="BX53" s="90"/>
     </row>
-    <row r="54" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:76" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="91" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="B54" s="83">
-        <v>9501195328</v>
+        <v>9501199827</v>
       </c>
       <c r="C54" s="98">
         <v>46023</v>
@@ -8023,7 +7916,7 @@
         <v>146</v>
       </c>
       <c r="F54" s="92" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G54" s="92">
         <v>41500000</v>
@@ -8038,10 +7931,10 @@
         <v>2321403</v>
       </c>
       <c r="K54" s="99">
-        <v>36000</v>
+        <v>577400</v>
       </c>
       <c r="L54" s="102" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M54" s="103" t="s">
         <v>166</v>
@@ -8149,23 +8042,45 @@
       <c r="BX54" s="90"/>
     </row>
     <row r="55" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A55" s="91"/>
-      <c r="B55" s="83"/>
-      <c r="C55" s="92"/>
-      <c r="D55" s="92"/>
-      <c r="E55" s="92"/>
+      <c r="A55" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" s="83">
+        <v>9501195328</v>
+      </c>
+      <c r="C55" s="98">
+        <v>46023</v>
+      </c>
+      <c r="D55" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E55" s="92" t="s">
+        <v>146</v>
+      </c>
       <c r="F55" s="92" t="s">
-        <v>152</v>
-      </c>
-      <c r="G55" s="92"/>
-      <c r="H55" s="92"/>
-      <c r="I55" s="92"/>
-      <c r="J55" s="92"/>
-      <c r="K55" s="93"/>
+        <v>151</v>
+      </c>
+      <c r="G55" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H55" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I55" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J55" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K55" s="99">
+        <v>36000</v>
+      </c>
       <c r="L55" s="102" t="s">
-        <v>204</v>
-      </c>
-      <c r="M55" s="103"/>
+        <v>203</v>
+      </c>
+      <c r="M55" s="103" t="s">
+        <v>166</v>
+      </c>
       <c r="N55" s="82"/>
       <c r="O55" s="83"/>
       <c r="P55" s="83"/>
@@ -8275,7 +8190,7 @@
       <c r="D56" s="92"/>
       <c r="E56" s="92"/>
       <c r="F56" s="92" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G56" s="92"/>
       <c r="H56" s="92"/>
@@ -8283,7 +8198,7 @@
       <c r="J56" s="92"/>
       <c r="K56" s="93"/>
       <c r="L56" s="102" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M56" s="103"/>
       <c r="N56" s="82"/>
@@ -8389,45 +8304,23 @@
       <c r="BX56" s="90"/>
     </row>
     <row r="57" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A57" s="91" t="s">
-        <v>10</v>
-      </c>
-      <c r="B57" s="83">
-        <v>9501212179</v>
-      </c>
-      <c r="C57" s="98">
-        <v>46023</v>
-      </c>
-      <c r="D57" s="92" t="s">
-        <v>154</v>
-      </c>
-      <c r="E57" s="92" t="s">
-        <v>146</v>
-      </c>
+      <c r="A57" s="91"/>
+      <c r="B57" s="83"/>
+      <c r="C57" s="92"/>
+      <c r="D57" s="92"/>
+      <c r="E57" s="92"/>
       <c r="F57" s="92" t="s">
-        <v>155</v>
-      </c>
-      <c r="G57" s="92">
-        <v>41500000</v>
-      </c>
-      <c r="H57" s="92">
-        <v>1400</v>
-      </c>
-      <c r="I57" s="92" t="s">
-        <v>105</v>
-      </c>
-      <c r="J57" s="92">
-        <v>2321403</v>
-      </c>
-      <c r="K57" s="99">
-        <v>334732.5</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="G57" s="92"/>
+      <c r="H57" s="92"/>
+      <c r="I57" s="92"/>
+      <c r="J57" s="92"/>
+      <c r="K57" s="93"/>
       <c r="L57" s="102" t="s">
-        <v>206</v>
-      </c>
-      <c r="M57" s="103" t="s">
-        <v>166</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="M57" s="103"/>
       <c r="N57" s="82"/>
       <c r="O57" s="83"/>
       <c r="P57" s="83"/>
@@ -8530,24 +8423,24 @@
       <c r="BW57" s="89"/>
       <c r="BX57" s="90"/>
     </row>
-    <row r="58" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A58" s="91" t="s">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="B58" s="83">
-        <v>9501196824</v>
+        <v>9501212179</v>
       </c>
       <c r="C58" s="98">
         <v>46023</v>
       </c>
-      <c r="D58" s="98">
-        <v>46387</v>
+      <c r="D58" s="92" t="s">
+        <v>154</v>
       </c>
       <c r="E58" s="92" t="s">
         <v>146</v>
       </c>
       <c r="F58" s="92" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G58" s="92">
         <v>41500000</v>
@@ -8562,10 +8455,10 @@
         <v>2321403</v>
       </c>
       <c r="K58" s="99">
-        <v>433000</v>
+        <v>334732.5</v>
       </c>
       <c r="L58" s="102" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M58" s="103" t="s">
         <v>166</v>
@@ -8674,10 +8567,10 @@
     </row>
     <row r="59" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="91" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="B59" s="83">
-        <v>9501196865</v>
+        <v>9501196824</v>
       </c>
       <c r="C59" s="98">
         <v>46023</v>
@@ -8689,7 +8582,7 @@
         <v>146</v>
       </c>
       <c r="F59" s="92" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G59" s="92">
         <v>41500000</v>
@@ -8704,10 +8597,10 @@
         <v>2321403</v>
       </c>
       <c r="K59" s="99">
-        <v>335904</v>
+        <v>433000</v>
       </c>
       <c r="L59" s="102" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M59" s="103" t="s">
         <v>166</v>
@@ -8816,10 +8709,10 @@
     </row>
     <row r="60" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="91" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="B60" s="83">
-        <v>9501158806</v>
+        <v>9501196865</v>
       </c>
       <c r="C60" s="98">
         <v>46023</v>
@@ -8831,7 +8724,7 @@
         <v>146</v>
       </c>
       <c r="F60" s="92" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G60" s="92">
         <v>41500000</v>
@@ -8846,10 +8739,10 @@
         <v>2321403</v>
       </c>
       <c r="K60" s="99">
-        <v>376200</v>
+        <v>335904</v>
       </c>
       <c r="L60" s="102" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M60" s="103" t="s">
         <v>166</v>
@@ -8958,10 +8851,10 @@
     </row>
     <row r="61" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="91" t="s">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="B61" s="83">
-        <v>9501159633</v>
+        <v>9501158806</v>
       </c>
       <c r="C61" s="98">
         <v>46023</v>
@@ -8970,13 +8863,13 @@
         <v>46387</v>
       </c>
       <c r="E61" s="92" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F61" s="92" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G61" s="92">
-        <v>61010000</v>
+        <v>41500000</v>
       </c>
       <c r="H61" s="92">
         <v>1400</v>
@@ -8988,10 +8881,10 @@
         <v>2321403</v>
       </c>
       <c r="K61" s="99">
-        <v>146493</v>
+        <v>376200</v>
       </c>
       <c r="L61" s="102" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M61" s="103" t="s">
         <v>166</v>
@@ -9100,40 +8993,40 @@
     </row>
     <row r="62" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="91" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B62" s="83">
-        <v>9501199250</v>
+        <v>9501159633</v>
       </c>
       <c r="C62" s="98">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="D62" s="98">
-        <v>46418</v>
+        <v>46387</v>
       </c>
       <c r="E62" s="92" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="F62" s="92" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G62" s="92">
-        <v>41010100</v>
+        <v>61010000</v>
       </c>
       <c r="H62" s="92">
-        <v>7280</v>
+        <v>1400</v>
       </c>
       <c r="I62" s="92" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="J62" s="92">
-        <v>2662855</v>
+        <v>2321403</v>
       </c>
       <c r="K62" s="99">
-        <v>69429</v>
+        <v>146493</v>
       </c>
       <c r="L62" s="102" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M62" s="103" t="s">
         <v>166</v>
@@ -9240,20 +9133,46 @@
       <c r="BW62" s="89"/>
       <c r="BX62" s="90"/>
     </row>
-    <row r="63" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A63" s="91"/>
-      <c r="B63" s="83"/>
-      <c r="C63" s="92"/>
-      <c r="D63" s="92"/>
-      <c r="E63" s="92"/>
-      <c r="F63" s="92"/>
-      <c r="G63" s="92"/>
-      <c r="H63" s="92"/>
-      <c r="I63" s="92"/>
-      <c r="J63" s="92"/>
-      <c r="K63" s="93"/>
-      <c r="L63" s="92"/>
-      <c r="M63" s="90"/>
+    <row r="63" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="91" t="s">
+        <v>163</v>
+      </c>
+      <c r="B63" s="83">
+        <v>9501199250</v>
+      </c>
+      <c r="C63" s="98">
+        <v>46054</v>
+      </c>
+      <c r="D63" s="98">
+        <v>46418</v>
+      </c>
+      <c r="E63" s="92" t="s">
+        <v>139</v>
+      </c>
+      <c r="F63" s="92" t="s">
+        <v>164</v>
+      </c>
+      <c r="G63" s="92">
+        <v>41010100</v>
+      </c>
+      <c r="H63" s="92">
+        <v>7280</v>
+      </c>
+      <c r="I63" s="92" t="s">
+        <v>141</v>
+      </c>
+      <c r="J63" s="92">
+        <v>2662855</v>
+      </c>
+      <c r="K63" s="99">
+        <v>69429</v>
+      </c>
+      <c r="L63" s="102" t="s">
+        <v>211</v>
+      </c>
+      <c r="M63" s="103" t="s">
+        <v>166</v>
+      </c>
       <c r="N63" s="82"/>
       <c r="O63" s="83"/>
       <c r="P63" s="83"/>
@@ -9472,243 +9391,358 @@
       <c r="BW64" s="89"/>
       <c r="BX64" s="90"/>
     </row>
-    <row r="65" spans="1:139" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="66" t="s">
+    <row r="65" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A65" s="91"/>
+      <c r="B65" s="83"/>
+      <c r="C65" s="92"/>
+      <c r="D65" s="92"/>
+      <c r="E65" s="92"/>
+      <c r="F65" s="92"/>
+      <c r="G65" s="92"/>
+      <c r="H65" s="92"/>
+      <c r="I65" s="92"/>
+      <c r="J65" s="92"/>
+      <c r="K65" s="93"/>
+      <c r="L65" s="92"/>
+      <c r="M65" s="90"/>
+      <c r="N65" s="82"/>
+      <c r="O65" s="83"/>
+      <c r="P65" s="83"/>
+      <c r="Q65" s="84"/>
+      <c r="R65" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S65" s="85"/>
+      <c r="T65" s="83"/>
+      <c r="U65" s="83"/>
+      <c r="V65" s="84"/>
+      <c r="W65" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X65" s="87"/>
+      <c r="Y65" s="83"/>
+      <c r="Z65" s="83"/>
+      <c r="AA65" s="84"/>
+      <c r="AB65" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC65" s="87"/>
+      <c r="AD65" s="83"/>
+      <c r="AE65" s="83"/>
+      <c r="AF65" s="84"/>
+      <c r="AG65" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH65" s="87"/>
+      <c r="AI65" s="83"/>
+      <c r="AJ65" s="83"/>
+      <c r="AK65" s="84"/>
+      <c r="AL65" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM65" s="87"/>
+      <c r="AN65" s="83"/>
+      <c r="AO65" s="83"/>
+      <c r="AP65" s="84"/>
+      <c r="AQ65" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR65" s="87"/>
+      <c r="AS65" s="83"/>
+      <c r="AT65" s="83"/>
+      <c r="AU65" s="84"/>
+      <c r="AV65" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW65" s="87"/>
+      <c r="AX65" s="83"/>
+      <c r="AY65" s="83"/>
+      <c r="AZ65" s="84"/>
+      <c r="BA65" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB65" s="87"/>
+      <c r="BC65" s="83"/>
+      <c r="BD65" s="83"/>
+      <c r="BE65" s="84"/>
+      <c r="BF65" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG65" s="87"/>
+      <c r="BH65" s="83"/>
+      <c r="BI65" s="83"/>
+      <c r="BJ65" s="84"/>
+      <c r="BK65" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL65" s="87"/>
+      <c r="BM65" s="83"/>
+      <c r="BN65" s="83"/>
+      <c r="BO65" s="84"/>
+      <c r="BP65" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ65" s="87"/>
+      <c r="BR65" s="83"/>
+      <c r="BS65" s="83"/>
+      <c r="BT65" s="84"/>
+      <c r="BU65" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV65" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW65" s="89"/>
+      <c r="BX65" s="90"/>
+    </row>
+    <row r="66" spans="1:139" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="B65" s="67"/>
-      <c r="C65" s="68"/>
-      <c r="D65" s="68"/>
-      <c r="E65" s="69"/>
-      <c r="F65" s="69"/>
-      <c r="G65" s="69"/>
-      <c r="H65" s="69"/>
-      <c r="I65" s="69"/>
-      <c r="J65" s="69"/>
-      <c r="K65" s="70"/>
-      <c r="L65" s="69"/>
-      <c r="M65" s="71"/>
-      <c r="N65" s="72"/>
-      <c r="O65" s="73"/>
-      <c r="P65" s="73"/>
-      <c r="Q65" s="74"/>
-      <c r="R65" s="74" t="str">
-        <f>IF(OR(P65="",Q65=""),"",P65-Q65)</f>
+      <c r="B66" s="67"/>
+      <c r="C66" s="68"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="69"/>
+      <c r="F66" s="69"/>
+      <c r="G66" s="69"/>
+      <c r="H66" s="69"/>
+      <c r="I66" s="69"/>
+      <c r="J66" s="69"/>
+      <c r="K66" s="70"/>
+      <c r="L66" s="69"/>
+      <c r="M66" s="71"/>
+      <c r="N66" s="72"/>
+      <c r="O66" s="73"/>
+      <c r="P66" s="73"/>
+      <c r="Q66" s="74"/>
+      <c r="R66" s="74" t="str">
+        <f>IF(OR(P66="",Q66=""),"",P66-Q66)</f>
         <v/>
       </c>
-      <c r="S65" s="75"/>
-      <c r="T65" s="73"/>
-      <c r="U65" s="73"/>
-      <c r="V65" s="74"/>
-      <c r="W65" s="76"/>
-      <c r="X65" s="77"/>
-      <c r="Y65" s="73"/>
-      <c r="Z65" s="73"/>
-      <c r="AA65" s="74"/>
-      <c r="AB65" s="76"/>
-      <c r="AC65" s="77"/>
-      <c r="AD65" s="73"/>
-      <c r="AE65" s="73"/>
-      <c r="AF65" s="74"/>
-      <c r="AG65" s="76" t="str">
-        <f t="shared" ref="AG65" si="36">IF(OR(AE65="",AF65=""),"",AE65-AF65)</f>
+      <c r="S66" s="75"/>
+      <c r="T66" s="73"/>
+      <c r="U66" s="73"/>
+      <c r="V66" s="74"/>
+      <c r="W66" s="76"/>
+      <c r="X66" s="77"/>
+      <c r="Y66" s="73"/>
+      <c r="Z66" s="73"/>
+      <c r="AA66" s="74"/>
+      <c r="AB66" s="76"/>
+      <c r="AC66" s="77"/>
+      <c r="AD66" s="73"/>
+      <c r="AE66" s="73"/>
+      <c r="AF66" s="74"/>
+      <c r="AG66" s="76" t="str">
+        <f t="shared" ref="AG66" si="36">IF(OR(AE66="",AF66=""),"",AE66-AF66)</f>
         <v/>
       </c>
-      <c r="AH65" s="77"/>
-      <c r="AI65" s="73"/>
-      <c r="AJ65" s="73"/>
-      <c r="AK65" s="74"/>
-      <c r="AL65" s="76" t="str">
-        <f t="shared" ref="AL65" si="37">IF(OR(AJ65="",AK65=""),"",AJ65-AK65)</f>
+      <c r="AH66" s="77"/>
+      <c r="AI66" s="73"/>
+      <c r="AJ66" s="73"/>
+      <c r="AK66" s="74"/>
+      <c r="AL66" s="76" t="str">
+        <f t="shared" ref="AL66" si="37">IF(OR(AJ66="",AK66=""),"",AJ66-AK66)</f>
         <v/>
       </c>
-      <c r="AM65" s="77"/>
-      <c r="AN65" s="73"/>
-      <c r="AO65" s="73"/>
-      <c r="AP65" s="74"/>
-      <c r="AQ65" s="76" t="str">
-        <f t="shared" ref="AQ65" si="38">IF(OR(AO65="",AP65=""),"",AO65-AP65)</f>
+      <c r="AM66" s="77"/>
+      <c r="AN66" s="73"/>
+      <c r="AO66" s="73"/>
+      <c r="AP66" s="74"/>
+      <c r="AQ66" s="76" t="str">
+        <f t="shared" ref="AQ66" si="38">IF(OR(AO66="",AP66=""),"",AO66-AP66)</f>
         <v/>
       </c>
-      <c r="AR65" s="77"/>
-      <c r="AS65" s="73"/>
-      <c r="AT65" s="73"/>
-      <c r="AU65" s="74"/>
-      <c r="AV65" s="76" t="str">
-        <f t="shared" ref="AV65" si="39">IF(OR(AT65="",AU65=""),"",AT65-AU65)</f>
+      <c r="AR66" s="77"/>
+      <c r="AS66" s="73"/>
+      <c r="AT66" s="73"/>
+      <c r="AU66" s="74"/>
+      <c r="AV66" s="76" t="str">
+        <f t="shared" ref="AV66" si="39">IF(OR(AT66="",AU66=""),"",AT66-AU66)</f>
         <v/>
       </c>
-      <c r="AW65" s="77"/>
-      <c r="AX65" s="73"/>
-      <c r="AY65" s="73"/>
-      <c r="AZ65" s="74"/>
-      <c r="BA65" s="76" t="str">
-        <f t="shared" ref="BA65" si="40">IF(OR(AY65="",AZ65=""),"",AY65-AZ65)</f>
+      <c r="AW66" s="77"/>
+      <c r="AX66" s="73"/>
+      <c r="AY66" s="73"/>
+      <c r="AZ66" s="74"/>
+      <c r="BA66" s="76" t="str">
+        <f t="shared" ref="BA66" si="40">IF(OR(AY66="",AZ66=""),"",AY66-AZ66)</f>
         <v/>
       </c>
-      <c r="BB65" s="77"/>
-      <c r="BC65" s="73"/>
-      <c r="BD65" s="73"/>
-      <c r="BE65" s="74"/>
-      <c r="BF65" s="76" t="str">
-        <f t="shared" ref="BF65" si="41">IF(OR(BD65="",BE65=""),"",BD65-BE65)</f>
+      <c r="BB66" s="77"/>
+      <c r="BC66" s="73"/>
+      <c r="BD66" s="73"/>
+      <c r="BE66" s="74"/>
+      <c r="BF66" s="76" t="str">
+        <f t="shared" ref="BF66" si="41">IF(OR(BD66="",BE66=""),"",BD66-BE66)</f>
         <v/>
       </c>
-      <c r="BG65" s="77"/>
-      <c r="BH65" s="73"/>
-      <c r="BI65" s="73"/>
-      <c r="BJ65" s="74"/>
-      <c r="BK65" s="76" t="str">
-        <f t="shared" ref="BK65" si="42">IF(OR(BI65="",BJ65=""),"",BI65-BJ65)</f>
+      <c r="BG66" s="77"/>
+      <c r="BH66" s="73"/>
+      <c r="BI66" s="73"/>
+      <c r="BJ66" s="74"/>
+      <c r="BK66" s="76" t="str">
+        <f t="shared" ref="BK66" si="42">IF(OR(BI66="",BJ66=""),"",BI66-BJ66)</f>
         <v/>
       </c>
-      <c r="BL65" s="77"/>
-      <c r="BM65" s="73"/>
-      <c r="BN65" s="73"/>
-      <c r="BO65" s="74"/>
-      <c r="BP65" s="76" t="str">
-        <f t="shared" ref="BP65" si="43">IF(OR(BN65="",BO65=""),"",BN65-BO65)</f>
+      <c r="BL66" s="77"/>
+      <c r="BM66" s="73"/>
+      <c r="BN66" s="73"/>
+      <c r="BO66" s="74"/>
+      <c r="BP66" s="76" t="str">
+        <f t="shared" ref="BP66" si="43">IF(OR(BN66="",BO66=""),"",BN66-BO66)</f>
         <v/>
       </c>
-      <c r="BQ65" s="77"/>
-      <c r="BR65" s="73"/>
-      <c r="BS65" s="73"/>
-      <c r="BT65" s="74"/>
-      <c r="BU65" s="76" t="str">
-        <f t="shared" ref="BU65" si="44">IF(OR(BS65="",BT65=""),"",BS65-BT65)</f>
+      <c r="BQ66" s="77"/>
+      <c r="BR66" s="73"/>
+      <c r="BS66" s="73"/>
+      <c r="BT66" s="74"/>
+      <c r="BU66" s="76" t="str">
+        <f t="shared" ref="BU66" si="44">IF(OR(BS66="",BT66=""),"",BS66-BT66)</f>
         <v/>
       </c>
-      <c r="BV65" s="75"/>
-      <c r="BW65" s="53"/>
-      <c r="BX65" s="49"/>
-      <c r="BY65"/>
-      <c r="BZ65"/>
-      <c r="CA65"/>
-      <c r="CB65"/>
-      <c r="CC65"/>
-      <c r="CD65"/>
-      <c r="CE65"/>
-      <c r="CF65"/>
-      <c r="CG65"/>
-      <c r="CH65"/>
-      <c r="CI65"/>
-      <c r="CJ65"/>
-      <c r="CK65"/>
-      <c r="CL65"/>
-      <c r="CM65"/>
-      <c r="CN65"/>
-      <c r="CO65"/>
-      <c r="CP65"/>
-      <c r="CQ65"/>
-      <c r="CR65"/>
-      <c r="CS65"/>
-      <c r="CT65"/>
-      <c r="CU65"/>
-      <c r="CV65"/>
-      <c r="CW65"/>
-      <c r="CX65"/>
-      <c r="CY65"/>
-      <c r="CZ65"/>
-      <c r="DA65"/>
-      <c r="DB65"/>
-      <c r="DC65"/>
-      <c r="DD65"/>
-      <c r="DE65"/>
-      <c r="DF65"/>
-      <c r="DG65"/>
-      <c r="DH65"/>
-      <c r="DI65"/>
-      <c r="DJ65"/>
-      <c r="DK65"/>
-      <c r="DL65"/>
-      <c r="DM65"/>
-      <c r="DN65"/>
-      <c r="DO65"/>
-      <c r="DP65"/>
-      <c r="DQ65"/>
-      <c r="DR65"/>
-      <c r="DS65"/>
-      <c r="DT65"/>
-      <c r="DU65"/>
-      <c r="DV65"/>
-      <c r="DW65"/>
-      <c r="DX65"/>
-      <c r="DY65"/>
-      <c r="DZ65"/>
-      <c r="EA65"/>
-      <c r="EB65"/>
-      <c r="EC65"/>
-      <c r="ED65"/>
-      <c r="EE65"/>
-      <c r="EF65"/>
-      <c r="EG65"/>
-      <c r="EH65"/>
-      <c r="EI65"/>
+      <c r="BV66" s="75"/>
+      <c r="BW66" s="53"/>
+      <c r="BX66" s="49"/>
+      <c r="BY66"/>
+      <c r="BZ66"/>
+      <c r="CA66"/>
+      <c r="CB66"/>
+      <c r="CC66"/>
+      <c r="CD66"/>
+      <c r="CE66"/>
+      <c r="CF66"/>
+      <c r="CG66"/>
+      <c r="CH66"/>
+      <c r="CI66"/>
+      <c r="CJ66"/>
+      <c r="CK66"/>
+      <c r="CL66"/>
+      <c r="CM66"/>
+      <c r="CN66"/>
+      <c r="CO66"/>
+      <c r="CP66"/>
+      <c r="CQ66"/>
+      <c r="CR66"/>
+      <c r="CS66"/>
+      <c r="CT66"/>
+      <c r="CU66"/>
+      <c r="CV66"/>
+      <c r="CW66"/>
+      <c r="CX66"/>
+      <c r="CY66"/>
+      <c r="CZ66"/>
+      <c r="DA66"/>
+      <c r="DB66"/>
+      <c r="DC66"/>
+      <c r="DD66"/>
+      <c r="DE66"/>
+      <c r="DF66"/>
+      <c r="DG66"/>
+      <c r="DH66"/>
+      <c r="DI66"/>
+      <c r="DJ66"/>
+      <c r="DK66"/>
+      <c r="DL66"/>
+      <c r="DM66"/>
+      <c r="DN66"/>
+      <c r="DO66"/>
+      <c r="DP66"/>
+      <c r="DQ66"/>
+      <c r="DR66"/>
+      <c r="DS66"/>
+      <c r="DT66"/>
+      <c r="DU66"/>
+      <c r="DV66"/>
+      <c r="DW66"/>
+      <c r="DX66"/>
+      <c r="DY66"/>
+      <c r="DZ66"/>
+      <c r="EA66"/>
+      <c r="EB66"/>
+      <c r="EC66"/>
+      <c r="ED66"/>
+      <c r="EE66"/>
+      <c r="EF66"/>
+      <c r="EG66"/>
+      <c r="EH66"/>
+      <c r="EI66"/>
     </row>
-    <row r="66" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="67" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>96</v>
       </c>
-      <c r="AA66" s="3"/>
-      <c r="BV66" s="95"/>
+      <c r="AA67" s="3"/>
+      <c r="BV67" s="95"/>
     </row>
   </sheetData>
-  <autoFilter ref="A14:BY18" xr:uid="{177F1DEB-197D-49C6-A2E3-152C1AC7B373}"/>
-  <mergeCells count="40">
-    <mergeCell ref="BQ11:BU11"/>
+  <autoFilter ref="A15:BY19" xr:uid="{177F1DEB-197D-49C6-A2E3-152C1AC7B373}"/>
+  <mergeCells count="39">
     <mergeCell ref="BQ13:BU13"/>
-    <mergeCell ref="S11:W11"/>
-    <mergeCell ref="N11:R11"/>
-    <mergeCell ref="X11:AB11"/>
-    <mergeCell ref="AC11:AG11"/>
-    <mergeCell ref="AH11:AL11"/>
-    <mergeCell ref="AM11:AQ11"/>
-    <mergeCell ref="AR11:AV11"/>
-    <mergeCell ref="AW11:BA11"/>
-    <mergeCell ref="BB11:BF11"/>
-    <mergeCell ref="BG11:BK11"/>
-    <mergeCell ref="BL11:BP11"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="BB14:BF14"/>
+    <mergeCell ref="BG14:BK14"/>
+    <mergeCell ref="BL14:BP14"/>
+    <mergeCell ref="N13:R13"/>
     <mergeCell ref="S13:W13"/>
-    <mergeCell ref="N13:R13"/>
     <mergeCell ref="X13:AB13"/>
-    <mergeCell ref="BB12:BF12"/>
-    <mergeCell ref="BG12:BK12"/>
-    <mergeCell ref="BL12:BP12"/>
     <mergeCell ref="AC13:AG13"/>
     <mergeCell ref="AH13:AL13"/>
     <mergeCell ref="AM13:AQ13"/>
     <mergeCell ref="AR13:AV13"/>
     <mergeCell ref="AW13:BA13"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="BQ12:BU12"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="L13:M13"/>
     <mergeCell ref="BB13:BF13"/>
     <mergeCell ref="BG13:BK13"/>
     <mergeCell ref="BL13:BP13"/>
+    <mergeCell ref="AC14:AG14"/>
+    <mergeCell ref="AH14:AL14"/>
+    <mergeCell ref="AM14:AQ14"/>
+    <mergeCell ref="AR14:AV14"/>
+    <mergeCell ref="AW14:BA14"/>
+    <mergeCell ref="BQ12:BU12"/>
+    <mergeCell ref="BQ14:BU14"/>
+    <mergeCell ref="S12:W12"/>
     <mergeCell ref="N12:R12"/>
-    <mergeCell ref="S12:W12"/>
     <mergeCell ref="X12:AB12"/>
     <mergeCell ref="AC12:AG12"/>
     <mergeCell ref="AH12:AL12"/>
     <mergeCell ref="AM12:AQ12"/>
     <mergeCell ref="AR12:AV12"/>
     <mergeCell ref="AW12:BA12"/>
+    <mergeCell ref="BB12:BF12"/>
+    <mergeCell ref="BG12:BK12"/>
+    <mergeCell ref="BL12:BP12"/>
+    <mergeCell ref="S14:W14"/>
+    <mergeCell ref="N14:R14"/>
+    <mergeCell ref="X14:AB14"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q65 V65 AA65 AF65 AK65 AP65 AU65 AZ65 BE65 BJ65 BO65 BT65">
-    <cfRule type="expression" dxfId="2" priority="8">
-      <formula>IF(AND(P65&gt;0,Q65=0),TRUE,FALSE)</formula>
+  <conditionalFormatting sqref="Q66 V66 AA66 AF66 AK66 AP66 AU66 AZ66 BE66 BJ66 BO66 BT66">
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>IF(AND(P66&gt;0,Q66=0),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT10 V65:X65 AB65:AC65 AG65:AH65 AL65:AM65 AQ65:AR65 AV65:AW65 BA65:BB65 BF65:BG65 BK65:BL65 BP65:BQ65 BU65">
-    <cfRule type="expression" dxfId="1" priority="9">
-      <formula>IF(AND(U10&lt;&gt;"",V10="",TODAY()&gt;DATE(YEAR(TODAY()),MONTH(DATEVALUE("1-"&amp;LEFT(#REF!,3)&amp;"-1900")),20)),TRUE,FALSE)</formula>
+  <conditionalFormatting sqref="BT11 V66:X66 AB66:AC66 AG66:AH66 AL66:AM66 AQ66:AR66 AV66:AW66 BA66:BB66 BF66:BG66 BK66:BL66 BP66:BQ66 BU66">
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>IF(AND(U11&lt;&gt;"",V11="",TODAY()&gt;DATE(YEAR(TODAY()),MONTH(DATEVALUE("1-"&amp;LEFT(#REF!,3)&amp;"-1900")),20)),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BW11:BW12">
-    <cfRule type="expression" dxfId="0" priority="7">
-      <formula>IF(BW11&lt;0,TRUE,FALSE)</formula>
+  <conditionalFormatting sqref="BW12:BW13">
+    <cfRule type="expression" dxfId="4" priority="7">
+      <formula>IF(BW12&lt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9717,26 +9751,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19b1ad6d-7bbd-4338-adb0-a51e11e836c7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002B3B1E9AF76D8540A21B723585178CF2" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9038a3d09b9201f70a536d69b3ffdde9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="19b1ad6d-7bbd-4338-adb0-a51e11e836c7" xmlns:ns3="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9f1b7b0d1eaccac7f713200a7ec3f32" ns2:_="" ns3:_="">
     <xsd:import namespace="19b1ad6d-7bbd-4338-adb0-a51e11e836c7"/>
@@ -9979,26 +9993,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC2B212-31BA-49FB-B215-9E14B2C60948}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09"/>
-    <ds:schemaRef ds:uri="19b1ad6d-7bbd-4338-adb0-a51e11e836c7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3614A8F8-9AED-4C02-B640-81A3A1FEB080}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19b1ad6d-7bbd-4338-adb0-a51e11e836c7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B6774AE-0D33-4944-9922-507715E1B0E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10015,4 +10030,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3614A8F8-9AED-4C02-B640-81A3A1FEB080}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC2B212-31BA-49FB-B215-9E14B2C60948}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09"/>
+    <ds:schemaRef ds:uri="19b1ad6d-7bbd-4338-adb0-a51e11e836c7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/templates/financial_template_v2_2026.xlsx
+++ b/data/templates/financial_template_v2_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pfizer-my.sharepoint.com/personal/hoveyo_pfizer_com/Documents/financial-automation-project/data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="8_{783183DD-73AE-4283-AD85-EEFD805851D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2275B3F8-8E5A-4910-A117-4523E2FD9255}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="8_{783183DD-73AE-4283-AD85-EEFD805851D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB629235-3EE4-4E21-A30B-8A9198D4224A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" tabRatio="590" xr2:uid="{0996C49B-04E6-42AE-AA83-2F64BE89A626}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Template" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Template!$A$15:$BY$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Template!$A$16:$BY$16</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1613,7 +1613,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1822,6 +1822,21 @@
     <xf numFmtId="3" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1831,20 +1846,11 @@
     <xf numFmtId="166" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1853,35 +1859,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 2" xfId="3" xr:uid="{EFDA3BDD-7E2C-4F3B-BEB7-091BB23895D4}"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -2213,7 +2191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177F1DEB-197D-49C6-A2E3-152C1AC7B373}">
-  <dimension ref="A1:EI67"/>
+  <dimension ref="A1:EI68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -2233,7 +2211,7 @@
     <col min="76" max="76" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:139" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
       <c r="B1" s="29"/>
       <c r="C1" s="14"/>
@@ -2245,7 +2223,7 @@
       <c r="I1" s="37"/>
       <c r="J1" s="37"/>
     </row>
-    <row r="2" spans="1:139" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -2266,7 +2244,7 @@
       <c r="I2" s="46"/>
       <c r="J2" s="46"/>
     </row>
-    <row r="3" spans="1:139" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
@@ -2290,7 +2268,7 @@
       <c r="I3" s="46"/>
       <c r="J3" s="46"/>
     </row>
-    <row r="4" spans="1:139" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -2307,7 +2285,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
     </row>
-    <row r="5" spans="1:139" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
@@ -2326,7 +2304,7 @@
       <c r="I5" s="37"/>
       <c r="J5" s="37"/>
     </row>
-    <row r="6" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18"/>
       <c r="B6" s="19"/>
       <c r="C6" s="20"/>
@@ -2338,11 +2316,11 @@
       <c r="I6" s="37"/>
       <c r="J6" s="37"/>
     </row>
-    <row r="7" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K7" s="42"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:139" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A8" s="105" t="s">
         <v>7</v>
       </c>
@@ -2360,7 +2338,7 @@
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="1:139" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
         <v>9</v>
       </c>
@@ -2375,7 +2353,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="1:139" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
         <v>12</v>
       </c>
@@ -2391,7 +2369,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="43"/>
     </row>
-    <row r="11" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>15</v>
       </c>
@@ -2410,126 +2388,27 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:139" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="118"/>
+      <c r="B12" s="119"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
       <c r="K12" s="44"/>
-      <c r="L12" s="113" t="s">
+      <c r="BW12" s="9"/>
+    </row>
+    <row r="13" spans="1:77" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="44"/>
+      <c r="L13" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="114"/>
-      <c r="N12" s="107" cm="1">
-        <f t="array" ref="N12">SUM(Q16:Q66)+SUM(_xlfn._xlws.FILTER(P16:P66,Q16:Q66=""))+SUM(_xlfn._xlws.FILTER(O16:O66,(P16:P66="")*(Q16:Q66="")))+SUMIFS(R16:R66,Q16:Q66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(N16:N66)</f>
-        <v>0</v>
-      </c>
-      <c r="O12" s="108"/>
-      <c r="P12" s="108"/>
-      <c r="Q12" s="108"/>
-      <c r="R12" s="109"/>
-      <c r="S12" s="107" cm="1">
-        <f t="array" ref="S12">SUM(V16:V66)+SUM(_xlfn._xlws.FILTER(U16:U66,V16:V66=""))+SUM(_xlfn._xlws.FILTER(T16:T66,(U16:U66="")*(V16:V66="")))+SUMIFS(W16:W66,V16:V66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(S16:S66)</f>
-        <v>0</v>
-      </c>
-      <c r="T12" s="108"/>
-      <c r="U12" s="108"/>
-      <c r="V12" s="108"/>
-      <c r="W12" s="109"/>
-      <c r="X12" s="107" cm="1">
-        <f t="array" ref="X12">SUM(AA16:AA66)+SUM(_xlfn._xlws.FILTER(Z16:Z66,AA16:AA66=""))+SUM(_xlfn._xlws.FILTER(Y16:Y66,(Z16:Z66="")*(AA16:AA66="")))+SUMIFS(AB16:AB66,AA16:AA66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(X16:X66)</f>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="108"/>
-      <c r="Z12" s="108"/>
-      <c r="AA12" s="108"/>
-      <c r="AB12" s="109"/>
-      <c r="AC12" s="107" cm="1">
-        <f t="array" ref="AC12">SUM(AF16:AF66)+SUM(_xlfn._xlws.FILTER(AE16:AE66,AF16:AF66=""))+SUM(_xlfn._xlws.FILTER(AD16:AD66,(AE16:AE66="")*(AF16:AF66="")))+SUMIFS(AG16:AG66,AF16:AF66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(AC16:AC66)</f>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="108"/>
-      <c r="AE12" s="108"/>
-      <c r="AF12" s="108"/>
-      <c r="AG12" s="109"/>
-      <c r="AH12" s="107" cm="1">
-        <f t="array" ref="AH12">SUM(AK16:AK66)+SUM(_xlfn._xlws.FILTER(AJ16:AJ66,AK16:AK66=""))+SUM(_xlfn._xlws.FILTER(AI16:AI66,(AJ16:AJ66="")*(AK16:AK66="")))+SUMIFS(AL16:AL66,AK16:AK66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(AH16:AH66)</f>
-        <v>0</v>
-      </c>
-      <c r="AI12" s="108"/>
-      <c r="AJ12" s="108"/>
-      <c r="AK12" s="108"/>
-      <c r="AL12" s="109"/>
-      <c r="AM12" s="107" cm="1">
-        <f t="array" ref="AM12">SUM(AP16:AP66)+SUM(_xlfn._xlws.FILTER(AO16:AO66,AP16:AP66=""))+SUM(_xlfn._xlws.FILTER(AN16:AN66,(AO16:AO66="")*(AP16:AP66="")))+SUMIFS(AQ16:AQ66,AP16:AP66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(AM16:AM66)</f>
-        <v>0</v>
-      </c>
-      <c r="AN12" s="108"/>
-      <c r="AO12" s="108"/>
-      <c r="AP12" s="108"/>
-      <c r="AQ12" s="109"/>
-      <c r="AR12" s="107" cm="1">
-        <f t="array" ref="AR12">SUM(AU16:AU66)+SUM(_xlfn._xlws.FILTER(AT16:AT66,AU16:AU66=""))+SUM(_xlfn._xlws.FILTER(AS16:AS66,(AT16:AT66="")*(AU16:AU66="")))+SUMIFS(AV16:AV66,AU16:AU66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(AR16:AR66)</f>
-        <v>0</v>
-      </c>
-      <c r="AS12" s="108"/>
-      <c r="AT12" s="108"/>
-      <c r="AU12" s="108"/>
-      <c r="AV12" s="109"/>
-      <c r="AW12" s="107" cm="1">
-        <f t="array" ref="AW12">SUM(AZ16:AZ66)+SUM(_xlfn._xlws.FILTER(AY16:AY66,AZ16:AZ66=""))+SUM(_xlfn._xlws.FILTER(AX16:AX66,(AY16:AY66="")*(AZ16:AZ66="")))+SUMIFS(BA16:BA66,AZ16:AZ66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(AW16:AW66)</f>
-        <v>0</v>
-      </c>
-      <c r="AX12" s="108"/>
-      <c r="AY12" s="108"/>
-      <c r="AZ12" s="108"/>
-      <c r="BA12" s="109"/>
-      <c r="BB12" s="107" cm="1">
-        <f t="array" ref="BB12">SUM(BE16:BE66)+SUM(_xlfn._xlws.FILTER(BD16:BD66,BE16:BE66=""))+SUM(_xlfn._xlws.FILTER(BC16:BC66,(BD16:BD66="")*(BE16:BE66="")))+SUMIFS(BF16:BF66,BE16:BE66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(BB16:BB66)</f>
-        <v>0</v>
-      </c>
-      <c r="BC12" s="108"/>
-      <c r="BD12" s="108"/>
-      <c r="BE12" s="108"/>
-      <c r="BF12" s="109"/>
-      <c r="BG12" s="107" cm="1">
-        <f t="array" ref="BG12">SUM(BJ16:BJ66)+SUM(_xlfn._xlws.FILTER(BI16:BI66,BJ16:BJ66=""))+SUM(_xlfn._xlws.FILTER(BH16:BH66,(BI16:BI66="")*(BJ16:BJ66="")))+SUMIFS(BK16:BK66,BJ16:BJ66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(BG16:BG66)</f>
-        <v>0</v>
-      </c>
-      <c r="BH12" s="108"/>
-      <c r="BI12" s="108"/>
-      <c r="BJ12" s="108"/>
-      <c r="BK12" s="109"/>
-      <c r="BL12" s="107" cm="1">
-        <f t="array" ref="BL12">SUM(BO16:BO66)+SUM(_xlfn._xlws.FILTER(BN16:BN66,BO16:BO66=""))+SUM(_xlfn._xlws.FILTER(BM16:BM66,(BN16:BN66="")*(BO16:BO66="")))+SUMIFS(BP16:BP66,BO16:BO66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(BL16:BL66)</f>
-        <v>0</v>
-      </c>
-      <c r="BM12" s="108"/>
-      <c r="BN12" s="108"/>
-      <c r="BO12" s="108"/>
-      <c r="BP12" s="109"/>
-      <c r="BQ12" s="107" cm="1">
-        <f t="array" ref="BQ12">SUM(BT16:BT66)+SUM(_xlfn._xlws.FILTER(BS16:BS66,BT16:BT66=""))+SUM(_xlfn._xlws.FILTER(BR16:BR66,(BS16:BS66="")*(BT16:BT66="")))+SUMIFS(BU16:BU66,BT16:BT66,"&lt;&gt;"&amp;"",$P$16:$P$66,"&lt;&gt;"&amp;"")+SUM(BQ16:BQ66)</f>
-        <v>0</v>
-      </c>
-      <c r="BR12" s="108"/>
-      <c r="BS12" s="108"/>
-      <c r="BT12" s="108"/>
-      <c r="BU12" s="109"/>
-      <c r="BV12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="BW12" s="5">
-        <f>BW14-BV14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K13" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="117" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13" s="116"/>
+      <c r="M13" s="111"/>
       <c r="N13" s="107" cm="1">
-        <f t="array" ref="N13">SUM(Q16:Q66)+SUM(_xlfn._xlws.FILTER(P16:P66,Q16:Q66=""))+SUM(_xlfn._xlws.FILTER(O16:O66,(P16:P66="")*(Q16:Q66="")))</f>
+        <f t="array" ref="N13">SUM(Q17:Q67)+SUM(_xlfn._xlws.FILTER(P17:P67,Q17:Q67=""))+SUM(_xlfn._xlws.FILTER(O17:O67,(P17:P67="")*(Q17:Q67="")))+SUMIFS(R17:R67,Q17:Q67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(N17:N67)</f>
         <v>0</v>
       </c>
       <c r="O13" s="108"/>
@@ -2537,7 +2416,7 @@
       <c r="Q13" s="108"/>
       <c r="R13" s="109"/>
       <c r="S13" s="107" cm="1">
-        <f t="array" ref="S13">SUM(V16:V66)+SUM(_xlfn._xlws.FILTER(U16:U66,V16:V66=""))+SUM(_xlfn._xlws.FILTER(T16:T66,(U16:U66="")*(V16:V66="")))</f>
+        <f t="array" ref="S13">SUM(V17:V67)+SUM(_xlfn._xlws.FILTER(U17:U67,V17:V67=""))+SUM(_xlfn._xlws.FILTER(T17:T67,(U17:U67="")*(V17:V67="")))+SUMIFS(W17:W67,V17:V67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(S17:S67)</f>
         <v>0</v>
       </c>
       <c r="T13" s="108"/>
@@ -2545,7 +2424,7 @@
       <c r="V13" s="108"/>
       <c r="W13" s="109"/>
       <c r="X13" s="107" cm="1">
-        <f t="array" ref="X13">SUM(AA16:AA66)+SUM(_xlfn._xlws.FILTER(Z16:Z66,AA16:AA66=""))+SUM(_xlfn._xlws.FILTER(Y16:Y66,(Z16:Z66="")*(AA16:AA66="")))</f>
+        <f t="array" ref="X13">SUM(AA17:AA67)+SUM(_xlfn._xlws.FILTER(Z17:Z67,AA17:AA67=""))+SUM(_xlfn._xlws.FILTER(Y17:Y67,(Z17:Z67="")*(AA17:AA67="")))+SUMIFS(AB17:AB67,AA17:AA67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(X17:X67)</f>
         <v>0</v>
       </c>
       <c r="Y13" s="108"/>
@@ -2553,7 +2432,7 @@
       <c r="AA13" s="108"/>
       <c r="AB13" s="109"/>
       <c r="AC13" s="107" cm="1">
-        <f t="array" ref="AC13">SUM(AF16:AF66)+SUM(_xlfn._xlws.FILTER(AE16:AE66,AF16:AF66=""))+SUM(_xlfn._xlws.FILTER(AD16:AD66,(AE16:AE66="")*(AF16:AF66="")))</f>
+        <f t="array" ref="AC13">SUM(AF17:AF67)+SUM(_xlfn._xlws.FILTER(AE17:AE67,AF17:AF67=""))+SUM(_xlfn._xlws.FILTER(AD17:AD67,(AE17:AE67="")*(AF17:AF67="")))+SUMIFS(AG17:AG67,AF17:AF67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(AC17:AC67)</f>
         <v>0</v>
       </c>
       <c r="AD13" s="108"/>
@@ -2561,7 +2440,7 @@
       <c r="AF13" s="108"/>
       <c r="AG13" s="109"/>
       <c r="AH13" s="107" cm="1">
-        <f t="array" ref="AH13">SUM(AK16:AK66)+SUM(_xlfn._xlws.FILTER(AJ16:AJ66,AK16:AK66=""))+SUM(_xlfn._xlws.FILTER(AI16:AI66,(AJ16:AJ66="")*(AK16:AK66="")))</f>
+        <f t="array" ref="AH13">SUM(AK17:AK67)+SUM(_xlfn._xlws.FILTER(AJ17:AJ67,AK17:AK67=""))+SUM(_xlfn._xlws.FILTER(AI17:AI67,(AJ17:AJ67="")*(AK17:AK67="")))+SUMIFS(AL17:AL67,AK17:AK67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(AH17:AH67)</f>
         <v>0</v>
       </c>
       <c r="AI13" s="108"/>
@@ -2569,7 +2448,7 @@
       <c r="AK13" s="108"/>
       <c r="AL13" s="109"/>
       <c r="AM13" s="107" cm="1">
-        <f t="array" ref="AM13">SUM(AP16:AP66)+SUM(_xlfn._xlws.FILTER(AO16:AO66,AP16:AP66=""))+SUM(_xlfn._xlws.FILTER(AN16:AN66,(AO16:AO66="")*(AP16:AP66="")))</f>
+        <f t="array" ref="AM13">SUM(AP17:AP67)+SUM(_xlfn._xlws.FILTER(AO17:AO67,AP17:AP67=""))+SUM(_xlfn._xlws.FILTER(AN17:AN67,(AO17:AO67="")*(AP17:AP67="")))+SUMIFS(AQ17:AQ67,AP17:AP67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(AM17:AM67)</f>
         <v>0</v>
       </c>
       <c r="AN13" s="108"/>
@@ -2577,7 +2456,7 @@
       <c r="AP13" s="108"/>
       <c r="AQ13" s="109"/>
       <c r="AR13" s="107" cm="1">
-        <f t="array" ref="AR13">SUM(AU16:AU66)+SUM(_xlfn._xlws.FILTER(AT16:AT66,AU16:AU66=""))+SUM(_xlfn._xlws.FILTER(AS16:AS66,(AT16:AT66="")*(AU16:AU66="")))</f>
+        <f t="array" ref="AR13">SUM(AU17:AU67)+SUM(_xlfn._xlws.FILTER(AT17:AT67,AU17:AU67=""))+SUM(_xlfn._xlws.FILTER(AS17:AS67,(AT17:AT67="")*(AU17:AU67="")))+SUMIFS(AV17:AV67,AU17:AU67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(AR17:AR67)</f>
         <v>0</v>
       </c>
       <c r="AS13" s="108"/>
@@ -2585,7 +2464,7 @@
       <c r="AU13" s="108"/>
       <c r="AV13" s="109"/>
       <c r="AW13" s="107" cm="1">
-        <f t="array" ref="AW13">SUM(AZ16:AZ66)+SUM(_xlfn._xlws.FILTER(AY16:AY66,AZ16:AZ66=""))+SUM(_xlfn._xlws.FILTER(AX16:AX66,(AY16:AY66="")*(AZ16:AZ66="")))</f>
+        <f t="array" ref="AW13">SUM(AZ17:AZ67)+SUM(_xlfn._xlws.FILTER(AY17:AY67,AZ17:AZ67=""))+SUM(_xlfn._xlws.FILTER(AX17:AX67,(AY17:AY67="")*(AZ17:AZ67="")))+SUMIFS(BA17:BA67,AZ17:AZ67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(AW17:AW67)</f>
         <v>0</v>
       </c>
       <c r="AX13" s="108"/>
@@ -2593,7 +2472,7 @@
       <c r="AZ13" s="108"/>
       <c r="BA13" s="109"/>
       <c r="BB13" s="107" cm="1">
-        <f t="array" ref="BB13">SUM(BE16:BE66)+SUM(_xlfn._xlws.FILTER(BD16:BD66,BE16:BE66=""))+SUM(_xlfn._xlws.FILTER(BC16:BC66,(BD16:BD66="")*(BE16:BE66="")))</f>
+        <f t="array" ref="BB13">SUM(BE17:BE67)+SUM(_xlfn._xlws.FILTER(BD17:BD67,BE17:BE67=""))+SUM(_xlfn._xlws.FILTER(BC17:BC67,(BD17:BD67="")*(BE17:BE67="")))+SUMIFS(BF17:BF67,BE17:BE67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(BB17:BB67)</f>
         <v>0</v>
       </c>
       <c r="BC13" s="108"/>
@@ -2601,7 +2480,7 @@
       <c r="BE13" s="108"/>
       <c r="BF13" s="109"/>
       <c r="BG13" s="107" cm="1">
-        <f t="array" ref="BG13">SUM(BJ16:BJ66)+SUM(_xlfn._xlws.FILTER(BI16:BI66,BJ16:BJ66=""))+SUM(_xlfn._xlws.FILTER(BH16:BH66,(BI16:BI66="")*(BJ16:BJ66="")))</f>
+        <f t="array" ref="BG13">SUM(BJ17:BJ67)+SUM(_xlfn._xlws.FILTER(BI17:BI67,BJ17:BJ67=""))+SUM(_xlfn._xlws.FILTER(BH17:BH67,(BI17:BI67="")*(BJ17:BJ67="")))+SUMIFS(BK17:BK67,BJ17:BJ67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(BG17:BG67)</f>
         <v>0</v>
       </c>
       <c r="BH13" s="108"/>
@@ -2609,7 +2488,7 @@
       <c r="BJ13" s="108"/>
       <c r="BK13" s="109"/>
       <c r="BL13" s="107" cm="1">
-        <f t="array" ref="BL13">SUM(BO16:BO66)+SUM(_xlfn._xlws.FILTER(BN16:BN66,BO16:BO66=""))+SUM(_xlfn._xlws.FILTER(BM16:BM66,(BN16:BN66="")*(BO16:BO66="")))</f>
+        <f t="array" ref="BL13">SUM(BO17:BO67)+SUM(_xlfn._xlws.FILTER(BN17:BN67,BO17:BO67=""))+SUM(_xlfn._xlws.FILTER(BM17:BM67,(BN17:BN67="")*(BO17:BO67="")))+SUMIFS(BP17:BP67,BO17:BO67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(BL17:BL67)</f>
         <v>0</v>
       </c>
       <c r="BM13" s="108"/>
@@ -2617,617 +2496,524 @@
       <c r="BO13" s="108"/>
       <c r="BP13" s="109"/>
       <c r="BQ13" s="107" cm="1">
-        <f t="array" ref="BQ13">SUM(BT16:BT66)+SUM(_xlfn._xlws.FILTER(BS16:BS66,BT16:BT66=""))+SUM(_xlfn._xlws.FILTER(BR16:BR66,(BS16:BS66="")*(BT16:BT66="")))</f>
+        <f t="array" ref="BQ13">SUM(BT17:BT67)+SUM(_xlfn._xlws.FILTER(BS17:BS67,BT17:BT67=""))+SUM(_xlfn._xlws.FILTER(BR17:BR67,(BS17:BS67="")*(BT17:BT67="")))+SUMIFS(BU17:BU67,BT17:BT67,"&lt;&gt;"&amp;"",$P$17:$P$67,"&lt;&gt;"&amp;"")+SUM(BQ17:BQ67)</f>
         <v>0</v>
       </c>
       <c r="BR13" s="108"/>
       <c r="BS13" s="108"/>
       <c r="BT13" s="108"/>
       <c r="BU13" s="109"/>
-      <c r="BV13" s="4"/>
-      <c r="BW13" s="5"/>
+      <c r="BV13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="BW13" s="5">
+        <f>BW15-BV15</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:139" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="112" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" s="113"/>
+      <c r="N14" s="107" cm="1">
+        <f t="array" ref="N14">SUM(Q17:Q67)+SUM(_xlfn._xlws.FILTER(P17:P67,Q17:Q67=""))+SUM(_xlfn._xlws.FILTER(O17:O67,(P17:P67="")*(Q17:Q67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="108"/>
+      <c r="P14" s="108"/>
+      <c r="Q14" s="108"/>
+      <c r="R14" s="109"/>
+      <c r="S14" s="107" cm="1">
+        <f t="array" ref="S14">SUM(V17:V67)+SUM(_xlfn._xlws.FILTER(U17:U67,V17:V67=""))+SUM(_xlfn._xlws.FILTER(T17:T67,(U17:U67="")*(V17:V67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="T14" s="108"/>
+      <c r="U14" s="108"/>
+      <c r="V14" s="108"/>
+      <c r="W14" s="109"/>
+      <c r="X14" s="107" cm="1">
+        <f t="array" ref="X14">SUM(AA17:AA67)+SUM(_xlfn._xlws.FILTER(Z17:Z67,AA17:AA67=""))+SUM(_xlfn._xlws.FILTER(Y17:Y67,(Z17:Z67="")*(AA17:AA67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="108"/>
+      <c r="Z14" s="108"/>
+      <c r="AA14" s="108"/>
+      <c r="AB14" s="109"/>
+      <c r="AC14" s="107" cm="1">
+        <f t="array" ref="AC14">SUM(AF17:AF67)+SUM(_xlfn._xlws.FILTER(AE17:AE67,AF17:AF67=""))+SUM(_xlfn._xlws.FILTER(AD17:AD67,(AE17:AE67="")*(AF17:AF67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="108"/>
+      <c r="AE14" s="108"/>
+      <c r="AF14" s="108"/>
+      <c r="AG14" s="109"/>
+      <c r="AH14" s="107" cm="1">
+        <f t="array" ref="AH14">SUM(AK17:AK67)+SUM(_xlfn._xlws.FILTER(AJ17:AJ67,AK17:AK67=""))+SUM(_xlfn._xlws.FILTER(AI17:AI67,(AJ17:AJ67="")*(AK17:AK67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AI14" s="108"/>
+      <c r="AJ14" s="108"/>
+      <c r="AK14" s="108"/>
+      <c r="AL14" s="109"/>
+      <c r="AM14" s="107" cm="1">
+        <f t="array" ref="AM14">SUM(AP17:AP67)+SUM(_xlfn._xlws.FILTER(AO17:AO67,AP17:AP67=""))+SUM(_xlfn._xlws.FILTER(AN17:AN67,(AO17:AO67="")*(AP17:AP67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AN14" s="108"/>
+      <c r="AO14" s="108"/>
+      <c r="AP14" s="108"/>
+      <c r="AQ14" s="109"/>
+      <c r="AR14" s="107" cm="1">
+        <f t="array" ref="AR14">SUM(AU17:AU67)+SUM(_xlfn._xlws.FILTER(AT17:AT67,AU17:AU67=""))+SUM(_xlfn._xlws.FILTER(AS17:AS67,(AT17:AT67="")*(AU17:AU67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AS14" s="108"/>
+      <c r="AT14" s="108"/>
+      <c r="AU14" s="108"/>
+      <c r="AV14" s="109"/>
+      <c r="AW14" s="107" cm="1">
+        <f t="array" ref="AW14">SUM(AZ17:AZ67)+SUM(_xlfn._xlws.FILTER(AY17:AY67,AZ17:AZ67=""))+SUM(_xlfn._xlws.FILTER(AX17:AX67,(AY17:AY67="")*(AZ17:AZ67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="AX14" s="108"/>
+      <c r="AY14" s="108"/>
+      <c r="AZ14" s="108"/>
+      <c r="BA14" s="109"/>
+      <c r="BB14" s="107" cm="1">
+        <f t="array" ref="BB14">SUM(BE17:BE67)+SUM(_xlfn._xlws.FILTER(BD17:BD67,BE17:BE67=""))+SUM(_xlfn._xlws.FILTER(BC17:BC67,(BD17:BD67="")*(BE17:BE67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BC14" s="108"/>
+      <c r="BD14" s="108"/>
+      <c r="BE14" s="108"/>
+      <c r="BF14" s="109"/>
+      <c r="BG14" s="107" cm="1">
+        <f t="array" ref="BG14">SUM(BJ17:BJ67)+SUM(_xlfn._xlws.FILTER(BI17:BI67,BJ17:BJ67=""))+SUM(_xlfn._xlws.FILTER(BH17:BH67,(BI17:BI67="")*(BJ17:BJ67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BH14" s="108"/>
+      <c r="BI14" s="108"/>
+      <c r="BJ14" s="108"/>
+      <c r="BK14" s="109"/>
+      <c r="BL14" s="107" cm="1">
+        <f t="array" ref="BL14">SUM(BO17:BO67)+SUM(_xlfn._xlws.FILTER(BN17:BN67,BO17:BO67=""))+SUM(_xlfn._xlws.FILTER(BM17:BM67,(BN17:BN67="")*(BO17:BO67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BM14" s="108"/>
+      <c r="BN14" s="108"/>
+      <c r="BO14" s="108"/>
+      <c r="BP14" s="109"/>
+      <c r="BQ14" s="107" cm="1">
+        <f t="array" ref="BQ14">SUM(BT17:BT67)+SUM(_xlfn._xlws.FILTER(BS17:BS67,BT17:BT67=""))+SUM(_xlfn._xlws.FILTER(BR17:BR67,(BS17:BS67="")*(BT17:BT67="")))</f>
+        <v>0</v>
+      </c>
+      <c r="BR14" s="108"/>
+      <c r="BS14" s="108"/>
+      <c r="BT14" s="108"/>
+      <c r="BU14" s="109"/>
+      <c r="BV14" s="4"/>
+      <c r="BW14" s="5"/>
+    </row>
+    <row r="15" spans="1:77" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="54">
-        <f>SUBTOTAL(9,K16:K17)</f>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="54">
+        <f>SUBTOTAL(9,K17:K18)</f>
         <v>190781</v>
       </c>
-      <c r="L14" s="115" t="s">
+      <c r="L15" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="116"/>
-      <c r="N14" s="110">
+      <c r="M15" s="113"/>
+      <c r="N15" s="115">
         <v>46053</v>
       </c>
-      <c r="O14" s="111" t="s">
+      <c r="O15" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="P14" s="111"/>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="111"/>
-      <c r="S14" s="110">
+      <c r="P15" s="116"/>
+      <c r="Q15" s="116"/>
+      <c r="R15" s="116"/>
+      <c r="S15" s="115">
         <v>46054</v>
       </c>
-      <c r="T14" s="111"/>
-      <c r="U14" s="111"/>
-      <c r="V14" s="111"/>
-      <c r="W14" s="112"/>
-      <c r="X14" s="110">
+      <c r="T15" s="116"/>
+      <c r="U15" s="116"/>
+      <c r="V15" s="116"/>
+      <c r="W15" s="117"/>
+      <c r="X15" s="115">
         <v>46112</v>
       </c>
-      <c r="Y14" s="111" t="s">
+      <c r="Y15" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="Z14" s="111"/>
-      <c r="AA14" s="111"/>
-      <c r="AB14" s="112"/>
-      <c r="AC14" s="110">
+      <c r="Z15" s="116"/>
+      <c r="AA15" s="116"/>
+      <c r="AB15" s="117"/>
+      <c r="AC15" s="115">
         <v>46142</v>
       </c>
-      <c r="AD14" s="111" t="s">
+      <c r="AD15" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="AE14" s="111"/>
-      <c r="AF14" s="111"/>
-      <c r="AG14" s="112"/>
-      <c r="AH14" s="110">
+      <c r="AE15" s="116"/>
+      <c r="AF15" s="116"/>
+      <c r="AG15" s="117"/>
+      <c r="AH15" s="115">
         <v>46173</v>
       </c>
-      <c r="AI14" s="111" t="s">
+      <c r="AI15" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="AJ14" s="111"/>
-      <c r="AK14" s="111"/>
-      <c r="AL14" s="112"/>
-      <c r="AM14" s="110">
+      <c r="AJ15" s="116"/>
+      <c r="AK15" s="116"/>
+      <c r="AL15" s="117"/>
+      <c r="AM15" s="115">
         <v>46203</v>
       </c>
-      <c r="AN14" s="111" t="s">
+      <c r="AN15" s="116" t="s">
         <v>24</v>
       </c>
-      <c r="AO14" s="111"/>
-      <c r="AP14" s="111"/>
-      <c r="AQ14" s="112"/>
-      <c r="AR14" s="110">
+      <c r="AO15" s="116"/>
+      <c r="AP15" s="116"/>
+      <c r="AQ15" s="117"/>
+      <c r="AR15" s="115">
         <v>46234</v>
       </c>
-      <c r="AS14" s="111" t="s">
+      <c r="AS15" s="116" t="s">
         <v>25</v>
       </c>
-      <c r="AT14" s="111"/>
-      <c r="AU14" s="111"/>
-      <c r="AV14" s="112"/>
-      <c r="AW14" s="110">
+      <c r="AT15" s="116"/>
+      <c r="AU15" s="116"/>
+      <c r="AV15" s="117"/>
+      <c r="AW15" s="115">
         <v>46265</v>
       </c>
-      <c r="AX14" s="111" t="s">
+      <c r="AX15" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="AY14" s="111"/>
-      <c r="AZ14" s="111"/>
-      <c r="BA14" s="112"/>
-      <c r="BB14" s="110">
+      <c r="AY15" s="116"/>
+      <c r="AZ15" s="116"/>
+      <c r="BA15" s="117"/>
+      <c r="BB15" s="115">
         <v>46295</v>
       </c>
-      <c r="BC14" s="111" t="s">
+      <c r="BC15" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="BD14" s="111"/>
-      <c r="BE14" s="111"/>
-      <c r="BF14" s="112"/>
-      <c r="BG14" s="110">
+      <c r="BD15" s="116"/>
+      <c r="BE15" s="116"/>
+      <c r="BF15" s="117"/>
+      <c r="BG15" s="115">
         <v>46326</v>
       </c>
-      <c r="BH14" s="111" t="s">
+      <c r="BH15" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="BI14" s="111"/>
-      <c r="BJ14" s="111"/>
-      <c r="BK14" s="112"/>
-      <c r="BL14" s="110">
+      <c r="BI15" s="116"/>
+      <c r="BJ15" s="116"/>
+      <c r="BK15" s="117"/>
+      <c r="BL15" s="115">
         <v>46356</v>
       </c>
-      <c r="BM14" s="111" t="s">
+      <c r="BM15" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="BN14" s="111"/>
-      <c r="BO14" s="111"/>
-      <c r="BP14" s="112"/>
-      <c r="BQ14" s="110">
+      <c r="BN15" s="116"/>
+      <c r="BO15" s="116"/>
+      <c r="BP15" s="117"/>
+      <c r="BQ15" s="115">
         <v>46387</v>
       </c>
-      <c r="BR14" s="111" t="s">
+      <c r="BR15" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="BS14" s="111"/>
-      <c r="BT14" s="111"/>
-      <c r="BU14" s="112"/>
-      <c r="BV14" s="7">
-        <f>SUM(BV16:BV66)</f>
-        <v>0</v>
-      </c>
-      <c r="BW14" s="8"/>
-      <c r="BY14" s="3"/>
+      <c r="BS15" s="116"/>
+      <c r="BT15" s="116"/>
+      <c r="BU15" s="117"/>
+      <c r="BV15" s="7">
+        <f>SUM(BV17:BV67)</f>
+        <v>0</v>
+      </c>
+      <c r="BW15" s="8"/>
+      <c r="BY15" s="3"/>
     </row>
-    <row r="15" spans="1:139" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="56" t="s">
+    <row r="16" spans="1:77" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="57" t="s">
+      <c r="B16" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C16" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="59" t="s">
+      <c r="D16" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="60" t="s">
+      <c r="E16" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="60" t="s">
+      <c r="F16" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="58" t="s">
+      <c r="G16" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="58" t="s">
+      <c r="H16" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="58" t="s">
+      <c r="I16" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="58" t="s">
+      <c r="J16" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K15" s="61" t="s">
+      <c r="K16" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="L15" s="62" t="s">
+      <c r="L16" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="M15" s="48" t="s">
+      <c r="M16" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="N15" s="51" t="s">
+      <c r="N16" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="O15" s="52" t="s">
+      <c r="O16" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="P15" s="52" t="s">
+      <c r="P16" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="Q15" s="52" t="s">
+      <c r="Q16" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="R15" s="50" t="s">
+      <c r="R16" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="S15" s="63" t="s">
+      <c r="S16" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="T15" s="52" t="s">
+      <c r="T16" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="U15" s="52" t="s">
+      <c r="U16" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="V15" s="64" t="s">
+      <c r="V16" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="W15" s="65" t="s">
+      <c r="W16" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="X15" s="63" t="s">
+      <c r="X16" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="Y15" s="52" t="s">
+      <c r="Y16" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="Z15" s="52" t="s">
+      <c r="Z16" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="AA15" s="64" t="s">
+      <c r="AA16" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="AB15" s="65" t="s">
+      <c r="AB16" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AC15" s="63" t="s">
+      <c r="AC16" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="AD15" s="52" t="s">
+      <c r="AD16" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="AE15" s="52" t="s">
+      <c r="AE16" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="AF15" s="64" t="s">
+      <c r="AF16" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="AG15" s="65" t="s">
+      <c r="AG16" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AH15" s="63" t="s">
+      <c r="AH16" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="AI15" s="52" t="s">
+      <c r="AI16" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="AJ15" s="52" t="s">
+      <c r="AJ16" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="AK15" s="64" t="s">
+      <c r="AK16" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="AL15" s="65" t="s">
+      <c r="AL16" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AM15" s="63" t="s">
+      <c r="AM16" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="AN15" s="52" t="s">
+      <c r="AN16" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="AO15" s="52" t="s">
+      <c r="AO16" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="AP15" s="64" t="s">
+      <c r="AP16" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="AQ15" s="65" t="s">
+      <c r="AQ16" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AR15" s="63" t="s">
+      <c r="AR16" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="AS15" s="52" t="s">
+      <c r="AS16" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="AT15" s="52" t="s">
+      <c r="AT16" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="AU15" s="64" t="s">
+      <c r="AU16" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="AV15" s="65" t="s">
+      <c r="AV16" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AW15" s="63" t="s">
+      <c r="AW16" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="AX15" s="52" t="s">
+      <c r="AX16" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="AY15" s="52" t="s">
+      <c r="AY16" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="AZ15" s="64" t="s">
+      <c r="AZ16" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="BA15" s="65" t="s">
+      <c r="BA16" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="BB15" s="63" t="s">
+      <c r="BB16" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="BC15" s="52" t="s">
+      <c r="BC16" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="BD15" s="52" t="s">
+      <c r="BD16" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="BE15" s="64" t="s">
+      <c r="BE16" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="BF15" s="65" t="s">
+      <c r="BF16" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="BG15" s="63" t="s">
+      <c r="BG16" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="BH15" s="52" t="s">
+      <c r="BH16" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="BI15" s="52" t="s">
+      <c r="BI16" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="BJ15" s="64" t="s">
+      <c r="BJ16" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="BK15" s="65" t="s">
+      <c r="BK16" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="BL15" s="63" t="s">
+      <c r="BL16" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="BM15" s="52" t="s">
+      <c r="BM16" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="BN15" s="52" t="s">
+      <c r="BN16" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="BO15" s="64" t="s">
+      <c r="BO16" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="BP15" s="65" t="s">
+      <c r="BP16" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="BQ15" s="63" t="s">
+      <c r="BQ16" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="BR15" s="52" t="s">
+      <c r="BR16" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="BS15" s="52" t="s">
+      <c r="BS16" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="BT15" s="64" t="s">
+      <c r="BT16" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="BU15" s="65" t="s">
+      <c r="BU16" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="BV15" s="51" t="s">
+      <c r="BV16" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="BW15" s="52" t="s">
+      <c r="BW16" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="BX15" s="48" t="s">
+      <c r="BX16" s="48" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="16" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A16" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" s="94">
-        <v>9501133449</v>
-      </c>
-      <c r="C16" s="96">
-        <v>45993</v>
-      </c>
-      <c r="D16" s="96">
-        <v>46173</v>
-      </c>
-      <c r="E16" s="81" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" s="80" t="s">
-        <v>99</v>
-      </c>
-      <c r="G16" s="80">
-        <v>41500000</v>
-      </c>
-      <c r="H16" s="80">
-        <v>3840</v>
-      </c>
-      <c r="I16" s="80" t="s">
-        <v>100</v>
-      </c>
-      <c r="J16" s="80">
-        <v>2430238</v>
-      </c>
-      <c r="K16" s="97">
-        <v>66363</v>
-      </c>
-      <c r="L16" s="100" t="s">
-        <v>165</v>
-      </c>
-      <c r="M16" s="101" t="s">
-        <v>166</v>
-      </c>
-      <c r="N16" s="82"/>
-      <c r="O16" s="83"/>
-      <c r="P16" s="83"/>
-      <c r="Q16" s="84"/>
-      <c r="R16" s="84">
-        <f>P16-Q16</f>
-        <v>0</v>
-      </c>
-      <c r="S16" s="85"/>
-      <c r="T16" s="83"/>
-      <c r="U16" s="83"/>
-      <c r="V16" s="84"/>
-      <c r="W16" s="86">
-        <f>U16-V16</f>
-        <v>0</v>
-      </c>
-      <c r="X16" s="87"/>
-      <c r="Y16" s="83"/>
-      <c r="Z16" s="83"/>
-      <c r="AA16" s="84"/>
-      <c r="AB16" s="86">
-        <f>Z16-AA16</f>
-        <v>0</v>
-      </c>
-      <c r="AC16" s="87"/>
-      <c r="AD16" s="83"/>
-      <c r="AE16" s="83"/>
-      <c r="AF16" s="83"/>
-      <c r="AG16" s="86">
-        <f>AE16-AF16</f>
-        <v>0</v>
-      </c>
-      <c r="AH16" s="87"/>
-      <c r="AI16" s="83"/>
-      <c r="AJ16" s="83"/>
-      <c r="AK16" s="83"/>
-      <c r="AL16" s="86">
-        <f>AJ16-AK16</f>
-        <v>0</v>
-      </c>
-      <c r="AM16" s="87"/>
-      <c r="AN16" s="83"/>
-      <c r="AO16" s="83"/>
-      <c r="AP16" s="83"/>
-      <c r="AQ16" s="86">
-        <f>AO16-AP16</f>
-        <v>0</v>
-      </c>
-      <c r="AR16" s="87"/>
-      <c r="AS16" s="83"/>
-      <c r="AT16" s="83"/>
-      <c r="AU16" s="83"/>
-      <c r="AV16" s="86">
-        <f>AT16-AU16</f>
-        <v>0</v>
-      </c>
-      <c r="AW16" s="87"/>
-      <c r="AX16" s="83"/>
-      <c r="AY16" s="83"/>
-      <c r="AZ16" s="83"/>
-      <c r="BA16" s="86">
-        <f>AY16-AZ16</f>
-        <v>0</v>
-      </c>
-      <c r="BB16" s="87"/>
-      <c r="BC16" s="83"/>
-      <c r="BD16" s="83"/>
-      <c r="BE16" s="83"/>
-      <c r="BF16" s="86">
-        <f>BD16-BE16</f>
-        <v>0</v>
-      </c>
-      <c r="BG16" s="87"/>
-      <c r="BH16" s="83"/>
-      <c r="BI16" s="83"/>
-      <c r="BJ16" s="83"/>
-      <c r="BK16" s="86">
-        <f>BI16-BJ16</f>
-        <v>0</v>
-      </c>
-      <c r="BL16" s="87"/>
-      <c r="BM16" s="83"/>
-      <c r="BN16" s="83"/>
-      <c r="BO16" s="83"/>
-      <c r="BP16" s="86">
-        <f>BN16-BO16</f>
-        <v>0</v>
-      </c>
-      <c r="BQ16" s="87"/>
-      <c r="BR16" s="83"/>
-      <c r="BS16" s="83"/>
-      <c r="BT16" s="83"/>
-      <c r="BU16" s="86">
-        <f>BS16-BT16</f>
-        <v>0</v>
-      </c>
-      <c r="BV16" s="88">
-        <v>0</v>
-      </c>
-      <c r="BW16" s="89"/>
-      <c r="BX16" s="90"/>
-      <c r="BY16" s="78"/>
-      <c r="BZ16" s="78"/>
-      <c r="CA16" s="78"/>
-      <c r="CB16" s="78"/>
-      <c r="CC16" s="78"/>
-      <c r="CD16" s="78"/>
-      <c r="CE16" s="78"/>
-      <c r="CF16" s="78"/>
-      <c r="CG16" s="78"/>
-      <c r="CH16" s="78"/>
-      <c r="CI16" s="78"/>
-      <c r="CJ16" s="78"/>
-      <c r="CK16" s="78"/>
-      <c r="CL16" s="78"/>
-      <c r="CM16" s="78"/>
-      <c r="CN16" s="78"/>
-      <c r="CO16" s="78"/>
-      <c r="CP16" s="78"/>
-      <c r="CQ16" s="78"/>
-      <c r="CR16" s="78"/>
-      <c r="CS16" s="78"/>
-      <c r="CT16" s="78"/>
-      <c r="CU16" s="78"/>
-      <c r="CV16" s="78"/>
-      <c r="CW16" s="78"/>
-      <c r="CX16" s="78"/>
-      <c r="CY16" s="78"/>
-      <c r="CZ16" s="78"/>
-      <c r="DA16" s="78"/>
-      <c r="DB16" s="78"/>
-      <c r="DC16" s="78"/>
-      <c r="DD16" s="78"/>
-      <c r="DE16" s="78"/>
-      <c r="DF16" s="78"/>
-      <c r="DG16" s="78"/>
-      <c r="DH16" s="78"/>
-      <c r="DI16" s="78"/>
-      <c r="DJ16" s="78"/>
-      <c r="DK16" s="78"/>
-      <c r="DL16" s="78"/>
-      <c r="DM16" s="78"/>
-      <c r="DN16" s="78"/>
-      <c r="DO16" s="78"/>
-      <c r="DP16" s="78"/>
-      <c r="DQ16" s="78"/>
-      <c r="DR16" s="78"/>
-      <c r="DS16" s="78"/>
-      <c r="DT16" s="78"/>
-      <c r="DU16" s="78"/>
-      <c r="DV16" s="78"/>
-      <c r="DW16" s="78"/>
-      <c r="DX16" s="78"/>
-      <c r="DY16" s="78"/>
-      <c r="DZ16" s="78"/>
-      <c r="EA16" s="78"/>
-      <c r="EB16" s="78"/>
-      <c r="EC16" s="78"/>
-      <c r="ED16" s="78"/>
-      <c r="EE16" s="78"/>
-      <c r="EF16" s="78"/>
-      <c r="EG16" s="78"/>
-      <c r="EH16" s="78"/>
-      <c r="EI16" s="78"/>
     </row>
     <row r="17" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="79" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="83">
-        <v>9501133442</v>
-      </c>
-      <c r="C17" s="98">
+      <c r="B17" s="94">
+        <v>9501133449</v>
+      </c>
+      <c r="C17" s="96">
         <v>45993</v>
       </c>
-      <c r="D17" s="98">
-        <v>46356</v>
-      </c>
-      <c r="E17" s="92" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="92" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" s="92">
+      <c r="D17" s="96">
+        <v>46173</v>
+      </c>
+      <c r="E17" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="80" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="80">
         <v>41500000</v>
       </c>
-      <c r="H17" s="92">
+      <c r="H17" s="80">
         <v>3840</v>
       </c>
-      <c r="I17" s="92" t="s">
+      <c r="I17" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="J17" s="92">
+      <c r="J17" s="80">
         <v>2430238</v>
       </c>
-      <c r="K17" s="99">
-        <v>124418</v>
-      </c>
-      <c r="L17" s="102" t="s">
-        <v>167</v>
-      </c>
-      <c r="M17" s="103" t="s">
+      <c r="K17" s="97">
+        <v>66363</v>
+      </c>
+      <c r="L17" s="100" t="s">
+        <v>165</v>
+      </c>
+      <c r="M17" s="101" t="s">
         <v>166</v>
       </c>
       <c r="N17" s="82"/>
@@ -3257,7 +3043,7 @@
       <c r="AC17" s="87"/>
       <c r="AD17" s="83"/>
       <c r="AE17" s="83"/>
-      <c r="AF17" s="84"/>
+      <c r="AF17" s="83"/>
       <c r="AG17" s="86">
         <f>AE17-AF17</f>
         <v>0</v>
@@ -3265,7 +3051,7 @@
       <c r="AH17" s="87"/>
       <c r="AI17" s="83"/>
       <c r="AJ17" s="83"/>
-      <c r="AK17" s="84"/>
+      <c r="AK17" s="83"/>
       <c r="AL17" s="86">
         <f>AJ17-AK17</f>
         <v>0</v>
@@ -3273,7 +3059,7 @@
       <c r="AM17" s="87"/>
       <c r="AN17" s="83"/>
       <c r="AO17" s="83"/>
-      <c r="AP17" s="84"/>
+      <c r="AP17" s="83"/>
       <c r="AQ17" s="86">
         <f>AO17-AP17</f>
         <v>0</v>
@@ -3281,7 +3067,7 @@
       <c r="AR17" s="87"/>
       <c r="AS17" s="83"/>
       <c r="AT17" s="83"/>
-      <c r="AU17" s="84"/>
+      <c r="AU17" s="83"/>
       <c r="AV17" s="86">
         <f>AT17-AU17</f>
         <v>0</v>
@@ -3289,7 +3075,7 @@
       <c r="AW17" s="87"/>
       <c r="AX17" s="83"/>
       <c r="AY17" s="83"/>
-      <c r="AZ17" s="84"/>
+      <c r="AZ17" s="83"/>
       <c r="BA17" s="86">
         <f>AY17-AZ17</f>
         <v>0</v>
@@ -3297,7 +3083,7 @@
       <c r="BB17" s="87"/>
       <c r="BC17" s="83"/>
       <c r="BD17" s="83"/>
-      <c r="BE17" s="84"/>
+      <c r="BE17" s="83"/>
       <c r="BF17" s="86">
         <f>BD17-BE17</f>
         <v>0</v>
@@ -3305,7 +3091,7 @@
       <c r="BG17" s="87"/>
       <c r="BH17" s="83"/>
       <c r="BI17" s="83"/>
-      <c r="BJ17" s="84"/>
+      <c r="BJ17" s="83"/>
       <c r="BK17" s="86">
         <f>BI17-BJ17</f>
         <v>0</v>
@@ -3313,7 +3099,7 @@
       <c r="BL17" s="87"/>
       <c r="BM17" s="83"/>
       <c r="BN17" s="83"/>
-      <c r="BO17" s="84"/>
+      <c r="BO17" s="83"/>
       <c r="BP17" s="86">
         <f>BN17-BO17</f>
         <v>0</v>
@@ -3321,12 +3107,12 @@
       <c r="BQ17" s="87"/>
       <c r="BR17" s="83"/>
       <c r="BS17" s="83"/>
-      <c r="BT17" s="84"/>
+      <c r="BT17" s="83"/>
       <c r="BU17" s="86">
         <f>BS17-BT17</f>
         <v>0</v>
       </c>
-      <c r="BV17" s="85">
+      <c r="BV17" s="88">
         <v>0</v>
       </c>
       <c r="BW17" s="89"/>
@@ -3395,42 +3181,42 @@
       <c r="EH17" s="78"/>
       <c r="EI17" s="78"/>
     </row>
-    <row r="18" spans="1:139" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:139" x14ac:dyDescent="0.25">
       <c r="A18" s="91" t="s">
         <v>97</v>
       </c>
       <c r="B18" s="83">
-        <v>9100561560</v>
+        <v>9501133442</v>
       </c>
       <c r="C18" s="98">
-        <v>46137</v>
+        <v>45993</v>
       </c>
       <c r="D18" s="98">
-        <v>46501</v>
+        <v>46356</v>
       </c>
       <c r="E18" s="92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F18" s="92" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G18" s="92">
-        <v>61010000</v>
+        <v>41500000</v>
       </c>
       <c r="H18" s="92">
-        <v>1400</v>
+        <v>3840</v>
       </c>
       <c r="I18" s="92" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J18" s="92">
-        <v>2321403</v>
+        <v>2430238</v>
       </c>
       <c r="K18" s="99">
-        <v>21098.22</v>
-      </c>
-      <c r="L18" s="104" t="s">
-        <v>168</v>
+        <v>124418</v>
+      </c>
+      <c r="L18" s="102" t="s">
+        <v>167</v>
       </c>
       <c r="M18" s="103" t="s">
         <v>166</v>
@@ -3440,7 +3226,7 @@
       <c r="P18" s="83"/>
       <c r="Q18" s="84"/>
       <c r="R18" s="84">
-        <f t="shared" ref="R18:R25" si="0">P18-Q18</f>
+        <f>P18-Q18</f>
         <v>0</v>
       </c>
       <c r="S18" s="85"/>
@@ -3448,7 +3234,7 @@
       <c r="U18" s="83"/>
       <c r="V18" s="84"/>
       <c r="W18" s="86">
-        <f t="shared" ref="W18:W25" si="1">U18-V18</f>
+        <f>U18-V18</f>
         <v>0</v>
       </c>
       <c r="X18" s="87"/>
@@ -3456,7 +3242,7 @@
       <c r="Z18" s="83"/>
       <c r="AA18" s="84"/>
       <c r="AB18" s="86">
-        <f t="shared" ref="AB18:AB25" si="2">Z18-AA18</f>
+        <f>Z18-AA18</f>
         <v>0</v>
       </c>
       <c r="AC18" s="87"/>
@@ -3464,7 +3250,7 @@
       <c r="AE18" s="83"/>
       <c r="AF18" s="84"/>
       <c r="AG18" s="86">
-        <f t="shared" ref="AG18:AG25" si="3">AE18-AF18</f>
+        <f>AE18-AF18</f>
         <v>0</v>
       </c>
       <c r="AH18" s="87"/>
@@ -3472,7 +3258,7 @@
       <c r="AJ18" s="83"/>
       <c r="AK18" s="84"/>
       <c r="AL18" s="86">
-        <f t="shared" ref="AL18:AL25" si="4">AJ18-AK18</f>
+        <f>AJ18-AK18</f>
         <v>0</v>
       </c>
       <c r="AM18" s="87"/>
@@ -3480,7 +3266,7 @@
       <c r="AO18" s="83"/>
       <c r="AP18" s="84"/>
       <c r="AQ18" s="86">
-        <f t="shared" ref="AQ18:AQ25" si="5">AO18-AP18</f>
+        <f>AO18-AP18</f>
         <v>0</v>
       </c>
       <c r="AR18" s="87"/>
@@ -3488,7 +3274,7 @@
       <c r="AT18" s="83"/>
       <c r="AU18" s="84"/>
       <c r="AV18" s="86">
-        <f t="shared" ref="AV18:AV25" si="6">AT18-AU18</f>
+        <f>AT18-AU18</f>
         <v>0</v>
       </c>
       <c r="AW18" s="87"/>
@@ -3496,7 +3282,7 @@
       <c r="AY18" s="83"/>
       <c r="AZ18" s="84"/>
       <c r="BA18" s="86">
-        <f t="shared" ref="BA18:BA25" si="7">AY18-AZ18</f>
+        <f>AY18-AZ18</f>
         <v>0</v>
       </c>
       <c r="BB18" s="87"/>
@@ -3504,7 +3290,7 @@
       <c r="BD18" s="83"/>
       <c r="BE18" s="84"/>
       <c r="BF18" s="86">
-        <f t="shared" ref="BF18:BF25" si="8">BD18-BE18</f>
+        <f>BD18-BE18</f>
         <v>0</v>
       </c>
       <c r="BG18" s="87"/>
@@ -3512,7 +3298,7 @@
       <c r="BI18" s="83"/>
       <c r="BJ18" s="84"/>
       <c r="BK18" s="86">
-        <f t="shared" ref="BK18:BK25" si="9">BI18-BJ18</f>
+        <f>BI18-BJ18</f>
         <v>0</v>
       </c>
       <c r="BL18" s="87"/>
@@ -3520,7 +3306,7 @@
       <c r="BN18" s="83"/>
       <c r="BO18" s="84"/>
       <c r="BP18" s="86">
-        <f t="shared" ref="BP18:BP25" si="10">BN18-BO18</f>
+        <f>BN18-BO18</f>
         <v>0</v>
       </c>
       <c r="BQ18" s="87"/>
@@ -3528,7 +3314,7 @@
       <c r="BS18" s="83"/>
       <c r="BT18" s="84"/>
       <c r="BU18" s="86">
-        <f t="shared" ref="BU18:BU25" si="11">BS18-BT18</f>
+        <f>BS18-BT18</f>
         <v>0</v>
       </c>
       <c r="BV18" s="85">
@@ -3536,37 +3322,116 @@
       </c>
       <c r="BW18" s="89"/>
       <c r="BX18" s="90"/>
+      <c r="BY18" s="78"/>
+      <c r="BZ18" s="78"/>
+      <c r="CA18" s="78"/>
+      <c r="CB18" s="78"/>
+      <c r="CC18" s="78"/>
+      <c r="CD18" s="78"/>
+      <c r="CE18" s="78"/>
+      <c r="CF18" s="78"/>
+      <c r="CG18" s="78"/>
+      <c r="CH18" s="78"/>
+      <c r="CI18" s="78"/>
+      <c r="CJ18" s="78"/>
+      <c r="CK18" s="78"/>
+      <c r="CL18" s="78"/>
+      <c r="CM18" s="78"/>
+      <c r="CN18" s="78"/>
+      <c r="CO18" s="78"/>
+      <c r="CP18" s="78"/>
+      <c r="CQ18" s="78"/>
+      <c r="CR18" s="78"/>
+      <c r="CS18" s="78"/>
+      <c r="CT18" s="78"/>
+      <c r="CU18" s="78"/>
+      <c r="CV18" s="78"/>
+      <c r="CW18" s="78"/>
+      <c r="CX18" s="78"/>
+      <c r="CY18" s="78"/>
+      <c r="CZ18" s="78"/>
+      <c r="DA18" s="78"/>
+      <c r="DB18" s="78"/>
+      <c r="DC18" s="78"/>
+      <c r="DD18" s="78"/>
+      <c r="DE18" s="78"/>
+      <c r="DF18" s="78"/>
+      <c r="DG18" s="78"/>
+      <c r="DH18" s="78"/>
+      <c r="DI18" s="78"/>
+      <c r="DJ18" s="78"/>
+      <c r="DK18" s="78"/>
+      <c r="DL18" s="78"/>
+      <c r="DM18" s="78"/>
+      <c r="DN18" s="78"/>
+      <c r="DO18" s="78"/>
+      <c r="DP18" s="78"/>
+      <c r="DQ18" s="78"/>
+      <c r="DR18" s="78"/>
+      <c r="DS18" s="78"/>
+      <c r="DT18" s="78"/>
+      <c r="DU18" s="78"/>
+      <c r="DV18" s="78"/>
+      <c r="DW18" s="78"/>
+      <c r="DX18" s="78"/>
+      <c r="DY18" s="78"/>
+      <c r="DZ18" s="78"/>
+      <c r="EA18" s="78"/>
+      <c r="EB18" s="78"/>
+      <c r="EC18" s="78"/>
+      <c r="ED18" s="78"/>
+      <c r="EE18" s="78"/>
+      <c r="EF18" s="78"/>
+      <c r="EG18" s="78"/>
+      <c r="EH18" s="78"/>
+      <c r="EI18" s="78"/>
     </row>
-    <row r="19" spans="1:139" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:139" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="91" t="s">
         <v>97</v>
       </c>
       <c r="B19" s="83">
-        <v>9501079958</v>
+        <v>9100561560</v>
       </c>
       <c r="C19" s="98">
-        <v>45931</v>
+        <v>46137</v>
       </c>
       <c r="D19" s="98">
-        <v>46265</v>
+        <v>46501</v>
       </c>
       <c r="E19" s="92" t="s">
-        <v>106</v>
-      </c>
-      <c r="F19" s="92"/>
-      <c r="G19" s="92"/>
-      <c r="H19" s="92"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="93"/>
-      <c r="L19" s="104"/>
-      <c r="M19" s="103"/>
+        <v>103</v>
+      </c>
+      <c r="F19" s="92" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" s="92">
+        <v>61010000</v>
+      </c>
+      <c r="H19" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I19" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K19" s="99">
+        <v>21098.22</v>
+      </c>
+      <c r="L19" s="104" t="s">
+        <v>168</v>
+      </c>
+      <c r="M19" s="103" t="s">
+        <v>166</v>
+      </c>
       <c r="N19" s="82"/>
       <c r="O19" s="83"/>
       <c r="P19" s="83"/>
       <c r="Q19" s="84"/>
       <c r="R19" s="84">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="R19:R26" si="0">P19-Q19</f>
         <v>0</v>
       </c>
       <c r="S19" s="85"/>
@@ -3574,7 +3439,7 @@
       <c r="U19" s="83"/>
       <c r="V19" s="84"/>
       <c r="W19" s="86">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="W19:W26" si="1">U19-V19</f>
         <v>0</v>
       </c>
       <c r="X19" s="87"/>
@@ -3582,7 +3447,7 @@
       <c r="Z19" s="83"/>
       <c r="AA19" s="84"/>
       <c r="AB19" s="86">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AB19:AB26" si="2">Z19-AA19</f>
         <v>0</v>
       </c>
       <c r="AC19" s="87"/>
@@ -3590,7 +3455,7 @@
       <c r="AE19" s="83"/>
       <c r="AF19" s="84"/>
       <c r="AG19" s="86">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="AG19:AG26" si="3">AE19-AF19</f>
         <v>0</v>
       </c>
       <c r="AH19" s="87"/>
@@ -3598,7 +3463,7 @@
       <c r="AJ19" s="83"/>
       <c r="AK19" s="84"/>
       <c r="AL19" s="86">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="AL19:AL26" si="4">AJ19-AK19</f>
         <v>0</v>
       </c>
       <c r="AM19" s="87"/>
@@ -3606,7 +3471,7 @@
       <c r="AO19" s="83"/>
       <c r="AP19" s="84"/>
       <c r="AQ19" s="86">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="AQ19:AQ26" si="5">AO19-AP19</f>
         <v>0</v>
       </c>
       <c r="AR19" s="87"/>
@@ -3614,7 +3479,7 @@
       <c r="AT19" s="83"/>
       <c r="AU19" s="84"/>
       <c r="AV19" s="86">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="AV19:AV26" si="6">AT19-AU19</f>
         <v>0</v>
       </c>
       <c r="AW19" s="87"/>
@@ -3622,7 +3487,7 @@
       <c r="AY19" s="83"/>
       <c r="AZ19" s="84"/>
       <c r="BA19" s="86">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="BA19:BA26" si="7">AY19-AZ19</f>
         <v>0</v>
       </c>
       <c r="BB19" s="87"/>
@@ -3630,7 +3495,7 @@
       <c r="BD19" s="83"/>
       <c r="BE19" s="84"/>
       <c r="BF19" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="BF19:BF26" si="8">BD19-BE19</f>
         <v>0</v>
       </c>
       <c r="BG19" s="87"/>
@@ -3638,7 +3503,7 @@
       <c r="BI19" s="83"/>
       <c r="BJ19" s="84"/>
       <c r="BK19" s="86">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="BK19:BK26" si="9">BI19-BJ19</f>
         <v>0</v>
       </c>
       <c r="BL19" s="87"/>
@@ -3646,7 +3511,7 @@
       <c r="BN19" s="83"/>
       <c r="BO19" s="84"/>
       <c r="BP19" s="86">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="BP19:BP26" si="10">BN19-BO19</f>
         <v>0</v>
       </c>
       <c r="BQ19" s="87"/>
@@ -3654,7 +3519,7 @@
       <c r="BS19" s="83"/>
       <c r="BT19" s="84"/>
       <c r="BU19" s="86">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="BU19:BU26" si="11">BS19-BT19</f>
         <v>0</v>
       </c>
       <c r="BV19" s="85">
@@ -3665,44 +3530,28 @@
     </row>
     <row r="20" spans="1:139" x14ac:dyDescent="0.25">
       <c r="A20" s="91" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B20" s="83">
-        <v>9501215650</v>
+        <v>9501079958</v>
       </c>
       <c r="C20" s="98">
-        <v>46065</v>
+        <v>45931</v>
       </c>
       <c r="D20" s="98">
-        <v>46387</v>
+        <v>46265</v>
       </c>
       <c r="E20" s="92" t="s">
-        <v>108</v>
-      </c>
-      <c r="F20" s="92" t="s">
-        <v>109</v>
-      </c>
-      <c r="G20" s="92">
-        <v>41500000</v>
-      </c>
-      <c r="H20" s="92">
-        <v>1400</v>
-      </c>
-      <c r="I20" s="92" t="s">
-        <v>105</v>
-      </c>
-      <c r="J20" s="92">
-        <v>2340693</v>
-      </c>
-      <c r="K20" s="99">
-        <v>54880</v>
-      </c>
-      <c r="L20" s="104" t="s">
-        <v>169</v>
-      </c>
-      <c r="M20" s="103" t="s">
-        <v>166</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="F20" s="92"/>
+      <c r="G20" s="92"/>
+      <c r="H20" s="92"/>
+      <c r="I20" s="92"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="103"/>
       <c r="N20" s="82"/>
       <c r="O20" s="83"/>
       <c r="P20" s="83"/>
@@ -3805,28 +3654,46 @@
       <c r="BW20" s="89"/>
       <c r="BX20" s="90"/>
     </row>
-    <row r="21" spans="1:139" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="91"/>
-      <c r="B21" s="83" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="92"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92"/>
+    <row r="21" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A21" s="91" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="83">
+        <v>9501215650</v>
+      </c>
+      <c r="C21" s="98">
+        <v>46065</v>
+      </c>
+      <c r="D21" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E21" s="92" t="s">
+        <v>108</v>
+      </c>
       <c r="F21" s="92" t="s">
-        <v>111</v>
-      </c>
-      <c r="G21" s="92"/>
-      <c r="H21" s="92"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="92"/>
+        <v>109</v>
+      </c>
+      <c r="G21" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H21" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I21" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J21" s="92">
+        <v>2340693</v>
+      </c>
       <c r="K21" s="99">
-        <v>150000</v>
-      </c>
-      <c r="L21" s="102" t="s">
-        <v>170</v>
-      </c>
-      <c r="M21" s="103"/>
+        <v>54880</v>
+      </c>
+      <c r="L21" s="104" t="s">
+        <v>169</v>
+      </c>
+      <c r="M21" s="103" t="s">
+        <v>166</v>
+      </c>
       <c r="N21" s="82"/>
       <c r="O21" s="83"/>
       <c r="P21" s="83"/>
@@ -3929,34 +3796,26 @@
       <c r="BW21" s="89"/>
       <c r="BX21" s="90"/>
     </row>
-    <row r="22" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A22" s="91" t="s">
-        <v>112</v>
-      </c>
-      <c r="B22" s="83"/>
+    <row r="22" spans="1:139" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="91"/>
+      <c r="B22" s="83" t="s">
+        <v>110</v>
+      </c>
       <c r="C22" s="92"/>
       <c r="D22" s="92"/>
-      <c r="E22" s="92" t="s">
-        <v>101</v>
-      </c>
+      <c r="E22" s="92"/>
       <c r="F22" s="92" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" s="92">
-        <v>41500000</v>
-      </c>
-      <c r="H22" s="92">
-        <v>1400</v>
-      </c>
-      <c r="I22" s="92" t="s">
-        <v>105</v>
-      </c>
-      <c r="J22" s="92">
-        <v>2321403</v>
-      </c>
-      <c r="K22" s="93"/>
+        <v>111</v>
+      </c>
+      <c r="G22" s="92"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="99">
+        <v>150000</v>
+      </c>
       <c r="L22" s="102" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M22" s="103"/>
       <c r="N22" s="82"/>
@@ -4061,22 +3920,34 @@
       <c r="BW22" s="89"/>
       <c r="BX22" s="90"/>
     </row>
-    <row r="23" spans="1:139" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="91"/>
+    <row r="23" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A23" s="91" t="s">
+        <v>112</v>
+      </c>
       <c r="B23" s="83"/>
       <c r="C23" s="92"/>
       <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
+      <c r="E23" s="92" t="s">
+        <v>101</v>
+      </c>
       <c r="F23" s="92" t="s">
-        <v>113</v>
-      </c>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
+        <v>102</v>
+      </c>
+      <c r="G23" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H23" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I23" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J23" s="92">
+        <v>2321403</v>
+      </c>
       <c r="K23" s="93"/>
       <c r="L23" s="102" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M23" s="103"/>
       <c r="N23" s="82"/>
@@ -4188,7 +4059,7 @@
       <c r="D24" s="92"/>
       <c r="E24" s="92"/>
       <c r="F24" s="92" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G24" s="92"/>
       <c r="H24" s="92"/>
@@ -4196,7 +4067,7 @@
       <c r="J24" s="92"/>
       <c r="K24" s="93"/>
       <c r="L24" s="102" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M24" s="103"/>
       <c r="N24" s="82"/>
@@ -4301,14 +4172,14 @@
       <c r="BW24" s="89"/>
       <c r="BX24" s="90"/>
     </row>
-    <row r="25" spans="1:139" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:139" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="91"/>
       <c r="B25" s="83"/>
       <c r="C25" s="92"/>
       <c r="D25" s="92"/>
       <c r="E25" s="92"/>
       <c r="F25" s="92" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G25" s="92"/>
       <c r="H25" s="92"/>
@@ -4316,7 +4187,7 @@
       <c r="J25" s="92"/>
       <c r="K25" s="93"/>
       <c r="L25" s="102" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M25" s="103"/>
       <c r="N25" s="82"/>
@@ -4428,7 +4299,7 @@
       <c r="D26" s="92"/>
       <c r="E26" s="92"/>
       <c r="F26" s="92" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G26" s="92"/>
       <c r="H26" s="92"/>
@@ -4436,7 +4307,7 @@
       <c r="J26" s="92"/>
       <c r="K26" s="93"/>
       <c r="L26" s="102" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M26" s="103"/>
       <c r="N26" s="82"/>
@@ -4444,7 +4315,7 @@
       <c r="P26" s="83"/>
       <c r="Q26" s="84"/>
       <c r="R26" s="84">
-        <f t="shared" ref="R26:R30" si="12">P26-Q26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S26" s="85"/>
@@ -4452,7 +4323,7 @@
       <c r="U26" s="83"/>
       <c r="V26" s="84"/>
       <c r="W26" s="86">
-        <f t="shared" ref="W26:W30" si="13">U26-V26</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X26" s="87"/>
@@ -4460,7 +4331,7 @@
       <c r="Z26" s="83"/>
       <c r="AA26" s="84"/>
       <c r="AB26" s="86">
-        <f t="shared" ref="AB26:AB30" si="14">Z26-AA26</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC26" s="87"/>
@@ -4468,7 +4339,7 @@
       <c r="AE26" s="83"/>
       <c r="AF26" s="84"/>
       <c r="AG26" s="86">
-        <f t="shared" ref="AG26:AG30" si="15">AE26-AF26</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH26" s="87"/>
@@ -4476,7 +4347,7 @@
       <c r="AJ26" s="83"/>
       <c r="AK26" s="84"/>
       <c r="AL26" s="86">
-        <f t="shared" ref="AL26:AL30" si="16">AJ26-AK26</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AM26" s="87"/>
@@ -4484,7 +4355,7 @@
       <c r="AO26" s="83"/>
       <c r="AP26" s="84"/>
       <c r="AQ26" s="86">
-        <f t="shared" ref="AQ26:AQ30" si="17">AO26-AP26</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AR26" s="87"/>
@@ -4492,7 +4363,7 @@
       <c r="AT26" s="83"/>
       <c r="AU26" s="84"/>
       <c r="AV26" s="86">
-        <f t="shared" ref="AV26:AV30" si="18">AT26-AU26</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW26" s="87"/>
@@ -4500,7 +4371,7 @@
       <c r="AY26" s="83"/>
       <c r="AZ26" s="84"/>
       <c r="BA26" s="86">
-        <f t="shared" ref="BA26:BA30" si="19">AY26-AZ26</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BB26" s="87"/>
@@ -4508,7 +4379,7 @@
       <c r="BD26" s="83"/>
       <c r="BE26" s="84"/>
       <c r="BF26" s="86">
-        <f t="shared" ref="BF26:BF30" si="20">BD26-BE26</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BG26" s="87"/>
@@ -4516,7 +4387,7 @@
       <c r="BI26" s="83"/>
       <c r="BJ26" s="84"/>
       <c r="BK26" s="86">
-        <f t="shared" ref="BK26:BK30" si="21">BI26-BJ26</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BL26" s="87"/>
@@ -4524,7 +4395,7 @@
       <c r="BN26" s="83"/>
       <c r="BO26" s="84"/>
       <c r="BP26" s="86">
-        <f t="shared" ref="BP26:BP30" si="22">BN26-BO26</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BQ26" s="87"/>
@@ -4532,7 +4403,7 @@
       <c r="BS26" s="83"/>
       <c r="BT26" s="84"/>
       <c r="BU26" s="86">
-        <f t="shared" ref="BU26:BU30" si="23">BS26-BT26</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BV26" s="85">
@@ -4541,14 +4412,14 @@
       <c r="BW26" s="89"/>
       <c r="BX26" s="90"/>
     </row>
-    <row r="27" spans="1:139" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:139" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="91"/>
       <c r="B27" s="83"/>
       <c r="C27" s="92"/>
       <c r="D27" s="92"/>
       <c r="E27" s="92"/>
       <c r="F27" s="92" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G27" s="92"/>
       <c r="H27" s="92"/>
@@ -4556,7 +4427,7 @@
       <c r="J27" s="92"/>
       <c r="K27" s="93"/>
       <c r="L27" s="102" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M27" s="103"/>
       <c r="N27" s="82"/>
@@ -4564,7 +4435,7 @@
       <c r="P27" s="83"/>
       <c r="Q27" s="84"/>
       <c r="R27" s="84">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="R27:R31" si="12">P27-Q27</f>
         <v>0</v>
       </c>
       <c r="S27" s="85"/>
@@ -4572,7 +4443,7 @@
       <c r="U27" s="83"/>
       <c r="V27" s="84"/>
       <c r="W27" s="86">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="W27:W31" si="13">U27-V27</f>
         <v>0</v>
       </c>
       <c r="X27" s="87"/>
@@ -4580,7 +4451,7 @@
       <c r="Z27" s="83"/>
       <c r="AA27" s="84"/>
       <c r="AB27" s="86">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="AB27:AB31" si="14">Z27-AA27</f>
         <v>0</v>
       </c>
       <c r="AC27" s="87"/>
@@ -4588,7 +4459,7 @@
       <c r="AE27" s="83"/>
       <c r="AF27" s="84"/>
       <c r="AG27" s="86">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="AG27:AG31" si="15">AE27-AF27</f>
         <v>0</v>
       </c>
       <c r="AH27" s="87"/>
@@ -4596,7 +4467,7 @@
       <c r="AJ27" s="83"/>
       <c r="AK27" s="84"/>
       <c r="AL27" s="86">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="AL27:AL31" si="16">AJ27-AK27</f>
         <v>0</v>
       </c>
       <c r="AM27" s="87"/>
@@ -4604,7 +4475,7 @@
       <c r="AO27" s="83"/>
       <c r="AP27" s="84"/>
       <c r="AQ27" s="86">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="AQ27:AQ31" si="17">AO27-AP27</f>
         <v>0</v>
       </c>
       <c r="AR27" s="87"/>
@@ -4612,7 +4483,7 @@
       <c r="AT27" s="83"/>
       <c r="AU27" s="84"/>
       <c r="AV27" s="86">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="AV27:AV31" si="18">AT27-AU27</f>
         <v>0</v>
       </c>
       <c r="AW27" s="87"/>
@@ -4620,7 +4491,7 @@
       <c r="AY27" s="83"/>
       <c r="AZ27" s="84"/>
       <c r="BA27" s="86">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="BA27:BA31" si="19">AY27-AZ27</f>
         <v>0</v>
       </c>
       <c r="BB27" s="87"/>
@@ -4628,7 +4499,7 @@
       <c r="BD27" s="83"/>
       <c r="BE27" s="84"/>
       <c r="BF27" s="86">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="BF27:BF31" si="20">BD27-BE27</f>
         <v>0</v>
       </c>
       <c r="BG27" s="87"/>
@@ -4636,7 +4507,7 @@
       <c r="BI27" s="83"/>
       <c r="BJ27" s="84"/>
       <c r="BK27" s="86">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="BK27:BK31" si="21">BI27-BJ27</f>
         <v>0</v>
       </c>
       <c r="BL27" s="87"/>
@@ -4644,7 +4515,7 @@
       <c r="BN27" s="83"/>
       <c r="BO27" s="84"/>
       <c r="BP27" s="86">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="BP27:BP31" si="22">BN27-BO27</f>
         <v>0</v>
       </c>
       <c r="BQ27" s="87"/>
@@ -4652,7 +4523,7 @@
       <c r="BS27" s="83"/>
       <c r="BT27" s="84"/>
       <c r="BU27" s="86">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="BU27:BU31" si="23">BS27-BT27</f>
         <v>0</v>
       </c>
       <c r="BV27" s="85">
@@ -4661,14 +4532,14 @@
       <c r="BW27" s="89"/>
       <c r="BX27" s="90"/>
     </row>
-    <row r="28" spans="1:139" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:139" x14ac:dyDescent="0.25">
       <c r="A28" s="91"/>
       <c r="B28" s="83"/>
       <c r="C28" s="92"/>
       <c r="D28" s="92"/>
       <c r="E28" s="92"/>
       <c r="F28" s="92" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G28" s="92"/>
       <c r="H28" s="92"/>
@@ -4676,7 +4547,7 @@
       <c r="J28" s="92"/>
       <c r="K28" s="93"/>
       <c r="L28" s="102" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M28" s="103"/>
       <c r="N28" s="82"/>
@@ -4781,14 +4652,14 @@
       <c r="BW28" s="89"/>
       <c r="BX28" s="90"/>
     </row>
-    <row r="29" spans="1:139" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:139" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="91"/>
       <c r="B29" s="83"/>
       <c r="C29" s="92"/>
       <c r="D29" s="92"/>
       <c r="E29" s="92"/>
       <c r="F29" s="92" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G29" s="92"/>
       <c r="H29" s="92"/>
@@ -4796,7 +4667,7 @@
       <c r="J29" s="92"/>
       <c r="K29" s="93"/>
       <c r="L29" s="102" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M29" s="103"/>
       <c r="N29" s="82"/>
@@ -4908,7 +4779,7 @@
       <c r="D30" s="92"/>
       <c r="E30" s="92"/>
       <c r="F30" s="92" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G30" s="92"/>
       <c r="H30" s="92"/>
@@ -5021,14 +4892,14 @@
       <c r="BW30" s="89"/>
       <c r="BX30" s="90"/>
     </row>
-    <row r="31" spans="1:139" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:139" x14ac:dyDescent="0.25">
       <c r="A31" s="91"/>
       <c r="B31" s="83"/>
       <c r="C31" s="92"/>
       <c r="D31" s="92"/>
       <c r="E31" s="92"/>
       <c r="F31" s="92" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G31" s="92"/>
       <c r="H31" s="92"/>
@@ -5036,7 +4907,7 @@
       <c r="J31" s="92"/>
       <c r="K31" s="93"/>
       <c r="L31" s="102" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M31" s="103"/>
       <c r="N31" s="82"/>
@@ -5044,7 +4915,7 @@
       <c r="P31" s="83"/>
       <c r="Q31" s="84"/>
       <c r="R31" s="84">
-        <f t="shared" ref="R31:R65" si="24">P31-Q31</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S31" s="85"/>
@@ -5052,7 +4923,7 @@
       <c r="U31" s="83"/>
       <c r="V31" s="84"/>
       <c r="W31" s="86">
-        <f t="shared" ref="W31:W65" si="25">U31-V31</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="X31" s="87"/>
@@ -5060,7 +4931,7 @@
       <c r="Z31" s="83"/>
       <c r="AA31" s="84"/>
       <c r="AB31" s="86">
-        <f t="shared" ref="AB31:AB65" si="26">Z31-AA31</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC31" s="87"/>
@@ -5068,7 +4939,7 @@
       <c r="AE31" s="83"/>
       <c r="AF31" s="84"/>
       <c r="AG31" s="86">
-        <f t="shared" ref="AG31:AG65" si="27">AE31-AF31</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH31" s="87"/>
@@ -5076,7 +4947,7 @@
       <c r="AJ31" s="83"/>
       <c r="AK31" s="84"/>
       <c r="AL31" s="86">
-        <f t="shared" ref="AL31:AL65" si="28">AJ31-AK31</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AM31" s="87"/>
@@ -5084,7 +4955,7 @@
       <c r="AO31" s="83"/>
       <c r="AP31" s="84"/>
       <c r="AQ31" s="86">
-        <f t="shared" ref="AQ31:AQ65" si="29">AO31-AP31</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AR31" s="87"/>
@@ -5092,7 +4963,7 @@
       <c r="AT31" s="83"/>
       <c r="AU31" s="84"/>
       <c r="AV31" s="86">
-        <f t="shared" ref="AV31:AV65" si="30">AT31-AU31</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AW31" s="87"/>
@@ -5100,7 +4971,7 @@
       <c r="AY31" s="83"/>
       <c r="AZ31" s="84"/>
       <c r="BA31" s="86">
-        <f t="shared" ref="BA31:BA65" si="31">AY31-AZ31</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB31" s="87"/>
@@ -5108,7 +4979,7 @@
       <c r="BD31" s="83"/>
       <c r="BE31" s="84"/>
       <c r="BF31" s="86">
-        <f t="shared" ref="BF31:BF65" si="32">BD31-BE31</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BG31" s="87"/>
@@ -5116,7 +4987,7 @@
       <c r="BI31" s="83"/>
       <c r="BJ31" s="84"/>
       <c r="BK31" s="86">
-        <f t="shared" ref="BK31:BK65" si="33">BI31-BJ31</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BL31" s="87"/>
@@ -5124,7 +4995,7 @@
       <c r="BN31" s="83"/>
       <c r="BO31" s="84"/>
       <c r="BP31" s="86">
-        <f t="shared" ref="BP31:BP65" si="34">BN31-BO31</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BQ31" s="87"/>
@@ -5132,7 +5003,7 @@
       <c r="BS31" s="83"/>
       <c r="BT31" s="84"/>
       <c r="BU31" s="86">
-        <f t="shared" ref="BU31:BU65" si="35">BS31-BT31</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BV31" s="85">
@@ -5148,7 +5019,7 @@
       <c r="D32" s="92"/>
       <c r="E32" s="92"/>
       <c r="F32" s="92" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G32" s="92"/>
       <c r="H32" s="92"/>
@@ -5156,7 +5027,7 @@
       <c r="J32" s="92"/>
       <c r="K32" s="93"/>
       <c r="L32" s="102" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M32" s="103"/>
       <c r="N32" s="82"/>
@@ -5164,7 +5035,7 @@
       <c r="P32" s="83"/>
       <c r="Q32" s="84"/>
       <c r="R32" s="84">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="R32:R66" si="24">P32-Q32</f>
         <v>0</v>
       </c>
       <c r="S32" s="85"/>
@@ -5172,7 +5043,7 @@
       <c r="U32" s="83"/>
       <c r="V32" s="84"/>
       <c r="W32" s="86">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="W32:W66" si="25">U32-V32</f>
         <v>0</v>
       </c>
       <c r="X32" s="87"/>
@@ -5180,7 +5051,7 @@
       <c r="Z32" s="83"/>
       <c r="AA32" s="84"/>
       <c r="AB32" s="86">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="AB32:AB66" si="26">Z32-AA32</f>
         <v>0</v>
       </c>
       <c r="AC32" s="87"/>
@@ -5188,7 +5059,7 @@
       <c r="AE32" s="83"/>
       <c r="AF32" s="84"/>
       <c r="AG32" s="86">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="AG32:AG66" si="27">AE32-AF32</f>
         <v>0</v>
       </c>
       <c r="AH32" s="87"/>
@@ -5196,7 +5067,7 @@
       <c r="AJ32" s="83"/>
       <c r="AK32" s="84"/>
       <c r="AL32" s="86">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="AL32:AL66" si="28">AJ32-AK32</f>
         <v>0</v>
       </c>
       <c r="AM32" s="87"/>
@@ -5204,7 +5075,7 @@
       <c r="AO32" s="83"/>
       <c r="AP32" s="84"/>
       <c r="AQ32" s="86">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="AQ32:AQ66" si="29">AO32-AP32</f>
         <v>0</v>
       </c>
       <c r="AR32" s="87"/>
@@ -5212,7 +5083,7 @@
       <c r="AT32" s="83"/>
       <c r="AU32" s="84"/>
       <c r="AV32" s="86">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="AV32:AV66" si="30">AT32-AU32</f>
         <v>0</v>
       </c>
       <c r="AW32" s="87"/>
@@ -5220,7 +5091,7 @@
       <c r="AY32" s="83"/>
       <c r="AZ32" s="84"/>
       <c r="BA32" s="86">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="BA32:BA66" si="31">AY32-AZ32</f>
         <v>0</v>
       </c>
       <c r="BB32" s="87"/>
@@ -5228,7 +5099,7 @@
       <c r="BD32" s="83"/>
       <c r="BE32" s="84"/>
       <c r="BF32" s="86">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="BF32:BF66" si="32">BD32-BE32</f>
         <v>0</v>
       </c>
       <c r="BG32" s="87"/>
@@ -5236,7 +5107,7 @@
       <c r="BI32" s="83"/>
       <c r="BJ32" s="84"/>
       <c r="BK32" s="86">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="BK32:BK66" si="33">BI32-BJ32</f>
         <v>0</v>
       </c>
       <c r="BL32" s="87"/>
@@ -5244,7 +5115,7 @@
       <c r="BN32" s="83"/>
       <c r="BO32" s="84"/>
       <c r="BP32" s="86">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="BP32:BP66" si="34">BN32-BO32</f>
         <v>0</v>
       </c>
       <c r="BQ32" s="87"/>
@@ -5252,7 +5123,7 @@
       <c r="BS32" s="83"/>
       <c r="BT32" s="84"/>
       <c r="BU32" s="86">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="BU32:BU66" si="35">BS32-BT32</f>
         <v>0</v>
       </c>
       <c r="BV32" s="85">
@@ -5261,14 +5132,14 @@
       <c r="BW32" s="89"/>
       <c r="BX32" s="90"/>
     </row>
-    <row r="33" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="91"/>
       <c r="B33" s="83"/>
       <c r="C33" s="92"/>
       <c r="D33" s="92"/>
       <c r="E33" s="92"/>
       <c r="F33" s="92" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G33" s="92"/>
       <c r="H33" s="92"/>
@@ -5276,7 +5147,7 @@
       <c r="J33" s="92"/>
       <c r="K33" s="93"/>
       <c r="L33" s="102" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M33" s="103"/>
       <c r="N33" s="82"/>
@@ -5381,14 +5252,14 @@
       <c r="BW33" s="89"/>
       <c r="BX33" s="90"/>
     </row>
-    <row r="34" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:76" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="91"/>
       <c r="B34" s="83"/>
       <c r="C34" s="92"/>
       <c r="D34" s="92"/>
       <c r="E34" s="92"/>
       <c r="F34" s="92" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G34" s="92"/>
       <c r="H34" s="92"/>
@@ -5396,7 +5267,7 @@
       <c r="J34" s="92"/>
       <c r="K34" s="93"/>
       <c r="L34" s="102" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M34" s="103"/>
       <c r="N34" s="82"/>
@@ -5501,14 +5372,14 @@
       <c r="BW34" s="89"/>
       <c r="BX34" s="90"/>
     </row>
-    <row r="35" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A35" s="91"/>
       <c r="B35" s="83"/>
       <c r="C35" s="92"/>
       <c r="D35" s="92"/>
       <c r="E35" s="92"/>
       <c r="F35" s="92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G35" s="92"/>
       <c r="H35" s="92"/>
@@ -5516,7 +5387,7 @@
       <c r="J35" s="92"/>
       <c r="K35" s="93"/>
       <c r="L35" s="102" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M35" s="103"/>
       <c r="N35" s="82"/>
@@ -5621,14 +5492,14 @@
       <c r="BW35" s="89"/>
       <c r="BX35" s="90"/>
     </row>
-    <row r="36" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="91"/>
       <c r="B36" s="83"/>
       <c r="C36" s="92"/>
       <c r="D36" s="92"/>
       <c r="E36" s="92"/>
       <c r="F36" s="92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G36" s="92"/>
       <c r="H36" s="92"/>
@@ -5636,7 +5507,7 @@
       <c r="J36" s="92"/>
       <c r="K36" s="93"/>
       <c r="L36" s="102" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M36" s="103"/>
       <c r="N36" s="82"/>
@@ -5748,7 +5619,7 @@
       <c r="D37" s="92"/>
       <c r="E37" s="92"/>
       <c r="F37" s="92" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G37" s="92"/>
       <c r="H37" s="92"/>
@@ -5756,7 +5627,7 @@
       <c r="J37" s="92"/>
       <c r="K37" s="93"/>
       <c r="L37" s="102" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M37" s="103"/>
       <c r="N37" s="82"/>
@@ -5868,7 +5739,7 @@
       <c r="D38" s="92"/>
       <c r="E38" s="92"/>
       <c r="F38" s="92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G38" s="92"/>
       <c r="H38" s="92"/>
@@ -5876,7 +5747,7 @@
       <c r="J38" s="92"/>
       <c r="K38" s="93"/>
       <c r="L38" s="102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M38" s="103"/>
       <c r="N38" s="82"/>
@@ -5988,7 +5859,7 @@
       <c r="D39" s="92"/>
       <c r="E39" s="92"/>
       <c r="F39" s="92" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="G39" s="92"/>
       <c r="H39" s="92"/>
@@ -5996,7 +5867,7 @@
       <c r="J39" s="92"/>
       <c r="K39" s="93"/>
       <c r="L39" s="102" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M39" s="103"/>
       <c r="N39" s="82"/>
@@ -6101,14 +5972,14 @@
       <c r="BW39" s="89"/>
       <c r="BX39" s="90"/>
     </row>
-    <row r="40" spans="1:76" ht="60" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A40" s="91"/>
       <c r="B40" s="83"/>
       <c r="C40" s="92"/>
       <c r="D40" s="92"/>
       <c r="E40" s="92"/>
       <c r="F40" s="92" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="G40" s="92"/>
       <c r="H40" s="92"/>
@@ -6116,7 +5987,7 @@
       <c r="J40" s="92"/>
       <c r="K40" s="93"/>
       <c r="L40" s="102" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M40" s="103"/>
       <c r="N40" s="82"/>
@@ -6221,14 +6092,14 @@
       <c r="BW40" s="89"/>
       <c r="BX40" s="90"/>
     </row>
-    <row r="41" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:76" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="91"/>
       <c r="B41" s="83"/>
       <c r="C41" s="92"/>
       <c r="D41" s="92"/>
       <c r="E41" s="92"/>
       <c r="F41" s="92" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G41" s="92"/>
       <c r="H41" s="92"/>
@@ -6236,7 +6107,7 @@
       <c r="J41" s="92"/>
       <c r="K41" s="93"/>
       <c r="L41" s="102" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M41" s="103"/>
       <c r="N41" s="82"/>
@@ -6341,14 +6212,14 @@
       <c r="BW41" s="89"/>
       <c r="BX41" s="90"/>
     </row>
-    <row r="42" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="91"/>
       <c r="B42" s="83"/>
       <c r="C42" s="92"/>
       <c r="D42" s="92"/>
       <c r="E42" s="92"/>
       <c r="F42" s="92" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G42" s="92"/>
       <c r="H42" s="92"/>
@@ -6356,7 +6227,7 @@
       <c r="J42" s="92"/>
       <c r="K42" s="93"/>
       <c r="L42" s="102" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M42" s="103"/>
       <c r="N42" s="82"/>
@@ -6461,16 +6332,14 @@
       <c r="BW42" s="89"/>
       <c r="BX42" s="90"/>
     </row>
-    <row r="43" spans="1:76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="91" t="s">
-        <v>132</v>
-      </c>
+    <row r="43" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="91"/>
       <c r="B43" s="83"/>
       <c r="C43" s="92"/>
       <c r="D43" s="92"/>
       <c r="E43" s="92"/>
       <c r="F43" s="92" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G43" s="92"/>
       <c r="H43" s="92"/>
@@ -6478,7 +6347,7 @@
       <c r="J43" s="92"/>
       <c r="K43" s="93"/>
       <c r="L43" s="102" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M43" s="103"/>
       <c r="N43" s="82"/>
@@ -6585,14 +6454,14 @@
     </row>
     <row r="44" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="91" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B44" s="83"/>
       <c r="C44" s="92"/>
       <c r="D44" s="92"/>
       <c r="E44" s="92"/>
       <c r="F44" s="92" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G44" s="92"/>
       <c r="H44" s="92"/>
@@ -6600,7 +6469,7 @@
       <c r="J44" s="92"/>
       <c r="K44" s="93"/>
       <c r="L44" s="102" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M44" s="103"/>
       <c r="N44" s="82"/>
@@ -6705,14 +6574,16 @@
       <c r="BW44" s="89"/>
       <c r="BX44" s="90"/>
     </row>
-    <row r="45" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A45" s="91"/>
+    <row r="45" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="91" t="s">
+        <v>134</v>
+      </c>
       <c r="B45" s="83"/>
       <c r="C45" s="92"/>
       <c r="D45" s="92"/>
       <c r="E45" s="92"/>
       <c r="F45" s="92" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G45" s="92"/>
       <c r="H45" s="92"/>
@@ -6720,7 +6591,7 @@
       <c r="J45" s="92"/>
       <c r="K45" s="93"/>
       <c r="L45" s="102" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M45" s="103"/>
       <c r="N45" s="82"/>
@@ -6832,7 +6703,7 @@
       <c r="D46" s="92"/>
       <c r="E46" s="92"/>
       <c r="F46" s="92" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G46" s="92"/>
       <c r="H46" s="92"/>
@@ -6840,7 +6711,7 @@
       <c r="J46" s="92"/>
       <c r="K46" s="93"/>
       <c r="L46" s="102" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M46" s="103"/>
       <c r="N46" s="82"/>
@@ -6945,46 +6816,24 @@
       <c r="BW46" s="89"/>
       <c r="BX46" s="90"/>
     </row>
-    <row r="47" spans="1:76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="91" t="s">
-        <v>138</v>
-      </c>
-      <c r="B47" s="83">
-        <v>9501137831</v>
-      </c>
-      <c r="C47" s="98">
-        <v>45992</v>
-      </c>
-      <c r="D47" s="98">
-        <v>46356</v>
-      </c>
-      <c r="E47" s="92" t="s">
-        <v>139</v>
-      </c>
+    <row r="47" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A47" s="91"/>
+      <c r="B47" s="83"/>
+      <c r="C47" s="92"/>
+      <c r="D47" s="92"/>
+      <c r="E47" s="92"/>
       <c r="F47" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="G47" s="92">
-        <v>41010100</v>
-      </c>
-      <c r="H47" s="92">
-        <v>7280</v>
-      </c>
-      <c r="I47" s="92" t="s">
-        <v>141</v>
-      </c>
-      <c r="J47" s="92">
-        <v>2662855</v>
-      </c>
-      <c r="K47" s="99">
-        <v>38005</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="G47" s="92"/>
+      <c r="H47" s="92"/>
+      <c r="I47" s="92"/>
+      <c r="J47" s="92"/>
+      <c r="K47" s="93"/>
       <c r="L47" s="102" t="s">
-        <v>195</v>
-      </c>
-      <c r="M47" s="103" t="s">
-        <v>166</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="M47" s="103"/>
       <c r="N47" s="82"/>
       <c r="O47" s="83"/>
       <c r="P47" s="83"/>
@@ -7087,12 +6936,12 @@
       <c r="BW47" s="89"/>
       <c r="BX47" s="90"/>
     </row>
-    <row r="48" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="91" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="B48" s="83">
-        <v>9501137269</v>
+        <v>9501137831</v>
       </c>
       <c r="C48" s="98">
         <v>45992</v>
@@ -7101,10 +6950,10 @@
         <v>46356</v>
       </c>
       <c r="E48" s="92" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F48" s="92" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G48" s="92">
         <v>41010100</v>
@@ -7119,10 +6968,10 @@
         <v>2662855</v>
       </c>
       <c r="K48" s="99">
-        <v>9980</v>
+        <v>38005</v>
       </c>
       <c r="L48" s="102" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M48" s="103" t="s">
         <v>166</v>
@@ -7229,26 +7078,46 @@
       <c r="BW48" s="89"/>
       <c r="BX48" s="90"/>
     </row>
-    <row r="49" spans="1:76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="91"/>
-      <c r="B49" s="83"/>
-      <c r="C49" s="92"/>
-      <c r="D49" s="92"/>
-      <c r="E49" s="92"/>
+    <row r="49" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="83">
+        <v>9501137269</v>
+      </c>
+      <c r="C49" s="98">
+        <v>45992</v>
+      </c>
+      <c r="D49" s="98">
+        <v>46356</v>
+      </c>
+      <c r="E49" s="92" t="s">
+        <v>142</v>
+      </c>
       <c r="F49" s="92" t="s">
-        <v>144</v>
-      </c>
-      <c r="G49" s="92"/>
-      <c r="H49" s="92"/>
-      <c r="I49" s="92"/>
-      <c r="J49" s="92"/>
+        <v>143</v>
+      </c>
+      <c r="G49" s="92">
+        <v>41010100</v>
+      </c>
+      <c r="H49" s="92">
+        <v>7280</v>
+      </c>
+      <c r="I49" s="92" t="s">
+        <v>141</v>
+      </c>
+      <c r="J49" s="92">
+        <v>2662855</v>
+      </c>
       <c r="K49" s="99">
-        <v>12000</v>
+        <v>9980</v>
       </c>
       <c r="L49" s="102" t="s">
-        <v>197</v>
-      </c>
-      <c r="M49" s="103"/>
+        <v>196</v>
+      </c>
+      <c r="M49" s="103" t="s">
+        <v>166</v>
+      </c>
       <c r="N49" s="82"/>
       <c r="O49" s="83"/>
       <c r="P49" s="83"/>
@@ -7351,24 +7220,24 @@
       <c r="BW49" s="89"/>
       <c r="BX49" s="90"/>
     </row>
-    <row r="50" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="91"/>
       <c r="B50" s="83"/>
       <c r="C50" s="92"/>
       <c r="D50" s="92"/>
       <c r="E50" s="92"/>
       <c r="F50" s="92" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G50" s="92"/>
       <c r="H50" s="92"/>
       <c r="I50" s="92"/>
       <c r="J50" s="92"/>
       <c r="K50" s="99">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="L50" s="102" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M50" s="103"/>
       <c r="N50" s="82"/>
@@ -7473,46 +7342,26 @@
       <c r="BW50" s="89"/>
       <c r="BX50" s="90"/>
     </row>
-    <row r="51" spans="1:76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="91" t="s">
-        <v>97</v>
-      </c>
-      <c r="B51" s="83">
-        <v>9501166164</v>
-      </c>
-      <c r="C51" s="98">
-        <v>46023</v>
-      </c>
-      <c r="D51" s="98">
-        <v>46387</v>
-      </c>
-      <c r="E51" s="92" t="s">
-        <v>146</v>
-      </c>
+    <row r="51" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="91"/>
+      <c r="B51" s="83"/>
+      <c r="C51" s="92"/>
+      <c r="D51" s="92"/>
+      <c r="E51" s="92"/>
       <c r="F51" s="92" t="s">
-        <v>147</v>
-      </c>
-      <c r="G51" s="92">
-        <v>41500000</v>
-      </c>
-      <c r="H51" s="92">
-        <v>1400</v>
-      </c>
-      <c r="I51" s="92" t="s">
-        <v>105</v>
-      </c>
-      <c r="J51" s="92">
-        <v>2321403</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="G51" s="92"/>
+      <c r="H51" s="92"/>
+      <c r="I51" s="92"/>
+      <c r="J51" s="92"/>
       <c r="K51" s="99">
-        <v>4651600</v>
+        <v>0</v>
       </c>
       <c r="L51" s="102" t="s">
-        <v>199</v>
-      </c>
-      <c r="M51" s="103" t="s">
-        <v>166</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="M51" s="103"/>
       <c r="N51" s="82"/>
       <c r="O51" s="83"/>
       <c r="P51" s="83"/>
@@ -7615,18 +7464,18 @@
       <c r="BW51" s="89"/>
       <c r="BX51" s="90"/>
     </row>
-    <row r="52" spans="1:76" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="91" t="s">
         <v>97</v>
       </c>
       <c r="B52" s="83">
-        <v>9501190667</v>
+        <v>9501166164</v>
       </c>
       <c r="C52" s="98">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="D52" s="98">
-        <v>46296</v>
+        <v>46387</v>
       </c>
       <c r="E52" s="92" t="s">
         <v>146</v>
@@ -7647,10 +7496,10 @@
         <v>2321403</v>
       </c>
       <c r="K52" s="99">
-        <v>62500</v>
+        <v>4651600</v>
       </c>
       <c r="L52" s="102" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M52" s="103" t="s">
         <v>166</v>
@@ -7759,22 +7608,22 @@
     </row>
     <row r="53" spans="1:76" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="91" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="B53" s="83">
-        <v>9501199822</v>
+        <v>9501190667</v>
       </c>
       <c r="C53" s="98">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="D53" s="98">
-        <v>46387</v>
+        <v>46296</v>
       </c>
       <c r="E53" s="92" t="s">
         <v>146</v>
       </c>
       <c r="F53" s="92" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G53" s="92">
         <v>41500000</v>
@@ -7789,10 +7638,10 @@
         <v>2321403</v>
       </c>
       <c r="K53" s="99">
-        <v>1058400</v>
+        <v>62500</v>
       </c>
       <c r="L53" s="102" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M53" s="103" t="s">
         <v>166</v>
@@ -7901,10 +7750,10 @@
     </row>
     <row r="54" spans="1:76" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="91" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B54" s="83">
-        <v>9501199827</v>
+        <v>9501199822</v>
       </c>
       <c r="C54" s="98">
         <v>46023</v>
@@ -7931,10 +7780,10 @@
         <v>2321403</v>
       </c>
       <c r="K54" s="99">
-        <v>577400</v>
+        <v>1058400</v>
       </c>
       <c r="L54" s="102" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M54" s="103" t="s">
         <v>166</v>
@@ -8041,12 +7890,12 @@
       <c r="BW54" s="89"/>
       <c r="BX54" s="90"/>
     </row>
-    <row r="55" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:76" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="91" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="B55" s="83">
-        <v>9501195328</v>
+        <v>9501199827</v>
       </c>
       <c r="C55" s="98">
         <v>46023</v>
@@ -8058,7 +7907,7 @@
         <v>146</v>
       </c>
       <c r="F55" s="92" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G55" s="92">
         <v>41500000</v>
@@ -8073,10 +7922,10 @@
         <v>2321403</v>
       </c>
       <c r="K55" s="99">
-        <v>36000</v>
+        <v>577400</v>
       </c>
       <c r="L55" s="102" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M55" s="103" t="s">
         <v>166</v>
@@ -8184,23 +8033,45 @@
       <c r="BX55" s="90"/>
     </row>
     <row r="56" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A56" s="91"/>
-      <c r="B56" s="83"/>
-      <c r="C56" s="92"/>
-      <c r="D56" s="92"/>
-      <c r="E56" s="92"/>
+      <c r="A56" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="83">
+        <v>9501195328</v>
+      </c>
+      <c r="C56" s="98">
+        <v>46023</v>
+      </c>
+      <c r="D56" s="98">
+        <v>46387</v>
+      </c>
+      <c r="E56" s="92" t="s">
+        <v>146</v>
+      </c>
       <c r="F56" s="92" t="s">
-        <v>152</v>
-      </c>
-      <c r="G56" s="92"/>
-      <c r="H56" s="92"/>
-      <c r="I56" s="92"/>
-      <c r="J56" s="92"/>
-      <c r="K56" s="93"/>
+        <v>151</v>
+      </c>
+      <c r="G56" s="92">
+        <v>41500000</v>
+      </c>
+      <c r="H56" s="92">
+        <v>1400</v>
+      </c>
+      <c r="I56" s="92" t="s">
+        <v>105</v>
+      </c>
+      <c r="J56" s="92">
+        <v>2321403</v>
+      </c>
+      <c r="K56" s="99">
+        <v>36000</v>
+      </c>
       <c r="L56" s="102" t="s">
-        <v>204</v>
-      </c>
-      <c r="M56" s="103"/>
+        <v>203</v>
+      </c>
+      <c r="M56" s="103" t="s">
+        <v>166</v>
+      </c>
       <c r="N56" s="82"/>
       <c r="O56" s="83"/>
       <c r="P56" s="83"/>
@@ -8310,7 +8181,7 @@
       <c r="D57" s="92"/>
       <c r="E57" s="92"/>
       <c r="F57" s="92" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G57" s="92"/>
       <c r="H57" s="92"/>
@@ -8318,7 +8189,7 @@
       <c r="J57" s="92"/>
       <c r="K57" s="93"/>
       <c r="L57" s="102" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M57" s="103"/>
       <c r="N57" s="82"/>
@@ -8424,45 +8295,23 @@
       <c r="BX57" s="90"/>
     </row>
     <row r="58" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A58" s="91" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="83">
-        <v>9501212179</v>
-      </c>
-      <c r="C58" s="98">
-        <v>46023</v>
-      </c>
-      <c r="D58" s="92" t="s">
-        <v>154</v>
-      </c>
-      <c r="E58" s="92" t="s">
-        <v>146</v>
-      </c>
+      <c r="A58" s="91"/>
+      <c r="B58" s="83"/>
+      <c r="C58" s="92"/>
+      <c r="D58" s="92"/>
+      <c r="E58" s="92"/>
       <c r="F58" s="92" t="s">
-        <v>155</v>
-      </c>
-      <c r="G58" s="92">
-        <v>41500000</v>
-      </c>
-      <c r="H58" s="92">
-        <v>1400</v>
-      </c>
-      <c r="I58" s="92" t="s">
-        <v>105</v>
-      </c>
-      <c r="J58" s="92">
-        <v>2321403</v>
-      </c>
-      <c r="K58" s="99">
-        <v>334732.5</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="G58" s="92"/>
+      <c r="H58" s="92"/>
+      <c r="I58" s="92"/>
+      <c r="J58" s="92"/>
+      <c r="K58" s="93"/>
       <c r="L58" s="102" t="s">
-        <v>206</v>
-      </c>
-      <c r="M58" s="103" t="s">
-        <v>166</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="M58" s="103"/>
       <c r="N58" s="82"/>
       <c r="O58" s="83"/>
       <c r="P58" s="83"/>
@@ -8565,24 +8414,24 @@
       <c r="BW58" s="89"/>
       <c r="BX58" s="90"/>
     </row>
-    <row r="59" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A59" s="91" t="s">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="B59" s="83">
-        <v>9501196824</v>
+        <v>9501212179</v>
       </c>
       <c r="C59" s="98">
         <v>46023</v>
       </c>
-      <c r="D59" s="98">
-        <v>46387</v>
+      <c r="D59" s="92" t="s">
+        <v>154</v>
       </c>
       <c r="E59" s="92" t="s">
         <v>146</v>
       </c>
       <c r="F59" s="92" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G59" s="92">
         <v>41500000</v>
@@ -8597,10 +8446,10 @@
         <v>2321403</v>
       </c>
       <c r="K59" s="99">
-        <v>433000</v>
+        <v>334732.5</v>
       </c>
       <c r="L59" s="102" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M59" s="103" t="s">
         <v>166</v>
@@ -8709,10 +8558,10 @@
     </row>
     <row r="60" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="91" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="B60" s="83">
-        <v>9501196865</v>
+        <v>9501196824</v>
       </c>
       <c r="C60" s="98">
         <v>46023</v>
@@ -8724,7 +8573,7 @@
         <v>146</v>
       </c>
       <c r="F60" s="92" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G60" s="92">
         <v>41500000</v>
@@ -8739,10 +8588,10 @@
         <v>2321403</v>
       </c>
       <c r="K60" s="99">
-        <v>335904</v>
+        <v>433000</v>
       </c>
       <c r="L60" s="102" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M60" s="103" t="s">
         <v>166</v>
@@ -8851,10 +8700,10 @@
     </row>
     <row r="61" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="91" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="B61" s="83">
-        <v>9501158806</v>
+        <v>9501196865</v>
       </c>
       <c r="C61" s="98">
         <v>46023</v>
@@ -8866,7 +8715,7 @@
         <v>146</v>
       </c>
       <c r="F61" s="92" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G61" s="92">
         <v>41500000</v>
@@ -8881,10 +8730,10 @@
         <v>2321403</v>
       </c>
       <c r="K61" s="99">
-        <v>376200</v>
+        <v>335904</v>
       </c>
       <c r="L61" s="102" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M61" s="103" t="s">
         <v>166</v>
@@ -8993,10 +8842,10 @@
     </row>
     <row r="62" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="91" t="s">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="B62" s="83">
-        <v>9501159633</v>
+        <v>9501158806</v>
       </c>
       <c r="C62" s="98">
         <v>46023</v>
@@ -9005,13 +8854,13 @@
         <v>46387</v>
       </c>
       <c r="E62" s="92" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F62" s="92" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G62" s="92">
-        <v>61010000</v>
+        <v>41500000</v>
       </c>
       <c r="H62" s="92">
         <v>1400</v>
@@ -9023,10 +8872,10 @@
         <v>2321403</v>
       </c>
       <c r="K62" s="99">
-        <v>146493</v>
+        <v>376200</v>
       </c>
       <c r="L62" s="102" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M62" s="103" t="s">
         <v>166</v>
@@ -9135,40 +8984,40 @@
     </row>
     <row r="63" spans="1:76" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="91" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B63" s="83">
-        <v>9501199250</v>
+        <v>9501159633</v>
       </c>
       <c r="C63" s="98">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="D63" s="98">
-        <v>46418</v>
+        <v>46387</v>
       </c>
       <c r="E63" s="92" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="F63" s="92" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G63" s="92">
-        <v>41010100</v>
+        <v>61010000</v>
       </c>
       <c r="H63" s="92">
-        <v>7280</v>
+        <v>1400</v>
       </c>
       <c r="I63" s="92" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="J63" s="92">
-        <v>2662855</v>
+        <v>2321403</v>
       </c>
       <c r="K63" s="99">
-        <v>69429</v>
+        <v>146493</v>
       </c>
       <c r="L63" s="102" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M63" s="103" t="s">
         <v>166</v>
@@ -9275,20 +9124,46 @@
       <c r="BW63" s="89"/>
       <c r="BX63" s="90"/>
     </row>
-    <row r="64" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A64" s="91"/>
-      <c r="B64" s="83"/>
-      <c r="C64" s="92"/>
-      <c r="D64" s="92"/>
-      <c r="E64" s="92"/>
-      <c r="F64" s="92"/>
-      <c r="G64" s="92"/>
-      <c r="H64" s="92"/>
-      <c r="I64" s="92"/>
-      <c r="J64" s="92"/>
-      <c r="K64" s="93"/>
-      <c r="L64" s="92"/>
-      <c r="M64" s="90"/>
+    <row r="64" spans="1:76" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="91" t="s">
+        <v>163</v>
+      </c>
+      <c r="B64" s="83">
+        <v>9501199250</v>
+      </c>
+      <c r="C64" s="98">
+        <v>46054</v>
+      </c>
+      <c r="D64" s="98">
+        <v>46418</v>
+      </c>
+      <c r="E64" s="92" t="s">
+        <v>139</v>
+      </c>
+      <c r="F64" s="92" t="s">
+        <v>164</v>
+      </c>
+      <c r="G64" s="92">
+        <v>41010100</v>
+      </c>
+      <c r="H64" s="92">
+        <v>7280</v>
+      </c>
+      <c r="I64" s="92" t="s">
+        <v>141</v>
+      </c>
+      <c r="J64" s="92">
+        <v>2662855</v>
+      </c>
+      <c r="K64" s="99">
+        <v>69429</v>
+      </c>
+      <c r="L64" s="102" t="s">
+        <v>211</v>
+      </c>
+      <c r="M64" s="103" t="s">
+        <v>166</v>
+      </c>
       <c r="N64" s="82"/>
       <c r="O64" s="83"/>
       <c r="P64" s="83"/>
@@ -9507,198 +9382,309 @@
       <c r="BW65" s="89"/>
       <c r="BX65" s="90"/>
     </row>
-    <row r="66" spans="1:139" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="66" t="s">
+    <row r="66" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A66" s="91"/>
+      <c r="B66" s="83"/>
+      <c r="C66" s="92"/>
+      <c r="D66" s="92"/>
+      <c r="E66" s="92"/>
+      <c r="F66" s="92"/>
+      <c r="G66" s="92"/>
+      <c r="H66" s="92"/>
+      <c r="I66" s="92"/>
+      <c r="J66" s="92"/>
+      <c r="K66" s="93"/>
+      <c r="L66" s="92"/>
+      <c r="M66" s="90"/>
+      <c r="N66" s="82"/>
+      <c r="O66" s="83"/>
+      <c r="P66" s="83"/>
+      <c r="Q66" s="84"/>
+      <c r="R66" s="84">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S66" s="85"/>
+      <c r="T66" s="83"/>
+      <c r="U66" s="83"/>
+      <c r="V66" s="84"/>
+      <c r="W66" s="86">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X66" s="87"/>
+      <c r="Y66" s="83"/>
+      <c r="Z66" s="83"/>
+      <c r="AA66" s="84"/>
+      <c r="AB66" s="86">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC66" s="87"/>
+      <c r="AD66" s="83"/>
+      <c r="AE66" s="83"/>
+      <c r="AF66" s="84"/>
+      <c r="AG66" s="86">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AH66" s="87"/>
+      <c r="AI66" s="83"/>
+      <c r="AJ66" s="83"/>
+      <c r="AK66" s="84"/>
+      <c r="AL66" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AM66" s="87"/>
+      <c r="AN66" s="83"/>
+      <c r="AO66" s="83"/>
+      <c r="AP66" s="84"/>
+      <c r="AQ66" s="86">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AR66" s="87"/>
+      <c r="AS66" s="83"/>
+      <c r="AT66" s="83"/>
+      <c r="AU66" s="84"/>
+      <c r="AV66" s="86">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AW66" s="87"/>
+      <c r="AX66" s="83"/>
+      <c r="AY66" s="83"/>
+      <c r="AZ66" s="84"/>
+      <c r="BA66" s="86">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BB66" s="87"/>
+      <c r="BC66" s="83"/>
+      <c r="BD66" s="83"/>
+      <c r="BE66" s="84"/>
+      <c r="BF66" s="86">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BG66" s="87"/>
+      <c r="BH66" s="83"/>
+      <c r="BI66" s="83"/>
+      <c r="BJ66" s="84"/>
+      <c r="BK66" s="86">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BL66" s="87"/>
+      <c r="BM66" s="83"/>
+      <c r="BN66" s="83"/>
+      <c r="BO66" s="84"/>
+      <c r="BP66" s="86">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BQ66" s="87"/>
+      <c r="BR66" s="83"/>
+      <c r="BS66" s="83"/>
+      <c r="BT66" s="84"/>
+      <c r="BU66" s="86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BV66" s="85">
+        <v>0</v>
+      </c>
+      <c r="BW66" s="89"/>
+      <c r="BX66" s="90"/>
+    </row>
+    <row r="67" spans="1:139" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="B66" s="67"/>
-      <c r="C66" s="68"/>
-      <c r="D66" s="68"/>
-      <c r="E66" s="69"/>
-      <c r="F66" s="69"/>
-      <c r="G66" s="69"/>
-      <c r="H66" s="69"/>
-      <c r="I66" s="69"/>
-      <c r="J66" s="69"/>
-      <c r="K66" s="70"/>
-      <c r="L66" s="69"/>
-      <c r="M66" s="71"/>
-      <c r="N66" s="72"/>
-      <c r="O66" s="73"/>
-      <c r="P66" s="73"/>
-      <c r="Q66" s="74"/>
-      <c r="R66" s="74" t="str">
-        <f>IF(OR(P66="",Q66=""),"",P66-Q66)</f>
+      <c r="B67" s="67"/>
+      <c r="C67" s="68"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="69"/>
+      <c r="F67" s="69"/>
+      <c r="G67" s="69"/>
+      <c r="H67" s="69"/>
+      <c r="I67" s="69"/>
+      <c r="J67" s="69"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="69"/>
+      <c r="M67" s="71"/>
+      <c r="N67" s="72"/>
+      <c r="O67" s="73"/>
+      <c r="P67" s="73"/>
+      <c r="Q67" s="74"/>
+      <c r="R67" s="74" t="str">
+        <f>IF(OR(P67="",Q67=""),"",P67-Q67)</f>
         <v/>
       </c>
-      <c r="S66" s="75"/>
-      <c r="T66" s="73"/>
-      <c r="U66" s="73"/>
-      <c r="V66" s="74"/>
-      <c r="W66" s="76"/>
-      <c r="X66" s="77"/>
-      <c r="Y66" s="73"/>
-      <c r="Z66" s="73"/>
-      <c r="AA66" s="74"/>
-      <c r="AB66" s="76"/>
-      <c r="AC66" s="77"/>
-      <c r="AD66" s="73"/>
-      <c r="AE66" s="73"/>
-      <c r="AF66" s="74"/>
-      <c r="AG66" s="76" t="str">
-        <f t="shared" ref="AG66" si="36">IF(OR(AE66="",AF66=""),"",AE66-AF66)</f>
+      <c r="S67" s="75"/>
+      <c r="T67" s="73"/>
+      <c r="U67" s="73"/>
+      <c r="V67" s="74"/>
+      <c r="W67" s="76"/>
+      <c r="X67" s="77"/>
+      <c r="Y67" s="73"/>
+      <c r="Z67" s="73"/>
+      <c r="AA67" s="74"/>
+      <c r="AB67" s="76"/>
+      <c r="AC67" s="77"/>
+      <c r="AD67" s="73"/>
+      <c r="AE67" s="73"/>
+      <c r="AF67" s="74"/>
+      <c r="AG67" s="76" t="str">
+        <f t="shared" ref="AG67" si="36">IF(OR(AE67="",AF67=""),"",AE67-AF67)</f>
         <v/>
       </c>
-      <c r="AH66" s="77"/>
-      <c r="AI66" s="73"/>
-      <c r="AJ66" s="73"/>
-      <c r="AK66" s="74"/>
-      <c r="AL66" s="76" t="str">
-        <f t="shared" ref="AL66" si="37">IF(OR(AJ66="",AK66=""),"",AJ66-AK66)</f>
+      <c r="AH67" s="77"/>
+      <c r="AI67" s="73"/>
+      <c r="AJ67" s="73"/>
+      <c r="AK67" s="74"/>
+      <c r="AL67" s="76" t="str">
+        <f t="shared" ref="AL67" si="37">IF(OR(AJ67="",AK67=""),"",AJ67-AK67)</f>
         <v/>
       </c>
-      <c r="AM66" s="77"/>
-      <c r="AN66" s="73"/>
-      <c r="AO66" s="73"/>
-      <c r="AP66" s="74"/>
-      <c r="AQ66" s="76" t="str">
-        <f t="shared" ref="AQ66" si="38">IF(OR(AO66="",AP66=""),"",AO66-AP66)</f>
+      <c r="AM67" s="77"/>
+      <c r="AN67" s="73"/>
+      <c r="AO67" s="73"/>
+      <c r="AP67" s="74"/>
+      <c r="AQ67" s="76" t="str">
+        <f t="shared" ref="AQ67" si="38">IF(OR(AO67="",AP67=""),"",AO67-AP67)</f>
         <v/>
       </c>
-      <c r="AR66" s="77"/>
-      <c r="AS66" s="73"/>
-      <c r="AT66" s="73"/>
-      <c r="AU66" s="74"/>
-      <c r="AV66" s="76" t="str">
-        <f t="shared" ref="AV66" si="39">IF(OR(AT66="",AU66=""),"",AT66-AU66)</f>
+      <c r="AR67" s="77"/>
+      <c r="AS67" s="73"/>
+      <c r="AT67" s="73"/>
+      <c r="AU67" s="74"/>
+      <c r="AV67" s="76" t="str">
+        <f t="shared" ref="AV67" si="39">IF(OR(AT67="",AU67=""),"",AT67-AU67)</f>
         <v/>
       </c>
-      <c r="AW66" s="77"/>
-      <c r="AX66" s="73"/>
-      <c r="AY66" s="73"/>
-      <c r="AZ66" s="74"/>
-      <c r="BA66" s="76" t="str">
-        <f t="shared" ref="BA66" si="40">IF(OR(AY66="",AZ66=""),"",AY66-AZ66)</f>
+      <c r="AW67" s="77"/>
+      <c r="AX67" s="73"/>
+      <c r="AY67" s="73"/>
+      <c r="AZ67" s="74"/>
+      <c r="BA67" s="76" t="str">
+        <f t="shared" ref="BA67" si="40">IF(OR(AY67="",AZ67=""),"",AY67-AZ67)</f>
         <v/>
       </c>
-      <c r="BB66" s="77"/>
-      <c r="BC66" s="73"/>
-      <c r="BD66" s="73"/>
-      <c r="BE66" s="74"/>
-      <c r="BF66" s="76" t="str">
-        <f t="shared" ref="BF66" si="41">IF(OR(BD66="",BE66=""),"",BD66-BE66)</f>
+      <c r="BB67" s="77"/>
+      <c r="BC67" s="73"/>
+      <c r="BD67" s="73"/>
+      <c r="BE67" s="74"/>
+      <c r="BF67" s="76" t="str">
+        <f t="shared" ref="BF67" si="41">IF(OR(BD67="",BE67=""),"",BD67-BE67)</f>
         <v/>
       </c>
-      <c r="BG66" s="77"/>
-      <c r="BH66" s="73"/>
-      <c r="BI66" s="73"/>
-      <c r="BJ66" s="74"/>
-      <c r="BK66" s="76" t="str">
-        <f t="shared" ref="BK66" si="42">IF(OR(BI66="",BJ66=""),"",BI66-BJ66)</f>
+      <c r="BG67" s="77"/>
+      <c r="BH67" s="73"/>
+      <c r="BI67" s="73"/>
+      <c r="BJ67" s="74"/>
+      <c r="BK67" s="76" t="str">
+        <f t="shared" ref="BK67" si="42">IF(OR(BI67="",BJ67=""),"",BI67-BJ67)</f>
         <v/>
       </c>
-      <c r="BL66" s="77"/>
-      <c r="BM66" s="73"/>
-      <c r="BN66" s="73"/>
-      <c r="BO66" s="74"/>
-      <c r="BP66" s="76" t="str">
-        <f t="shared" ref="BP66" si="43">IF(OR(BN66="",BO66=""),"",BN66-BO66)</f>
+      <c r="BL67" s="77"/>
+      <c r="BM67" s="73"/>
+      <c r="BN67" s="73"/>
+      <c r="BO67" s="74"/>
+      <c r="BP67" s="76" t="str">
+        <f t="shared" ref="BP67" si="43">IF(OR(BN67="",BO67=""),"",BN67-BO67)</f>
         <v/>
       </c>
-      <c r="BQ66" s="77"/>
-      <c r="BR66" s="73"/>
-      <c r="BS66" s="73"/>
-      <c r="BT66" s="74"/>
-      <c r="BU66" s="76" t="str">
-        <f t="shared" ref="BU66" si="44">IF(OR(BS66="",BT66=""),"",BS66-BT66)</f>
+      <c r="BQ67" s="77"/>
+      <c r="BR67" s="73"/>
+      <c r="BS67" s="73"/>
+      <c r="BT67" s="74"/>
+      <c r="BU67" s="76" t="str">
+        <f t="shared" ref="BU67" si="44">IF(OR(BS67="",BT67=""),"",BS67-BT67)</f>
         <v/>
       </c>
-      <c r="BV66" s="75"/>
-      <c r="BW66" s="53"/>
-      <c r="BX66" s="49"/>
-      <c r="BY66"/>
-      <c r="BZ66"/>
-      <c r="CA66"/>
-      <c r="CB66"/>
-      <c r="CC66"/>
-      <c r="CD66"/>
-      <c r="CE66"/>
-      <c r="CF66"/>
-      <c r="CG66"/>
-      <c r="CH66"/>
-      <c r="CI66"/>
-      <c r="CJ66"/>
-      <c r="CK66"/>
-      <c r="CL66"/>
-      <c r="CM66"/>
-      <c r="CN66"/>
-      <c r="CO66"/>
-      <c r="CP66"/>
-      <c r="CQ66"/>
-      <c r="CR66"/>
-      <c r="CS66"/>
-      <c r="CT66"/>
-      <c r="CU66"/>
-      <c r="CV66"/>
-      <c r="CW66"/>
-      <c r="CX66"/>
-      <c r="CY66"/>
-      <c r="CZ66"/>
-      <c r="DA66"/>
-      <c r="DB66"/>
-      <c r="DC66"/>
-      <c r="DD66"/>
-      <c r="DE66"/>
-      <c r="DF66"/>
-      <c r="DG66"/>
-      <c r="DH66"/>
-      <c r="DI66"/>
-      <c r="DJ66"/>
-      <c r="DK66"/>
-      <c r="DL66"/>
-      <c r="DM66"/>
-      <c r="DN66"/>
-      <c r="DO66"/>
-      <c r="DP66"/>
-      <c r="DQ66"/>
-      <c r="DR66"/>
-      <c r="DS66"/>
-      <c r="DT66"/>
-      <c r="DU66"/>
-      <c r="DV66"/>
-      <c r="DW66"/>
-      <c r="DX66"/>
-      <c r="DY66"/>
-      <c r="DZ66"/>
-      <c r="EA66"/>
-      <c r="EB66"/>
-      <c r="EC66"/>
-      <c r="ED66"/>
-      <c r="EE66"/>
-      <c r="EF66"/>
-      <c r="EG66"/>
-      <c r="EH66"/>
-      <c r="EI66"/>
+      <c r="BV67" s="75"/>
+      <c r="BW67" s="53"/>
+      <c r="BX67" s="49"/>
+      <c r="BY67"/>
+      <c r="BZ67"/>
+      <c r="CA67"/>
+      <c r="CB67"/>
+      <c r="CC67"/>
+      <c r="CD67"/>
+      <c r="CE67"/>
+      <c r="CF67"/>
+      <c r="CG67"/>
+      <c r="CH67"/>
+      <c r="CI67"/>
+      <c r="CJ67"/>
+      <c r="CK67"/>
+      <c r="CL67"/>
+      <c r="CM67"/>
+      <c r="CN67"/>
+      <c r="CO67"/>
+      <c r="CP67"/>
+      <c r="CQ67"/>
+      <c r="CR67"/>
+      <c r="CS67"/>
+      <c r="CT67"/>
+      <c r="CU67"/>
+      <c r="CV67"/>
+      <c r="CW67"/>
+      <c r="CX67"/>
+      <c r="CY67"/>
+      <c r="CZ67"/>
+      <c r="DA67"/>
+      <c r="DB67"/>
+      <c r="DC67"/>
+      <c r="DD67"/>
+      <c r="DE67"/>
+      <c r="DF67"/>
+      <c r="DG67"/>
+      <c r="DH67"/>
+      <c r="DI67"/>
+      <c r="DJ67"/>
+      <c r="DK67"/>
+      <c r="DL67"/>
+      <c r="DM67"/>
+      <c r="DN67"/>
+      <c r="DO67"/>
+      <c r="DP67"/>
+      <c r="DQ67"/>
+      <c r="DR67"/>
+      <c r="DS67"/>
+      <c r="DT67"/>
+      <c r="DU67"/>
+      <c r="DV67"/>
+      <c r="DW67"/>
+      <c r="DX67"/>
+      <c r="DY67"/>
+      <c r="DZ67"/>
+      <c r="EA67"/>
+      <c r="EB67"/>
+      <c r="EC67"/>
+      <c r="ED67"/>
+      <c r="EE67"/>
+      <c r="EF67"/>
+      <c r="EG67"/>
+      <c r="EH67"/>
+      <c r="EI67"/>
     </row>
-    <row r="67" spans="1:139" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="68" spans="1:139" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>96</v>
       </c>
-      <c r="AA67" s="3"/>
-      <c r="BV67" s="95"/>
+      <c r="AA68" s="3"/>
+      <c r="BV68" s="95"/>
     </row>
   </sheetData>
-  <autoFilter ref="A15:BY19" xr:uid="{177F1DEB-197D-49C6-A2E3-152C1AC7B373}"/>
+  <autoFilter ref="A16:BY20" xr:uid="{177F1DEB-197D-49C6-A2E3-152C1AC7B373}"/>
   <mergeCells count="39">
     <mergeCell ref="BQ13:BU13"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="BB14:BF14"/>
-    <mergeCell ref="BG14:BK14"/>
-    <mergeCell ref="BL14:BP14"/>
+    <mergeCell ref="BQ15:BU15"/>
+    <mergeCell ref="S13:W13"/>
     <mergeCell ref="N13:R13"/>
-    <mergeCell ref="S13:W13"/>
     <mergeCell ref="X13:AB13"/>
     <mergeCell ref="AC13:AG13"/>
     <mergeCell ref="AH13:AL13"/>
@@ -9708,41 +9694,46 @@
     <mergeCell ref="BB13:BF13"/>
     <mergeCell ref="BG13:BK13"/>
     <mergeCell ref="BL13:BP13"/>
+    <mergeCell ref="S15:W15"/>
+    <mergeCell ref="N15:R15"/>
+    <mergeCell ref="X15:AB15"/>
+    <mergeCell ref="BG14:BK14"/>
+    <mergeCell ref="BL14:BP14"/>
+    <mergeCell ref="AC15:AG15"/>
+    <mergeCell ref="AH15:AL15"/>
+    <mergeCell ref="AM15:AQ15"/>
+    <mergeCell ref="AR15:AV15"/>
+    <mergeCell ref="AW15:BA15"/>
+    <mergeCell ref="BQ14:BU14"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="BB15:BF15"/>
+    <mergeCell ref="BG15:BK15"/>
+    <mergeCell ref="BL15:BP15"/>
+    <mergeCell ref="N14:R14"/>
+    <mergeCell ref="S14:W14"/>
+    <mergeCell ref="X14:AB14"/>
     <mergeCell ref="AC14:AG14"/>
     <mergeCell ref="AH14:AL14"/>
     <mergeCell ref="AM14:AQ14"/>
     <mergeCell ref="AR14:AV14"/>
     <mergeCell ref="AW14:BA14"/>
-    <mergeCell ref="BQ12:BU12"/>
-    <mergeCell ref="BQ14:BU14"/>
-    <mergeCell ref="S12:W12"/>
-    <mergeCell ref="N12:R12"/>
-    <mergeCell ref="X12:AB12"/>
-    <mergeCell ref="AC12:AG12"/>
-    <mergeCell ref="AH12:AL12"/>
-    <mergeCell ref="AM12:AQ12"/>
-    <mergeCell ref="AR12:AV12"/>
-    <mergeCell ref="AW12:BA12"/>
-    <mergeCell ref="BB12:BF12"/>
-    <mergeCell ref="BG12:BK12"/>
-    <mergeCell ref="BL12:BP12"/>
-    <mergeCell ref="S14:W14"/>
-    <mergeCell ref="N14:R14"/>
-    <mergeCell ref="X14:AB14"/>
+    <mergeCell ref="BB14:BF14"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q66 V66 AA66 AF66 AK66 AP66 AU66 AZ66 BE66 BJ66 BO66 BT66">
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>IF(AND(P66&gt;0,Q66=0),TRUE,FALSE)</formula>
+  <conditionalFormatting sqref="Q67 V67 AA67 AF67 AK67 AP67 AU67 AZ67 BE67 BJ67 BO67 BT67">
+    <cfRule type="expression" dxfId="2" priority="8">
+      <formula>IF(AND(P67&gt;0,Q67=0),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT11 V66:X66 AB66:AC66 AG66:AH66 AL66:AM66 AQ66:AR66 AV66:AW66 BA66:BB66 BF66:BG66 BK66:BL66 BP66:BQ66 BU66">
-    <cfRule type="expression" dxfId="5" priority="9">
+  <conditionalFormatting sqref="BT11:BT12 V67:X67 AB67:AC67 AG67:AH67 AL67:AM67 AQ67:AR67 AV67:AW67 BA67:BB67 BF67:BG67 BK67:BL67 BP67:BQ67 BU67">
+    <cfRule type="expression" dxfId="1" priority="9">
       <formula>IF(AND(U11&lt;&gt;"",V11="",TODAY()&gt;DATE(YEAR(TODAY()),MONTH(DATEVALUE("1-"&amp;LEFT(#REF!,3)&amp;"-1900")),20)),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BW12:BW13">
-    <cfRule type="expression" dxfId="4" priority="7">
-      <formula>IF(BW12&lt;0,TRUE,FALSE)</formula>
+  <conditionalFormatting sqref="BW13:BW14">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>IF(BW13&lt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9751,6 +9742,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19b1ad6d-7bbd-4338-adb0-a51e11e836c7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002B3B1E9AF76D8540A21B723585178CF2" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9038a3d09b9201f70a536d69b3ffdde9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="19b1ad6d-7bbd-4338-adb0-a51e11e836c7" xmlns:ns3="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9f1b7b0d1eaccac7f713200a7ec3f32" ns2:_="" ns3:_="">
     <xsd:import namespace="19b1ad6d-7bbd-4338-adb0-a51e11e836c7"/>
@@ -9993,27 +10004,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC2B212-31BA-49FB-B215-9E14B2C60948}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09"/>
+    <ds:schemaRef ds:uri="19b1ad6d-7bbd-4338-adb0-a51e11e836c7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19b1ad6d-7bbd-4338-adb0-a51e11e836c7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3614A8F8-9AED-4C02-B640-81A3A1FEB080}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B6774AE-0D33-4944-9922-507715E1B0E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10030,23 +10040,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3614A8F8-9AED-4C02-B640-81A3A1FEB080}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC2B212-31BA-49FB-B215-9E14B2C60948}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8aede0e7-b4a5-4e74-9fbf-51d976a6ba09"/>
-    <ds:schemaRef ds:uri="19b1ad6d-7bbd-4338-adb0-a51e11e836c7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>